--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -53,7 +53,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'advance_cost_bands'!$A$1:$C$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'advances'!$A$1:$M$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'advances_cell_remap'!$A$1:$F$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'building_uniticon'!$A$1:$B$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'building_uniticon'!$A$1:$B$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'civ2_converted_graphics'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'concept_mask'!$A$1:$A$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'feats'!$A$1:$B$1</definedName>
@@ -61,7 +61,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'gl_text_rewrites'!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'governicon_fallback'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'improveicon'!$A$1:$A$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'improvements'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'improvements'!$A$1:$F$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'order_mask'!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'players'!$A$1:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'slic_inventory'!$A$1:$G$18</definedName>
@@ -69,7 +69,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'terrain'!$A$1:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'tileimp'!$A$1:$T$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'tileimp_mask'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'tileimp_mask'!$A$1:$C$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'tribe_cities'!$A$1:$P$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'unit_block_overrides'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" t="n">
         <v>6</v>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
@@ -10200,7 +10200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10795,8 +10795,20 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ICON_IMPROVE_AUDIENCE_HALL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ICON_IMPROVE_AUDIENCE_HALL { FirstFrame "ICON_IMPROVE_WIZARDS_FORTRESS.tga" Movie "NULL" Gameplay "IMPROVE_AUDIENCE_HALL_GAMEPLAY" Historical "IMPROVE_AUDIENCE_HALL_HISTORICAL" Prereq "IMPROVE_AUDIENCE_HALL_PREREQ" Vari "IMPROVE_AUDIENCE_HALL_STATISTICS" Icon "ICON_IMPROVE_WIZARDS_FORTRESS.tga" LargeIcon "NULL" SmallIcon "NULL" StatText "IMPROVE_AUDIENCE_HALL_STATISTICS" }</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B49"/>
+  <autoFilter ref="A1:B50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12987,7 +12999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14502,8 +14514,40 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Audience Hall</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ICON_IMPROVE_WIZARDS_FORTRESS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F47"/>
+  <autoFilter ref="A1:F48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22455,7 +22499,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Processing Tower</t>
+          <t>Ritual Tower</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -22511,12 +22555,12 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>ADVANCE_ADV_URBAN_PLANNING</t>
+          <t>ADVANCE_ALCHEMY</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -22546,12 +22590,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ADVANCE_ADV_URBAN_PLANNING</t>
+          <t>ADVANCE_ALCHEMY</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -22581,12 +22625,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ADVANCE_ADV_URBAN_PLANNING</t>
+          <t>ADVANCE_ALCHEMY</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -24819,7 +24863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -25094,7 +25138,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TILEIMP_PROCESSING_TOWER</t>
+          <t>TILEIMP_UNDERSEA_TUNNEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -25104,21 +25148,8 @@
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TILEIMP_UNDERSEA_TUNNEL</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>out_of_genre</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C18"/>
+  <autoFilter ref="A1:C17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -57,7 +57,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'advance_cost_bands'!$A$1:$C$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'advance_mask'!$A$1:$C$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'advance_reanchor'!$A$1:$D$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'advances'!$A$1:$M$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'advances'!$A$1:$M$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'advances_cell_remap'!$A$1:$F$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'building_uniticon'!$A$1:$B$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'civ2_converted_graphics'!$A$1:$G$27</definedName>
@@ -68,7 +68,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'gl_text_rewrites'!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'governicon_fallback'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'improveicon'!$A$1:$A$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improvements'!$A$1:$G$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improvements'!$A$1:$H$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'order_mask'!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'players'!$A$1:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$56</definedName>
@@ -82,7 +82,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'unit_factions'!$A$1:$I$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$D$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E22" t="n">
         <v>13</v>
@@ -1130,7 +1130,7 @@
         <v>46</v>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -1452,7 +1452,7 @@
         <v>28</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4573,7 +4573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4661,23 +4661,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>User Def Tech A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cmp</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4687,62 +4687,62 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3    ; AFl</t>
+          <t>0    ; Aut</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_ALCHEMY</t>
+          <t>ICON_ADVANCE_USER_DEF_TECH_A</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADVANCE_ALCHEMY_GAMEPLAY</t>
+          <t>ADVANCE_USER_DEF_TECH_A_GAMEPLAY</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ADVANCE_ALCHEMY_HISTORICAL</t>
+          <t>ADVANCE_USER_DEF_TECH_A_HISTORICAL</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ADVANCE_ALCHEMY_PREREQ</t>
+          <t>ADVANCE_USER_DEF_TECH_A_PREREQ</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ADVANCE_ALCHEMY_STATISTICS</t>
+          <t>ADVANCE_USER_DEF_TECH_A_STATISTICS</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ADVANCE_ALCHEMY_PREREQ</t>
+          <t>ADVANCE_USER_DEF_TECH_A_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Chivalry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Feu</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>nil</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>nil</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>0</t>
@@ -4750,55 +4750,55 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3    ; Alp</t>
+          <t>0    ; Chi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_ALPHABET</t>
+          <t>ICON_ADVANCE_CHIVALRY</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ADVANCE_ALPHABET_GAMEPLAY</t>
+          <t>ADVANCE_CHIVALRY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ADVANCE_ALPHABET_HISTORICAL</t>
+          <t>ADVANCE_CHIVALRY_HISTORICAL</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ADVANCE_ALPHABET_PREREQ</t>
+          <t>ADVANCE_CHIVALRY_PREREQ</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ADVANCE_ALPHABET_STATISTICS</t>
+          <t>ADVANCE_CHIVALRY_STATISTICS</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ADVANCE_ALPHABET_PREREQ</t>
+          <t>ADVANCE_CHIVALRY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Animism</t>
+          <t>Extra Advance 4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Uni</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4813,60 +4813,60 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3    ; Amp</t>
+          <t>0    ; Cmn</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_ANIMISM</t>
+          <t>ICON_ADVANCE_EXTRA_ADVANCE_4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ADVANCE_ANIMISM_GAMEPLAY</t>
+          <t>ADVANCE_EXTRA_ADVANCE_4_GAMEPLAY</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ADVANCE_ANIMISM_HISTORICAL</t>
+          <t>ADVANCE_EXTRA_ADVANCE_4_HISTORICAL</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ADVANCE_ANIMISM_PREREQ</t>
+          <t>ADVANCE_EXTRA_ADVANCE_4_PREREQ</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ADVANCE_ANIMISM_STATISTICS</t>
+          <t>ADVANCE_EXTRA_ADVANCE_4_STATISTICS</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ADVANCE_ANIMISM_PREREQ</t>
+          <t>ADVANCE_EXTRA_ADVANCE_4_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Astrology</t>
+          <t>Tactics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mys</t>
+          <t>Tac</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4876,55 +4876,55 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3    ; Ast</t>
+          <t>0    ; Exp</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_ASTROLOGY</t>
+          <t>ICON_ADVANCE_TACTICS</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ADVANCE_ASTROLOGY_GAMEPLAY</t>
+          <t>ADVANCE_TACTICS_GAMEPLAY</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ADVANCE_ASTROLOGY_HISTORICAL</t>
+          <t>ADVANCE_TACTICS_HISTORICAL</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ADVANCE_ASTROLOGY_PREREQ</t>
+          <t>ADVANCE_TACTICS_PREREQ</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ADVANCE_ASTROLOGY_STATISTICS</t>
+          <t>ADVANCE_TACTICS_STATISTICS</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ADVANCE_ASTROLOGY_PREREQ</t>
+          <t>ADVANCE_TACTICS_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eldritch Lore</t>
+          <t>Feudalism</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ast</t>
+          <t>War</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4939,37 +4939,37 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3    ; Ato</t>
+          <t>0    ; Feu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_ELDRITCH_LORE</t>
+          <t>ICON_ADVANCE_FEUDALISM</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ADVANCE_ELDRITCH_LORE_GAMEPLAY</t>
+          <t>ADVANCE_FEUDALISM_GAMEPLAY</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ADVANCE_ELDRITCH_LORE_HISTORICAL</t>
+          <t>ADVANCE_FEUDALISM_HISTORICAL</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ADVANCE_ELDRITCH_LORE_PREREQ</t>
+          <t>ADVANCE_FEUDALISM_PREREQ</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ADVANCE_ELDRITCH_LORE_STATISTICS</t>
+          <t>ADVANCE_FEUDALISM_STATISTICS</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ADVANCE_ELDRITCH_LORE_PREREQ</t>
+          <t>ADVANCE_FEUDALISM_PREREQ</t>
         </is>
       </c>
     </row>
@@ -4981,18 +4981,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>User Def Tech A</t>
+          <t>Holy Warriors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Chi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>The</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5002,60 +5002,60 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0    ; Aut</t>
+          <t>0    ; Ldr</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_USER_DEF_TECH_A</t>
+          <t>ICON_ADVANCE_HOLY_WARRIORS</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ADVANCE_USER_DEF_TECH_A_GAMEPLAY</t>
+          <t>ADVANCE_HOLY_WARRIORS_GAMEPLAY</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ADVANCE_USER_DEF_TECH_A_HISTORICAL</t>
+          <t>ADVANCE_HOLY_WARRIORS_HISTORICAL</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ADVANCE_USER_DEF_TECH_A_PREREQ</t>
+          <t>ADVANCE_HOLY_WARRIORS_PREREQ</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ADVANCE_USER_DEF_TECH_A_STATISTICS</t>
+          <t>ADVANCE_HOLY_WARRIORS_STATISTICS</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ADVANCE_USER_DEF_TECH_A_PREREQ</t>
+          <t>ADVANCE_HOLY_WARRIORS_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Banking</t>
+          <t>Grand Mastery</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Rep</t>
+          <t>Exp</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tra</t>
+          <t>Fli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5065,60 +5065,60 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1    ; Ban</t>
+          <t>0    ; NF</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_BANKING</t>
+          <t>ICON_ADVANCE_GRAND_MASTERY</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADVANCE_BANKING_GAMEPLAY</t>
+          <t>ADVANCE_GRAND_MASTERY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ADVANCE_BANKING_HISTORICAL</t>
+          <t>ADVANCE_GRAND_MASTERY_HISTORICAL</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ADVANCE_BANKING_PREREQ</t>
+          <t>ADVANCE_GRAND_MASTERY_PREREQ</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ADVANCE_BANKING_STATISTICS</t>
+          <t>ADVANCE_GRAND_MASTERY_STATISTICS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ADVANCE_BANKING_PREREQ</t>
+          <t>ADVANCE_GRAND_MASTERY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bridge Building</t>
+          <t>Leadership</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Iro</t>
+          <t>Chi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cst</t>
+          <t>Uni</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5128,49 +5128,49 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4    ; Bri</t>
+          <t>0    ; Tac</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_BRIDGE_BUILDING</t>
+          <t>ICON_ADVANCE_LEADERSHIP</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ADVANCE_BRIDGE_BUILDING_GAMEPLAY</t>
+          <t>ADVANCE_LEADERSHIP_GAMEPLAY</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ADVANCE_BRIDGE_BUILDING_HISTORICAL</t>
+          <t>ADVANCE_LEADERSHIP_HISTORICAL</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ADVANCE_BRIDGE_BUILDING_PREREQ</t>
+          <t>ADVANCE_LEADERSHIP_PREREQ</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ADVANCE_BRIDGE_BUILDING_STATISTICS</t>
+          <t>ADVANCE_LEADERSHIP_STATISTICS</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ADVANCE_BRIDGE_BUILDING_PREREQ</t>
+          <t>ADVANCE_LEADERSHIP_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bronze Working</t>
+          <t>Warrior Code</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -5191,37 +5191,37 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4    ; Bro</t>
+          <t>0    ; War</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_BRONZE_WORKING</t>
+          <t>ICON_ADVANCE_WARRIOR_CODE</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ADVANCE_BRONZE_WORKING_GAMEPLAY</t>
+          <t>ADVANCE_WARRIOR_CODE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ADVANCE_BRONZE_WORKING_HISTORICAL</t>
+          <t>ADVANCE_WARRIOR_CODE_HISTORICAL</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ADVANCE_BRONZE_WORKING_PREREQ</t>
+          <t>ADVANCE_WARRIOR_CODE_PREREQ</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ADVANCE_BRONZE_WORKING_STATISTICS</t>
+          <t>ADVANCE_WARRIOR_CODE_STATISTICS</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ADVANCE_BRONZE_WORKING_PREREQ</t>
+          <t>ADVANCE_WARRIOR_CODE_PREREQ</t>
         </is>
       </c>
     </row>
@@ -5291,18 +5291,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Greater Fauna Lore</t>
+          <t>Code of Laws</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>X4</t>
+          <t>Alp</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5317,60 +5317,60 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3    ; Che</t>
+          <t>2    ; CoL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_GREATER_FAUNA_LORE</t>
+          <t>ICON_ADVANCE_CODE_OF_LAWS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_FAUNA_LORE_GAMEPLAY</t>
+          <t>ADVANCE_CODE_OF_LAWS_GAMEPLAY</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_FAUNA_LORE_HISTORICAL</t>
+          <t>ADVANCE_CODE_OF_LAWS_HISTORICAL</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_FAUNA_LORE_PREREQ</t>
+          <t>ADVANCE_CODE_OF_LAWS_PREREQ</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_FAUNA_LORE_STATISTICS</t>
+          <t>ADVANCE_CODE_OF_LAWS_STATISTICS</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_FAUNA_LORE_PREREQ</t>
+          <t>ADVANCE_CODE_OF_LAWS_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chivalry</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Feu</t>
+          <t>Cer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>CoL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -5380,37 +5380,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0    ; Chi</t>
+          <t>2    ; Mon</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_CHIVALRY</t>
+          <t>ICON_ADVANCE_MONARCHY</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ADVANCE_CHIVALRY_GAMEPLAY</t>
+          <t>ADVANCE_MONARCHY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ADVANCE_CHIVALRY_HISTORICAL</t>
+          <t>ADVANCE_MONARCHY_HISTORICAL</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>ADVANCE_CHIVALRY_PREREQ</t>
+          <t>ADVANCE_MONARCHY_PREREQ</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ADVANCE_CHIVALRY_STATISTICS</t>
+          <t>ADVANCE_MONARCHY_STATISTICS</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>ADVANCE_CHIVALRY_PREREQ</t>
+          <t>ADVANCE_MONARCHY_PREREQ</t>
         </is>
       </c>
     </row>
@@ -5422,18 +5422,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Code of Laws</t>
+          <t>Theology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alp</t>
+          <t>Phi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Feu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5443,60 +5443,60 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2    ; CoL</t>
+          <t>2    ; MT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_CODE_OF_LAWS</t>
+          <t>ICON_ADVANCE_THEOLOGY</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ADVANCE_CODE_OF_LAWS_GAMEPLAY</t>
+          <t>ADVANCE_THEOLOGY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ADVANCE_CODE_OF_LAWS_HISTORICAL</t>
+          <t>ADVANCE_THEOLOGY_HISTORICAL</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>ADVANCE_CODE_OF_LAWS_PREREQ</t>
+          <t>ADVANCE_THEOLOGY_PREREQ</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ADVANCE_CODE_OF_LAWS_STATISTICS</t>
+          <t>ADVANCE_THEOLOGY_STATISTICS</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ADVANCE_CODE_OF_LAWS_PREREQ</t>
+          <t>ADVANCE_THEOLOGY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Healing</t>
+          <t>Mysticism</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ast</t>
+          <t>Cer</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Phi</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5506,60 +5506,60 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3    ; CA</t>
+          <t>2    ; Mys</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_HEALING</t>
+          <t>ICON_ADVANCE_MYSTICISM</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ADVANCE_HEALING_GAMEPLAY</t>
+          <t>ADVANCE_MYSTICISM_GAMEPLAY</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ADVANCE_HEALING_HISTORICAL</t>
+          <t>ADVANCE_MYSTICISM_HISTORICAL</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>ADVANCE_HEALING_PREREQ</t>
+          <t>ADVANCE_MYSTICISM_PREREQ</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ADVANCE_HEALING_STATISTICS</t>
+          <t>ADVANCE_MYSTICISM_STATISTICS</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ADVANCE_HEALING_PREREQ</t>
+          <t>ADVANCE_MYSTICISM_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lesser Enchanments</t>
+          <t>Philosophy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Mys</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Lit</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5569,60 +5569,60 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3    ; Cmb</t>
+          <t>2    ; Phi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_LESSER_ENCHANMENTS</t>
+          <t>ICON_ADVANCE_PHILOSOPHY</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_ENCHANMENTS_GAMEPLAY</t>
+          <t>ADVANCE_PHILOSOPHY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_ENCHANMENTS_HISTORICAL</t>
+          <t>ADVANCE_PHILOSOPHY_HISTORICAL</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_ENCHANMENTS_PREREQ</t>
+          <t>ADVANCE_PHILOSOPHY_PREREQ</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_ENCHANMENTS_STATISTICS</t>
+          <t>ADVANCE_PHILOSOPHY_STATISTICS</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_ENCHANMENTS_PREREQ</t>
+          <t>ADVANCE_PHILOSOPHY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Extra Advance 4</t>
+          <t>The Republic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Lit</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5632,60 +5632,60 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0    ; Cmn</t>
+          <t>2    ; Rep</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_EXTRA_ADVANCE_4</t>
+          <t>ICON_ADVANCE_THE_REPUBLIC</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ADVANCE_EXTRA_ADVANCE_4_GAMEPLAY</t>
+          <t>ADVANCE_THE_REPUBLIC_GAMEPLAY</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ADVANCE_EXTRA_ADVANCE_4_HISTORICAL</t>
+          <t>ADVANCE_THE_REPUBLIC_HISTORICAL</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>ADVANCE_EXTRA_ADVANCE_4_PREREQ</t>
+          <t>ADVANCE_THE_REPUBLIC_PREREQ</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ADVANCE_EXTRA_ADVANCE_4_STATISTICS</t>
+          <t>ADVANCE_THE_REPUBLIC_STATISTICS</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ADVANCE_EXTRA_ADVANCE_4_PREREQ</t>
+          <t>ADVANCE_THE_REPUBLIC_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Metamorphosis</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Rep</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cst</t>
+          <t>Tra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5695,60 +5695,60 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3    ; Cmp</t>
+          <t>1    ; Ban</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_METAMORPHOSIS</t>
+          <t>ICON_ADVANCE_BANKING</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ADVANCE_METAMORPHOSIS_GAMEPLAY</t>
+          <t>ADVANCE_BANKING_GAMEPLAY</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ADVANCE_METAMORPHOSIS_HISTORICAL</t>
+          <t>ADVANCE_BANKING_HISTORICAL</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ADVANCE_METAMORPHOSIS_PREREQ</t>
+          <t>ADVANCE_BANKING_PREREQ</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ADVANCE_METAMORPHOSIS_STATISTICS</t>
+          <t>ADVANCE_BANKING_STATISTICS</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>ADVANCE_METAMORPHOSIS_PREREQ</t>
+          <t>ADVANCE_BANKING_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Bro</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cur</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5758,60 +5758,60 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4    ; Cst</t>
+          <t>1    ; Cur</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_CONSTRUCTION</t>
+          <t>ICON_ADVANCE_CURRENCY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ADVANCE_CONSTRUCTION_GAMEPLAY</t>
+          <t>ADVANCE_CURRENCY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ADVANCE_CONSTRUCTION_HISTORICAL</t>
+          <t>ADVANCE_CURRENCY_HISTORICAL</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ADVANCE_CONSTRUCTION_PREREQ</t>
+          <t>ADVANCE_CURRENCY_PREREQ</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ADVANCE_CONSTRUCTION_STATISTICS</t>
+          <t>ADVANCE_CURRENCY_STATISTICS</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ADVANCE_CONSTRUCTION_PREREQ</t>
+          <t>ADVANCE_CURRENCY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pantheism</t>
+          <t>Map Making</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cer</t>
+          <t>Alp</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Env</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5821,37 +5821,37 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3    ; Cor</t>
+          <t>1    ; Map</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_PANTHEISM</t>
+          <t>ICON_ADVANCE_MAP_MAKING</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ADVANCE_PANTHEISM_GAMEPLAY</t>
+          <t>ADVANCE_MAP_MAKING_GAMEPLAY</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ADVANCE_PANTHEISM_HISTORICAL</t>
+          <t>ADVANCE_MAP_MAKING_HISTORICAL</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>ADVANCE_PANTHEISM_PREREQ</t>
+          <t>ADVANCE_MAP_MAKING_PREREQ</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ADVANCE_PANTHEISM_STATISTICS</t>
+          <t>ADVANCE_MAP_MAKING_STATISTICS</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ADVANCE_PANTHEISM_PREREQ</t>
+          <t>ADVANCE_MAP_MAKING_PREREQ</t>
         </is>
       </c>
     </row>
@@ -5863,18 +5863,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bro</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Ast</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5884,60 +5884,60 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1    ; Cur</t>
+          <t>1    ; Nav</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_CURRENCY</t>
+          <t>ICON_ADVANCE_NAVIGATION</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ADVANCE_CURRENCY_GAMEPLAY</t>
+          <t>ADVANCE_NAVIGATION_GAMEPLAY</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>ADVANCE_CURRENCY_HISTORICAL</t>
+          <t>ADVANCE_NAVIGATION_HISTORICAL</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>ADVANCE_CURRENCY_PREREQ</t>
+          <t>ADVANCE_NAVIGATION_PREREQ</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ADVANCE_CURRENCY_STATISTICS</t>
+          <t>ADVANCE_NAVIGATION_STATISTICS</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ADVANCE_CURRENCY_PREREQ</t>
+          <t>ADVANCE_NAVIGATION_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rune Lore</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>X6</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lit</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5947,60 +5947,60 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3    ; E1</t>
+          <t>1    ; Pot</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_RUNE_LORE</t>
+          <t>ICON_ADVANCE_POTTERY</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ADVANCE_RUNE_LORE_GAMEPLAY</t>
+          <t>ADVANCE_POTTERY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ADVANCE_RUNE_LORE_HISTORICAL</t>
+          <t>ADVANCE_POTTERY_HISTORICAL</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>ADVANCE_RUNE_LORE_PREREQ</t>
+          <t>ADVANCE_POTTERY_PREREQ</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ADVANCE_RUNE_LORE_STATISTICS</t>
+          <t>ADVANCE_POTTERY_STATISTICS</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>ADVANCE_RUNE_LORE_PREREQ</t>
+          <t>ADVANCE_POTTERY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sea Mastery</t>
+          <t>Sanitation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Iro</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -6010,60 +6010,60 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3    ; Eng</t>
+          <t>1    ; San</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SEA_MASTERY</t>
+          <t>ICON_ADVANCE_SANITATION</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_MASTERY_GAMEPLAY</t>
+          <t>ADVANCE_SANITATION_GAMEPLAY</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_MASTERY_HISTORICAL</t>
+          <t>ADVANCE_SANITATION_HISTORICAL</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_MASTERY_PREREQ</t>
+          <t>ADVANCE_SANITATION_PREREQ</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_MASTERY_STATISTICS</t>
+          <t>ADVANCE_SANITATION_STATISTICS</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_MASTERY_PREREQ</t>
+          <t>ADVANCE_SANITATION_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shamanism</t>
+          <t>Seafaring</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Map</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Pot</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6073,60 +6073,60 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3    ; Env</t>
+          <t>1    ; Sea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SHAMANISM</t>
+          <t>ICON_ADVANCE_SEAFARING</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ADVANCE_SHAMANISM_GAMEPLAY</t>
+          <t>ADVANCE_SEAFARING_GAMEPLAY</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>ADVANCE_SHAMANISM_HISTORICAL</t>
+          <t>ADVANCE_SEAFARING_HISTORICAL</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>ADVANCE_SHAMANISM_PREREQ</t>
+          <t>ADVANCE_SEAFARING_PREREQ</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ADVANCE_SHAMANISM_STATISTICS</t>
+          <t>ADVANCE_SEAFARING_STATISTICS</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>ADVANCE_SHAMANISM_PREREQ</t>
+          <t>ADVANCE_SEAFARING_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Thaumaturgy</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The</t>
+          <t>Cur</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>X6</t>
+          <t>CoL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -6136,60 +6136,60 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3    ; Esp</t>
+          <t>1    ; Tra</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_THAUMATURGY</t>
+          <t>ICON_ADVANCE_TRADE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ADVANCE_THAUMATURGY_GAMEPLAY</t>
+          <t>ADVANCE_TRADE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ADVANCE_THAUMATURGY_HISTORICAL</t>
+          <t>ADVANCE_TRADE_HISTORICAL</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ADVANCE_THAUMATURGY_PREREQ</t>
+          <t>ADVANCE_TRADE_PREREQ</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ADVANCE_THAUMATURGY_STATISTICS</t>
+          <t>ADVANCE_TRADE_STATISTICS</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>ADVANCE_THAUMATURGY_PREREQ</t>
+          <t>ADVANCE_TRADE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tactics</t>
+          <t>Ecognomics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tac</t>
+          <t>Uni</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Uni</t>
+          <t>Ban</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -6199,60 +6199,60 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0    ; Exp</t>
+          <t>1    ; Eco</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_TACTICS</t>
+          <t>ICON_ADVANCE_ECOGNOMICS</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ADVANCE_TACTICS_GAMEPLAY</t>
+          <t>ADVANCE_ECOGNOMICS_GAMEPLAY</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>ADVANCE_TACTICS_HISTORICAL</t>
+          <t>ADVANCE_ECOGNOMICS_HISTORICAL</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ADVANCE_TACTICS_PREREQ</t>
+          <t>ADVANCE_ECOGNOMICS_PREREQ</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ADVANCE_TACTICS_STATISTICS</t>
+          <t>ADVANCE_ECOGNOMICS_STATISTICS</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>ADVANCE_TACTICS_PREREQ</t>
+          <t>ADVANCE_ECOGNOMICS_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Feudalism</t>
+          <t>Bridge Building</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Iro</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Cst</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6262,55 +6262,55 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0    ; Feu</t>
+          <t>4    ; Bri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_FEUDALISM</t>
+          <t>ICON_ADVANCE_BRIDGE_BUILDING</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ADVANCE_FEUDALISM_GAMEPLAY</t>
+          <t>ADVANCE_BRIDGE_BUILDING_GAMEPLAY</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>ADVANCE_FEUDALISM_HISTORICAL</t>
+          <t>ADVANCE_BRIDGE_BUILDING_HISTORICAL</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ADVANCE_FEUDALISM_PREREQ</t>
+          <t>ADVANCE_BRIDGE_BUILDING_PREREQ</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ADVANCE_FEUDALISM_STATISTICS</t>
+          <t>ADVANCE_BRIDGE_BUILDING_STATISTICS</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>ADVANCE_FEUDALISM_PREREQ</t>
+          <t>ADVANCE_BRIDGE_BUILDING_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wizardry</t>
+          <t>Bronze Working</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AFl</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6325,60 +6325,60 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3    ; Fli</t>
+          <t>4    ; Bro</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_WIZARDRY</t>
+          <t>ICON_ADVANCE_BRONZE_WORKING</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ADVANCE_WIZARDRY_GAMEPLAY</t>
+          <t>ADVANCE_BRONZE_WORKING_GAMEPLAY</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>ADVANCE_WIZARDRY_HISTORICAL</t>
+          <t>ADVANCE_BRONZE_WORKING_HISTORICAL</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>ADVANCE_WIZARDRY_PREREQ</t>
+          <t>ADVANCE_BRONZE_WORKING_PREREQ</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ADVANCE_WIZARDRY_STATISTICS</t>
+          <t>ADVANCE_BRONZE_WORKING_STATISTICS</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>ADVANCE_WIZARDRY_PREREQ</t>
+          <t>ADVANCE_BRONZE_WORKING_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Glyphs</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Cur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6388,118 +6388,118 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3    ; FP</t>
+          <t>4    ; Cst</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_GLYPHS</t>
+          <t>ICON_ADVANCE_CONSTRUCTION</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ADVANCE_GLYPHS_GAMEPLAY</t>
+          <t>ADVANCE_CONSTRUCTION_GAMEPLAY</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>ADVANCE_GLYPHS_HISTORICAL</t>
+          <t>ADVANCE_CONSTRUCTION_HISTORICAL</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>ADVANCE_GLYPHS_PREREQ</t>
+          <t>ADVANCE_CONSTRUCTION_PREREQ</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ADVANCE_GLYPHS_STATISTICS</t>
+          <t>ADVANCE_CONSTRUCTION_STATISTICS</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>ADVANCE_GLYPHS_PREREQ</t>
+          <t>ADVANCE_CONSTRUCTION_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Life Magic</t>
+          <t>Iron Working</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>Bro</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>War</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2    ; Gen</t>
+          <t>4    ; Iro</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_LIFE_MAGIC</t>
+          <t>ICON_ADVANCE_IRON_WORKING</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGIC_GAMEPLAY</t>
+          <t>ADVANCE_IRON_WORKING_GAMEPLAY</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGIC_HISTORICAL</t>
+          <t>ADVANCE_IRON_WORKING_HISTORICAL</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGIC_PREREQ</t>
+          <t>ADVANCE_IRON_WORKING_PREREQ</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGIC_STATISTICS</t>
+          <t>ADVANCE_IRON_WORKING_STATISTICS</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGIC_PREREQ</t>
+          <t>ADVANCE_IRON_WORKING_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chaos Magic</t>
+          <t>Masonry</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6509,65 +6509,65 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0    ; Gun</t>
+          <t>4    ; Mas</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_CHAOS_MAGIC</t>
+          <t>ICON_ADVANCE_MASONRY</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGIC_GAMEPLAY</t>
+          <t>ADVANCE_MASONRY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGIC_HISTORICAL</t>
+          <t>ADVANCE_MASONRY_HISTORICAL</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGIC_PREREQ</t>
+          <t>ADVANCE_MASONRY_PREREQ</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGIC_STATISTICS</t>
+          <t>ADVANCE_MASONRY_STATISTICS</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGIC_PREREQ</t>
+          <t>ADVANCE_MASONRY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sorcery</t>
+          <t>Nature Lore</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Ato</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6577,60 +6577,60 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4    ; Hor</t>
+          <t>1    ; Plu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SORCERY</t>
+          <t>ICON_ADVANCE_NATURE_LORE</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_GAMEPLAY</t>
+          <t>ADVANCE_NATURE_LORE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_HISTORICAL</t>
+          <t>ADVANCE_NATURE_LORE_HISTORICAL</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_PREREQ</t>
+          <t>ADVANCE_NATURE_LORE_PREREQ</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_STATISTICS</t>
+          <t>ADVANCE_NATURE_LORE_STATISTICS</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_PREREQ</t>
+          <t>ADVANCE_NATURE_LORE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Life Lore</t>
+          <t>Nature Adept</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gen</t>
+          <t>Plu</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ato</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6640,118 +6640,118 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2    ; Inv</t>
+          <t>1    ; PT</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_LIFE_LORE</t>
+          <t>ICON_ADVANCE_NATURE_ADEPT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_LORE_GAMEPLAY</t>
+          <t>ADVANCE_NATURE_ADEPT_GAMEPLAY</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_LORE_HISTORICAL</t>
+          <t>ADVANCE_NATURE_ADEPT_HISTORICAL</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_LORE_PREREQ</t>
+          <t>ADVANCE_NATURE_ADEPT_PREREQ</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_LORE_STATISTICS</t>
+          <t>ADVANCE_NATURE_ADEPT_STATISTICS</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_LORE_PREREQ</t>
+          <t>ADVANCE_NATURE_ADEPT_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Iron Working</t>
+          <t>Nature Mage</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bro</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4    ; Iro</t>
+          <t>1    ; Rad</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_IRON_WORKING</t>
+          <t>ICON_ADVANCE_NATURE_MAGE</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ADVANCE_IRON_WORKING_GAMEPLAY</t>
+          <t>ADVANCE_NATURE_MAGE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ADVANCE_IRON_WORKING_HISTORICAL</t>
+          <t>ADVANCE_NATURE_MAGE_HISTORICAL</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>ADVANCE_IRON_WORKING_PREREQ</t>
+          <t>ADVANCE_NATURE_MAGE_PREREQ</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ADVANCE_IRON_WORKING_STATISTICS</t>
+          <t>ADVANCE_NATURE_MAGE_STATISTICS</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>ADVANCE_IRON_WORKING_PREREQ</t>
+          <t>ADVANCE_NATURE_MAGE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Life Adept</t>
+          <t>Nature Wizard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Inv</t>
+          <t>Rad</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6766,55 +6766,55 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2    ; Lab</t>
+          <t>1    ; Rec</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_LIFE_ADEPT</t>
+          <t>ICON_ADVANCE_NATURE_WIZARD</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_ADEPT_GAMEPLAY</t>
+          <t>ADVANCE_NATURE_WIZARD_GAMEPLAY</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_ADEPT_HISTORICAL</t>
+          <t>ADVANCE_NATURE_WIZARD_HISTORICAL</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_ADEPT_PREREQ</t>
+          <t>ADVANCE_NATURE_WIZARD_PREREQ</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_ADEPT_STATISTICS</t>
+          <t>ADVANCE_NATURE_WIZARD_STATISTICS</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_ADEPT_PREREQ</t>
+          <t>ADVANCE_NATURE_WIZARD_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Life Mage</t>
+          <t>Nature Master</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lab</t>
+          <t>Rec</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6829,100 +6829,100 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2    ; Las</t>
+          <t>1    ; Ref</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_LIFE_MAGE</t>
+          <t>ICON_ADVANCE_NATURE_MASTER</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGE_GAMEPLAY</t>
+          <t>ADVANCE_NATURE_MASTER_GAMEPLAY</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGE_HISTORICAL</t>
+          <t>ADVANCE_NATURE_MASTER_HISTORICAL</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGE_PREREQ</t>
+          <t>ADVANCE_NATURE_MASTER_PREREQ</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGE_STATISTICS</t>
+          <t>ADVANCE_NATURE_MASTER_STATISTICS</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGE_PREREQ</t>
+          <t>ADVANCE_NATURE_MASTER_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Holy Warriors</t>
+          <t>Nature Magic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>The</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0    ; Ldr</t>
+          <t>1    ; X1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_HOLY_WARRIORS</t>
+          <t>ICON_ADVANCE_NATURE_MAGIC</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ADVANCE_HOLY_WARRIORS_GAMEPLAY</t>
+          <t>ADVANCE_NATURE_MAGIC_GAMEPLAY</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>ADVANCE_HOLY_WARRIORS_HISTORICAL</t>
+          <t>ADVANCE_NATURE_MAGIC_HISTORICAL</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>ADVANCE_HOLY_WARRIORS_PREREQ</t>
+          <t>ADVANCE_NATURE_MAGIC_PREREQ</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ADVANCE_HOLY_WARRIORS_STATISTICS</t>
+          <t>ADVANCE_NATURE_MAGIC_STATISTICS</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>ADVANCE_HOLY_WARRIORS_PREREQ</t>
+          <t>ADVANCE_NATURE_MAGIC_PREREQ</t>
         </is>
       </c>
     </row>
@@ -6934,18 +6934,18 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Literacy</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wri</t>
+          <t>Cmp</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CoL</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6955,55 +6955,55 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3    ; Lit</t>
+          <t>3    ; AFl</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_LITERACY</t>
+          <t>ICON_ADVANCE_ALCHEMY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ADVANCE_LITERACY_GAMEPLAY</t>
+          <t>ADVANCE_ALCHEMY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ADVANCE_LITERACY_HISTORICAL</t>
+          <t>ADVANCE_ALCHEMY_HISTORICAL</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ADVANCE_LITERACY_PREREQ</t>
+          <t>ADVANCE_ALCHEMY_PREREQ</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ADVANCE_LITERACY_STATISTICS</t>
+          <t>ADVANCE_ALCHEMY_STATISTICS</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>ADVANCE_LITERACY_PREREQ</t>
+          <t>ADVANCE_ALCHEMY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Life Wizard</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Las</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -7013,128 +7013,128 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2    ; Too</t>
+          <t>3    ; Alp</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_LIFE_WIZARD</t>
+          <t>ICON_ADVANCE_ALPHABET</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_WIZARD_GAMEPLAY</t>
+          <t>ADVANCE_ALPHABET_GAMEPLAY</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_WIZARD_HISTORICAL</t>
+          <t>ADVANCE_ALPHABET_HISTORICAL</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_WIZARD_PREREQ</t>
+          <t>ADVANCE_ALPHABET_PREREQ</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_WIZARD_STATISTICS</t>
+          <t>ADVANCE_ALPHABET_STATISTICS</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_WIZARD_PREREQ</t>
+          <t>ADVANCE_ALPHABET_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Life Master</t>
+          <t>Animism</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Too</t>
+          <t>Uni</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2    ; Mag</t>
+          <t>3    ; Amp</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_LIFE_MASTER</t>
+          <t>ICON_ADVANCE_ANIMISM</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MASTER_GAMEPLAY</t>
+          <t>ADVANCE_ANIMISM_GAMEPLAY</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MASTER_HISTORICAL</t>
+          <t>ADVANCE_ANIMISM_HISTORICAL</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MASTER_PREREQ</t>
+          <t>ADVANCE_ANIMISM_PREREQ</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MASTER_STATISTICS</t>
+          <t>ADVANCE_ANIMISM_STATISTICS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MASTER_PREREQ</t>
+          <t>ADVANCE_ANIMISM_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Map Making</t>
+          <t>Astrology</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Alp</t>
+          <t>Mys</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7144,62 +7144,62 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1    ; Map</t>
+          <t>3    ; Ast</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_MAP_MAKING</t>
+          <t>ICON_ADVANCE_ASTROLOGY</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>ADVANCE_MAP_MAKING_GAMEPLAY</t>
+          <t>ADVANCE_ASTROLOGY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>ADVANCE_MAP_MAKING_HISTORICAL</t>
+          <t>ADVANCE_ASTROLOGY_HISTORICAL</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>ADVANCE_MAP_MAKING_PREREQ</t>
+          <t>ADVANCE_ASTROLOGY_PREREQ</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ADVANCE_MAP_MAKING_STATISTICS</t>
+          <t>ADVANCE_ASTROLOGY_STATISTICS</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>ADVANCE_MAP_MAKING_PREREQ</t>
+          <t>ADVANCE_ASTROLOGY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Masonry</t>
+          <t>Eldritch Lore</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
+          <t>Ast</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>nil</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>nil</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>0</t>
@@ -7207,100 +7207,100 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4    ; Mas</t>
+          <t>3    ; Ato</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_MASONRY</t>
+          <t>ICON_ADVANCE_ELDRITCH_LORE</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ADVANCE_MASONRY_GAMEPLAY</t>
+          <t>ADVANCE_ELDRITCH_LORE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ADVANCE_MASONRY_HISTORICAL</t>
+          <t>ADVANCE_ELDRITCH_LORE_HISTORICAL</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ADVANCE_MASONRY_PREREQ</t>
+          <t>ADVANCE_ELDRITCH_LORE_PREREQ</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ADVANCE_MASONRY_STATISTICS</t>
+          <t>ADVANCE_ELDRITCH_LORE_STATISTICS</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>ADVANCE_MASONRY_PREREQ</t>
+          <t>ADVANCE_ELDRITCH_LORE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chaos Lore</t>
+          <t>Greater Fauna Lore</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Gun</t>
+          <t>X4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ato</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0    ; MP</t>
+          <t>3    ; Che</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_CHAOS_LORE</t>
+          <t>ICON_ADVANCE_GREATER_FAUNA_LORE</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_LORE_GAMEPLAY</t>
+          <t>ADVANCE_GREATER_FAUNA_LORE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_LORE_HISTORICAL</t>
+          <t>ADVANCE_GREATER_FAUNA_LORE_HISTORICAL</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_LORE_PREREQ</t>
+          <t>ADVANCE_GREATER_FAUNA_LORE_PREREQ</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_LORE_STATISTICS</t>
+          <t>ADVANCE_GREATER_FAUNA_LORE_STATISTICS</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_LORE_PREREQ</t>
+          <t>ADVANCE_GREATER_FAUNA_LORE_PREREQ</t>
         </is>
       </c>
     </row>
@@ -7312,18 +7312,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Healing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Alp</t>
+          <t>Ast</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Phi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -7333,55 +7333,55 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3    ; Mat</t>
+          <t>3    ; CA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_MATHEMATICS</t>
+          <t>ICON_ADVANCE_HEALING</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ADVANCE_MATHEMATICS_GAMEPLAY</t>
+          <t>ADVANCE_HEALING_GAMEPLAY</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ADVANCE_MATHEMATICS_HISTORICAL</t>
+          <t>ADVANCE_HEALING_HISTORICAL</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>ADVANCE_MATHEMATICS_PREREQ</t>
+          <t>ADVANCE_HEALING_PREREQ</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ADVANCE_MATHEMATICS_STATISTICS</t>
+          <t>ADVANCE_HEALING_STATISTICS</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>ADVANCE_MATHEMATICS_PREREQ</t>
+          <t>ADVANCE_HEALING_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chaos Adept</t>
+          <t>Lesser Enchanments</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Mys</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -7391,254 +7391,254 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0    ; Med</t>
+          <t>3    ; Cmb</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_CHAOS_ADEPT</t>
+          <t>ICON_ADVANCE_LESSER_ENCHANMENTS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_ADEPT_GAMEPLAY</t>
+          <t>ADVANCE_LESSER_ENCHANMENTS_GAMEPLAY</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_ADEPT_HISTORICAL</t>
+          <t>ADVANCE_LESSER_ENCHANMENTS_HISTORICAL</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_ADEPT_PREREQ</t>
+          <t>ADVANCE_LESSER_ENCHANMENTS_PREREQ</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_ADEPT_STATISTICS</t>
+          <t>ADVANCE_LESSER_ENCHANMENTS_STATISTICS</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_ADEPT_PREREQ</t>
+          <t>ADVANCE_LESSER_ENCHANMENTS_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chaos Mage</t>
+          <t>Metamorphosis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Cst</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0    ; Met</t>
+          <t>3    ; Cmp</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_CHAOS_MAGE</t>
+          <t>ICON_ADVANCE_METAMORPHOSIS</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGE_GAMEPLAY</t>
+          <t>ADVANCE_METAMORPHOSIS_GAMEPLAY</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGE_HISTORICAL</t>
+          <t>ADVANCE_METAMORPHOSIS_HISTORICAL</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGE_PREREQ</t>
+          <t>ADVANCE_METAMORPHOSIS_PREREQ</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGE_STATISTICS</t>
+          <t>ADVANCE_METAMORPHOSIS_STATISTICS</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGE_PREREQ</t>
+          <t>ADVANCE_METAMORPHOSIS_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chaos Wizard</t>
+          <t>Pantheism</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>Cer</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Env</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0    ; Min</t>
+          <t>3    ; Cor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_CHAOS_WIZARD</t>
+          <t>ICON_ADVANCE_PANTHEISM</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_WIZARD_GAMEPLAY</t>
+          <t>ADVANCE_PANTHEISM_GAMEPLAY</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_WIZARD_HISTORICAL</t>
+          <t>ADVANCE_PANTHEISM_HISTORICAL</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_WIZARD_PREREQ</t>
+          <t>ADVANCE_PANTHEISM_PREREQ</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_WIZARD_STATISTICS</t>
+          <t>ADVANCE_PANTHEISM_STATISTICS</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_WIZARD_PREREQ</t>
+          <t>ADVANCE_PANTHEISM_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chaos Master</t>
+          <t>Rune Lore</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>X6</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Lit</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0    ; Mob</t>
+          <t>3    ; E1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_CHAOS_MASTER</t>
+          <t>ICON_ADVANCE_RUNE_LORE</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MASTER_GAMEPLAY</t>
+          <t>ADVANCE_RUNE_LORE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MASTER_HISTORICAL</t>
+          <t>ADVANCE_RUNE_LORE_HISTORICAL</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MASTER_PREREQ</t>
+          <t>ADVANCE_RUNE_LORE_PREREQ</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MASTER_STATISTICS</t>
+          <t>ADVANCE_RUNE_LORE_STATISTICS</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MASTER_PREREQ</t>
+          <t>ADVANCE_RUNE_LORE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Sea Mastery</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cer</t>
+          <t>Iro</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CoL</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -7648,60 +7648,60 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2    ; Mon</t>
+          <t>3    ; Eng</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_MONARCHY</t>
+          <t>ICON_ADVANCE_SEA_MASTERY</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ADVANCE_MONARCHY_GAMEPLAY</t>
+          <t>ADVANCE_SEA_MASTERY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>ADVANCE_MONARCHY_HISTORICAL</t>
+          <t>ADVANCE_SEA_MASTERY_HISTORICAL</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>ADVANCE_MONARCHY_PREREQ</t>
+          <t>ADVANCE_SEA_MASTERY_PREREQ</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ADVANCE_MONARCHY_STATISTICS</t>
+          <t>ADVANCE_SEA_MASTERY_STATISTICS</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>ADVANCE_MONARCHY_PREREQ</t>
+          <t>ADVANCE_SEA_MASTERY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Theology</t>
+          <t>Shamanism</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Phi</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Feu</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7711,60 +7711,60 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2    ; MT</t>
+          <t>3    ; Env</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_THEOLOGY</t>
+          <t>ICON_ADVANCE_SHAMANISM</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ADVANCE_THEOLOGY_GAMEPLAY</t>
+          <t>ADVANCE_SHAMANISM_GAMEPLAY</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>ADVANCE_THEOLOGY_HISTORICAL</t>
+          <t>ADVANCE_SHAMANISM_HISTORICAL</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>ADVANCE_THEOLOGY_PREREQ</t>
+          <t>ADVANCE_SHAMANISM_PREREQ</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ADVANCE_THEOLOGY_STATISTICS</t>
+          <t>ADVANCE_SHAMANISM_STATISTICS</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>ADVANCE_THEOLOGY_PREREQ</t>
+          <t>ADVANCE_SHAMANISM_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mysticism</t>
+          <t>Thaumaturgy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cer</t>
+          <t>The</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>X6</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7774,60 +7774,60 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2    ; Mys</t>
+          <t>3    ; Esp</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_MYSTICISM</t>
+          <t>ICON_ADVANCE_THAUMATURGY</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ADVANCE_MYSTICISM_GAMEPLAY</t>
+          <t>ADVANCE_THAUMATURGY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>ADVANCE_MYSTICISM_HISTORICAL</t>
+          <t>ADVANCE_THAUMATURGY_HISTORICAL</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>ADVANCE_MYSTICISM_PREREQ</t>
+          <t>ADVANCE_THAUMATURGY_PREREQ</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ADVANCE_MYSTICISM_STATISTICS</t>
+          <t>ADVANCE_THAUMATURGY_STATISTICS</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>ADVANCE_MYSTICISM_PREREQ</t>
+          <t>ADVANCE_THAUMATURGY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Wizardry</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>AFl</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ast</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7837,60 +7837,60 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1    ; Nav</t>
+          <t>3    ; Fli</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_NAVIGATION</t>
+          <t>ICON_ADVANCE_WIZARDRY</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ADVANCE_NAVIGATION_GAMEPLAY</t>
+          <t>ADVANCE_WIZARDRY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>ADVANCE_NAVIGATION_HISTORICAL</t>
+          <t>ADVANCE_WIZARDRY_HISTORICAL</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>ADVANCE_NAVIGATION_PREREQ</t>
+          <t>ADVANCE_WIZARDRY_PREREQ</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ADVANCE_NAVIGATION_STATISTICS</t>
+          <t>ADVANCE_WIZARDRY_STATISTICS</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>ADVANCE_NAVIGATION_PREREQ</t>
+          <t>ADVANCE_WIZARDRY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Grand Mastery</t>
+          <t>Glyphs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Exp</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fli</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7900,123 +7900,123 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0    ; NF</t>
+          <t>3    ; FP</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_GRAND_MASTERY</t>
+          <t>ICON_ADVANCE_GLYPHS</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ADVANCE_GRAND_MASTERY_GAMEPLAY</t>
+          <t>ADVANCE_GLYPHS_GAMEPLAY</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>ADVANCE_GRAND_MASTERY_HISTORICAL</t>
+          <t>ADVANCE_GLYPHS_HISTORICAL</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>ADVANCE_GRAND_MASTERY_PREREQ</t>
+          <t>ADVANCE_GLYPHS_PREREQ</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ADVANCE_GRAND_MASTERY_STATISTICS</t>
+          <t>ADVANCE_GLYPHS_STATISTICS</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>ADVANCE_GRAND_MASTERY_PREREQ</t>
+          <t>ADVANCE_GLYPHS_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sorcery Mage</t>
+          <t>Literacy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>Wri</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>CoL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4    ; NP</t>
+          <t>3    ; Lit</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SORCERY_MAGE</t>
+          <t>ICON_ADVANCE_LITERACY</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MAGE_GAMEPLAY</t>
+          <t>ADVANCE_LITERACY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MAGE_HISTORICAL</t>
+          <t>ADVANCE_LITERACY_HISTORICAL</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MAGE_PREREQ</t>
+          <t>ADVANCE_LITERACY_PREREQ</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MAGE_STATISTICS</t>
+          <t>ADVANCE_LITERACY_STATISTICS</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MAGE_PREREQ</t>
+          <t>ADVANCE_LITERACY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Philosophy</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mys</t>
+          <t>Alp</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lit</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -8026,55 +8026,55 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2    ; Phi</t>
+          <t>3    ; Mat</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_PHILOSOPHY</t>
+          <t>ICON_ADVANCE_MATHEMATICS</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ADVANCE_PHILOSOPHY_GAMEPLAY</t>
+          <t>ADVANCE_MATHEMATICS_GAMEPLAY</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ADVANCE_PHILOSOPHY_HISTORICAL</t>
+          <t>ADVANCE_MATHEMATICS_HISTORICAL</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>ADVANCE_PHILOSOPHY_PREREQ</t>
+          <t>ADVANCE_MATHEMATICS_PREREQ</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ADVANCE_PHILOSOPHY_STATISTICS</t>
+          <t>ADVANCE_MATHEMATICS_STATISTICS</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>ADVANCE_PHILOSOPHY_PREREQ</t>
+          <t>ADVANCE_MATHEMATICS_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sorcery Wizard</t>
+          <t>Greater Enchantments</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>Cmb</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -8084,186 +8084,186 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4    ; Phy</t>
+          <t>3    ; RR</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SORCERY_WIZARD</t>
+          <t>ICON_ADVANCE_GREATER_ENCHANTMENTS</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_WIZARD_GAMEPLAY</t>
+          <t>ADVANCE_GREATER_ENCHANTMENTS_GAMEPLAY</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_WIZARD_HISTORICAL</t>
+          <t>ADVANCE_GREATER_ENCHANTMENTS_HISTORICAL</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_WIZARD_PREREQ</t>
+          <t>ADVANCE_GREATER_ENCHANTMENTS_PREREQ</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_WIZARD_STATISTICS</t>
+          <t>ADVANCE_GREATER_ENCHANTMENTS_STATISTICS</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_WIZARD_PREREQ</t>
+          <t>ADVANCE_GREATER_ENCHANTMENTS_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sorcery Master</t>
+          <t>University</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Phy</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Phi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4    ; Pla</t>
+          <t>3    ; Uni</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SORCERY_MASTER</t>
+          <t>ICON_ADVANCE_UNIVERSITY</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MASTER_GAMEPLAY</t>
+          <t>ADVANCE_UNIVERSITY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MASTER_HISTORICAL</t>
+          <t>ADVANCE_UNIVERSITY_HISTORICAL</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MASTER_PREREQ</t>
+          <t>ADVANCE_UNIVERSITY_PREREQ</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MASTER_STATISTICS</t>
+          <t>ADVANCE_UNIVERSITY_STATISTICS</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MASTER_PREREQ</t>
+          <t>ADVANCE_UNIVERSITY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nature Lore</t>
+          <t>Writing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>Alp</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ato</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1    ; Plu</t>
+          <t>3    ; Wri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_NATURE_LORE</t>
+          <t>ICON_ADVANCE_WRITING</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_LORE_GAMEPLAY</t>
+          <t>ADVANCE_WRITING_GAMEPLAY</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_LORE_HISTORICAL</t>
+          <t>ADVANCE_WRITING_HISTORICAL</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_LORE_PREREQ</t>
+          <t>ADVANCE_WRITING_PREREQ</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_LORE_STATISTICS</t>
+          <t>ADVANCE_WRITING_STATISTICS</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_LORE_PREREQ</t>
+          <t>ADVANCE_WRITING_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nature Adept</t>
+          <t>Forces of Nature</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Plu</t>
+          <t>Amp</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -8273,67 +8273,67 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1    ; PT</t>
+          <t>3    ; U1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_NATURE_ADEPT</t>
+          <t>ICON_ADVANCE_FORCES_OF_NATURE</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_ADEPT_GAMEPLAY</t>
+          <t>ADVANCE_FORCES_OF_NATURE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_ADEPT_HISTORICAL</t>
+          <t>ADVANCE_FORCES_OF_NATURE_HISTORICAL</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_ADEPT_PREREQ</t>
+          <t>ADVANCE_FORCES_OF_NATURE_PREREQ</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_ADEPT_STATISTICS</t>
+          <t>ADVANCE_FORCES_OF_NATURE_STATISTICS</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_ADEPT_PREREQ</t>
+          <t>ADVANCE_FORCES_OF_NATURE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Sea Lore</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
+          <t>Nav</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>nil</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>nil</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>0</t>
@@ -8341,55 +8341,55 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1    ; Pot</t>
+          <t>3    ; U3</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_POTTERY</t>
+          <t>ICON_ADVANCE_SEA_LORE</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ADVANCE_POTTERY_GAMEPLAY</t>
+          <t>ADVANCE_SEA_LORE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ADVANCE_POTTERY_HISTORICAL</t>
+          <t>ADVANCE_SEA_LORE_HISTORICAL</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>ADVANCE_POTTERY_PREREQ</t>
+          <t>ADVANCE_SEA_LORE_PREREQ</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>ADVANCE_POTTERY_STATISTICS</t>
+          <t>ADVANCE_SEA_LORE_STATISTICS</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>ADVANCE_POTTERY_PREREQ</t>
+          <t>ADVANCE_SEA_LORE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nature Mage</t>
+          <t>Artificing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Esp</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -8399,42 +8399,42 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1    ; Rad</t>
+          <t>3    ; X3</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_NATURE_MAGE</t>
+          <t>ICON_ADVANCE_ARTIFICING</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGE_GAMEPLAY</t>
+          <t>ADVANCE_ARTIFICING_GAMEPLAY</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGE_HISTORICAL</t>
+          <t>ADVANCE_ARTIFICING_HISTORICAL</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGE_PREREQ</t>
+          <t>ADVANCE_ARTIFICING_PREREQ</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGE_STATISTICS</t>
+          <t>ADVANCE_ARTIFICING_STATISTICS</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGE_PREREQ</t>
+          <t>ADVANCE_ARTIFICING_PREREQ</t>
         </is>
       </c>
     </row>
@@ -8446,13 +8446,13 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Greater Enchantments</t>
+          <t>Lesser Fauna Lore</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Amp</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -8467,55 +8467,55 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3    ; RR</t>
+          <t>3    ; X4</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_GREATER_ENCHANTMENTS</t>
+          <t>ICON_ADVANCE_LESSER_FAUNA_LORE</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_ENCHANTMENTS_GAMEPLAY</t>
+          <t>ADVANCE_LESSER_FAUNA_LORE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_ENCHANTMENTS_HISTORICAL</t>
+          <t>ADVANCE_LESSER_FAUNA_LORE_HISTORICAL</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_ENCHANTMENTS_PREREQ</t>
+          <t>ADVANCE_LESSER_FAUNA_LORE_PREREQ</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_ENCHANTMENTS_STATISTICS</t>
+          <t>ADVANCE_LESSER_FAUNA_LORE_STATISTICS</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_ENCHANTMENTS_PREREQ</t>
+          <t>ADVANCE_LESSER_FAUNA_LORE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nature Wizard</t>
+          <t>Pyrotechnics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Rad</t>
+          <t>Ato</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -8525,60 +8525,60 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1    ; Rec</t>
+          <t>3    ; X5</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_NATURE_WIZARD</t>
+          <t>ICON_ADVANCE_PYROTECHNICS</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_WIZARD_GAMEPLAY</t>
+          <t>ADVANCE_PYROTECHNICS_GAMEPLAY</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_WIZARD_HISTORICAL</t>
+          <t>ADVANCE_PYROTECHNICS_HISTORICAL</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_WIZARD_PREREQ</t>
+          <t>ADVANCE_PYROTECHNICS_PREREQ</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_WIZARD_STATISTICS</t>
+          <t>ADVANCE_PYROTECHNICS_STATISTICS</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_WIZARD_PREREQ</t>
+          <t>ADVANCE_PYROTECHNICS_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nature Master</t>
+          <t>Occult Studies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Rec</t>
+          <t>Env</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -8588,65 +8588,65 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1    ; Ref</t>
+          <t>3    ; X6</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_NATURE_MASTER</t>
+          <t>ICON_ADVANCE_OCCULT_STUDIES</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MASTER_GAMEPLAY</t>
+          <t>ADVANCE_OCCULT_STUDIES_GAMEPLAY</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MASTER_HISTORICAL</t>
+          <t>ADVANCE_OCCULT_STUDIES_HISTORICAL</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MASTER_PREREQ</t>
+          <t>ADVANCE_OCCULT_STUDIES_PREREQ</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MASTER_STATISTICS</t>
+          <t>ADVANCE_OCCULT_STUDIES_STATISTICS</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MASTER_PREREQ</t>
+          <t>ADVANCE_OCCULT_STUDIES_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Death Lore</t>
+          <t>Life Magic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ato</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8656,118 +8656,118 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3    ; Rfg</t>
+          <t>2    ; Gen</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_DEATH_LORE</t>
+          <t>ICON_ADVANCE_LIFE_MAGIC</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_LORE_GAMEPLAY</t>
+          <t>ADVANCE_LIFE_MAGIC_GAMEPLAY</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_LORE_HISTORICAL</t>
+          <t>ADVANCE_LIFE_MAGIC_HISTORICAL</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_LORE_PREREQ</t>
+          <t>ADVANCE_LIFE_MAGIC_PREREQ</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_LORE_STATISTICS</t>
+          <t>ADVANCE_LIFE_MAGIC_STATISTICS</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_LORE_PREREQ</t>
+          <t>ADVANCE_LIFE_MAGIC_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Republic</t>
+          <t>Life Lore</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lit</t>
+          <t>Gen</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Ato</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2    ; Rep</t>
+          <t>2    ; Inv</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_THE_REPUBLIC</t>
+          <t>ICON_ADVANCE_LIFE_LORE</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ADVANCE_THE_REPUBLIC_GAMEPLAY</t>
+          <t>ADVANCE_LIFE_LORE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>ADVANCE_THE_REPUBLIC_HISTORICAL</t>
+          <t>ADVANCE_LIFE_LORE_HISTORICAL</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>ADVANCE_THE_REPUBLIC_PREREQ</t>
+          <t>ADVANCE_LIFE_LORE_PREREQ</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>ADVANCE_THE_REPUBLIC_STATISTICS</t>
+          <t>ADVANCE_LIFE_LORE_STATISTICS</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>ADVANCE_THE_REPUBLIC_PREREQ</t>
+          <t>ADVANCE_LIFE_LORE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Death Adept</t>
+          <t>Life Adept</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Rfg</t>
+          <t>Inv</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8782,55 +8782,55 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3    ; Rob</t>
+          <t>2    ; Lab</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_DEATH_ADEPT</t>
+          <t>ICON_ADVANCE_LIFE_ADEPT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_ADEPT_GAMEPLAY</t>
+          <t>ADVANCE_LIFE_ADEPT_GAMEPLAY</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_ADEPT_HISTORICAL</t>
+          <t>ADVANCE_LIFE_ADEPT_HISTORICAL</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_ADEPT_PREREQ</t>
+          <t>ADVANCE_LIFE_ADEPT_PREREQ</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_ADEPT_STATISTICS</t>
+          <t>ADVANCE_LIFE_ADEPT_STATISTICS</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_ADEPT_PREREQ</t>
+          <t>ADVANCE_LIFE_ADEPT_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sanitation</t>
+          <t>Life Mage</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Lab</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8840,123 +8840,123 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1    ; San</t>
+          <t>2    ; Las</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SANITATION</t>
+          <t>ICON_ADVANCE_LIFE_MAGE</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ADVANCE_SANITATION_GAMEPLAY</t>
+          <t>ADVANCE_LIFE_MAGE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>ADVANCE_SANITATION_HISTORICAL</t>
+          <t>ADVANCE_LIFE_MAGE_HISTORICAL</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>ADVANCE_SANITATION_PREREQ</t>
+          <t>ADVANCE_LIFE_MAGE_PREREQ</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ADVANCE_SANITATION_STATISTICS</t>
+          <t>ADVANCE_LIFE_MAGE_STATISTICS</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>ADVANCE_SANITATION_PREREQ</t>
+          <t>ADVANCE_LIFE_MAGE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Seafaring</t>
+          <t>Life Wizard</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Map</t>
+          <t>Las</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pot</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1    ; Sea</t>
+          <t>2    ; Too</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SEAFARING</t>
+          <t>ICON_ADVANCE_LIFE_WIZARD</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ADVANCE_SEAFARING_GAMEPLAY</t>
+          <t>ADVANCE_LIFE_WIZARD_GAMEPLAY</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>ADVANCE_SEAFARING_HISTORICAL</t>
+          <t>ADVANCE_LIFE_WIZARD_HISTORICAL</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>ADVANCE_SEAFARING_PREREQ</t>
+          <t>ADVANCE_LIFE_WIZARD_PREREQ</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>ADVANCE_SEAFARING_STATISTICS</t>
+          <t>ADVANCE_LIFE_WIZARD_STATISTICS</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>ADVANCE_SEAFARING_PREREQ</t>
+          <t>ADVANCE_LIFE_WIZARD_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Death Mage</t>
+          <t>Life Master</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Too</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8971,37 +8971,37 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3    ; SFl</t>
+          <t>2    ; Mag</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_DEATH_MAGE</t>
+          <t>ICON_ADVANCE_LIFE_MASTER</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGE_GAMEPLAY</t>
+          <t>ADVANCE_LIFE_MASTER_GAMEPLAY</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGE_HISTORICAL</t>
+          <t>ADVANCE_LIFE_MASTER_HISTORICAL</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGE_PREREQ</t>
+          <t>ADVANCE_LIFE_MASTER_PREREQ</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGE_STATISTICS</t>
+          <t>ADVANCE_LIFE_MASTER_STATISTICS</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGE_PREREQ</t>
+          <t>ADVANCE_LIFE_MASTER_PREREQ</t>
         </is>
       </c>
     </row>
@@ -9013,18 +9013,18 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Death Wizard</t>
+          <t>Death Lore</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SFl</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Ato</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -9034,37 +9034,37 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3    ; Sth</t>
+          <t>3    ; Rfg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_DEATH_WIZARD</t>
+          <t>ICON_ADVANCE_DEATH_LORE</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_WIZARD_GAMEPLAY</t>
+          <t>ADVANCE_DEATH_LORE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_WIZARD_HISTORICAL</t>
+          <t>ADVANCE_DEATH_LORE_HISTORICAL</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_WIZARD_PREREQ</t>
+          <t>ADVANCE_DEATH_LORE_PREREQ</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_WIZARD_STATISTICS</t>
+          <t>ADVANCE_DEATH_LORE_STATISTICS</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_WIZARD_PREREQ</t>
+          <t>ADVANCE_DEATH_LORE_PREREQ</t>
         </is>
       </c>
     </row>
@@ -9076,13 +9076,13 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Death Master</t>
+          <t>Death Adept</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sth</t>
+          <t>Rfg</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -9097,123 +9097,123 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3    ; SE</t>
+          <t>3    ; Rob</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_DEATH_MASTER</t>
+          <t>ICON_ADVANCE_DEATH_ADEPT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MASTER_GAMEPLAY</t>
+          <t>ADVANCE_DEATH_ADEPT_GAMEPLAY</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MASTER_HISTORICAL</t>
+          <t>ADVANCE_DEATH_ADEPT_HISTORICAL</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MASTER_PREREQ</t>
+          <t>ADVANCE_DEATH_ADEPT_PREREQ</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MASTER_STATISTICS</t>
+          <t>ADVANCE_DEATH_ADEPT_STATISTICS</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MASTER_PREREQ</t>
+          <t>ADVANCE_DEATH_ADEPT_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Leadership</t>
+          <t>Death Mage</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Uni</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0    ; Tac</t>
+          <t>3    ; SFl</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_LEADERSHIP</t>
+          <t>ICON_ADVANCE_DEATH_MAGE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ADVANCE_LEADERSHIP_GAMEPLAY</t>
+          <t>ADVANCE_DEATH_MAGE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>ADVANCE_LEADERSHIP_HISTORICAL</t>
+          <t>ADVANCE_DEATH_MAGE_HISTORICAL</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>ADVANCE_LEADERSHIP_PREREQ</t>
+          <t>ADVANCE_DEATH_MAGE_PREREQ</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ADVANCE_LEADERSHIP_STATISTICS</t>
+          <t>ADVANCE_DEATH_MAGE_STATISTICS</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>ADVANCE_LEADERSHIP_PREREQ</t>
+          <t>ADVANCE_DEATH_MAGE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sorcerous Lore</t>
+          <t>Death Wizard</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Hor</t>
+          <t>SFl</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ato</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -9223,244 +9223,244 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4    ; The</t>
+          <t>3    ; Sth</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SORCEROUS_LORE</t>
+          <t>ICON_ADVANCE_DEATH_WIZARD</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCEROUS_LORE_GAMEPLAY</t>
+          <t>ADVANCE_DEATH_WIZARD_GAMEPLAY</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCEROUS_LORE_HISTORICAL</t>
+          <t>ADVANCE_DEATH_WIZARD_HISTORICAL</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCEROUS_LORE_PREREQ</t>
+          <t>ADVANCE_DEATH_WIZARD_PREREQ</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCEROUS_LORE_STATISTICS</t>
+          <t>ADVANCE_DEATH_WIZARD_STATISTICS</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCEROUS_LORE_PREREQ</t>
+          <t>ADVANCE_DEATH_WIZARD_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Death Master</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cur</t>
+          <t>Sth</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CoL</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1    ; Tra</t>
+          <t>3    ; SE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_TRADE</t>
+          <t>ICON_ADVANCE_DEATH_MASTER</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ADVANCE_TRADE_GAMEPLAY</t>
+          <t>ADVANCE_DEATH_MASTER_GAMEPLAY</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>ADVANCE_TRADE_HISTORICAL</t>
+          <t>ADVANCE_DEATH_MASTER_HISTORICAL</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>ADVANCE_TRADE_PREREQ</t>
+          <t>ADVANCE_DEATH_MASTER_PREREQ</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>ADVANCE_TRADE_STATISTICS</t>
+          <t>ADVANCE_DEATH_MASTER_STATISTICS</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>ADVANCE_TRADE_PREREQ</t>
+          <t>ADVANCE_DEATH_MASTER_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Death Magic</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Phi</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3    ; Uni</t>
+          <t>3    ; U2</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_UNIVERSITY</t>
+          <t>ICON_ADVANCE_DEATH_MAGIC</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ADVANCE_UNIVERSITY_GAMEPLAY</t>
+          <t>ADVANCE_DEATH_MAGIC_GAMEPLAY</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>ADVANCE_UNIVERSITY_HISTORICAL</t>
+          <t>ADVANCE_DEATH_MAGIC_HISTORICAL</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ADVANCE_UNIVERSITY_PREREQ</t>
+          <t>ADVANCE_DEATH_MAGIC_PREREQ</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>ADVANCE_UNIVERSITY_STATISTICS</t>
+          <t>ADVANCE_DEATH_MAGIC_STATISTICS</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>ADVANCE_UNIVERSITY_PREREQ</t>
+          <t>ADVANCE_DEATH_MAGIC_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Warrior Code</t>
+          <t>Sorcery</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>nil</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>nil</t>
-        </is>
-      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0    ; War</t>
+          <t>4    ; Hor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_WARRIOR_CODE</t>
+          <t>ICON_ADVANCE_SORCERY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ADVANCE_WARRIOR_CODE_GAMEPLAY</t>
+          <t>ADVANCE_SORCERY_GAMEPLAY</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>ADVANCE_WARRIOR_CODE_HISTORICAL</t>
+          <t>ADVANCE_SORCERY_HISTORICAL</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>ADVANCE_WARRIOR_CODE_PREREQ</t>
+          <t>ADVANCE_SORCERY_PREREQ</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>ADVANCE_WARRIOR_CODE_STATISTICS</t>
+          <t>ADVANCE_SORCERY_STATISTICS</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>ADVANCE_WARRIOR_CODE_PREREQ</t>
+          <t>ADVANCE_SORCERY_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Writing</t>
+          <t>Sorcery Mage</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Alp</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -9470,123 +9470,123 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3    ; Wri</t>
+          <t>4    ; NP</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_WRITING</t>
+          <t>ICON_ADVANCE_SORCERY_MAGE</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ADVANCE_WRITING_GAMEPLAY</t>
+          <t>ADVANCE_SORCERY_MAGE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ADVANCE_WRITING_HISTORICAL</t>
+          <t>ADVANCE_SORCERY_MAGE_HISTORICAL</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>ADVANCE_WRITING_PREREQ</t>
+          <t>ADVANCE_SORCERY_MAGE_PREREQ</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>ADVANCE_WRITING_STATISTICS</t>
+          <t>ADVANCE_SORCERY_MAGE_STATISTICS</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>ADVANCE_WRITING_PREREQ</t>
+          <t>ADVANCE_SORCERY_MAGE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Future Technology</t>
+          <t>Sorcery Wizard</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sth</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>nil</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>3    ; ...</t>
+          <t>4    ; Phy</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_FUTURE_TECHNOLOGY</t>
+          <t>ICON_ADVANCE_SORCERY_WIZARD</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ADVANCE_FUTURE_TECHNOLOGY_GAMEPLAY</t>
+          <t>ADVANCE_SORCERY_WIZARD_GAMEPLAY</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ADVANCE_FUTURE_TECHNOLOGY_HISTORICAL</t>
+          <t>ADVANCE_SORCERY_WIZARD_HISTORICAL</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>ADVANCE_FUTURE_TECHNOLOGY_PREREQ</t>
+          <t>ADVANCE_SORCERY_WIZARD_PREREQ</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>ADVANCE_FUTURE_TECHNOLOGY_STATISTICS</t>
+          <t>ADVANCE_SORCERY_WIZARD_STATISTICS</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>ADVANCE_FUTURE_TECHNOLOGY_PREREQ</t>
+          <t>ADVANCE_SORCERY_WIZARD_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Forces of Nature</t>
+          <t>Sorcery Master</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Amp</t>
+          <t>Phy</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9596,65 +9596,65 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3    ; U1</t>
+          <t>4    ; Pla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_FORCES_OF_NATURE</t>
+          <t>ICON_ADVANCE_SORCERY_MASTER</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ADVANCE_FORCES_OF_NATURE_GAMEPLAY</t>
+          <t>ADVANCE_SORCERY_MASTER_GAMEPLAY</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>ADVANCE_FORCES_OF_NATURE_HISTORICAL</t>
+          <t>ADVANCE_SORCERY_MASTER_HISTORICAL</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>ADVANCE_FORCES_OF_NATURE_PREREQ</t>
+          <t>ADVANCE_SORCERY_MASTER_PREREQ</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>ADVANCE_FORCES_OF_NATURE_STATISTICS</t>
+          <t>ADVANCE_SORCERY_MASTER_STATISTICS</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>ADVANCE_FORCES_OF_NATURE_PREREQ</t>
+          <t>ADVANCE_SORCERY_MASTER_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Death Magic</t>
+          <t>Sorcerous Lore</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>Hor</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Ato</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9664,55 +9664,55 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3    ; U2</t>
+          <t>4    ; The</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_DEATH_MAGIC</t>
+          <t>ICON_ADVANCE_SORCEROUS_LORE</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGIC_GAMEPLAY</t>
+          <t>ADVANCE_SORCEROUS_LORE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGIC_HISTORICAL</t>
+          <t>ADVANCE_SORCEROUS_LORE_HISTORICAL</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGIC_PREREQ</t>
+          <t>ADVANCE_SORCEROUS_LORE_PREREQ</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGIC_STATISTICS</t>
+          <t>ADVANCE_SORCEROUS_LORE_STATISTICS</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGIC_PREREQ</t>
+          <t>ADVANCE_SORCEROUS_LORE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sea Lore</t>
+          <t>Sorcery Adept</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Nav</t>
+          <t>The</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9722,54 +9722,54 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3    ; U3</t>
+          <t>4    ; X2</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SEA_LORE</t>
+          <t>ICON_ADVANCE_SORCERY_ADEPT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_LORE_GAMEPLAY</t>
+          <t>ADVANCE_SORCERY_ADEPT_GAMEPLAY</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_LORE_HISTORICAL</t>
+          <t>ADVANCE_SORCERY_ADEPT_HISTORICAL</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_LORE_PREREQ</t>
+          <t>ADVANCE_SORCERY_ADEPT_PREREQ</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_LORE_STATISTICS</t>
+          <t>ADVANCE_SORCERY_ADEPT_STATISTICS</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_LORE_PREREQ</t>
+          <t>ADVANCE_SORCERY_ADEPT_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nature Magic</t>
+          <t>Chaos Magic</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -9790,60 +9790,60 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1    ; X1</t>
+          <t>0    ; Gun</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_NATURE_MAGIC</t>
+          <t>ICON_ADVANCE_CHAOS_MAGIC</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGIC_GAMEPLAY</t>
+          <t>ADVANCE_CHAOS_MAGIC_GAMEPLAY</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGIC_HISTORICAL</t>
+          <t>ADVANCE_CHAOS_MAGIC_HISTORICAL</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGIC_PREREQ</t>
+          <t>ADVANCE_CHAOS_MAGIC_PREREQ</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGIC_STATISTICS</t>
+          <t>ADVANCE_CHAOS_MAGIC_STATISTICS</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGIC_PREREQ</t>
+          <t>ADVANCE_CHAOS_MAGIC_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sorcery Adept</t>
+          <t>Chaos Lore</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>The</t>
+          <t>Gun</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>nil</t>
+          <t>Ato</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9853,55 +9853,55 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4    ; X2</t>
+          <t>0    ; MP</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_SORCERY_ADEPT</t>
+          <t>ICON_ADVANCE_CHAOS_LORE</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_ADEPT_GAMEPLAY</t>
+          <t>ADVANCE_CHAOS_LORE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_ADEPT_HISTORICAL</t>
+          <t>ADVANCE_CHAOS_LORE_HISTORICAL</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_ADEPT_PREREQ</t>
+          <t>ADVANCE_CHAOS_LORE_PREREQ</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_ADEPT_STATISTICS</t>
+          <t>ADVANCE_CHAOS_LORE_STATISTICS</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_ADEPT_PREREQ</t>
+          <t>ADVANCE_CHAOS_LORE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Artificing</t>
+          <t>Chaos Adept</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Esp</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9911,60 +9911,60 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>3    ; X3</t>
+          <t>0    ; Med</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_ARTIFICING</t>
+          <t>ICON_ADVANCE_CHAOS_ADEPT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ADVANCE_ARTIFICING_GAMEPLAY</t>
+          <t>ADVANCE_CHAOS_ADEPT_GAMEPLAY</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>ADVANCE_ARTIFICING_HISTORICAL</t>
+          <t>ADVANCE_CHAOS_ADEPT_HISTORICAL</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>ADVANCE_ARTIFICING_PREREQ</t>
+          <t>ADVANCE_CHAOS_ADEPT_PREREQ</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>ADVANCE_ARTIFICING_STATISTICS</t>
+          <t>ADVANCE_CHAOS_ADEPT_STATISTICS</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>ADVANCE_ARTIFICING_PREREQ</t>
+          <t>ADVANCE_CHAOS_ADEPT_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lesser Fauna Lore</t>
+          <t>Chaos Mage</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Amp</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9974,60 +9974,60 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>3    ; X4</t>
+          <t>0    ; Met</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_LESSER_FAUNA_LORE</t>
+          <t>ICON_ADVANCE_CHAOS_MAGE</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_FAUNA_LORE_GAMEPLAY</t>
+          <t>ADVANCE_CHAOS_MAGE_GAMEPLAY</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_FAUNA_LORE_HISTORICAL</t>
+          <t>ADVANCE_CHAOS_MAGE_HISTORICAL</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_FAUNA_LORE_PREREQ</t>
+          <t>ADVANCE_CHAOS_MAGE_PREREQ</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_FAUNA_LORE_STATISTICS</t>
+          <t>ADVANCE_CHAOS_MAGE_STATISTICS</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_FAUNA_LORE_PREREQ</t>
+          <t>ADVANCE_CHAOS_MAGE_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pyrotechnics</t>
+          <t>Chaos Wizard</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ato</t>
+          <t>Met</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -10037,60 +10037,60 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>3    ; X5</t>
+          <t>0    ; Min</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_PYROTECHNICS</t>
+          <t>ICON_ADVANCE_CHAOS_WIZARD</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ADVANCE_PYROTECHNICS_GAMEPLAY</t>
+          <t>ADVANCE_CHAOS_WIZARD_GAMEPLAY</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>ADVANCE_PYROTECHNICS_HISTORICAL</t>
+          <t>ADVANCE_CHAOS_WIZARD_HISTORICAL</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>ADVANCE_PYROTECHNICS_PREREQ</t>
+          <t>ADVANCE_CHAOS_WIZARD_PREREQ</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>ADVANCE_PYROTECHNICS_STATISTICS</t>
+          <t>ADVANCE_CHAOS_WIZARD_STATISTICS</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>ADVANCE_PYROTECHNICS_PREREQ</t>
+          <t>ADVANCE_CHAOS_WIZARD_PREREQ</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Occult Studies</t>
+          <t>Chaos Master</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Env</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10100,47 +10100,110 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>3    ; X6</t>
+          <t>0    ; Mob</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>ICON_ADVANCE_OCCULT_STUDIES</t>
+          <t>ICON_ADVANCE_CHAOS_MASTER</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ADVANCE_OCCULT_STUDIES_GAMEPLAY</t>
+          <t>ADVANCE_CHAOS_MASTER_GAMEPLAY</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>ADVANCE_OCCULT_STUDIES_HISTORICAL</t>
+          <t>ADVANCE_CHAOS_MASTER_HISTORICAL</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>ADVANCE_OCCULT_STUDIES_PREREQ</t>
+          <t>ADVANCE_CHAOS_MASTER_PREREQ</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>ADVANCE_OCCULT_STUDIES_STATISTICS</t>
+          <t>ADVANCE_CHAOS_MASTER_STATISTICS</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>ADVANCE_OCCULT_STUDIES_PREREQ</t>
+          <t>ADVANCE_CHAOS_MASTER_PREREQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Future Technology</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Sth</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>3    ; ...</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>ICON_ADVANCE_FUTURE_TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUTURE_TECHNOLOGY_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUTURE_TECHNOLOGY_HISTORICAL</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUTURE_TECHNOLOGY_PREREQ</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUTURE_TECHNOLOGY_STATISTICS</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUTURE_TECHNOLOGY_PREREQ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M88"/>
+  <autoFilter ref="A1:M89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19653,28 +19716,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_WIZARDS_FORTRESS"ICON_IMPROVE_WIZARDS_FORTRESS.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_WIZARDS_FORTRESS"ICON_IMPROVE_WIZARDS_FORTRESS.tga""CA023A.avi""IMPROVE_WIZARDS_FORTRESS_GAMEPLAY""IMPROVE_WIZARDS_FORTRESS_HISTORICAL""IMPROVE_WIZARDS_FORTRESS_PREREQ""IMPROVE_WIZARDS_FORTRESS_STATISTICS""UPM001.tga""IMPROVE_WIZARDS_FORTRESS_STATISTICS"</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_BARRACKS"ICON_IMPROVE_BARRACKS.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_BARRACKS"ICON_IMPROVE_BARRACKS.tga""CA023A.avi""IMPROVE_BARRACKS_GAMEPLAY""IMPROVE_BARRACKS_HISTORICAL""IMPROVE_BARRACKS_PREREQ""IMPROVE_BARRACKS_STATISTICS""UPM001.tga""IMPROVE_BARRACKS_STATISTICS"</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_GRANARY"ICON_IMPROVE_GRANARY.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_GRANARY"ICON_IMPROVE_GRANARY.tga""CA023A.avi""IMPROVE_GRANARY_GAMEPLAY""IMPROVE_GRANARY_HISTORICAL""IMPROVE_GRANARY_PREREQ""IMPROVE_GRANARY_STATISTICS""UPM001.tga""IMPROVE_GRANARY_STATISTICS"</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_TEMPLE"ICON_IMPROVE_TEMPLE.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_TEMPLE"ICON_IMPROVE_TEMPLE.tga""CA023A.avi""IMPROVE_TEMPLE_GAMEPLAY""IMPROVE_TEMPLE_HISTORICAL""IMPROVE_TEMPLE_PREREQ""IMPROVE_TEMPLE_STATISTICS""UPM001.tga""IMPROVE_TEMPLE_STATISTICS"</t>
         </is>
       </c>
     </row>
@@ -19688,28 +19751,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_LIBRARY"ICON_IMPROVE_LIBRARY.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_LIBRARY"ICON_IMPROVE_LIBRARY.tga""CA023A.avi""IMPROVE_LIBRARY_GAMEPLAY""IMPROVE_LIBRARY_HISTORICAL""IMPROVE_LIBRARY_PREREQ""IMPROVE_LIBRARY_STATISTICS""UPM001.tga""IMPROVE_LIBRARY_STATISTICS"</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_COURTHOUSE"ICON_IMPROVE_COURTHOUSE.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_COURTHOUSE"ICON_IMPROVE_COURTHOUSE.tga""CA023A.avi""IMPROVE_COURTHOUSE_GAMEPLAY""IMPROVE_COURTHOUSE_HISTORICAL""IMPROVE_COURTHOUSE_PREREQ""IMPROVE_COURTHOUSE_STATISTICS""UPM001.tga""IMPROVE_COURTHOUSE_STATISTICS"</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_CITY_WALLS"ICON_IMPROVE_CITY_WALLS.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_CITY_WALLS"ICON_IMPROVE_CITY_WALLS.tga""CA023A.avi""IMPROVE_CITY_WALLS_GAMEPLAY""IMPROVE_CITY_WALLS_HISTORICAL""IMPROVE_CITY_WALLS_PREREQ""IMPROVE_CITY_WALLS_STATISTICS""UPM001.tga""IMPROVE_CITY_WALLS_STATISTICS"</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_AQUEDUCT"ICON_IMPROVE_AQUEDUCT.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_AQUEDUCT"ICON_IMPROVE_AQUEDUCT.tga""CA023A.avi""IMPROVE_AQUEDUCT_GAMEPLAY""IMPROVE_AQUEDUCT_HISTORICAL""IMPROVE_AQUEDUCT_PREREQ""IMPROVE_AQUEDUCT_STATISTICS""UPM001.tga""IMPROVE_AQUEDUCT_STATISTICS"</t>
         </is>
       </c>
     </row>
@@ -19723,14 +19786,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_CATHEDRAL"ICON_IMPROVE_CATHEDRAL.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_CATHEDRAL"ICON_IMPROVE_CATHEDRAL.tga""CA023A.avi""IMPROVE_CATHEDRAL_GAMEPLAY""IMPROVE_CATHEDRAL_HISTORICAL""IMPROVE_CATHEDRAL_PREREQ""IMPROVE_CATHEDRAL_STATISTICS""UPM001.tga""IMPROVE_CATHEDRAL_STATISTICS"</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_UNIVERSITY"ICON_IMPROVE_UNIVERSITY.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_UNIVERSITY"ICON_IMPROVE_UNIVERSITY.tga""CA023A.avi""IMPROVE_UNIVERSITY_GAMEPLAY""IMPROVE_UNIVERSITY_HISTORICAL""IMPROVE_UNIVERSITY_PREREQ""IMPROVE_UNIVERSITY_STATISTICS""UPM001.tga""IMPROVE_UNIVERSITY_STATISTICS"</t>
         </is>
       </c>
     </row>
@@ -19744,14 +19807,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_COLOSSEUM"ICON_IMPROVE_COLOSSEUM.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_COLOSSEUM"ICON_IMPROVE_COLOSSEUM.tga""CA023A.avi""IMPROVE_COLOSSEUM_GAMEPLAY""IMPROVE_COLOSSEUM_HISTORICAL""IMPROVE_COLOSSEUM_PREREQ""IMPROVE_COLOSSEUM_STATISTICS""UPM001.tga""IMPROVE_COLOSSEUM_STATISTICS"</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_MECHANICIANS_GUILD"ICON_IMPROVE_MECHANICIANS_GUILD.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_MECHANICIANS_GUILD"ICON_IMPROVE_MECHANICIANS_GUILD.tga""CA023A.avi""IMPROVE_MECHANICIANS_GUILD_GAMEPLAY""IMPROVE_MECHANICIANS_GUILD_HISTORICAL""IMPROVE_MECHANICIANS_GUILD_PREREQ""IMPROVE_MECHANICIANS_GUILD_STATISTICS""UPM001.tga""IMPROVE_MECHANICIANS_GUILD_STATISTICS"</t>
         </is>
       </c>
     </row>
@@ -19793,14 +19856,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_PRIMAL_SOURCE"ICON_IMPROVE_PRIMAL_SOURCE.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_PRIMAL_SOURCE"ICON_IMPROVE_PRIMAL_SOURCE.tga""CA023A.avi""IMPROVE_PRIMAL_SOURCE_GAMEPLAY""IMPROVE_PRIMAL_SOURCE_HISTORICAL""IMPROVE_PRIMAL_SOURCE_PREREQ""IMPROVE_PRIMAL_SOURCE_STATISTICS""UPM001.tga""IMPROVE_PRIMAL_SOURCE_STATISTICS"</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_MERCHANTS_GUILD"ICON_IMPROVE_MERCHANTS_GUILD.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_MERCHANTS_GUILD"ICON_IMPROVE_MERCHANTS_GUILD.tga""CA023A.avi""IMPROVE_MERCHANTS_GUILD_GAMEPLAY""IMPROVE_MERCHANTS_GUILD_HISTORICAL""IMPROVE_MERCHANTS_GUILD_PREREQ""IMPROVE_MERCHANTS_GUILD_STATISTICS""UPM001.tga""IMPROVE_MERCHANTS_GUILD_STATISTICS"</t>
         </is>
       </c>
     </row>
@@ -19828,7 +19891,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_BEACON_OF_WISDOM"ICON_IMPROVE_BEACON_OF_WISDOM.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_BEACON_OF_WISDOM"ICON_IMPROVE_BEACON_OF_WISDOM.tga""CA023A.avi""IMPROVE_BEACON_OF_WISDOM_GAMEPLAY""IMPROVE_BEACON_OF_WISDOM_HISTORICAL""IMPROVE_BEACON_OF_WISDOM_PREREQ""IMPROVE_BEACON_OF_WISDOM_STATISTICS""UPM001.tga""IMPROVE_BEACON_OF_WISDOM_STATISTICS"</t>
         </is>
       </c>
     </row>
@@ -19842,7 +19905,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_COASTAL_FORTRESS"ICON_IMPROVE_COASTAL_FORTRESS.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_COASTAL_FORTRESS"ICON_IMPROVE_COASTAL_FORTRESS.tga""CA023A.avi""IMPROVE_COASTAL_FORTRESS_GAMEPLAY""IMPROVE_COASTAL_FORTRESS_HISTORICAL""IMPROVE_COASTAL_FORTRESS_PREREQ""IMPROVE_COASTAL_FORTRESS_STATISTICS""UPM001.tga""IMPROVE_COASTAL_FORTRESS_STATISTICS"</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19919,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_HARBOR"ICON_IMPROVE_HARBOR.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_HARBOR"ICON_IMPROVE_HARBOR.tga""CA023A.avi""IMPROVE_HARBOR_GAMEPLAY""IMPROVE_HARBOR_HISTORICAL""IMPROVE_HARBOR_PREREQ""IMPROVE_HARBOR_STATISTICS""UPM001.tga""IMPROVE_HARBOR_STATISTICS"</t>
         </is>
       </c>
     </row>
@@ -19870,7 +19933,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_FANTASTIC_STABLE"ICON_IMPROVE_FANTASTIC_STABLE.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_FANTASTIC_STABLE"ICON_IMPROVE_FANTASTIC_STABLE.tga""CA023A.avi""IMPROVE_FANTASTIC_STABLE_GAMEPLAY""IMPROVE_FANTASTIC_STABLE_HISTORICAL""IMPROVE_FANTASTIC_STABLE_PREREQ""IMPROVE_FANTASTIC_STABLE_STATISTICS""UPM001.tga""IMPROVE_FANTASTIC_STABLE_STATISTICS"</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19947,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ICON_IMPROVE_PORT"ICON_IMPROVE_PORT.tga""CA023A.avi""GAMEM001.txt""HISTM001.txt""PREQM001.txt""VARIM001.txt""UPM001.tga""STATM001.txt"</t>
+          <t>ICON_IMPROVE_PORT"ICON_IMPROVE_PORT.tga""CA023A.avi""IMPROVE_PORT_GAMEPLAY""IMPROVE_PORT_HISTORICAL""IMPROVE_PORT_PREREQ""IMPROVE_PORT_STATISTICS""UPM001.tga""IMPROVE_PORT_STATISTICS"</t>
         </is>
       </c>
     </row>
@@ -19935,7 +19998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19945,6 +20008,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19983,6 +20047,11 @@
           <t>sphere</t>
         </is>
       </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>effects</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20020,6 +20089,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Capitol; HappyInc 1; DefendersPercent 25</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20057,6 +20131,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EnablesLandVeterans; DefendersPercent 10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20094,6 +20173,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FoodPercent 0.1; StarvationProtection 2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20131,6 +20215,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>HappyInc 1; IsReligious; Cathedral</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20168,6 +20257,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SciencePercent 0.1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20205,6 +20299,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>LowerCrime -0.1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20242,6 +20341,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DefendersPercent 15; PreventConversion 0.5; PreventSlavery 0.5; CityWalls; CantBuildInSea</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20279,6 +20383,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>RaiseOvercrowdingLevel 6; RaiseMaxPopulation 14</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20316,6 +20425,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>HappyInc 3; IsReligious; Cathedral</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20353,6 +20467,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SciencePercent 0.15</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20390,6 +20509,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>HappyInc 2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20427,6 +20551,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ProductionPercent 0.15; AllowGrunts</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20464,6 +20593,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20501,6 +20631,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20538,6 +20669,11 @@
           <t>nature</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>FoodPercent 0.15; HappyInc 1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20575,6 +20711,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CommercePercent 0.15; Brokerage</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20612,6 +20753,11 @@
           <t>sorcery</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SciencePercent 0.2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20649,6 +20795,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CoastalBuilding; OffenseBonusWater 25; DefendersPercent 10</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -20686,6 +20837,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CoastalBuilding; FoodPercent 0.1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -20723,6 +20879,11 @@
           <t>nature</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>OffenseBonusLand 25; IncreaseHP 5</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20760,6 +20921,11 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CoastalBuilding; CommercePercent 0.1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -20797,6 +20963,7 @@
           <t>nature</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -20834,6 +21001,7 @@
           <t>sorcery</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -20871,6 +21039,7 @@
           <t>nature</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20908,6 +21077,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -20945,6 +21115,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20982,6 +21153,7 @@
           <t>death</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -21019,6 +21191,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -21056,6 +21229,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -21093,6 +21267,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -21130,6 +21305,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -21167,6 +21343,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -21204,6 +21381,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -21241,6 +21419,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -21278,6 +21457,7 @@
           <t>chaos</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -21315,6 +21495,7 @@
           <t>life</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -21352,6 +21533,7 @@
           <t>sorcery</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -21389,6 +21571,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -21426,6 +21609,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -21463,6 +21647,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -21500,6 +21685,7 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -21537,6 +21723,7 @@
           <t>chaos</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -21574,6 +21761,7 @@
           <t>death</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -21611,6 +21799,7 @@
           <t>sorcery</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -21648,6 +21837,7 @@
           <t>life</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -21685,9 +21875,10 @@
           <t>neutral</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G47"/>
+  <autoFilter ref="A1:H47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42996,13 +43187,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43024,6 +43216,11 @@
       <c r="D1" s="3" t="inlineStr">
         <is>
           <t>IncludeInMoM</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>effects</t>
         </is>
       </c>
     </row>
@@ -43053,6 +43250,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>IncreaseFoodAllCities 2; NoPollutionUnhappiness</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43080,6 +43282,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>IncHappinessEmpire 2; TemporaryFullHappiness 10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43107,6 +43314,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>IncreaseFoodAllCities 3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43134,6 +43346,7 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43161,6 +43374,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IncKnowledgePercent 20; IncreaseScientists 2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43188,6 +43406,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IncHappinessEmpire 2; IncreaseCathedrals 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43215,6 +43438,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ProtectFromBarbarians; PreventConversion</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43242,6 +43470,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IncreaseHp 10; ReduceReadinessCost 50</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43269,6 +43502,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DecEmpireSize 4; IncreaseRegard 25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -43296,6 +43534,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>IncHappinessEmpire 1; IncreaseRegard 25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43323,6 +43566,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>IncHappinessEmpire 3; IncreaseCathedrals 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -43350,6 +43598,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RandomAdvanceChance 10; GlobalRadar</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -43377,6 +43630,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IncreaseBoatMovement 3; GoldPerWaterTradeRoute 10; AllBoatsDeepWater</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43404,6 +43662,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>IncKnowledgePercent 15; IncreaseSpecialists 1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -43431,6 +43694,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>IncreaseProduction 25; IncreaseHp 10</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43458,6 +43726,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IncreaseFoodAllCities 2; IncHappinessEmpire 2</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43485,6 +43758,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IncKnowledgePercent 25; IncreaseScientists 2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43512,6 +43790,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BonusGold 250; IncreaseBrokerages 1; GoldPerInternationalTradeRoute 10</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43539,6 +43822,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RandomAdvanceChance 15; IncKnowledgePercent 10</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43566,6 +43854,7 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -43593,6 +43882,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SpiesEverywhere; EmbassiesEverywhere; DecCrimePercent 30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -43620,6 +43914,7 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -43647,6 +43942,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IncreaseProduction 30; DecreaseMaintenance 25</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -43674,6 +43974,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DecCrimePercent 50; FreeSlaves; ProhibitSlavers</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -43701,6 +44006,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>IncKnowledgePercent 30; RandomAdvanceChance 10; EmbassiesEverywhereEvenAtWar</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -43728,6 +44038,7 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -43755,6 +44066,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AllCitizensContent; IncHappinessEmpire 3</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -43782,9 +44098,10 @@
           <t>True</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D29"/>
+  <autoFilter ref="A1:E29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45547,12 +45864,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Ast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ADVANCE_MASONRY</t>
+          <t>ADVANCE_ASTRONOMY</t>
         </is>
       </c>
     </row>
@@ -45564,12 +45881,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pot</t>
+          <t>Ato</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ADVANCE_POTTERY</t>
+          <t>ADVANCE_ELDRITCH_LORE</t>
         </is>
       </c>
     </row>
@@ -45581,12 +45898,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bro</t>
+          <t>Ban</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADVANCE_BRONZE_WORKING</t>
+          <t>ADVANCE_BANKING</t>
         </is>
       </c>
     </row>
@@ -45598,12 +45915,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cer</t>
+          <t>Bro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADVANCE_CEREMONIAL_BURIAL</t>
+          <t>ADVANCE_BRONZE_WORKING</t>
         </is>
       </c>
     </row>
@@ -45615,12 +45932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cur</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADVANCE_CURRENCY</t>
+          <t>ADVANCE_HEALING</t>
         </is>
       </c>
     </row>
@@ -45632,12 +45949,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wri</t>
+          <t>Cer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ADVANCE_WRITING</t>
+          <t>ADVANCE_CEREMONIAL_BURIAL</t>
         </is>
       </c>
     </row>
@@ -45649,12 +45966,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CoL</t>
+          <t>Cmb</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ADVANCE_CODE_OF_LAWS</t>
+          <t>ADVANCE_LESSER_ENCHANMENTS</t>
         </is>
       </c>
     </row>
@@ -45666,12 +45983,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cst</t>
+          <t>Cmp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADVANCE_CONSTRUCTION</t>
+          <t>ADVANCE_METAMORPHOSIS</t>
         </is>
       </c>
     </row>
@@ -45683,12 +46000,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ban</t>
+          <t>CoL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ADVANCE_BANKING</t>
+          <t>ADVANCE_CODE_OF_LAWS</t>
         </is>
       </c>
     </row>
@@ -45700,12 +46017,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>Cst</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ADVANCE_COMMUNE_WITH_GODS</t>
+          <t>ADVANCE_CONSTRUCTION</t>
         </is>
       </c>
     </row>
@@ -45717,12 +46034,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Uni</t>
+          <t>Cur</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADVANCE_UNIVERSITY</t>
+          <t>ADVANCE_CURRENCY</t>
         </is>
       </c>
     </row>
@@ -45734,12 +46051,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tra</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ADVANCE_TRADE</t>
+          <t>ADVANCE_RUNE_LORE</t>
         </is>
       </c>
     </row>
@@ -45756,7 +46073,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADVANCE_ECONOMICS</t>
+          <t>ADVANCE_ECOGNOMICS</t>
         </is>
       </c>
     </row>
@@ -45768,12 +46085,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>San</t>
+          <t>Eng</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ADVANCE_SANITATION</t>
+          <t>ADVANCE_ENGINEERING</t>
         </is>
       </c>
     </row>
@@ -45785,12 +46102,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Feu</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADVANCE_SEAFARING</t>
+          <t>ADVANCE_FEUDALISM</t>
         </is>
       </c>
     </row>
@@ -45802,12 +46119,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Feu</t>
+          <t>Fli</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ADVANCE_FEUDALISM</t>
+          <t>ADVANCE_WIZARDRY</t>
         </is>
       </c>
     </row>
@@ -45819,12 +46136,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eng</t>
+          <t>Inv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ADVANCE_ENGINEERING</t>
+          <t>ADVANCE_INVENTION</t>
         </is>
       </c>
     </row>
@@ -45836,12 +46153,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inv</t>
+          <t>Lit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ADVANCE_INVENTION</t>
+          <t>ADVANCE_LITERACY</t>
         </is>
       </c>
     </row>
@@ -45853,12 +46170,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nav</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ADVANCE_NAVIGATION</t>
+          <t>ADVANCE_COMMUNE_WITH_GODS</t>
         </is>
       </c>
     </row>
@@ -45870,12 +46187,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ADVANCE_THEOLOGY</t>
+          <t>ADVANCE_MASONRY</t>
         </is>
       </c>
     </row>
@@ -45887,12 +46204,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ast</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ADVANCE_ASTRONOMY</t>
+          <t>ADVANCE_CHAOS_WIZARD</t>
         </is>
       </c>
     </row>
@@ -45904,12 +46221,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lit</t>
+          <t>Mys</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ADVANCE_LITERACY</t>
+          <t>ADVANCE_MYSTICISM</t>
         </is>
       </c>
     </row>
@@ -45921,12 +46238,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dem</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ADVANCE_DEMOCRACY</t>
+          <t>ADVANCE_GRAND_MASTERY</t>
         </is>
       </c>
     </row>
@@ -45938,12 +46255,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pho</t>
+          <t>Nav</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ADVANCE_PHILOSOPHY</t>
+          <t>ADVANCE_NAVIGATION</t>
         </is>
       </c>
     </row>
@@ -45955,12 +46272,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fli</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ADVANCE_WIZARDRY</t>
+          <t>ADVANCE_NATURE_ADEPT</t>
         </is>
       </c>
     </row>
@@ -45972,12 +46289,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rec</t>
+          <t>Pho</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_WIZARD</t>
+          <t>ADVANCE_PHILOSOPHY</t>
         </is>
       </c>
     </row>
@@ -45989,12 +46306,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>Phy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ADVANCE_FORCES_OF_NATURE</t>
+          <t>ADVANCE_SORCERY_WIZARD</t>
         </is>
       </c>
     </row>
@@ -46006,12 +46323,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>Plu</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_LORE</t>
+          <t>ADVANCE_NATURE_LORE</t>
         </is>
       </c>
     </row>
@@ -46023,12 +46340,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>X3</t>
+          <t>Pot</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ADVANCE_ARTIFICING</t>
+          <t>ADVANCE_POTTERY</t>
         </is>
       </c>
     </row>
@@ -46040,12 +46357,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>X4</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_FAUNA_LORE</t>
+          <t>ADVANCE_GREATER_ENCHANTMENTS</t>
         </is>
       </c>
     </row>
@@ -46057,12 +46374,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ato</t>
+          <t>Rec</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ADVANCE_ELDRITCH_LORE</t>
+          <t>ADVANCE_NATURE_WIZARD</t>
         </is>
       </c>
     </row>
@@ -46074,12 +46391,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ADVANCE_HEALING</t>
+          <t>ADVANCE_DEATH_ADEPT</t>
         </is>
       </c>
     </row>
@@ -46091,12 +46408,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cmb</t>
+          <t>San</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_ENCHANTMENTS</t>
+          <t>ADVANCE_SANITATION</t>
         </is>
       </c>
     </row>
@@ -46108,12 +46425,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cmp</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ADVANCE_METAMORPHOSIS</t>
+          <t>ADVANCE_SEAFARING</t>
         </is>
       </c>
     </row>
@@ -46125,12 +46442,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Sth</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ADVANCE_RUNE_LORE</t>
+          <t>ADVANCE_DEATH_WIZARD</t>
         </is>
       </c>
     </row>
@@ -46142,12 +46459,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>The</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_WIZARD</t>
+          <t>ADVANCE_THEOLOGY</t>
         </is>
       </c>
     </row>
@@ -46159,12 +46476,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mys</t>
+          <t>Too</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ADVANCE_MYSTICISM</t>
+          <t>ADVANCE_LIFE_WIZARD</t>
         </is>
       </c>
     </row>
@@ -46176,12 +46493,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>Tra</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ADVANCE_GRAND_MASTERY</t>
+          <t>ADVANCE_TRADE</t>
         </is>
       </c>
     </row>
@@ -46193,12 +46510,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_ADEPT</t>
+          <t>ADVANCE_FORCES_OF_NATURE</t>
         </is>
       </c>
     </row>
@@ -46210,12 +46527,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Phy</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_WIZARD</t>
+          <t>ADVANCE_SEA_LORE</t>
         </is>
       </c>
     </row>
@@ -46227,12 +46544,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Plu</t>
+          <t>Uni</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_LORE</t>
+          <t>ADVANCE_UNIVERSITY</t>
         </is>
       </c>
     </row>
@@ -46244,12 +46561,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>Wri</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_ENCHANTMENTS</t>
+          <t>ADVANCE_WRITING</t>
         </is>
       </c>
     </row>
@@ -46261,12 +46578,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>X3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_ADEPT</t>
+          <t>ADVANCE_ARTIFICING</t>
         </is>
       </c>
     </row>
@@ -46278,29 +46595,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sth</t>
+          <t>X4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_WIZARD</t>
+          <t>ADVANCE_LESSER_FAUNA_LORE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>prereq</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Too</t>
+          <t>AFl</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_WIZARD</t>
+          <t>ADVANCE_ALCHEMY</t>
         </is>
       </c>
     </row>
@@ -46312,12 +46629,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AFl</t>
+          <t>Alp</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ADVANCE_ALCHEMY</t>
+          <t>ADVANCE_ALPHABET</t>
         </is>
       </c>
     </row>
@@ -46329,12 +46646,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alp</t>
+          <t>Amp</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ADVANCE_ALPHABET</t>
+          <t>ADVANCE_ANIMISM</t>
         </is>
       </c>
     </row>
@@ -46346,12 +46663,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amp</t>
+          <t>Ast</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ADVANCE_ANIMISM</t>
+          <t>ADVANCE_ASTROLOGY</t>
         </is>
       </c>
     </row>
@@ -46363,12 +46680,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ast</t>
+          <t>Ato</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ADVANCE_ASTROLOGY</t>
+          <t>ADVANCE_ELDRITCH_LORE</t>
         </is>
       </c>
     </row>
@@ -46380,12 +46697,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ato</t>
+          <t>Ban</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ADVANCE_ELDRITCH_LORE</t>
+          <t>ADVANCE_BANKING</t>
         </is>
       </c>
     </row>
@@ -46397,12 +46714,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ban</t>
+          <t>Bri</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ADVANCE_BANKING</t>
+          <t>ADVANCE_BRIDGE_BUILDING</t>
         </is>
       </c>
     </row>
@@ -46414,12 +46731,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bri</t>
+          <t>Bro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ADVANCE_BRIDGE_BUILDING</t>
+          <t>ADVANCE_BRONZE_WORKING</t>
         </is>
       </c>
     </row>
@@ -46431,12 +46748,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bro</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ADVANCE_BRONZE_WORKING</t>
+          <t>ADVANCE_HEALING</t>
         </is>
       </c>
     </row>
@@ -46499,12 +46816,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CoL</t>
+          <t>Cmb</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ADVANCE_CODE_OF_LAWS</t>
+          <t>ADVANCE_LESSER_ENCHANMENTS</t>
         </is>
       </c>
     </row>
@@ -46516,12 +46833,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cmb</t>
+          <t>Cmp</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_ENCHANTMENTS</t>
+          <t>ADVANCE_METAMORPHOSIS</t>
         </is>
       </c>
     </row>
@@ -46533,12 +46850,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cmp</t>
+          <t>CoL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ADVANCE_METAMORPHOSIS</t>
+          <t>ADVANCE_CODE_OF_LAWS</t>
         </is>
       </c>
     </row>
@@ -46550,12 +46867,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cst</t>
+          <t>Cor</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ADVANCE_CONSTRUCTION</t>
+          <t>ADVANCE_PANTHEISM</t>
         </is>
       </c>
     </row>
@@ -46567,12 +46884,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cor</t>
+          <t>Cst</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ADVANCE_PANTHEISM</t>
+          <t>ADVANCE_CONSTRUCTION</t>
         </is>
       </c>
     </row>
@@ -46618,12 +46935,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Eng</t>
+          <t>Eco</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_MASTERY</t>
+          <t>ADVANCE_ECOGNOMICS</t>
         </is>
       </c>
     </row>
@@ -46635,12 +46952,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Env</t>
+          <t>Eng</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ADVANCE_SHAMANISM</t>
+          <t>ADVANCE_SEA_MASTERY</t>
         </is>
       </c>
     </row>
@@ -46652,12 +46969,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Esp</t>
+          <t>Env</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ADVANCE_THAUMATURGY</t>
+          <t>ADVANCE_SHAMANISM</t>
         </is>
       </c>
     </row>
@@ -46669,12 +46986,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Exp</t>
+          <t>Esp</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ADVANCE_TACTICS</t>
+          <t>ADVANCE_THAUMATURGY</t>
         </is>
       </c>
     </row>
@@ -46686,12 +47003,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Feu</t>
+          <t>Exp</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ADVANCE_FEUDALISM</t>
+          <t>ADVANCE_TACTICS</t>
         </is>
       </c>
     </row>
@@ -46703,12 +47020,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fli</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ADVANCE_WIZARDRY</t>
+          <t>ADVANCE_GLYPHS</t>
         </is>
       </c>
     </row>
@@ -46720,12 +47037,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>Feu</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ADVANCE_GLYPHS</t>
+          <t>ADVANCE_FEUDALISM</t>
         </is>
       </c>
     </row>
@@ -46737,12 +47054,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gen</t>
+          <t>Fli</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGIC</t>
+          <t>ADVANCE_WIZARDRY</t>
         </is>
       </c>
     </row>
@@ -46754,12 +47071,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Gun</t>
+          <t>Gen</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGIC</t>
+          <t>ADVANCE_LIFE_MAGIC</t>
         </is>
       </c>
     </row>
@@ -46771,12 +47088,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hor</t>
+          <t>Gun</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY</t>
+          <t>ADVANCE_CHAOS_MAGIC</t>
         </is>
       </c>
     </row>
@@ -46788,12 +47105,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Inv</t>
+          <t>Hor</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_LORE</t>
+          <t>ADVANCE_SORCERY</t>
         </is>
       </c>
     </row>
@@ -46805,12 +47122,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Iro</t>
+          <t>Inv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ADVANCE_IRON_WORKING</t>
+          <t>ADVANCE_LIFE_LORE</t>
         </is>
       </c>
     </row>
@@ -46822,12 +47139,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lab</t>
+          <t>Iro</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_ADEPT</t>
+          <t>ADVANCE_IRON_WORKING</t>
         </is>
       </c>
     </row>
@@ -46839,12 +47156,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Las</t>
+          <t>Lab</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MAGE</t>
+          <t>ADVANCE_LIFE_ADEPT</t>
         </is>
       </c>
     </row>
@@ -46856,12 +47173,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ldr</t>
+          <t>Las</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ADVANCE_HOLY_WARRIORS</t>
+          <t>ADVANCE_LIFE_MAGE</t>
         </is>
       </c>
     </row>
@@ -46873,12 +47190,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lit</t>
+          <t>Ldr</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ADVANCE_LITERACY</t>
+          <t>ADVANCE_HOLY_WARRIORS</t>
         </is>
       </c>
     </row>
@@ -46890,12 +47207,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Too</t>
+          <t>Lit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_WIZARD</t>
+          <t>ADVANCE_LITERACY</t>
         </is>
       </c>
     </row>
@@ -46907,12 +47224,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mag</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ADVANCE_LIFE_MASTER</t>
+          <t>ADVANCE_CHAOS_LORE</t>
         </is>
       </c>
     </row>
@@ -46924,12 +47241,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Map</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ADVANCE_MAP_MAKING</t>
+          <t>ADVANCE_THEOLOGY</t>
         </is>
       </c>
     </row>
@@ -46941,12 +47258,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Mag</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ADVANCE_MASONRY</t>
+          <t>ADVANCE_LIFE_MASTER</t>
         </is>
       </c>
     </row>
@@ -46958,12 +47275,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Map</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_LORE</t>
+          <t>ADVANCE_MAP_MAKING</t>
         </is>
       </c>
     </row>
@@ -46975,12 +47292,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mat</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ADVANCE_MATHEMATICS</t>
+          <t>ADVANCE_MASONRY</t>
         </is>
       </c>
     </row>
@@ -46992,12 +47309,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Mat</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_ADEPT</t>
+          <t>ADVANCE_MATHEMATICS</t>
         </is>
       </c>
     </row>
@@ -47009,12 +47326,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Met</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MAGE</t>
+          <t>ADVANCE_CHAOS_ADEPT</t>
         </is>
       </c>
     </row>
@@ -47026,12 +47343,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Met</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_WIZARD</t>
+          <t>ADVANCE_CHAOS_MAGE</t>
         </is>
       </c>
     </row>
@@ -47043,12 +47360,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mob</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ADVANCE_CHAOS_MASTER</t>
+          <t>ADVANCE_CHAOS_WIZARD</t>
         </is>
       </c>
     </row>
@@ -47060,12 +47377,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>Mob</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ADVANCE_THEOLOGY</t>
+          <t>ADVANCE_CHAOS_MASTER</t>
         </is>
       </c>
     </row>
@@ -47094,12 +47411,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nav</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ADVANCE_NAVIGATION</t>
+          <t>ADVANCE_GRAND_MASTERY</t>
         </is>
       </c>
     </row>
@@ -47111,12 +47428,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ADVANCE_GRAND_MASTERY</t>
+          <t>ADVANCE_SORCERY_MAGE</t>
         </is>
       </c>
     </row>
@@ -47128,12 +47445,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>Nav</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MAGE</t>
+          <t>ADVANCE_NAVIGATION</t>
         </is>
       </c>
     </row>
@@ -47145,12 +47462,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Phi</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ADVANCE_PHILOSOPHY</t>
+          <t>ADVANCE_NATURE_ADEPT</t>
         </is>
       </c>
     </row>
@@ -47162,12 +47479,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Phy</t>
+          <t>Phi</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_WIZARD</t>
+          <t>ADVANCE_PHILOSOPHY</t>
         </is>
       </c>
     </row>
@@ -47179,12 +47496,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Pla</t>
+          <t>Phy</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_MASTER</t>
+          <t>ADVANCE_SORCERY_WIZARD</t>
         </is>
       </c>
     </row>
@@ -47196,12 +47513,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Plu</t>
+          <t>Pla</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_LORE</t>
+          <t>ADVANCE_SORCERY_MASTER</t>
         </is>
       </c>
     </row>
@@ -47213,12 +47530,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Plu</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_ADEPT</t>
+          <t>ADVANCE_NATURE_LORE</t>
         </is>
       </c>
     </row>
@@ -47247,12 +47564,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Rad</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGE</t>
+          <t>ADVANCE_GREATER_ENCHANTMENTS</t>
         </is>
       </c>
     </row>
@@ -47264,12 +47581,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>Rad</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ADVANCE_GREATER_ENCHANTMENTS</t>
+          <t>ADVANCE_NATURE_MAGE</t>
         </is>
       </c>
     </row>
@@ -47315,12 +47632,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rfg</t>
+          <t>Rep</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_LORE</t>
+          <t>ADVANCE_THE_REPUBLIC</t>
         </is>
       </c>
     </row>
@@ -47332,12 +47649,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rep</t>
+          <t>Rfg</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ADVANCE_THE_REPUBLIC</t>
+          <t>ADVANCE_DEATH_LORE</t>
         </is>
       </c>
     </row>
@@ -47366,12 +47683,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>San</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ADVANCE_SANITATION</t>
+          <t>ADVANCE_DEATH_MASTER</t>
         </is>
       </c>
     </row>
@@ -47383,12 +47700,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>SFl</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ADVANCE_SEAFARING</t>
+          <t>ADVANCE_DEATH_MAGE</t>
         </is>
       </c>
     </row>
@@ -47400,12 +47717,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SFl</t>
+          <t>San</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGE</t>
+          <t>ADVANCE_SANITATION</t>
         </is>
       </c>
     </row>
@@ -47417,12 +47734,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sth</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_WIZARD</t>
+          <t>ADVANCE_SEAFARING</t>
         </is>
       </c>
     </row>
@@ -47434,12 +47751,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>Sth</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MASTER</t>
+          <t>ADVANCE_DEATH_WIZARD</t>
         </is>
       </c>
     </row>
@@ -47485,12 +47802,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tra</t>
+          <t>Too</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ADVANCE_TRADE</t>
+          <t>ADVANCE_LIFE_WIZARD</t>
         </is>
       </c>
     </row>
@@ -47502,12 +47819,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Uni</t>
+          <t>Tra</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ADVANCE_UNIVERSITY</t>
+          <t>ADVANCE_TRADE</t>
         </is>
       </c>
     </row>
@@ -47519,12 +47836,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ADVANCE_WARRIOR_CODE</t>
+          <t>ADVANCE_FORCES_OF_NATURE</t>
         </is>
       </c>
     </row>
@@ -47536,12 +47853,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wri</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ADVANCE_WRITING</t>
+          <t>ADVANCE_DEATH_MAGIC</t>
         </is>
       </c>
     </row>
@@ -47553,12 +47870,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ADVANCE_FORCES_OF_NATURE</t>
+          <t>ADVANCE_SEA_LORE</t>
         </is>
       </c>
     </row>
@@ -47570,12 +47887,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>Uni</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ADVANCE_DEATH_MAGIC</t>
+          <t>ADVANCE_UNIVERSITY</t>
         </is>
       </c>
     </row>
@@ -47587,12 +47904,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>War</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ADVANCE_SEA_LORE</t>
+          <t>ADVANCE_WARRIOR_CODE</t>
         </is>
       </c>
     </row>
@@ -47604,12 +47921,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>Wri</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ADVANCE_NATURE_MAGIC</t>
+          <t>ADVANCE_WRITING</t>
         </is>
       </c>
     </row>
@@ -47621,12 +47938,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>X2</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ADVANCE_SORCERY_ADEPT</t>
+          <t>ADVANCE_NATURE_MAGIC</t>
         </is>
       </c>
     </row>
@@ -47638,12 +47955,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>X3</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ADVANCE_ARTIFICING</t>
+          <t>ADVANCE_SORCERY_ADEPT</t>
         </is>
       </c>
     </row>
@@ -47655,12 +47972,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>X4</t>
+          <t>X3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ADVANCE_LESSER_FAUNA_LORE</t>
+          <t>ADVANCE_ARTIFICING</t>
         </is>
       </c>
     </row>
@@ -47672,12 +47989,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>X5</t>
+          <t>X4</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ADVANCE_PYROTECHNICS</t>
+          <t>ADVANCE_LESSER_FAUNA_LORE</t>
         </is>
       </c>
     </row>
@@ -47689,12 +48006,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>X6</t>
+          <t>X5</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ADVANCE_OCCULT_STUDIES</t>
+          <t>ADVANCE_PYROTECHNICS</t>
         </is>
       </c>
     </row>
@@ -47706,12 +48023,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>X6</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ADVANCE_HEALING</t>
+          <t>ADVANCE_OCCULT_STUDIES</t>
         </is>
       </c>
     </row>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -73,7 +73,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improvements'!$A$1:$H$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'order_mask'!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'players'!$A$1:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'sprite_pick_rules'!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'terrain'!$A$1:$J$27</definedName>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E36" t="n">
         <v>8</v>
@@ -23099,7 +23099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -23955,7 +23955,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mom_msg.slc</t>
+          <t>mom_summon.slc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -23965,7 +23965,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MomSphereBlessingMessages</t>
+          <t>MomSphereRungTick</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -23973,14 +23973,9 @@
           <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>?</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -23997,32 +23992,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mom_msg.slc</t>
+          <t>mom_summon.slc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MomSummonOrderTick</t>
+          <t>MomSummonRoll</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>spawn the creature ordered last turn, resolved from the CASTER'S OWN sphere; debits 75 mana</t>
+          <t>int_f(int_t p)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>?</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -24044,22 +24034,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MomMsgSlicAlive</t>
+          <t>MomSphereBlessingMessages</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>segment: SLIC liveness confirmation text</t>
+          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -24074,7 +24064,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -24086,22 +24076,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MomBlessLife</t>
+          <t>MomSummonOrderTick</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>segment: Life sphere blessing popup</t>
+          <t>spawn the creature ordered last turn, resolved from the CASTER'S OWN sphere; debits 75 mana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -24116,7 +24106,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24133,7 +24123,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MomBlessNature</t>
+          <t>MomMsgSlicAlive</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -24143,7 +24133,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>segment: Nature sphere blessing popup</t>
+          <t>segment: SLIC liveness confirmation text</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -24158,7 +24148,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24175,7 +24165,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MomBlessSorcery</t>
+          <t>MomBlessLife</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -24185,7 +24175,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>segment: Sorcery sphere blessing popup</t>
+          <t>segment: Life sphere blessing popup</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -24200,7 +24190,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>sorcery</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24207,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MomBlessDeath</t>
+          <t>MomBlessNature</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -24227,7 +24217,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>segment: Death sphere blessing popup</t>
+          <t>segment: Nature sphere blessing popup</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -24242,7 +24232,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>nature</t>
         </is>
       </c>
     </row>
@@ -24259,7 +24249,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MomBlessChaos</t>
+          <t>MomBlessSorcery</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -24269,7 +24259,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>segment: Chaos sphere blessing popup</t>
+          <t>segment: Sorcery sphere blessing popup</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -24284,7 +24274,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>sorcery</t>
         </is>
       </c>
     </row>
@@ -24301,7 +24291,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MomSummonGuard</t>
+          <t>MomBlessDeath</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -24311,7 +24301,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
+          <t>segment: Death sphere blessing popup</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -24326,7 +24316,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -24343,7 +24333,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MomSummonBear</t>
+          <t>MomBlessChaos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -24353,7 +24343,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>segment: Nature summon result (War Bear)</t>
+          <t>segment: Chaos sphere blessing popup</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -24368,7 +24358,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24375,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MomSummonMage</t>
+          <t>MomSummonGuard</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -24395,7 +24385,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>segment: Sorcery summon result (Mage)</t>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -24427,7 +24417,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MomSummonZombie</t>
+          <t>MomSummonBear</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -24437,7 +24427,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>segment: Death summon result (Zombies)</t>
+          <t>segment: Nature summon result (War Bear)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -24469,7 +24459,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MomSummonHound</t>
+          <t>MomSummonMage</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -24479,7 +24469,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>segment: Chaos summon result (Hell Hound)</t>
+          <t>segment: Sorcery summon result (Mage)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -24511,7 +24501,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MomSummonNoMana</t>
+          <t>MomSummonZombie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -24521,7 +24511,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+          <t>segment: Death summon result (Zombies)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -24553,7 +24543,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MomMagicPower</t>
+          <t>MomSummonHound</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -24563,7 +24553,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>segment: mana pool / income readout body</t>
+          <t>segment: Chaos summon result (Hell Hound)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -24590,22 +24580,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MagicMenu</t>
+          <t>MomSummonNoMana</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -24627,32 +24617,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MomRecalcMagicPerTurn</t>
+          <t>MomMagicPower</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>int_f(int_t mp_1)</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
+          <t>segment: mana pool / income readout body</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -24669,32 +24659,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MomMagicPoolTick</t>
+          <t>MagicMenu</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -24716,22 +24706,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MomMagicSchoolGrant</t>
+          <t>MomRecalcMagicPerTurn</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
+          <t>int_f(int_t mp_1)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>apply per-school mana multipliers when a magic advance is granted</t>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -24746,34 +24736,34 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MomCastFlameStrike</t>
+          <t>MomMagicPoolTick</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
+          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -24795,27 +24785,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MomCastDemonStrike</t>
+          <t>MomMagicSchoolGrant</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -24830,7 +24820,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -24847,7 +24837,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MomSpellShowBook</t>
+          <t>MomCastFlameStrike</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -24857,7 +24847,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -24872,7 +24862,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24884,22 +24874,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MomSpellMenuTick</t>
+          <t>MomCastDemonStrike</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -24914,7 +24904,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -24926,22 +24916,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MomOpenSpellbook</t>
+          <t>MomSpellShowBook</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UI trigger bound to the control-panel MagicButton</t>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -24956,7 +24946,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -24973,7 +24963,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MomSpellAICast</t>
+          <t>MomSpellMenuTick</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -24983,7 +24973,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>let AI players cast their sphere's spell when mana allows</t>
+          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -25010,22 +25000,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MomMsgSpellbook</t>
+          <t>MomOpenSpellbook</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>segment: generic spellbook menu</t>
+          <t>UI trigger bound to the control-panel MagicButton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -25052,22 +25042,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MomMsgSpellbookChaos</t>
+          <t>MomSpellAICast</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>segment: Chaos-specific spellbook menu</t>
+          <t>let AI players cast their sphere's spell when mana allows</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -25082,7 +25072,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25099,7 +25089,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MomMsgDemonCast</t>
+          <t>MomMsgSpellbook</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -25109,7 +25099,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>segment: Demon Strike cast confirmation</t>
+          <t>segment: generic spellbook menu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -25141,7 +25131,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MomMsgFlameCast</t>
+          <t>MomMsgSpellbookChaos</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -25151,7 +25141,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>segment: Flame Strike cast confirmation</t>
+          <t>segment: Chaos-specific spellbook menu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -25166,7 +25156,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -25183,7 +25173,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MomMsgNoTarget</t>
+          <t>MomMsgDemonCast</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -25193,7 +25183,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>segment: no enemy unit in range</t>
+          <t>segment: Demon Strike cast confirmation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -25225,7 +25215,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MomMsgNoMana</t>
+          <t>MomMsgFlameCast</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -25235,7 +25225,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+          <t>segment: Flame Strike cast confirmation</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -25267,7 +25257,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MomMsgNotChaos</t>
+          <t>MomMsgNoTarget</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -25277,7 +25267,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>segment: caster's sphere does not grant this spell</t>
+          <t>segment: no enemy unit in range</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -25292,39 +25282,39 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mod_CanPlayerHaveAdvance</t>
+          <t>MomMsgNoMana</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -25334,39 +25324,39 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildUnit</t>
+          <t>MomMsgNotChaos</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theUnit)</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+          <t>segment: caster's sphere does not grant this spell</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -25376,34 +25366,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_ai_magic.slc</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildBuilding</t>
+          <t>MomAiMagicTick</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theBuilding)</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -25435,37 +25420,163 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>mod_CanPlayerHaveAdvance</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>mod_CanCityBuildUnit</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theUnit)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>mod_CanCityBuildBuilding</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theBuilding)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>mod_CanCityBuildWonder</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>int_f(city_t theCity, int_t theWonder)</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>same wall for wonders.</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H56"/>
+  <autoFilter ref="A1:H59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44391,26 +44502,22 @@
     if (p == 1) {
         if (r == 5) {
             if (roll &lt; 16) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-            if (roll &lt; 24) { return UnitDB(UNIT_PALADINS); }
             if (roll &lt; 32) { return UnitDB(UNIT_UNICORN); }
             if (roll &lt; 48) { return UnitDB(UNIT_PEGASUS); }
             if (roll &lt; 100) { return UnitDB(UNIT_ARCHANGEL); }
         }
         if (r == 4) {
             if (roll &lt; 25) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-            if (roll &lt; 37) { return UnitDB(UNIT_PALADINS); }
             if (roll &lt; 50) { return UnitDB(UNIT_UNICORN); }
             if (roll &lt; 100) { return UnitDB(UNIT_PEGASUS); }
         }
         if (r == 3) {
             if (roll &lt; 25) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-            if (roll &lt; 37) { return UnitDB(UNIT_PALADINS); }
             if (roll &lt; 50) { return UnitDB(UNIT_UNICORN); }
             if (roll &lt; 100) { return UnitDB(UNIT_PEGASUS); }
         }
         if (r == 2) {
             if (roll &lt; 50) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-            if (roll &lt; 75) { return UnitDB(UNIT_PALADINS); }
             if (roll &lt; 100) { return UnitDB(UNIT_UNICORN); }
         }
         if (r == 1) {
@@ -44420,157 +44527,105 @@
     // NATURE (player 2)
     if (p == 2) {
         if (r == 5) {
-            if (roll &lt; 5) { return UnitDB(UNIT_CENTAURS); }
-            if (roll &lt; 10) { return UnitDB(UNIT_ELVEN_ARCHERS); }
             if (roll &lt; 16) { return UnitDB(UNIT_WARBEARS); }
-            if (roll &lt; 19) { return UnitDB(UNIT_COCKATRICE); }
-            if (roll &lt; 22) { return UnitDB(UNIT_GRIFFIN); }
-            if (roll &lt; 25) { return UnitDB(UNIT_MERFOLK); }
-            if (roll &lt; 28) { return UnitDB(UNIT_WAR_MAMMOTH); }
-            if (roll &lt; 32) { return UnitDB(UNIT_WAR_TROLL); }
-            if (roll &lt; 40) { return UnitDB(UNIT_BEHEMOTH); }
-            if (roll &lt; 48) { return UnitDB(UNIT_WYVERN); }
+            if (roll &lt; 32) { return UnitDB(UNIT_COCKATRICE); }
+            if (roll &lt; 48) { return UnitDB(UNIT_BEHEMOTH); }
             if (roll &lt; 100) { return UnitDB(UNIT_GREAT_WYRM); }
         }
         if (r == 4) {
-            if (roll &lt; 8) { return UnitDB(UNIT_CENTAURS); }
-            if (roll &lt; 16) { return UnitDB(UNIT_ELVEN_ARCHERS); }
             if (roll &lt; 25) { return UnitDB(UNIT_WARBEARS); }
-            if (roll &lt; 30) { return UnitDB(UNIT_COCKATRICE); }
-            if (roll &lt; 35) { return UnitDB(UNIT_GRIFFIN); }
-            if (roll &lt; 40) { return UnitDB(UNIT_MERFOLK); }
-            if (roll &lt; 45) { return UnitDB(UNIT_WAR_MAMMOTH); }
-            if (roll &lt; 50) { return UnitDB(UNIT_WAR_TROLL); }
-            if (roll &lt; 75) { return UnitDB(UNIT_BEHEMOTH); }
-            if (roll &lt; 100) { return UnitDB(UNIT_WYVERN); }
+            if (roll &lt; 50) { return UnitDB(UNIT_COCKATRICE); }
+            if (roll &lt; 100) { return UnitDB(UNIT_BEHEMOTH); }
         }
         if (r == 3) {
-            if (roll &lt; 8) { return UnitDB(UNIT_CENTAURS); }
-            if (roll &lt; 16) { return UnitDB(UNIT_ELVEN_ARCHERS); }
             if (roll &lt; 25) { return UnitDB(UNIT_WARBEARS); }
-            if (roll &lt; 30) { return UnitDB(UNIT_COCKATRICE); }
-            if (roll &lt; 35) { return UnitDB(UNIT_GRIFFIN); }
-            if (roll &lt; 40) { return UnitDB(UNIT_MERFOLK); }
-            if (roll &lt; 45) { return UnitDB(UNIT_WAR_MAMMOTH); }
-            if (roll &lt; 50) { return UnitDB(UNIT_WAR_TROLL); }
-            if (roll &lt; 75) { return UnitDB(UNIT_BEHEMOTH); }
-            if (roll &lt; 100) { return UnitDB(UNIT_WYVERN); }
+            if (roll &lt; 50) { return UnitDB(UNIT_COCKATRICE); }
+            if (roll &lt; 100) { return UnitDB(UNIT_BEHEMOTH); }
         }
         if (r == 2) {
-            if (roll &lt; 16) { return UnitDB(UNIT_CENTAURS); }
-            if (roll &lt; 32) { return UnitDB(UNIT_ELVEN_ARCHERS); }
             if (roll &lt; 50) { return UnitDB(UNIT_WARBEARS); }
-            if (roll &lt; 60) { return UnitDB(UNIT_COCKATRICE); }
-            if (roll &lt; 70) { return UnitDB(UNIT_GRIFFIN); }
-            if (roll &lt; 80) { return UnitDB(UNIT_MERFOLK); }
-            if (roll &lt; 90) { return UnitDB(UNIT_WAR_MAMMOTH); }
-            if (roll &lt; 100) { return UnitDB(UNIT_WAR_TROLL); }
+            if (roll &lt; 100) { return UnitDB(UNIT_COCKATRICE); }
         }
         if (r == 1) {
-            if (roll &lt; 33) { return UnitDB(UNIT_CENTAURS); }
-            if (roll &lt; 66) { return UnitDB(UNIT_ELVEN_ARCHERS); }
             if (roll &lt; 100) { return UnitDB(UNIT_WARBEARS); }
         }
     }
     // SORCERY (player 3)
     if (p == 3) {
         if (r == 5) {
-            if (roll &lt; 8) { return UnitDB(UNIT_MAGE); }
             if (roll &lt; 16) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
             if (roll &lt; 32) { return UnitDB(UNIT_AIR_ELEMENTAL); }
-            if (roll &lt; 40) { return UnitDB(UNIT_STORM_GIANT); }
-            if (roll &lt; 48) { return UnitDB(UNIT_WARLOCK); }
+            if (roll &lt; 48) { return UnitDB(UNIT_STORM_GIANT); }
             if (roll &lt; 100) { return UnitDB(UNIT_STORM_DRAKE); }
         }
         if (r == 4) {
-            if (roll &lt; 12) { return UnitDB(UNIT_MAGE); }
             if (roll &lt; 25) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
             if (roll &lt; 50) { return UnitDB(UNIT_AIR_ELEMENTAL); }
-            if (roll &lt; 75) { return UnitDB(UNIT_STORM_GIANT); }
-            if (roll &lt; 100) { return UnitDB(UNIT_WARLOCK); }
+            if (roll &lt; 100) { return UnitDB(UNIT_STORM_GIANT); }
         }
         if (r == 3) {
-            if (roll &lt; 12) { return UnitDB(UNIT_MAGE); }
             if (roll &lt; 25) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
             if (roll &lt; 50) { return UnitDB(UNIT_AIR_ELEMENTAL); }
-            if (roll &lt; 75) { return UnitDB(UNIT_STORM_GIANT); }
-            if (roll &lt; 100) { return UnitDB(UNIT_WARLOCK); }
+            if (roll &lt; 100) { return UnitDB(UNIT_STORM_GIANT); }
         }
         if (r == 2) {
-            if (roll &lt; 25) { return UnitDB(UNIT_MAGE); }
             if (roll &lt; 50) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
             if (roll &lt; 100) { return UnitDB(UNIT_AIR_ELEMENTAL); }
         }
         if (r == 1) {
-            if (roll &lt; 50) { return UnitDB(UNIT_MAGE); }
             if (roll &lt; 100) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
         }
     }
     // DEATH (player 4)
     if (p == 4) {
         if (r == 5) {
-            if (roll &lt; 8) { return UnitDB(UNIT_MINION); }
             if (roll &lt; 16) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 32) { return UnitDB(UNIT_WRAITH); }
             if (roll &lt; 48) { return UnitDB(UNIT_DEMON); }
             if (roll &lt; 100) { return UnitDB(UNIT_UNDEAD_DRAGON); }
         }
         if (r == 4) {
-            if (roll &lt; 12) { return UnitDB(UNIT_MINION); }
             if (roll &lt; 25) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 50) { return UnitDB(UNIT_WRAITH); }
             if (roll &lt; 100) { return UnitDB(UNIT_DEMON); }
         }
         if (r == 3) {
-            if (roll &lt; 12) { return UnitDB(UNIT_MINION); }
             if (roll &lt; 25) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 50) { return UnitDB(UNIT_WRAITH); }
             if (roll &lt; 100) { return UnitDB(UNIT_DEMON); }
         }
         if (r == 2) {
-            if (roll &lt; 25) { return UnitDB(UNIT_MINION); }
             if (roll &lt; 50) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 100) { return UnitDB(UNIT_WRAITH); }
         }
         if (r == 1) {
-            if (roll &lt; 50) { return UnitDB(UNIT_MINION); }
             if (roll &lt; 100) { return UnitDB(UNIT_ZOMBIES); }
         }
     }
     // CHAOS (player 5)
     if (p == 5) {
         if (r == 5) {
-            if (roll &lt; 6) { return UnitDB(UNIT_HELL_HOUNDS); }
-            if (roll &lt; 12) { return UnitDB(UNIT_MINOTAUR); }
-            if (roll &lt; 24) { return UnitDB(UNIT_GARGOYLE); }
-            if (roll &lt; 30) { return UnitDB(UNIT_EFREET); }
-            if (roll &lt; 36) { return UnitDB(UNIT_SALAMANDER); }
-            if (roll &lt; 48) { return UnitDB(UNIT_INFERNAL_DEVICE); }
+            if (roll &lt; 16) { return UnitDB(UNIT_HELL_HOUNDS); }
+            if (roll &lt; 32) { return UnitDB(UNIT_GARGOYLE); }
+            if (roll &lt; 48) { return UnitDB(UNIT_EFREET); }
             if (roll &lt; 100) { return UnitDB(UNIT_HYDRA); }
         }
         if (r == 4) {
-            if (roll &lt; 8) { return UnitDB(UNIT_HELL_HOUNDS); }
-            if (roll &lt; 16) { return UnitDB(UNIT_MINOTAUR); }
-            if (roll &lt; 32) { return UnitDB(UNIT_GARGOYLE); }
-            if (roll &lt; 40) { return UnitDB(UNIT_EFREET); }
-            if (roll &lt; 48) { return UnitDB(UNIT_SALAMANDER); }
-            if (roll &lt; 100) { return UnitDB(UNIT_INFERNAL_DEVICE); }
+            if (roll &lt; 25) { return UnitDB(UNIT_HELL_HOUNDS); }
+            if (roll &lt; 50) { return UnitDB(UNIT_GARGOYLE); }
+            if (roll &lt; 100) { return UnitDB(UNIT_EFREET); }
         }
         if (r == 3) {
-            if (roll &lt; 12) { return UnitDB(UNIT_HELL_HOUNDS); }
-            if (roll &lt; 25) { return UnitDB(UNIT_MINOTAUR); }
+            if (roll &lt; 25) { return UnitDB(UNIT_HELL_HOUNDS); }
             if (roll &lt; 50) { return UnitDB(UNIT_GARGOYLE); }
-            if (roll &lt; 75) { return UnitDB(UNIT_EFREET); }
-            if (roll &lt; 100) { return UnitDB(UNIT_SALAMANDER); }
+            if (roll &lt; 100) { return UnitDB(UNIT_EFREET); }
         }
         if (r == 2) {
-            if (roll &lt; 25) { return UnitDB(UNIT_HELL_HOUNDS); }
-            if (roll &lt; 50) { return UnitDB(UNIT_MINOTAUR); }
+            if (roll &lt; 50) { return UnitDB(UNIT_HELL_HOUNDS); }
             if (roll &lt; 100) { return UnitDB(UNIT_GARGOYLE); }
         }
         if (r == 1) {
-            if (roll &lt; 50) { return UnitDB(UNIT_HELL_HOUNDS); }
-            if (roll &lt; 100) { return UnitDB(UNIT_MINOTAUR); }
+            if (roll &lt; 100) { return UnitDB(UNIT_HELL_HOUNDS); }
         }
     }
     return 0;
@@ -44633,7 +44688,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>14607</v>
+        <v>11184</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
@@ -44723,26 +44778,22 @@
     if (p == 1) {
         if (r == 5) {
             if (roll &lt; 16) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-            if (roll &lt; 24) { return UnitDB(UNIT_PALADINS); }
             if (roll &lt; 32) { return UnitDB(UNIT_UNICORN); }
             if (roll &lt; 48) { return UnitDB(UNIT_PEGASUS); }
             if (roll &lt; 100) { return UnitDB(UNIT_ARCHANGEL); }
         }
         if (r == 4) {
             if (roll &lt; 25) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-            if (roll &lt; 37) { return UnitDB(UNIT_PALADINS); }
             if (roll &lt; 50) { return UnitDB(UNIT_UNICORN); }
             if (roll &lt; 100) { return UnitDB(UNIT_PEGASUS); }
         }
         if (r == 3) {
             if (roll &lt; 25) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-            if (roll &lt; 37) { return UnitDB(UNIT_PALADINS); }
             if (roll &lt; 50) { return UnitDB(UNIT_UNICORN); }
             if (roll &lt; 100) { return UnitDB(UNIT_PEGASUS); }
         }
         if (r == 2) {
             if (roll &lt; 50) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-            if (roll &lt; 75) { return UnitDB(UNIT_PALADINS); }
             if (roll &lt; 100) { return UnitDB(UNIT_UNICORN); }
         }
         if (r == 1) {
@@ -44752,157 +44803,105 @@
     // NATURE (player 2)
     if (p == 2) {
         if (r == 5) {
-            if (roll &lt; 5) { return UnitDB(UNIT_CENTAURS); }
-            if (roll &lt; 10) { return UnitDB(UNIT_ELVEN_ARCHERS); }
             if (roll &lt; 16) { return UnitDB(UNIT_WARBEARS); }
-            if (roll &lt; 19) { return UnitDB(UNIT_COCKATRICE); }
-            if (roll &lt; 22) { return UnitDB(UNIT_GRIFFIN); }
-            if (roll &lt; 25) { return UnitDB(UNIT_MERFOLK); }
-            if (roll &lt; 28) { return UnitDB(UNIT_WAR_MAMMOTH); }
-            if (roll &lt; 32) { return UnitDB(UNIT_WAR_TROLL); }
-            if (roll &lt; 40) { return UnitDB(UNIT_BEHEMOTH); }
-            if (roll &lt; 48) { return UnitDB(UNIT_WYVERN); }
+            if (roll &lt; 32) { return UnitDB(UNIT_COCKATRICE); }
+            if (roll &lt; 48) { return UnitDB(UNIT_BEHEMOTH); }
             if (roll &lt; 100) { return UnitDB(UNIT_GREAT_WYRM); }
         }
         if (r == 4) {
-            if (roll &lt; 8) { return UnitDB(UNIT_CENTAURS); }
-            if (roll &lt; 16) { return UnitDB(UNIT_ELVEN_ARCHERS); }
             if (roll &lt; 25) { return UnitDB(UNIT_WARBEARS); }
-            if (roll &lt; 30) { return UnitDB(UNIT_COCKATRICE); }
-            if (roll &lt; 35) { return UnitDB(UNIT_GRIFFIN); }
-            if (roll &lt; 40) { return UnitDB(UNIT_MERFOLK); }
-            if (roll &lt; 45) { return UnitDB(UNIT_WAR_MAMMOTH); }
-            if (roll &lt; 50) { return UnitDB(UNIT_WAR_TROLL); }
-            if (roll &lt; 75) { return UnitDB(UNIT_BEHEMOTH); }
-            if (roll &lt; 100) { return UnitDB(UNIT_WYVERN); }
+            if (roll &lt; 50) { return UnitDB(UNIT_COCKATRICE); }
+            if (roll &lt; 100) { return UnitDB(UNIT_BEHEMOTH); }
         }
         if (r == 3) {
-            if (roll &lt; 8) { return UnitDB(UNIT_CENTAURS); }
-            if (roll &lt; 16) { return UnitDB(UNIT_ELVEN_ARCHERS); }
             if (roll &lt; 25) { return UnitDB(UNIT_WARBEARS); }
-            if (roll &lt; 30) { return UnitDB(UNIT_COCKATRICE); }
-            if (roll &lt; 35) { return UnitDB(UNIT_GRIFFIN); }
-            if (roll &lt; 40) { return UnitDB(UNIT_MERFOLK); }
-            if (roll &lt; 45) { return UnitDB(UNIT_WAR_MAMMOTH); }
-            if (roll &lt; 50) { return UnitDB(UNIT_WAR_TROLL); }
-            if (roll &lt; 75) { return UnitDB(UNIT_BEHEMOTH); }
-            if (roll &lt; 100) { return UnitDB(UNIT_WYVERN); }
+            if (roll &lt; 50) { return UnitDB(UNIT_COCKATRICE); }
+            if (roll &lt; 100) { return UnitDB(UNIT_BEHEMOTH); }
         }
         if (r == 2) {
-            if (roll &lt; 16) { return UnitDB(UNIT_CENTAURS); }
-            if (roll &lt; 32) { return UnitDB(UNIT_ELVEN_ARCHERS); }
             if (roll &lt; 50) { return UnitDB(UNIT_WARBEARS); }
-            if (roll &lt; 60) { return UnitDB(UNIT_COCKATRICE); }
-            if (roll &lt; 70) { return UnitDB(UNIT_GRIFFIN); }
-            if (roll &lt; 80) { return UnitDB(UNIT_MERFOLK); }
-            if (roll &lt; 90) { return UnitDB(UNIT_WAR_MAMMOTH); }
-            if (roll &lt; 100) { return UnitDB(UNIT_WAR_TROLL); }
+            if (roll &lt; 100) { return UnitDB(UNIT_COCKATRICE); }
         }
         if (r == 1) {
-            if (roll &lt; 33) { return UnitDB(UNIT_CENTAURS); }
-            if (roll &lt; 66) { return UnitDB(UNIT_ELVEN_ARCHERS); }
             if (roll &lt; 100) { return UnitDB(UNIT_WARBEARS); }
         }
     }
     // SORCERY (player 3)
     if (p == 3) {
         if (r == 5) {
-            if (roll &lt; 8) { return UnitDB(UNIT_MAGE); }
             if (roll &lt; 16) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
             if (roll &lt; 32) { return UnitDB(UNIT_AIR_ELEMENTAL); }
-            if (roll &lt; 40) { return UnitDB(UNIT_STORM_GIANT); }
-            if (roll &lt; 48) { return UnitDB(UNIT_WARLOCK); }
+            if (roll &lt; 48) { return UnitDB(UNIT_STORM_GIANT); }
             if (roll &lt; 100) { return UnitDB(UNIT_STORM_DRAKE); }
         }
         if (r == 4) {
-            if (roll &lt; 12) { return UnitDB(UNIT_MAGE); }
             if (roll &lt; 25) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
             if (roll &lt; 50) { return UnitDB(UNIT_AIR_ELEMENTAL); }
-            if (roll &lt; 75) { return UnitDB(UNIT_STORM_GIANT); }
-            if (roll &lt; 100) { return UnitDB(UNIT_WARLOCK); }
+            if (roll &lt; 100) { return UnitDB(UNIT_STORM_GIANT); }
         }
         if (r == 3) {
-            if (roll &lt; 12) { return UnitDB(UNIT_MAGE); }
             if (roll &lt; 25) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
             if (roll &lt; 50) { return UnitDB(UNIT_AIR_ELEMENTAL); }
-            if (roll &lt; 75) { return UnitDB(UNIT_STORM_GIANT); }
-            if (roll &lt; 100) { return UnitDB(UNIT_WARLOCK); }
+            if (roll &lt; 100) { return UnitDB(UNIT_STORM_GIANT); }
         }
         if (r == 2) {
-            if (roll &lt; 25) { return UnitDB(UNIT_MAGE); }
             if (roll &lt; 50) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
             if (roll &lt; 100) { return UnitDB(UNIT_AIR_ELEMENTAL); }
         }
         if (r == 1) {
-            if (roll &lt; 50) { return UnitDB(UNIT_MAGE); }
             if (roll &lt; 100) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
         }
     }
     // DEATH (player 4)
     if (p == 4) {
         if (r == 5) {
-            if (roll &lt; 8) { return UnitDB(UNIT_MINION); }
             if (roll &lt; 16) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 32) { return UnitDB(UNIT_WRAITH); }
             if (roll &lt; 48) { return UnitDB(UNIT_DEMON); }
             if (roll &lt; 100) { return UnitDB(UNIT_UNDEAD_DRAGON); }
         }
         if (r == 4) {
-            if (roll &lt; 12) { return UnitDB(UNIT_MINION); }
             if (roll &lt; 25) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 50) { return UnitDB(UNIT_WRAITH); }
             if (roll &lt; 100) { return UnitDB(UNIT_DEMON); }
         }
         if (r == 3) {
-            if (roll &lt; 12) { return UnitDB(UNIT_MINION); }
             if (roll &lt; 25) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 50) { return UnitDB(UNIT_WRAITH); }
             if (roll &lt; 100) { return UnitDB(UNIT_DEMON); }
         }
         if (r == 2) {
-            if (roll &lt; 25) { return UnitDB(UNIT_MINION); }
             if (roll &lt; 50) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 100) { return UnitDB(UNIT_WRAITH); }
         }
         if (r == 1) {
-            if (roll &lt; 50) { return UnitDB(UNIT_MINION); }
             if (roll &lt; 100) { return UnitDB(UNIT_ZOMBIES); }
         }
     }
     // CHAOS (player 5)
     if (p == 5) {
         if (r == 5) {
-            if (roll &lt; 6) { return UnitDB(UNIT_HELL_HOUNDS); }
-            if (roll &lt; 12) { return UnitDB(UNIT_MINOTAUR); }
-            if (roll &lt; 24) { return UnitDB(UNIT_GARGOYLE); }
-            if (roll &lt; 30) { return UnitDB(UNIT_EFREET); }
-            if (roll &lt; 36) { return UnitDB(UNIT_SALAMANDER); }
-            if (roll &lt; 48) { return UnitDB(UNIT_INFERNAL_DEVICE); }
+            if (roll &lt; 16) { return UnitDB(UNIT_HELL_HOUNDS); }
+            if (roll &lt; 32) { return UnitDB(UNIT_GARGOYLE); }
+            if (roll &lt; 48) { return UnitDB(UNIT_EFREET); }
             if (roll &lt; 100) { return UnitDB(UNIT_HYDRA); }
         }
         if (r == 4) {
-            if (roll &lt; 8) { return UnitDB(UNIT_HELL_HOUNDS); }
-            if (roll &lt; 16) { return UnitDB(UNIT_MINOTAUR); }
-            if (roll &lt; 32) { return UnitDB(UNIT_GARGOYLE); }
-            if (roll &lt; 40) { return UnitDB(UNIT_EFREET); }
-            if (roll &lt; 48) { return UnitDB(UNIT_SALAMANDER); }
-            if (roll &lt; 100) { return UnitDB(UNIT_INFERNAL_DEVICE); }
+            if (roll &lt; 25) { return UnitDB(UNIT_HELL_HOUNDS); }
+            if (roll &lt; 50) { return UnitDB(UNIT_GARGOYLE); }
+            if (roll &lt; 100) { return UnitDB(UNIT_EFREET); }
         }
         if (r == 3) {
-            if (roll &lt; 12) { return UnitDB(UNIT_HELL_HOUNDS); }
-            if (roll &lt; 25) { return UnitDB(UNIT_MINOTAUR); }
+            if (roll &lt; 25) { return UnitDB(UNIT_HELL_HOUNDS); }
             if (roll &lt; 50) { return UnitDB(UNIT_GARGOYLE); }
-            if (roll &lt; 75) { return UnitDB(UNIT_EFREET); }
-            if (roll &lt; 100) { return UnitDB(UNIT_SALAMANDER); }
+            if (roll &lt; 100) { return UnitDB(UNIT_EFREET); }
         }
         if (r == 2) {
-            if (roll &lt; 25) { return UnitDB(UNIT_HELL_HOUNDS); }
-            if (roll &lt; 50) { return UnitDB(UNIT_MINOTAUR); }
+            if (roll &lt; 50) { return UnitDB(UNIT_HELL_HOUNDS); }
             if (roll &lt; 100) { return UnitDB(UNIT_GARGOYLE); }
         }
         if (r == 1) {
-            if (roll &lt; 50) { return UnitDB(UNIT_HELL_HOUNDS); }
-            if (roll &lt; 100) { return UnitDB(UNIT_MINOTAUR); }
+            if (roll &lt; 100) { return UnitDB(UNIT_HELL_HOUNDS); }
         }
     }
     return 0;

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -65,7 +65,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'civ2_converted_graphics'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'concept_mask'!$A$1:$A$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'feats'!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'gl_descriptions'!$A$1:$C$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'gl_descriptions'!$A$1:$C$282</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'gl_section_overrides'!$A$1:$E$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'gl_text_rewrites'!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'governicon_fallback'!$A$1:$B$3</definedName>
@@ -84,7 +84,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'unit_factions'!$A$1:$I$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'slic'!$A$1:$L$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$59</definedName>
   </definedNames>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E47" t="n">
         <v>5</v>
@@ -14831,7 +14831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C287"/>
+  <dimension ref="A1:C282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -16287,2009 +16287,1949 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WONDER_XAPOLLO_PROGRAM</t>
+          <t>TILEIMP_ADVANCED_FARMS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>The organised decision to leave the world entirely, undertaken for reasons that were half curiosity and half rivalry.</t>
+          <t>Rotation, drainage and selected seed. Nothing about it looks impressive, and it doubles what a valley can feed.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>WONDER_XCURE_FOR_CANCER</t>
+          <t>TILEIMP_ADVANCED_MINES</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>The end of one of the oldest quiet arithmetics of human life, achieved not by a genius but by an institution that refused to stop.</t>
+          <t>Deep shafts, pumps and timbering: the difference between scraping a hillside and genuinely working it.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>WONDER_XLIGHTHOUSE</t>
+          <t>TILEIMP_FARMS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>A fire kept burning so that strangers can find the harbour. One of the few monuments built entirely for other people's benefit.</t>
+          <t>Deliberate planting in worked ground. The first improvement any people ever make to the land, and the one everything else waits on.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>WONDER_XSTATUE_OF_LIBERTY</t>
+          <t>TILEIMP_FORTIFICATIONS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>A figure raised at a harbour mouth to state a proposition, addressed to arrivals rather than to residents.</t>
+          <t>Earth and stone arranged so that attacking costs more than defending. The whole of siege history is an argument with this.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>WONDER_XWOMENS_SUFFRAGE</t>
+          <t>TILEIMP_MINES</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>The extension of the vote to half the population, resisted for a century on grounds nobody can now restate without embarrassment.</t>
+          <t>Taking metal and stone out of the ground on purpose. Hard, short-lived work that every army in history has depended on.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TILEIMP_ADVANCED_FARMS</t>
+          <t>TILEIMP_NATURE_PRESERVE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Rotation, drainage and selected seed. Nothing about it looks impressive, and it doubles what a valley can feed.</t>
+          <t>Ground formally set aside from use. A late idea, and one that only occurs to peoples who have already used up somewhere else.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TILEIMP_ADVANCED_MINES</t>
+          <t>TILEIMP_NETS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Deep shafts, pumps and timbering: the difference between scraping a hillside and genuinely working it.</t>
+          <t>Fixed fishing works in shallow water: a harvest that arrives without being planted.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TILEIMP_FARMS</t>
+          <t>TILEIMP_RAILROAD</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Deliberate planting in worked ground. The first improvement any people ever make to the land, and the one everything else waits on.</t>
+          <t>Iron road and a machine that never tires. It collapsed distance more sharply than any invention before it.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TILEIMP_FORTIFICATIONS</t>
+          <t>TILEIMP_ROAD</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Earth and stone arranged so that attacking costs more than defending. The whole of siege history is an argument with this.</t>
+          <t>A prepared surface between two places. Trade, tax collection and armies all move at the speed of the worst road on the route.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TILEIMP_MINES</t>
+          <t>TILEIMP_TERRAFORM_BROWN_HILL</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Taking metal and stone out of the ground on purpose. Hard, short-lived work that every army in history has depended on.</t>
+          <t>Reshaping ground into arid upland, undertaken where the alternative was worse.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TILEIMP_NATURE_PRESERVE</t>
+          <t>TILEIMP_TERRAFORM_BROWN_MOUNTAIN</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ground formally set aside from use. A late idea, and one that only occurs to peoples who have already used up somewhere else.</t>
+          <t>Raising barren peaks by will rather than by geology, an act of engineering that reads as an act of vandalism.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TILEIMP_NETS</t>
+          <t>TILEIMP_TERRAFORM_DESERT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fixed fishing works in shallow water: a harvest that arrives without being planted.</t>
+          <t>Deliberately drying a region. Almost always done to deny it to someone else.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TILEIMP_RAILROAD</t>
+          <t>TILEIMP_TERRAFORM_FOREST</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Iron road and a machine that never tires. It collapsed distance more sharply than any invention before it.</t>
+          <t>Planting a forest where there was none and waiting, or refusing to wait and compelling it.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TILEIMP_ROAD</t>
+          <t>TILEIMP_TERRAFORM_GRASSLAND</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>A prepared surface between two places. Trade, tax collection and armies all move at the speed of the worst road on the route.</t>
+          <t>Turning difficult ground into pasture and field, the single most common ambition of every settled people.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_BROWN_HILL</t>
+          <t>TILEIMP_TERRAFORM_HILL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Reshaping ground into arid upland, undertaken where the alternative was worse.</t>
+          <t>Raising ground for the sake of the defensive advantage and the drainage that come with it.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_BROWN_MOUNTAIN</t>
+          <t>TILEIMP_TERRAFORM_JUNGLE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Raising barren peaks by will rather than by geology, an act of engineering that reads as an act of vandalism.</t>
+          <t>Encouraging dense growth, usually as a barrier, occasionally out of conviction.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_DESERT</t>
+          <t>TILEIMP_TERRAFORM_MOUNTAIN</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Deliberately drying a region. Almost always done to deny it to someone else.</t>
+          <t>Making mountains. The most expensive way ever devised to build a wall.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_FOREST</t>
+          <t>TILEIMP_TERRAFORM_PLAINS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Planting a forest where there was none and waiting, or refusing to wait and compelling it.</t>
+          <t>Flattening and clearing into open country: easy to farm, easy to cross, easy to invade.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_GRASSLAND</t>
+          <t>TILEIMP_TERRAFORM_SWAMP</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Turning difficult ground into pasture and field, the single most common ambition of every settled people.</t>
+          <t>Deliberate flooding. Miserable to hold, and historically very effective at stopping cavalry.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_HILL</t>
+          <t>TILEIMP_TERRAFORM_WHITE_HILL</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Raising ground for the sake of the defensive advantage and the drainage that come with it.</t>
+          <t>Raising frozen upland, generally at the edges of a realm that has run out of better land.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_JUNGLE</t>
+          <t>TILEIMP_TERRAFORM_WHITE_MOUNTAIN</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Encouraging dense growth, usually as a barrier, occasionally out of conviction.</t>
+          <t>Ice-locked peaks made to order, the harshest terrain anyone has bothered to manufacture.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_MOUNTAIN</t>
+          <t>TILEIMP_TRADING_POST</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Making mountains. The most expensive way ever devised to build a wall.</t>
+          <t>A shed, a scale and an agreed price, at the point where two peoples find it easier to deal than to raid.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_PLAINS</t>
+          <t>GOVERNMENT_MONARCHY</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Flattening and clearing into open country: easy to farm, easy to cross, easy to invade.</t>
+          <t>One family, one claim, and an inheritance treated as a constitution. Stable while the heirs are competent.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_SWAMP</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Deliberate flooding. Miserable to hold, and historically very effective at stopping cavalry.</t>
+          <t>CONCEPT_ANCIENT_AGE</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>The opening age. Research is cheap and slow, cities are small, and almost every advance you take opens two more. Expansion now compounds for the rest of the game.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_WHITE_HILL</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Raising frozen upland, generally at the edges of a realm that has run out of better land.</t>
+          <t>CONCEPT_CLASSIC_AGE</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>The second age. Writing, law and organised warfare arrive together; cities begin to support specialists, and the first wonders become buildable.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TILEIMP_TERRAFORM_WHITE_MOUNTAIN</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Ice-locked peaks made to order, the harshest terrain anyone has bothered to manufacture.</t>
+          <t>CONCEPT_MEDIEVAL_AGE</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>The age of walls, guilds and cavalry. Defensive improvements outpace attack, so wars become sieges and economies become the deciding factor.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TILEIMP_TRADING_POST</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>A shed, a scale and an agreed price, at the point where two peoples find it easier to deal than to raid.</t>
+          <t>CONCEPT_RENAISSANCE_AGE</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Science accelerates sharply and the map opens up. Advances arrive faster than governments adapt to them, which is what makes this age volatile.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>GOVERNMENT_MONARCHY</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>One family, one claim, and an inheritance treated as a constitution. Stable while the heirs are competent.</t>
+          <t>CONCEPT_INDUSTRIAL_AGE</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Production dominates. Output per city climbs steeply, and pollution and unhappiness become live constraints rather than background noise.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CONCEPT_ANCIENT_AGE</t>
+          <t>CONCEPT_COMPUTER_AGE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>The opening age. Research is cheap and slow, cities are small, and almost every advance you take opens two more. Expansion now compounds for the rest of the game.</t>
+          <t>Information becomes the limiting resource. Science and commerce multipliers matter more than raw production, and stealth and espionage units come into their own.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CONCEPT_CLASSIC_AGE</t>
+          <t>CONCEPT_DIAMOND_AGE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>The second age. Writing, law and organised warfare arrive together; cities begin to support specialists, and the first wonders become buildable.</t>
+          <t>Late-game engineering. Terraforming, extreme improvements and the most expensive wonders in the game all become reachable here.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CONCEPT_MEDIEVAL_AGE</t>
+          <t>CONCEPT_FUTURE_AGE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>The age of walls, guilds and cavalry. Defensive improvements outpace attack, so wars become sieges and economies become the deciding factor.</t>
+          <t>The final age. The advance tree is effectively exhausted and further research yields incremental Future Technology rather than new capabilities.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CONCEPT_RENAISSANCE_AGE</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Science accelerates sharply and the map opens up. Advances arrive faster than governments adapt to them, which is what makes this age volatile.</t>
+          <t>CONCEPT_ACTIVE_DEFENSE</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>The idea that a defender should not merely absorb an attack but answer it. Fortifications that shoot back are older than fortifications that do not.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CONCEPT_INDUSTRIAL_AGE</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Production dominates. Output per city climbs steeply, and pollution and unhappiness become live constraints rather than background noise.</t>
+          <t>CONCEPT_ADVANCES</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Knowledge accumulates in one direction only. What one generation discovers, the next assumes, which is why progress feels slow while it is happening and inevitable afterwards.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CONCEPT_COMPUTER_AGE</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Information becomes the limiting resource. Science and commerce multipliers matter more than raw production, and stealth and espionage units come into their own.</t>
+          <t>CONCEPT_ALLIANCE</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Two powers agreeing that a third is the more urgent problem. Most alliances outlive their reason for existing by exactly one war.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CONCEPT_DIAMOND_AGE</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Late-game engineering. Terraforming, extreme improvements and the most expensive wonders in the game all become reachable here.</t>
+          <t>CONCEPT_ATROCITY</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Acts that even warring peoples agree lie outside war. The category exists because it has repeatedly needed to be named.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CONCEPT_FUTURE_AGE</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>The final age. The advance tree is effectively exhausted and further research yields incremental Future Technology rather than new capabilities.</t>
+          <t>CONCEPT_BARBARIANS</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>The word every settled people uses for the peoples outside their walls. It says more about the speaker than the subject.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CONCEPT_ACTIVE_DEFENSE</t>
+          <t>CONCEPT_CAPITALIZATION</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>The idea that a defender should not merely absorb an attack but answer it. Fortifications that shoot back are older than fortifications that do not.</t>
+          <t>The decision to stop building things and simply take the money instead. A mature economy's admission that gold is more flexible than stone.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CONCEPT_ADVANCES</t>
+          <t>CONCEPT_CITY</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Knowledge accumulates in one direction only. What one generation discovers, the next assumes, which is why progress feels slow while it is happening and inevitable afterwards.</t>
+          <t>A settlement large enough that most of its inhabitants do not grow their own food. Every consequence of civilisation follows from that one fact.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CONCEPT_ALLIANCE</t>
+          <t>CONCEPT_COMMERCE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Two powers agreeing that a third is the more urgent problem. Most alliances outlive their reason for existing by exactly one war.</t>
+          <t>Exchange between strangers, conducted on trust in a system rather than trust in a person. The whole of urban wealth rests on it.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CONCEPT_ATROCITY</t>
+          <t>CONCEPT_CRIME</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Acts that even warring peoples agree lie outside war. The category exists because it has repeatedly needed to be named.</t>
+          <t>What happens in the gap between what a state forbids and what it can observe. The gap widens with distance from the capital.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CONCEPT_BARBARIANS</t>
+          <t>CONCEPT_DEFENSE</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>The word every settled people uses for the peoples outside their walls. It says more about the speaker than the subject.</t>
+          <t>The older and cheaper half of warfare. It is generally underfunded in peace and frantically overfunded the season after a raid.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CONCEPT_CAPITALIZATION</t>
+          <t>CONCEPT_DIPLOMACY</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>The decision to stop building things and simply take the money instead. A mature economy's admission that gold is more flexible than stone.</t>
+          <t>The practice of getting what an army would take, without the army. Cheaper, slower, and reversible.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CONCEPT_CITY</t>
+          <t>CONCEPT_DISBAND_CITY</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>A settlement large enough that most of its inhabitants do not grow their own food. Every consequence of civilisation follows from that one fact.</t>
+          <t>Unmaking a settlement deliberately. Rare, drastic, and almost always a decision about a frontier that could not be held.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CONCEPT_COMMERCE</t>
+          <t>CONCEPT_EMBARGO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Exchange between strangers, conducted on trust in a system rather than trust in a person. The whole of urban wealth rests on it.</t>
+          <t>War conducted through the ledger. It hurts slowly, indiscriminately, and often the wrong people.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CONCEPT_CRIME</t>
+          <t>CONCEPT_EMPIRE_SIZE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>What happens in the gap between what a state forbids and what it can observe. The gap widens with distance from the capital.</t>
+          <t>Every realm has a distance beyond which orders arrive late and taxes arrive short. Empires do not usually fall; they exceed this radius.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CONCEPT_DEFENSE</t>
+          <t>CONCEPT_FOOD</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>The older and cheaper half of warfare. It is generally underfunded in peace and frantically overfunded the season after a raid.</t>
+          <t>The first constraint and the last one. No policy, army or wonder survives a people that is not eating.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CONCEPT_DIPLOMACY</t>
+          <t>CONCEPT_GOLD</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>The practice of getting what an army would take, without the army. Cheaper, slower, and reversible.</t>
+          <t>Stored, portable agreement. Its usefulness is that it can become almost anything else on short notice.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CONCEPT_DISBAND_CITY</t>
+          <t>CONCEPT_GOODS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Unmaking a settlement deliberately. Rare, drastic, and almost always a decision about a frontier that could not be held.</t>
+          <t>Things worth carrying a long way, which is a much shorter list than things worth having.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CONCEPT_EMBARGO</t>
+          <t>CONCEPT_GOVERNMENTS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>War conducted through the ledger. It hurts slowly, indiscriminately, and often the wrong people.</t>
+          <t>The arrangement a people accepts for deciding who may compel whom. Every form is a different trade between order and consent.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CONCEPT_EMPIRE_SIZE</t>
+          <t>CONCEPT_GROWTH</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Every realm has a distance beyond which orders arrive late and taxes arrive short. Empires do not usually fall; they exceed this radius.</t>
+          <t>Populations expand to whatever their food, water and patience allow. Managing that ceiling is most of what governing a city is.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CONCEPT_FOOD</t>
+          <t>CONCEPT_HAPPINESS</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>The first constraint and the last one. No policy, army or wonder survives a people that is not eating.</t>
+          <t>The measure of whether a population consents to be governed. It is cheap to maintain and enormously expensive to restore.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CONCEPT_GOLD</t>
+          <t>CONCEPT_IMPROVEMENTS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Stored, portable agreement. Its usefulness is that it can become almost anything else on short notice.</t>
+          <t>Permanent works inside a city that change what it is capable of. Their cost is paid once and their upkeep forever.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CONCEPT_GOODS</t>
+          <t>CONCEPT_INFRASTRUCTURE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Things worth carrying a long way, which is a much shorter list than things worth having.</t>
+          <t>The works nobody notices until they fail: roads, drains, aqueducts, walls. Civilisation is largely maintenance.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CONCEPT_GOVERNMENTS</t>
+          <t>CONCEPT_MAINTENANCE_COST</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>The arrangement a people accepts for deciding who may compel whom. Every form is a different trade between order and consent.</t>
+          <t>Everything built must be kept. The standing cost of past decisions is what constrains present ones.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CONCEPT_GROWTH</t>
+          <t>CONCEPT_MILITARY_READINESS</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Populations expand to whatever their food, water and patience allow. Managing that ceiling is most of what governing a city is.</t>
+          <t>How much of a realm's substance is committed to the possibility of war. Too little invites it; too much causes it.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CONCEPT_HAPPINESS</t>
+          <t>CONCEPT_OFFER</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>The measure of whether a population consents to be governed. It is cheap to maintain and enormously expensive to restore.</t>
+          <t>A proposal made in the expectation of refusal, so that the refusal can be pointed to later.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CONCEPT_IMPROVEMENTS</t>
+          <t>CONCEPT_OVERCROWDING</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Permanent works inside a city that change what it is capable of. Their cost is paid once and their upkeep forever.</t>
+          <t>Past a certain density, adding people subtracts from everyone. Cities discover this threshold by crossing it.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CONCEPT_INFRASTRUCTURE</t>
+          <t>CONCEPT_POLLUTION</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>The works nobody notices until they fail: roads, drains, aqueducts, walls. Civilisation is largely maintenance.</t>
+          <t>The cost of production that is paid by whoever lives downstream, which is why it took so long to be counted at all.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CONCEPT_MAINTENANCE_COST</t>
+          <t>CONCEPT_POPULATION</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Everything built must be kept. The standing cost of past decisions is what constrains present ones.</t>
+          <t>The one resource that produces every other one, and the only one with an opinion about how it is used.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CONCEPT_MILITARY_READINESS</t>
+          <t>CONCEPT_PRODUCTION</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>How much of a realm's substance is committed to the possibility of war. Too little invites it; too much causes it.</t>
+          <t>Labour turned into things. The rate at which a realm can convert intent into fact.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CONCEPT_OFFER</t>
+          <t>CONCEPT_PUBLIC_WORKS</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>A proposal made in the expectation of refusal, so that the refusal can be pointed to later.</t>
+          <t>Effort spent on the land rather than in the city: roads, farms, mines. Slow to pay back and impossible to do without.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CONCEPT_OVERCROWDING</t>
+          <t>CONCEPT_RATIONS</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Past a certain density, adding people subtracts from everyone. Cities discover this threshold by crossing it.</t>
+          <t>Deciding how much a population eats is the bluntest instrument a government has, and the one most likely to end it.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CONCEPT_POLLUTION</t>
+          <t>CONCEPT_REGARD</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>The cost of production that is paid by whoever lives downstream, which is why it took so long to be counted at all.</t>
+          <t>What one power privately thinks of another, which governs everything it will do before it says anything.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CONCEPT_POPULATION</t>
+          <t>CONCEPT_REQUEST</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>The one resource that produces every other one, and the only one with an opinion about how it is used.</t>
+          <t>Asking, in circumstances where both parties understand what follows a refusal.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CONCEPT_PRODUCTION</t>
+          <t>CONCEPT_REVOLUTION</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Labour turned into things. The rate at which a realm can convert intent into fact.</t>
+          <t>The moment a population stops believing its government is inevitable. Everything after that is bookkeeping.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CONCEPT_PUBLIC_WORKS</t>
+          <t>CONCEPT_RIOTS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Effort spent on the land rather than in the city: roads, farms, mines. Slow to pay back and impossible to do without.</t>
+          <t>Disorder that has stopped being individual. A city in riot is not producing, defending, or listening.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CONCEPT_RATIONS</t>
+          <t>CONCEPT_RIVER</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Deciding how much a population eats is the bluntest instrument a government has, and the one most likely to end it.</t>
+          <t>Water, transport, defence and a boundary, all in one line on the map. Nearly every old city sits on one.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CONCEPT_REGARD</t>
+          <t>CONCEPT_RUINS</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>What one power privately thinks of another, which governs everything it will do before it says anything.</t>
+          <t>The physical evidence that this has all been attempted before, left standing as a matter of indifference rather than respect.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CONCEPT_REQUEST</t>
+          <t>CONCEPT_RUSH_BUY</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Asking, in circumstances where both parties understand what follows a refusal.</t>
+          <t>Paying in gold for the time you do not have. Always more expensive than planning, and occasionally worth it.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CONCEPT_REVOLUTION</t>
+          <t>CONCEPT_SCIENCE</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>The moment a population stops believing its government is inevitable. Everything after that is bookkeeping.</t>
+          <t>Organised doubt. Its power comes from being willing to discard its own conclusions, which no other institution manages.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CONCEPT_RIOTS</t>
+          <t>CONCEPT_SCIENCE_SETTING</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Disorder that has stopped being individual. A city in riot is not producing, defending, or listening.</t>
+          <t>The perennial decision between what a realm knows next year and what it can afford this year.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CONCEPT_RIVER</t>
+          <t>CONCEPT_SEA_COLONIES</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Water, transport, defence and a boundary, all in one line on the map. Nearly every old city sits on one.</t>
+          <t>Settlement of water, undertaken when the land is full or the sea holds something the land does not.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CONCEPT_RUINS</t>
+          <t>CONCEPT_SLAVE</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>The physical evidence that this has all been attempted before, left standing as a matter of indifference rather than respect.</t>
+          <t>Labour taken rather than bought. It builds quickly, costs continuously, and has never yet failed to be repaid.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CONCEPT_RUSH_BUY</t>
+          <t>CONCEPT_SPECIALISTS</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Paying in gold for the time you do not have. Always more expensive than planning, and occasionally worth it.</t>
+          <t>Citizens taken off the fields to do one thing extremely well. The surplus that permits this is the definition of wealth.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CONCEPT_SCIENCE</t>
+          <t>CONCEPT_SPECIAL_FORCES</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Organised doubt. Its power comes from being willing to discard its own conclusions, which no other institution manages.</t>
+          <t>Small numbers, chosen carefully, sent where an army cannot go and a diplomat will not.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CONCEPT_SCIENCE_SETTING</t>
+          <t>CONCEPT_STARVATION</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>The perennial decision between what a realm knows next year and what it can afford this year.</t>
+          <t>The failure state of every other system, and the one that arrives fastest.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CONCEPT_SEA_COLONIES</t>
+          <t>CONCEPT_STEALTH_UNITS</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Settlement of water, undertaken when the land is full or the sea holds something the land does not.</t>
+          <t>Forces whose advantage is not being seen. Their entire value collapses the moment they are, which makes them expensive to use well.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CONCEPT_SLAVE</t>
+          <t>CONCEPT_SUPPORT_COST</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Labour taken rather than bought. It builds quickly, costs continuously, and has never yet failed to be repaid.</t>
+          <t>Standing armies eat in peacetime too. The bill for readiness is paid every turn, in the currency of everything not built instead.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CONCEPT_SPECIALISTS</t>
+          <t>CONCEPT_TERRAFORM</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Citizens taken off the fields to do one thing extremely well. The surplus that permits this is the definition of wealth.</t>
+          <t>Rebuilding the land itself rather than adapting to it. The last stage of the argument between a people and their geography.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CONCEPT_SPECIAL_FORCES</t>
+          <t>CONCEPT_THREAT</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Small numbers, chosen carefully, sent where an army cannot go and a diplomat will not.</t>
+          <t>A promise made in the hope of never having to keep it. Its whole value lies in being believed, which is why a threat that is tested once is rarely worth making twice.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>CONCEPT_STARVATION</t>
+          <t>CONCEPT_TILE_IMPROVEMENTS</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>The failure state of every other system, and the one that arrives fastest.</t>
+          <t>Work done to the ground outside the walls, which is where a city's food, metal and roads actually come from.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>CONCEPT_STEALTH_UNITS</t>
+          <t>CONCEPT_TONE</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Forces whose advantage is not being seen. Their entire value collapses the moment they are, which makes them expensive to use well.</t>
+          <t>How a thing is said, which between powers is frequently more consequential than what is said.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CONCEPT_SUPPORT_COST</t>
+          <t>CONCEPT_TRADE</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Standing armies eat in peacetime too. The bill for readiness is paid every turn, in the currency of everything not built instead.</t>
+          <t>The discovery that both sides can end an exchange better off. Every peace that has ever lasted has been built on it.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CONCEPT_TERRAFORM</t>
+          <t>CONCEPT_TRADE_ROUTE</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Rebuilding the land itself rather than adapting to it. The last stage of the argument between a people and their geography.</t>
+          <t>A path along which goods move reliably enough to plan around. Protecting one is the commonest reason for a war nobody wanted.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CONCEPT_THREAT</t>
+          <t>CONCEPT_TREATIES</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>A promise made in the hope of never having to keep it. Its whole value lies in being believed, which is why a threat that is tested once is rarely worth making twice.</t>
+          <t>Written agreements between powers that recognise no higher authority, and are therefore held together by nothing but interest.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CONCEPT_TILE_IMPROVEMENTS</t>
+          <t>CONCEPT_UNITS</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Work done to the ground outside the walls, which is where a city's food, metal and roads actually come from.</t>
+          <t>An organised body of people acting as one. The basic instrument by which a realm applies force to the map.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>CONCEPT_TONE</t>
+          <t>CONCEPT_VETERANS</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>How a thing is said, which between powers is frequently more consequential than what is said.</t>
+          <t>Soldiers who have survived. What they know cannot be trained into recruits, only inherited from them.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CONCEPT_TRADE</t>
+          <t>CONCEPT_VICTORY_CONQUEST</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>The discovery that both sides can end an exchange better off. Every peace that has ever lasted has been built on it.</t>
+          <t>Winning by leaving no one else standing. The oldest definition, and the only one that requires no agreement.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>CONCEPT_TRADE_ROUTE</t>
+          <t>CONCEPT_VICTORY_DIPLOMATIC</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>A path along which goods move reliably enough to plan around. Protecting one is the commonest reason for a war nobody wanted.</t>
+          <t>Winning by being the power everyone else prefers. Slower than conquest and considerably harder to reverse.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CONCEPT_TREATIES</t>
+          <t>CONCEPT_VICTORY_PTS_AT_2300</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Written agreements between powers that recognise no higher authority, and are therefore held together by nothing but interest.</t>
+          <t>Judgement by accumulated account at a fixed date, which rewards steadiness over any single decisive stroke.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CONCEPT_UNITS</t>
+          <t>CONCEPT_VICTORY_SCIENCE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>An organised body of people acting as one. The basic instrument by which a realm applies force to the map.</t>
+          <t>Winning by understanding the world first, on the assumption that understanding is a lead nobody else can close.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CONCEPT_VETERANS</t>
+          <t>CONCEPT_VISION</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Soldiers who have survived. What they know cannot be trained into recruits, only inherited from them.</t>
+          <t>What a realm can actually see. Every decision is made about the map as known, not the map as it is.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CONCEPT_VICTORY_CONQUEST</t>
+          <t>CONCEPT_WAGES</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Winning by leaving no one else standing. The oldest definition, and the only one that requires no agreement.</t>
+          <t>What a state pays its own people to remain its own people. Set it too low and the labour leaves; set it too high and there is nothing left to govern with.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>CONCEPT_VICTORY_DIPLOMATIC</t>
+          <t>CONCEPT_WONDERS</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Winning by being the power everyone else prefers. Slower than conquest and considerably harder to reverse.</t>
+          <t>Works so large that only one of each can exist. They are built for the advantage and remembered for the ambition.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CONCEPT_VICTORY_PTS_AT_2300</t>
+          <t>CONCEPT_WORKER</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Judgement by accumulated account at a fixed date, which rewards steadiness over any single decisive stroke.</t>
+          <t>The person doing the work. Every abstraction on this page resolves, eventually, to them.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CONCEPT_VICTORY_SCIENCE</t>
+          <t>CONCEPT_WORK_HOURS</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Winning by understanding the world first, on the assumption that understanding is a lead nobody else can close.</t>
+          <t>How hard a population is asked to labour. Push it up and output rises, then consent falls, in that order.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CONCEPT_VISION</t>
+          <t>ORDER_ASSASSINATE</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>What a realm can actually see. Every decision is made about the map as known, not the map as it is.</t>
+          <t>Removing one person instead of an army. Cheap, deniable, and historically far less decisive than the people who order it expect.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CONCEPT_WAGES</t>
+          <t>ORDER_ATTACK</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>What a state pays its own people to remain its own people. Set it too low and the labour leaves; set it too high and there is nothing left to govern with.</t>
+          <t>The oldest instruction in warfare, and the one every other order exists to make unnecessary or survivable.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CONCEPT_WONDERS</t>
+          <t>ORDER_BOARD_TRANSPORT</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Works so large that only one of each can exist. They are built for the advantage and remembered for the ambition.</t>
+          <t>Putting an army aboard ship. The most vulnerable hour in any campaign is the one spent doing this.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CONCEPT_WORKER</t>
+          <t>ORDER_BOMBARD</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>The person doing the work. Every abstraction on this page resolves, eventually, to them.</t>
+          <t>Striking at range and accepting no reply. It wins ground slowly and costs almost nothing but ammunition and patience.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>CONCEPT_WORK_HOURS</t>
+          <t>ORDER_CONVERT</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>How hard a population is asked to labour. Push it up and output rises, then consent falls, in that order.</t>
+          <t>Changing what a population believes, on the correct assumption that belief decides who they will fight for.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ORDER_ASSASSINATE</t>
+          <t>ORDER_DISBAND_ARMY</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Removing one person instead of an army. Cheap, deniable, and historically far less decisive than the people who order it expect.</t>
+          <t>Sending soldiers home. Easy to order and, for many governments, extremely difficult to survive.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ORDER_ATTACK</t>
+          <t>ORDER_ESTABLISH_EMBASSY</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>The oldest instruction in warfare, and the one every other order exists to make unnecessary or survivable.</t>
+          <t>A permanent presence in someone else's capital, which is simultaneously a courtesy and a listening post.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ORDER_BOARD_TRANSPORT</t>
+          <t>ORDER_EXPEL</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Putting an army aboard ship. The most vulnerable hour in any campaign is the one spent doing this.</t>
+          <t>Removing a foreign force without killing it, so that a border dispute does not become a war.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ORDER_BOMBARD</t>
+          <t>ORDER_FAITH_HEALING</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Striking at range and accepting no reply. It wins ground slowly and costs almost nothing but ammunition and patience.</t>
+          <t>Treatment by conviction. It works often enough to be defended and rarely enough to be argued about forever.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ORDER_CONVERT</t>
+          <t>ORDER_FORTIFY</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Changing what a population believes, on the correct assumption that belief decides who they will fight for.</t>
+          <t>Digging in. The single cheapest multiplier a defender has ever had access to.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ORDER_DISBAND_ARMY</t>
+          <t>ORDER_INCITE_REVOLUTION</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Sending soldiers home. Easy to order and, for many governments, extremely difficult to survive.</t>
+          <t>Persuading a rival's own people to do what an army would otherwise have to. Slow, cheap, and impossible to control once begun.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ORDER_ESTABLISH_EMBASSY</t>
+          <t>ORDER_INCITE_UPRISING</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>A permanent presence in someone else's capital, which is simultaneously a courtesy and a listening post.</t>
+          <t>Turning a subject population against its occupier, which is easier to start than any commander has ever found it to stop.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ORDER_EXPEL</t>
+          <t>ORDER_INDULGENCE</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Removing a foreign force without killing it, so that a border dispute does not become a war.</t>
+          <t>Buying contentment outright. It works immediately, and teaches the population exactly what discontent is worth.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ORDER_FAITH_HEALING</t>
+          <t>ORDER_INTERCEPT_TRADE</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Treatment by conviction. It works often enough to be defended and rarely enough to be argued about forever.</t>
+          <t>Taking a rival's commerce rather than their territory. Less glorious, and generally more damaging.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ORDER_FORTIFY</t>
+          <t>ORDER_INVESTIGATE_CITY</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Digging in. The single cheapest multiplier a defender has ever had access to.</t>
+          <t>Finding out what is actually inside the walls before deciding whether to knock on them.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ORDER_INCITE_REVOLUTION</t>
+          <t>ORDER_PARADROP</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Persuading a rival's own people to do what an army would otherwise have to. Slow, cheap, and impossible to control once begun.</t>
+          <t>Placing troops behind a line instead of through it. Everything depends on what arrives with them, which is usually not enough.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ORDER_INCITE_UPRISING</t>
+          <t>ORDER_PILLAGE</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Turning a subject population against its occupier, which is easier to start than any commander has ever found it to stop.</t>
+          <t>Destroying what cannot be taken. It denies a rival their improvements and guarantees the ground is worthless to whoever holds it next.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ORDER_INDULGENCE</t>
+          <t>ORDER_PLAGUE</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Buying contentment outright. It works immediately, and teaches the population exactly what discontent is worth.</t>
+          <t>Deliberate contagion, the one weapon in history that has reliably come home to the side that used it.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ORDER_INTERCEPT_TRADE</t>
+          <t>ORDER_RANGED_ATTACK</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Taking a rival's commerce rather than their territory. Less glorious, and generally more damaging.</t>
+          <t>Hitting the enemy from outside the reach of their answer, which has been the central ambition of weapon design ever since the sling.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ORDER_INVESTIGATE_CITY</t>
+          <t>ORDER_REFORM</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Finding out what is actually inside the walls before deciding whether to knock on them.</t>
+          <t>Changing a system from inside it, at the pace the system permits, which is the whole difficulty.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ORDER_PARADROP</t>
+          <t>ORDER_SETTLE</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Placing troops behind a line instead of through it. Everything depends on what arrives with them, which is usually not enough.</t>
+          <t>Founding a city. The single most consequential act any group of people can perform on a map.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ORDER_PILLAGE</t>
+          <t>ORDER_SLAVE_RAID</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Destroying what cannot be taken. It denies a rival their improvements and guarantees the ground is worthless to whoever holds it next.</t>
+          <t>Taking people as property. It supplies labour immediately and creates an enemy permanently.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ORDER_PLAGUE</t>
+          <t>ORDER_SLEEP</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Deliberate contagion, the one weapon in history that has reliably come home to the side that used it.</t>
+          <t>Standing down until needed. Armies spend the overwhelming majority of their existence in this state.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ORDER_RANGED_ATTACK</t>
+          <t>ORDER_SOOTHSAY</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Hitting the enemy from outside the reach of their answer, which has been the central ambition of weapon design ever since the sling.</t>
+          <t>Announcing the future with enough authority that people begin arranging their affairs around it.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ORDER_REFORM</t>
+          <t>ORDER_STEAL_TECHNOLOGY</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Changing a system from inside it, at the pace the system permits, which is the whole difficulty.</t>
+          <t>Acquiring in one night what a rival spent a generation learning. The cheapest research any realm has ever conducted.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ORDER_SETTLE</t>
+          <t>ORDER_THROW_PARTY</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Founding a city. The single most consequential act any group of people can perform on a map.</t>
+          <t>Public generosity as policy. Rulers who understood this outlasted rulers who considered it beneath them.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ORDER_SLAVE_RAID</t>
+          <t>ORDER_UNDERGROUND_RAILWAY</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Taking people as property. It supplies labour immediately and creates an enemy permanently.</t>
+          <t>A route maintained by people with no authority, for people with no options, against a law everyone involved considers illegitimate.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ORDER_SLEEP</t>
+          <t>ORDER_UNLOAD</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Standing down until needed. Armies spend the overwhelming majority of their existence in this state.</t>
+          <t>Putting an army ashore. The moment a naval campaign becomes a land one.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ORDER_SOOTHSAY</t>
+          <t>ORDER_UPGRADE</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Announcing the future with enough authority that people begin arranging their affairs around it.</t>
+          <t>Re-equipping veterans rather than replacing them, which keeps the one thing that cannot be manufactured: experience.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ORDER_STEAL_TECHNOLOGY</t>
+          <t>TERRAIN_BROWN_HILL</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Acquiring in one night what a rival spent a generation learning. The cheapest research any realm has ever conducted.</t>
+          <t>Dry, broken upland where the soil has already left. Peoples settle it for what it overlooks rather than for what it grows.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ORDER_THROW_PARTY</t>
+          <t>TERRAIN_BROWN_MOUNTAIN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Public generosity as policy. Rulers who understood this outlasted rulers who considered it beneath them.</t>
+          <t>Bare rock in a dead range, holding neither snow nor forest. Its only exports have ever been ore and distance.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ORDER_UNDERGROUND_RAILWAY</t>
+          <t>TERRAIN_DEAD</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>A route maintained by people with no authority, for people with no options, against a law everyone involved considers illegitimate.</t>
+          <t>Ground that has been used up, poisoned or cursed past the point where anything returns to it. Every civilisation eventually makes some.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ORDER_UNLOAD</t>
+          <t>TERRAIN_DESERT</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Putting an army ashore. The moment a naval campaign becomes a land one.</t>
+          <t>Land defined by what it lacks. It has been crossed by every trading people in history and settled by very few of them.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ORDER_UPGRADE</t>
+          <t>TERRAIN_DESERT_GOOD_FOUR</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Re-equipping veterans rather than replacing them, which keeps the one thing that cannot be manufactured: experience.</t>
+          <t>The reason a caravan route runs where it does. Deserts hold their few valuable things where nobody would look without a guide.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TERRAIN_BROWN_HILL</t>
+          <t>TERRAIN_DESERT_GOOD_ONE</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Dry, broken upland where the soil has already left. Peoples settle it for what it overlooks rather than for what it grows.</t>
+          <t>A find worth the journey across dry country, which is the only justification anyone has ever needed for the journey.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TERRAIN_BROWN_MOUNTAIN</t>
+          <t>TERRAIN_FOREST</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Bare rock in a dead range, holding neither snow nor forest. Its only exports have ever been ore and distance.</t>
+          <t>Timber, game and cover. Forests fed the shipwrights and hid the armies, and were felled by both.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TERRAIN_DEAD</t>
+          <t>TERRAIN_FOREST_GOOD_ONE</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Ground that has been used up, poisoned or cursed past the point where anything returns to it. Every civilisation eventually makes some.</t>
+          <t>What the woods yield to those who know them, and withhold entirely from those who do not.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>TERRAIN_DESERT</t>
+          <t>TERRAIN_FOREST_GOOD_TWO</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Land defined by what it lacks. It has been crossed by every trading people in history and settled by very few of them.</t>
+          <t>A second gift of the deep woods, generally found by the people who live in them rather than by the people who claim them.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TERRAIN_DESERT_GOOD_FOUR</t>
+          <t>TERRAIN_GLACIER</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>The reason a caravan route runs where it does. Deserts hold their few valuable things where nobody would look without a guide.</t>
+          <t>Ice deep enough to have its own geography. It moves, slowly, and rearranges everything it passes over.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>TERRAIN_DESERT_GOOD_ONE</t>
+          <t>TERRAIN_GRASSLAND</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>A find worth the journey across dry country, which is the only justification anyone has ever needed for the journey.</t>
+          <t>Open, watered, level ground. Nearly every people who settled permanently did so on it, and nearly every war was about who would.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TERRAIN_FOREST</t>
+          <t>TERRAIN_GRASSLAND_GOOD_THREE</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Timber, game and cover. Forests fed the shipwrights and hid the armies, and were felled by both.</t>
+          <t>A staple crop that turns good land into crowded land. Populations rise to meet it within a generation.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TERRAIN_FOREST_GOOD_ONE</t>
+          <t>TERRAIN_HILL</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>What the woods yield to those who know them, and withhold entirely from those who do not.</t>
+          <t>High enough to see from and to hold, low enough to farm. Fortresses cluster on hills for a reason older than any of them.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TERRAIN_FOREST_GOOD_TWO</t>
+          <t>TERRAIN_HILL_GOOD_FOUR</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>A second gift of the deep woods, generally found by the people who live in them rather than by the people who claim them.</t>
+          <t>Something worth digging for under rising ground, which is where most of the world's metal has always come from.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>TERRAIN_GLACIER</t>
+          <t>TERRAIN_HILL_GOOD_ONE</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Ice deep enough to have its own geography. It moves, slowly, and rearranges everything it passes over.</t>
+          <t>A resource of the uplands, valuable enough that the people below have repeatedly come up for it.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>TERRAIN_GRASSLAND</t>
+          <t>TERRAIN_JUNGLE</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Open, watered, level ground. Nearly every people who settled permanently did so on it, and nearly every war was about who would.</t>
+          <t>Dense, wet and hostile to everything with wheels. It is crossed rarely and controlled almost never.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TERRAIN_GRASSLAND_GOOD_THREE</t>
+          <t>TERRAIN_JUNGLE_GOOD_ONE</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>A staple crop that turns good land into crowded land. Populations rise to meet it within a generation.</t>
+          <t>What grows in the deep green that grows nowhere else, and has therefore always been worth an expedition.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TERRAIN_HILL</t>
+          <t>TERRAIN_MOUNTAIN</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>High enough to see from and to hold, low enough to farm. Fortresses cluster on hills for a reason older than any of them.</t>
+          <t>The oldest border there is. Mountains divide peoples more reliably than any treaty and require no enforcement.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>TERRAIN_HILL_GOOD_FOUR</t>
+          <t>TERRAIN_PLAINS</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Something worth digging for under rising ground, which is where most of the world's metal has always come from.</t>
+          <t>Open ground, easily farmed and easily ridden across. Its history is one of prosperity punctuated by cavalry.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>TERRAIN_HILL_GOOD_ONE</t>
+          <t>TERRAIN_PLAINS_GOOD_FOUR</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>A resource of the uplands, valuable enough that the people below have repeatedly come up for it.</t>
+          <t>A prize of the open country, which is difficult to defend precisely because it is easy to reach.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>TERRAIN_JUNGLE</t>
+          <t>TERRAIN_SWAMP</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Dense, wet and hostile to everything with wheels. It is crossed rarely and controlled almost never.</t>
+          <t>Water that has not decided to be a lake. Miserable to live in, and historically excellent at stopping armies.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>TERRAIN_JUNGLE_GOOD_ONE</t>
+          <t>TERRAIN_SWAMP_GOOD_FOUR</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>What grows in the deep green that grows nowhere else, and has therefore always been worth an expedition.</t>
+          <t>Something valuable in the wet ground, recovered by people willing to accept the fever that comes with it.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>TERRAIN_MOUNTAIN</t>
+          <t>TERRAIN_SWAMP_GOOD_THREE</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>The oldest border there is. Mountains divide peoples more reliably than any treaty and require no enforcement.</t>
+          <t>The marsh's compensation for everything else about the marsh.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>TERRAIN_PLAINS</t>
+          <t>TERRAIN_TUNDRA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Open ground, easily farmed and easily ridden across. Its history is one of prosperity punctuated by cavalry.</t>
+          <t>Frozen a hand's depth down all year. It supports herds, herders, and almost nothing that stays put.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TERRAIN_PLAINS_GOOD_FOUR</t>
+          <t>TERRAIN_WATER_BEACH</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>A prize of the open country, which is difficult to defend precisely because it is easy to reach.</t>
+          <t>Where the sea gives ground. Every landing, every port and every invasion in history has begun on one.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>TERRAIN_SWAMP</t>
+          <t>TERRAIN_WATER_DEEP</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Water that has not decided to be a lake. Miserable to live in, and historically excellent at stopping armies.</t>
+          <t>Open ocean, out of sight of everything. It was the last part of the world to be mapped and the first to be feared.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TERRAIN_SWAMP_GOOD_FOUR</t>
+          <t>TERRAIN_WATER_KELP</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Something valuable in the wet ground, recovered by people willing to accept the fever that comes with it.</t>
+          <t>Underwater forest, sheltering the fish that feed the coast. Its value was understood by fishermen centuries before naturalists.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>TERRAIN_SWAMP_GOOD_THREE</t>
+          <t>TERRAIN_WATER_REEF</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>The marsh's compensation for everything else about the marsh.</t>
+          <t>Living stone just under the surface. It builds the richest waters anywhere and sinks the ships that come to use them.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>TERRAIN_TUNDRA</t>
+          <t>TERRAIN_WATER_RIFT</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Frozen a hand's depth down all year. It supports herds, herders, and almost nothing that stays put.</t>
+          <t>A tear in the sea floor where heat comes up from below. Whatever lives down there evolved without reference to the sun.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>TERRAIN_WATER_BEACH</t>
+          <t>TERRAIN_WATER_SHALLOW</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Where the sea gives ground. Every landing, every port and every invasion in history has begun on one.</t>
+          <t>Water a person can stand in. The whole of coastal fishing, and most of coastal defence, happens here.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TERRAIN_WATER_DEEP</t>
+          <t>TERRAIN_WATER_SHELF</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Open ocean, out of sight of everything. It was the last part of the world to be mapped and the first to be feared.</t>
+          <t>The drowned edge of the land, shallow enough to work and rich enough to be worth fighting over.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TERRAIN_WATER_KELP</t>
+          <t>TERRAIN_WATER_SHELF_GOOD_FOUR</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Underwater forest, sheltering the fish that feed the coast. Its value was understood by fishermen centuries before naturalists.</t>
+          <t>A yield of the continental shelf, reachable by any fleet with the patience to look for it.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>TERRAIN_WATER_REEF</t>
+          <t>TERRAIN_WATER_SHELF_GOOD_ONE</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Living stone just under the surface. It builds the richest waters anywhere and sinks the ships that come to use them.</t>
+          <t>What the shallow banks give up to anyone who has learned where the banks are.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>TERRAIN_WATER_RIFT</t>
+          <t>TERRAIN_WATER_SHELF_GOOD_TWO</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>A tear in the sea floor where heat comes up from below. Whatever lives down there evolved without reference to the sun.</t>
+          <t>A second harvest of the shelf, and a common reason for two coastal peoples to discover they disagree about borders.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TERRAIN_WATER_SHALLOW</t>
+          <t>TERRAIN_WATER_VOLCANO</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Water a person can stand in. The whole of coastal fishing, and most of coastal defence, happens here.</t>
+          <t>A mountain building itself out of the sea, one eruption at a time. New land, arriving violently.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TERRAIN_WATER_SHELF</t>
+          <t>TERRAIN_WHITE_HILL</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>The drowned edge of the land, shallow enough to work and rich enough to be worth fighting over.</t>
+          <t>Snow-covered upland, held mostly by people who were pushed there and stayed out of stubbornness.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TERRAIN_WATER_SHELF_GOOD_FOUR</t>
+          <t>TERRAIN_WHITE_MOUNTAIN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>A yield of the continental shelf, reachable by any fleet with the patience to look for it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHELF_GOOD_ONE</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>What the shallow banks give up to anyone who has learned where the banks are.</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHELF_GOOD_TWO</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>A second harvest of the shelf, and a common reason for two coastal peoples to discover they disagree about borders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_VOLCANO</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>A mountain building itself out of the sea, one eruption at a time. New land, arriving violently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>TERRAIN_WHITE_HILL</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Snow-covered upland, held mostly by people who were pushed there and stayed out of stubbornness.</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>TERRAIN_WHITE_MOUNTAIN</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
           <t>Peaks under permanent ice. They are crossed by perhaps one pass, and whoever holds that pass holds the region.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C287"/>
+  <autoFilter ref="A1:C282"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42457,7 +42397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -42593,37 +42533,10 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WONDER_XLIGHTHOUSE</t>
+          <t>WONDER_GREAT_LIBRARY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
-        <is>
-          <t>WONDER_XLIGHTHOUSE {
-   DefaultIcon ICON_WONDER_XLIGHTHOUSE
-   Description DESCRIPTION_WONDER_XLIGHTHOUSE
-   EnableAdvance ADVANCE_WARRIOR_CODE
-   ProductionCost 2160
-}</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MoM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WONDER_GREAT_LIBRARY</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
         <is>
           <t>WONDER_GREAT_LIBRARY {
    DefaultIcon ICON_WONDER_GREAT_LIBRARY
@@ -42633,29 +42546,29 @@
 }</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>IncKnowledgePercent 20; IncreaseScientists 2</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>WONDER_ORACLE</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>WONDER_ORACLE {
    DefaultIcon ICON_WONDER_ORACLE
@@ -42665,29 +42578,29 @@
 }</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>IncHappinessEmpire 2; IncreaseCathedrals 1</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>WONDER_WALL_OF_BONE</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>WONDER_WALL_OF_BONE {
    DefaultIcon ICON_WONDER_WALL_OF_BONE
@@ -42697,29 +42610,29 @@
 }</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>ProtectFromBarbarians; PreventConversion</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>WONDER_GUILD_OF_LEGENDS</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>WONDER_GUILD_OF_LEGENDS {
    DefaultIcon ICON_WONDER_GUILD_OF_LEGENDS
@@ -42729,29 +42642,29 @@
 }</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>IncreaseHp 10; ReduceReadinessCost 50</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>WONDER_RUNE_OF_RULERSHIP</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>WONDER_RUNE_OF_RULERSHIP {
    DefaultIcon ICON_WONDER_RUNE_OF_RULERSHIP
@@ -42761,29 +42674,29 @@
 }</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>DecEmpireSize 4; IncreaseRegard 25</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>WONDER_BARDIC_COLLEGE</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>WONDER_BARDIC_COLLEGE {
    DefaultIcon ICON_WONDER_BARDIC_COLLEGE
@@ -42793,29 +42706,29 @@
 }</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>IncHappinessEmpire 1; IncreaseRegard 25</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>WONDER_THE_PARTHENON</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>WONDER_THE_PARTHENON {
    DefaultIcon ICON_WONDER_THE_PARTHENON
@@ -42825,29 +42738,29 @@
 }</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>IncHappinessEmpire 3; IncreaseCathedrals 1</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>WONDER_MYSTIC_XS_TOWER</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>WONDER_MYSTIC_XS_TOWER {
    DefaultIcon ICON_WONDER_MYSTIC_XS_TOWER
@@ -42857,29 +42770,29 @@
 }</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>RandomAdvanceChance 10; GlobalRadar</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>WONDER_GUNTHARS_VOYAGE</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>WONDER_GUNTHARS_VOYAGE {
    DefaultIcon ICON_WONDER_GUNTHARS_VOYAGE
@@ -42889,29 +42802,29 @@
 }</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>IncreaseBoatMovement 3; GoldPerWaterTradeRoute 10; AllBoatsDeepWater</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>WONDER_PROSPEROS_CONSERVATORY</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>WONDER_PROSPEROS_CONSERVATORY {
    DefaultIcon ICON_WONDER_PROSPEROS_CONSERVATORY
@@ -42921,29 +42834,29 @@
 }</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>IncKnowledgePercent 15; IncreaseSpecialists 1</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>WONDER_ELIXIR_OF_METAMORPHOSIS</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>WONDER_ELIXIR_OF_METAMORPHOSIS {
    DefaultIcon ICON_WONDER_ELIXIR_OF_METAMORPHOSIS
@@ -42953,29 +42866,29 @@
 }</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>IncreaseProduction 25; IncreaseHp 10</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>WONDER_ENCHANTED_GROTTO</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>WONDER_ENCHANTED_GROTTO {
    DefaultIcon ICON_WONDER_ENCHANTED_GROTTO
@@ -42985,29 +42898,29 @@
 }</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>IncreaseFoodAllCities 2; IncHappinessEmpire 2</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>WONDER_ELDRITCH_COLLEGE</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>WONDER_ELDRITCH_COLLEGE {
    DefaultIcon ICON_WONDER_ELDRITCH_COLLEGE
@@ -43017,29 +42930,29 @@
 }</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>IncKnowledgePercent 25; IncreaseScientists 2</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>WONDER_GNOME_TREASURY</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>WONDER_GNOME_TREASURY {
    DefaultIcon ICON_WONDER_GNOME_TREASURY
@@ -43049,29 +42962,29 @@
 }</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>BonusGold 250; IncreaseBrokerages 1; GoldPerInternationalTradeRoute 10</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>WONDER_REYWINDS_DISCOVERY</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>WONDER_REYWINDS_DISCOVERY {
    DefaultIcon ICON_WONDER_REYWINDS_DISCOVERY
@@ -43081,56 +42994,29 @@
 }</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>RandomAdvanceChance 15; IncKnowledgePercent 10</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>WONDER_XSTATUE_OF_LIBERTY</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>WONDER_XSTATUE_OF_LIBERTY {
-   DefaultIcon ICON_WONDER_XSTATUE_OF_LIBERTY
-   Description DESCRIPTION_WONDER_XSTATUE_OF_LIBERTY
-   EnableAdvance ADVANCE_WARRIOR_CODE
-   ProductionCost 2160
-}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MoM</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>WONDER_MESMERS_TOWER</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>WONDER_MESMERS_TOWER {
    DefaultIcon ICON_WONDER_MESMERS_TOWER
@@ -43140,56 +43026,29 @@
 }</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>SpiesEverywhere; EmbassiesEverywhere; DecCrimePercent 30</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>WONDER_XWOMENS_SUFFRAGE</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>WONDER_XWOMENS_SUFFRAGE {
-   DefaultIcon ICON_WONDER_XWOMENS_SUFFRAGE
-   Description DESCRIPTION_WONDER_XWOMENS_SUFFRAGE
-   EnableAdvance ADVANCE_WARRIOR_CODE
-   ProductionCost 2160
-}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MoM</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>WONDER_FORGE_OF_CHAOS</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>WONDER_FORGE_OF_CHAOS {
    DefaultIcon ICON_WONDER_FORGE_OF_CHAOS
@@ -43199,29 +43058,29 @@
 }</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>IncreaseProduction 30; DecreaseMaintenance 25</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>WONDER_ENTROPY_ENGINE</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>WONDER_ENTROPY_ENGINE {
    DefaultIcon ICON_WONDER_ENTROPY_ENGINE
@@ -43231,29 +43090,29 @@
 }</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>DecCrimePercent 50; FreeSlaves; ProhibitSlavers</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>WONDER_LEAGUE_OF_WIZARDS</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>WONDER_LEAGUE_OF_WIZARDS {
    DefaultIcon ICON_WONDER_LEAGUE_OF_WIZARDS
@@ -43263,56 +43122,29 @@
 }</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>IncKnowledgePercent 30; RandomAdvanceChance 10; EmbassiesEverywhereEvenAtWar</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>WONDER_XAPOLLO_PROGRAM</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>WONDER_XAPOLLO_PROGRAM {
-   DefaultIcon ICON_WONDER_XAPOLLO_PROGRAM
-   Description DESCRIPTION_WONDER_XAPOLLO_PROGRAM
-   EnableAdvance ADVANCE_WARRIOR_CODE
-   ProductionCost 2160
-}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>MoM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>WONDER_CELESTIAL_BEACON</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>WONDER_CELESTIAL_BEACON {
    DefaultIcon ICON_WONDER_CELESTIAL_BEACON
@@ -43322,51 +43154,24 @@
 }</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>MoM</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>AllCitizensContent; IncHappinessEmpire 3</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>WONDER_XCURE_FOR_CANCER</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>WONDER_XCURE_FOR_CANCER {
-   DefaultIcon ICON_WONDER_XCURE_FOR_CANCER
-   Description DESCRIPTION_WONDER_XCURE_FOR_CANCER
-   EnableAdvance ADVANCE_WARRIOR_CODE
-   ProductionCost 2160
-}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>MoM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E29"/>
+  <autoFilter ref="A1:E24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43589,6 +43394,7 @@
 int_t MomMagicCurDisp;       // plain display scalars for the popup: {scalar} is base-verified
 int_t MomMagicMaxDisp;       // (AlexanderTheGreat {cityScore}); array-indexed {Arr[Idx]} is
 int_t MomMagicGenDisp;       // unsupported and silently drops the whole message
+int_t MomRungDisp;           // highest sphere-ladder rung reached, 0-5. Shown on the
 int_t MomSpellPromptArmed[31];   // re-arm below threshold, fire once on crossing
 int_t MomSpellCurDisp;           // display scalars for the spellbook popup
 int_t MomSpellMaxDisp;
@@ -43854,7 +43660,7 @@
         <v>16</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>11892</v>
+        <v>12232</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
@@ -44135,6 +43941,10 @@
 int_t MomMagicCurDisp;       // plain display scalars for the popup: {scalar} is base-verified
 int_t MomMagicMaxDisp;       // (AlexanderTheGreat {cityScore}); array-indexed {Arr[Idx]} is
 int_t MomMagicGenDisp;       // unsupported and silently drops the whole message
+int_t MomRungDisp;           // highest sphere-ladder rung reached, 0-5. Shown on the
+                             // 'j' MAGIC STATUS panel because the summon rolls over
+                             // every rung unlocked (mom_summon.slc) and the player had
+                             // NO way to see which pool they were drawing from.
 // Phase D spellbook globals (mom_spells.slc). They live HERE, not there, for the
 // same reason MomMagic*Disp does: mom_func.slc is the FIRST include, and a
 // messagebox/alertbox segment that interpolates a global declared in a
@@ -45576,6 +45386,14 @@
             MomMagicCurDisp = MomMagicCur[p];
             MomMagicMaxDisp = MomMagicMax[p];
             MomMagicGenDisp = MomMagicPerTurn[p];
+            // The rung decides WHICH creatures the 75-mana summon can roll
+            // (mom_summon.slc). Floored at 1 for the same reason MomSummonRoll
+            // floors it: a tribe that starts holding its sphere root never fires
+            // the GrantAdvance that would raise it off 0.
+            MomRungDisp = MomSphereRung[p];
+            if (MomRungDisp &lt; 1) {
+                MomRungDisp = 1;
+            }
         }
         // Periodic popup every 10 rounds: REMOVED 2026-07-25, redundant and harmful.
         //
@@ -45643,7 +45461,7 @@
         <v>3</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>7766</v>
+        <v>8189</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
@@ -45744,6 +45562,14 @@
             MomMagicCurDisp = MomMagicCur[p];
             MomMagicMaxDisp = MomMagicMax[p];
             MomMagicGenDisp = MomMagicPerTurn[p];
+            // The rung decides WHICH creatures the 75-mana summon can roll
+            // (mom_summon.slc). Floored at 1 for the same reason MomSummonRoll
+            // floors it: a tribe that starts holding its sphere root never fires
+            // the GrantAdvance that would raise it off 0.
+            MomRungDisp = MomSphereRung[p];
+            if (MomRungDisp &lt; 1) {
+                MomRungDisp = 1;
+            }
         }
         // Periodic popup every 10 rounds: REMOVED 2026-07-25, redundant and harmful.
         //

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -73,7 +73,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improvements'!$A$1:$H$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'order_mask'!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'players'!$A$1:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'sprite_pick_rules'!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'terrain'!$A$1:$J$27</definedName>
@@ -86,7 +86,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'slic'!$A$1:$L$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E36" t="n">
         <v>8</v>
@@ -23039,7 +23039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -23742,7 +23742,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>void_f(int_t p_13, int_t unitType)</t>
+          <t>void_f(int_t p_13, int_t unitType, int_t rung)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -23969,32 +23969,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mom_msg.slc</t>
+          <t>mom_summon.slc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MomSphereBlessingMessages</t>
+          <t>MomSummonRungOf</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
+          <t>int_f(int_t unitType)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>?</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -24004,7 +23999,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24021,17 +24016,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MomSummonOrderTick</t>
+          <t>MomSphereBlessingMessages</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>spawn the creature ordered last turn, resolved from the CASTER'S OWN sphere; debits 75 mana</t>
+          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -24046,7 +24041,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -24058,22 +24053,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MomMsgSlicAlive</t>
+          <t>MomSummonOrderTick</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>segment: SLIC liveness confirmation text</t>
+          <t>spawn the creature ordered last turn, resolved from the CASTER'S OWN sphere; debits 75 mana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -24105,7 +24100,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MomBlessLife</t>
+          <t>MomMsgSlicAlive</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -24115,7 +24110,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>segment: Life sphere blessing popup</t>
+          <t>segment: SLIC liveness confirmation text</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -24130,7 +24125,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24147,7 +24142,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MomBlessNature</t>
+          <t>MomBlessLife</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -24157,7 +24152,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>segment: Nature sphere blessing popup</t>
+          <t>segment: Life sphere blessing popup</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -24172,7 +24167,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -24189,7 +24184,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MomBlessSorcery</t>
+          <t>MomBlessNature</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -24199,7 +24194,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>segment: Sorcery sphere blessing popup</t>
+          <t>segment: Nature sphere blessing popup</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -24214,7 +24209,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>sorcery</t>
+          <t>nature</t>
         </is>
       </c>
     </row>
@@ -24231,7 +24226,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MomBlessDeath</t>
+          <t>MomBlessSorcery</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -24241,7 +24236,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>segment: Death sphere blessing popup</t>
+          <t>segment: Sorcery sphere blessing popup</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -24256,7 +24251,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>sorcery</t>
         </is>
       </c>
     </row>
@@ -24273,7 +24268,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MomBlessChaos</t>
+          <t>MomBlessDeath</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -24283,7 +24278,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>segment: Chaos sphere blessing popup</t>
+          <t>segment: Death sphere blessing popup</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -24298,7 +24293,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -24315,7 +24310,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MomSummonGuard</t>
+          <t>MomBlessChaos</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -24325,7 +24320,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
+          <t>segment: Chaos sphere blessing popup</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -24340,7 +24335,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -24357,17 +24352,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MomSummonBear</t>
+          <t>MomUpkeepDisband</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>messagebox</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>segment: Nature summon result (War Bear)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -24399,7 +24389,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MomSummonMage</t>
+          <t>MomSummonGuard</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -24409,7 +24399,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>segment: Sorcery summon result (Mage)</t>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -24441,7 +24431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MomSummonZombie</t>
+          <t>MomSummonBear</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -24451,7 +24441,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>segment: Death summon result (Zombies)</t>
+          <t>segment: Nature summon result (War Bear)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -24483,7 +24473,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MomSummonHound</t>
+          <t>MomSummonMage</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -24493,7 +24483,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>segment: Chaos summon result (Hell Hound)</t>
+          <t>segment: Sorcery summon result (Mage)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -24525,7 +24515,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MomSummonNoMana</t>
+          <t>MomSummonZombie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -24535,7 +24525,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+          <t>segment: Death summon result (Zombies)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -24567,7 +24557,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MomMagicPower</t>
+          <t>MomSummonHound</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -24577,7 +24567,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>segment: mana pool / income readout body</t>
+          <t>segment: Chaos summon result (Hell Hound)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -24604,22 +24594,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MagicMenu</t>
+          <t>MomSummonNoMana</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -24641,32 +24631,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MomRecalcMagicPerTurn</t>
+          <t>MomMagicPower</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>int_f(int_t mp_1)</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
+          <t>segment: mana pool / income readout body</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -24683,32 +24673,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MomMagicPoolTick</t>
+          <t>MagicMenu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -24730,22 +24720,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MomMagicSchoolGrant</t>
+          <t>MomRecalcMagicPerTurn</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
+          <t>int_f(int_t mp_1)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>apply per-school mana multipliers when a magic advance is granted</t>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -24760,34 +24750,34 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MomCastFlameStrike</t>
+          <t>MomMagicPoolTick</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
+          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -24809,27 +24799,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MomCastDemonStrike</t>
+          <t>MomMagicSchoolGrant</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -24844,7 +24834,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -24861,7 +24851,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MomSpellShowBook</t>
+          <t>MomCastFlameStrike</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -24871,7 +24861,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -24886,7 +24876,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24898,22 +24888,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MomSpellMenuTick</t>
+          <t>MomCastDemonStrike</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -24928,7 +24918,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -24940,22 +24930,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MomOpenSpellbook</t>
+          <t>MomSpellShowBook</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UI trigger bound to the control-panel MagicButton</t>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -24970,7 +24960,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24977,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MomSpellAICast</t>
+          <t>MomSpellMenuTick</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -24997,7 +24987,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>let AI players cast their sphere's spell when mana allows</t>
+          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -25024,22 +25014,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MomMsgSpellbook</t>
+          <t>MomOpenSpellbook</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>segment: generic spellbook menu</t>
+          <t>UI trigger bound to the control-panel MagicButton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -25066,22 +25056,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MomMsgSpellbookChaos</t>
+          <t>MomSpellAICast</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>segment: Chaos-specific spellbook menu</t>
+          <t>let AI players cast their sphere's spell when mana allows</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -25096,7 +25086,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25113,7 +25103,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MomMsgDemonCast</t>
+          <t>MomMsgSpellbook</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -25123,7 +25113,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>segment: Demon Strike cast confirmation</t>
+          <t>segment: generic spellbook menu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -25155,7 +25145,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MomMsgFlameCast</t>
+          <t>MomMsgSpellbookChaos</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -25165,7 +25155,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>segment: Flame Strike cast confirmation</t>
+          <t>segment: Chaos-specific spellbook menu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -25180,7 +25170,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -25197,7 +25187,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MomMsgNoTarget</t>
+          <t>MomMsgDemonCast</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -25207,7 +25197,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>segment: no enemy unit in range</t>
+          <t>segment: Demon Strike cast confirmation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -25239,7 +25229,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MomMsgNoMana</t>
+          <t>MomMsgFlameCast</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -25249,7 +25239,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+          <t>segment: Flame Strike cast confirmation</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -25281,7 +25271,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MomMsgNotChaos</t>
+          <t>MomMsgNoTarget</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -25291,7 +25281,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>segment: caster's sphere does not grant this spell</t>
+          <t>segment: no enemy unit in range</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -25306,34 +25296,39 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>mom_ai_magic.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MomAiMagicTick</t>
+          <t>MomMsgNoMana</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -25350,32 +25345,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mod_CanPlayerHaveAdvance</t>
+          <t>MomMsgNotChaos</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
+          <t>segment: caster's sphere does not grant this spell</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -25385,34 +25380,29 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_ai_magic.slc</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildUnit</t>
+          <t>MomAiMagicTick</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theUnit)</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -25444,17 +25434,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildBuilding</t>
+          <t>mod_CanPlayerHaveAdvance</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theBuilding)</t>
+          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -25469,7 +25459,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -25486,37 +25476,121 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>mod_CanCityBuildUnit</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theUnit)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>mod_CanCityBuildBuilding</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theBuilding)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>mod_CanCityBuildWonder</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>int_f(city_t theCity, int_t theWonder)</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>same wall for wonders.</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H59"/>
+  <autoFilter ref="A1:H61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43388,7 +43462,11 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>int_t MomMagicCur[31];       // current magic power per player
+          <t>unit_t MomSummonUnit[160];   // 5 players x 32 slots -- the creature handle
+int_t  MomSummonRung[160];   // its rung 1..5; 0 == FREE SLOT
+int_t  MomUpkeepDisp;        // display scalars for the 'j' MAGIC STATUS panel
+int_t  MomNetDisp;           // net = generation - upkeep, may be negative
+int_t MomMagicCur[31];       // current magic power per player
 int_t MomMagicMax[31];       // max storage per player (a school sets this in M2)
 int_t MomMagicPerTurn[31];   // last computed per-turn generation
 int_t MomMagicCurDisp;       // plain display scalars for the popup: {scalar} is base-verified
@@ -43605,13 +43683,20 @@
     }
     return focusCount;
 }
-void_f MomSpawnSphereUnit(int_t p_13, int_t unitType)
+// rung == 0 means DO NOT LEDGER: the one-time *_MAGIC milestone creature in
+// mom_city_effects.slc is a gift and correctly carries no upkeep. Every
+// repeatable spend path passes the real rung.
+void_f MomSpawnSphereUnit(int_t p_13, int_t unitType, int_t rung)
 {
     city_t tmpCity;
     location_t spawnLoc;
     location_t tryLoc;
     int_t d;
     int_t placed;
+    int_t s;
+    int_t base;
+    int_t slot;
+    unit_t newUnit;
     // NEVER player[1]: player[] is the event ARG array (size 1), so player[1] is
     // out of bounds -- the same rule mom_turns.slc documents. It did not raise a
     // SLIC error here because the write silently no-ops and the .cities read then
@@ -43647,7 +43732,31 @@
                     }
                 }
             }
-            CreateUnit(p_13, unitType, spawnLoc, 1);
+            // 5-arg CreateUnit hands the new unit back in its out-arg (62 uses
+            // across the mod corpus). That handle is the ONLY way to tell a
+            // summoned creature from an identical one built in a city, which is
+            // what "only summoned creatures pay upkeep" requires.
+            CreateUnit(p_13, unitType, spawnLoc, 1, newUnit);
+            if (rung &gt; 0) {
+                if (p_13 &gt;= 1 &amp;&amp; p_13 &lt;= 5) {
+                    base = (p_13 - 1) * 32;
+                    slot = -1;
+                    for (s = 0; s &lt; 32; s = s + 1) {
+                        if (slot &lt; 0) {
+                            if (MomSummonRung[base + s] == 0) {
+                                slot = s;
+                            }
+                        }
+                    }
+                    // No free slot: spawn anyway, ledger nothing. A hard cap on
+                    // TRACKED creatures is better than overwriting a live entry,
+                    // which would orphan that creature into permanent free upkeep.
+                    if (slot &gt;= 0) {
+                        MomSummonUnit[base + slot] = newUnit;
+                        MomSummonRung[base + slot] = rung;
+                    }
+                }
+            }
         }
     }
 }</t>
@@ -43660,7 +43769,7 @@
         <v>16</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>12232</v>
+        <v>15297</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
@@ -43887,13 +43996,46 @@
     }
     return focusCount;
 }
-void_f MomSpawnSphereUnit(int_t p_13, int_t unitType)
+// ---------------------------------------------------------------------------
+// SUMMONED-CREATURE LEDGER (2026-08-01)
+//
+// Upkeep is charged on SUMMONED creatures only -- a Centaur built in a city is
+// free, an identical Centaur that was summoned is not. SLIC has no per-unit
+// storage to hang an "I was summoned" flag on, so origin is recorded here
+// instead: MomSpawnSphereUnit stores the handle CreateUnit hands back, together
+// with the sphere rung that decides the rate.
+//
+// Layout is flat because SLIC has no 2-D arrays: index = (p-1)*32 + slot, for p
+// in 1..5. MomSummonRung[i] == 0 IS the free-slot sentinel, so the array is
+// self-describing and needs no separate occupancy counter.
+//
+// The ledger is SELF-CLEANING and deliberately needs no KillUnit handler: a
+// creature that dies leaves a handle that stops being .valid, and the per-turn
+// scan in mom_magic.slc frees the slot when it sees that. Billing a corpse
+// forever would look like balance rather than a bug, which is why
+// tools/gate_mana_upkeep.py asserts the clear-on-invalid branch specifically.
+//
+// DECLARED HERE, immediately above the only writer, for the same reason the
+// magic-power block sits above its readers: SLIC needs declaration-before-use
+// WITHIN a file, not just across the include order.
+unit_t MomSummonUnit[160];   // 5 players x 32 slots -- the creature handle
+int_t  MomSummonRung[160];   // its rung 1..5; 0 == FREE SLOT
+int_t  MomUpkeepDisp;        // display scalars for the 'j' MAGIC STATUS panel
+int_t  MomNetDisp;           // net = generation - upkeep, may be negative
+// rung == 0 means DO NOT LEDGER: the one-time *_MAGIC milestone creature in
+// mom_city_effects.slc is a gift and correctly carries no upkeep. Every
+// repeatable spend path passes the real rung.
+void_f MomSpawnSphereUnit(int_t p_13, int_t unitType, int_t rung)
 {
     city_t tmpCity;
     location_t spawnLoc;
     location_t tryLoc;
     int_t d;
     int_t placed;
+    int_t s;
+    int_t base;
+    int_t slot;
+    unit_t newUnit;
     // NEVER player[1]: player[] is the event ARG array (size 1), so player[1] is
     // out of bounds -- the same rule mom_turns.slc documents. It did not raise a
     // SLIC error here because the write silently no-ops and the .cities read then
@@ -43929,7 +44071,31 @@
                     }
                 }
             }
-            CreateUnit(p_13, unitType, spawnLoc, 1);
+            // 5-arg CreateUnit hands the new unit back in its out-arg (62 uses
+            // across the mod corpus). That handle is the ONLY way to tell a
+            // summoned creature from an identical one built in a city, which is
+            // what "only summoned creatures pay upkeep" requires.
+            CreateUnit(p_13, unitType, spawnLoc, 1, newUnit);
+            if (rung &gt; 0) {
+                if (p_13 &gt;= 1 &amp;&amp; p_13 &lt;= 5) {
+                    base = (p_13 - 1) * 32;
+                    slot = -1;
+                    for (s = 0; s &lt; 32; s = s + 1) {
+                        if (slot &lt; 0) {
+                            if (MomSummonRung[base + s] == 0) {
+                                slot = s;
+                            }
+                        }
+                    }
+                    // No free slot: spawn anyway, ledger nothing. A hard cap on
+                    // TRACKED creatures is better than overwriting a live entry,
+                    // which would orphan that creature into permanent free upkeep.
+                    if (slot &gt;= 0) {
+                        MomSummonUnit[base + slot] = newUnit;
+                        MomSummonRung[base + slot] = rung;
+                    }
+                }
+            }
         }
     }
 }
@@ -44099,22 +44265,22 @@
     if (value[0] != 0) {
         if (MomPlayerIsLife(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC)) {
             MomGrantLifeBuilding(p);
-            MomSpawnSphereUnit(p, UnitDB(UNIT_GUARDIAN_SPIRIT));
+            MomSpawnSphereUnit(p, UnitDB(UNIT_GUARDIAN_SPIRIT), 0);
         } elseif (MomPlayerIsNature(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC)) {
             MomGrantNatureBuilding(p);
-            MomSpawnSphereUnit(p, UnitDB(UNIT_WARBEARS));
+            MomSpawnSphereUnit(p, UnitDB(UNIT_WARBEARS), 0);
         } elseif (MomPlayerIsSorcery(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY)) {
             MomGrantSorceryBuilding(p);
-            MomSpawnSphereUnit(p, UnitDB(UNIT_MAGE));
+            MomSpawnSphereUnit(p, UnitDB(UNIT_MAGE), 0);
         } elseif (MomPlayerIsDeath(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC)) {
             MomGrantDeathBuilding(p);
-            MomSpawnSphereUnit(p, UnitDB(UNIT_ZOMBIES));
+            MomSpawnSphereUnit(p, UnitDB(UNIT_ZOMBIES), 0);
         } elseif (MomPlayerIsChaos(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC)) {
             // Chaos KEEPS its random windfall -- that is its B1 identity -- but
             // it now also gets the building+unit milestone every other sphere
             // had, so the 5-column matrix is square.
             MomGrantChaosBuilding(p);
-            MomSpawnSphereUnit(p, UnitDB(UNIT_HELL_HOUNDS));
+            MomSpawnSphereUnit(p, UnitDB(UNIT_HELL_HOUNDS), 0);
             AddGold(p, 50 + Random(100));
         }
     }
@@ -44167,7 +44333,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>4603</v>
+        <v>4716</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
@@ -44201,22 +44367,22 @@
     if (value[0] != 0) {
         if (MomPlayerIsLife(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC)) {
             MomGrantLifeBuilding(p);
-            MomSpawnSphereUnit(p, UnitDB(UNIT_GUARDIAN_SPIRIT));
+            MomSpawnSphereUnit(p, UnitDB(UNIT_GUARDIAN_SPIRIT), 0);
         } elseif (MomPlayerIsNature(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC)) {
             MomGrantNatureBuilding(p);
-            MomSpawnSphereUnit(p, UnitDB(UNIT_WARBEARS));
+            MomSpawnSphereUnit(p, UnitDB(UNIT_WARBEARS), 0);
         } elseif (MomPlayerIsSorcery(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY)) {
             MomGrantSorceryBuilding(p);
-            MomSpawnSphereUnit(p, UnitDB(UNIT_MAGE));
+            MomSpawnSphereUnit(p, UnitDB(UNIT_MAGE), 0);
         } elseif (MomPlayerIsDeath(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC)) {
             MomGrantDeathBuilding(p);
-            MomSpawnSphereUnit(p, UnitDB(UNIT_ZOMBIES));
+            MomSpawnSphereUnit(p, UnitDB(UNIT_ZOMBIES), 0);
         } elseif (MomPlayerIsChaos(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC)) {
             // Chaos KEEPS its random windfall -- that is its B1 identity -- but
             // it now also gets the building+unit milestone every other sphere
             // had, so the 5-column matrix is square.
             MomGrantChaosBuilding(p);
-            MomSpawnSphereUnit(p, UnitDB(UNIT_HELL_HOUNDS));
+            MomSpawnSphereUnit(p, UnitDB(UNIT_HELL_HOUNDS), 0);
             AddGold(p, 50 + Random(100));
         }
     }
@@ -44439,6 +44605,33 @@
         }
     }
     return 0;
+}
+// Rung that owns each summonable creature -- the mana-upkeep rate table.
+// GENERATED alongside the roll above from the same pools, so the rate a
+// creature is charged can never drift from the rung it was rolled at.
+int_f MomSummonRungOf(int_t unitType)
+{
+    if (unitType == UnitDB(UNIT_AIR_ELEMENTAL)) { return 2; }
+    if (unitType == UnitDB(UNIT_ARCHANGEL)) { return 5; }
+    if (unitType == UnitDB(UNIT_BEHEMOTH)) { return 3; }
+    if (unitType == UnitDB(UNIT_COCKATRICE)) { return 2; }
+    if (unitType == UnitDB(UNIT_DEMON)) { return 3; }
+    if (unitType == UnitDB(UNIT_EFREET)) { return 3; }
+    if (unitType == UnitDB(UNIT_GARGOYLE)) { return 2; }
+    if (unitType == UnitDB(UNIT_GREAT_WYRM)) { return 5; }
+    if (unitType == UnitDB(UNIT_GUARDIAN_SPIRIT)) { return 1; }
+    if (unitType == UnitDB(UNIT_HELL_HOUNDS)) { return 1; }
+    if (unitType == UnitDB(UNIT_HYDRA)) { return 5; }
+    if (unitType == UnitDB(UNIT_PEGASUS)) { return 3; }
+    if (unitType == UnitDB(UNIT_PHANTOM_WARRIORS)) { return 1; }
+    if (unitType == UnitDB(UNIT_STORM_DRAKE)) { return 5; }
+    if (unitType == UnitDB(UNIT_STORM_GIANT)) { return 3; }
+    if (unitType == UnitDB(UNIT_UNDEAD_DRAGON)) { return 5; }
+    if (unitType == UnitDB(UNIT_UNICORN)) { return 2; }
+    if (unitType == UnitDB(UNIT_WARBEARS)) { return 1; }
+    if (unitType == UnitDB(UNIT_WRAITH)) { return 2; }
+    if (unitType == UnitDB(UNIT_ZOMBIES)) { return 1; }
+    return 0;
 }</t>
         </is>
       </c>
@@ -44495,10 +44688,10 @@
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>11184</v>
+        <v>12625</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
@@ -44715,6 +44908,33 @@
         }
     }
     return 0;
+}
+// Rung that owns each summonable creature -- the mana-upkeep rate table.
+// GENERATED alongside the roll above from the same pools, so the rate a
+// creature is charged can never drift from the rung it was rolled at.
+int_f MomSummonRungOf(int_t unitType)
+{
+    if (unitType == UnitDB(UNIT_AIR_ELEMENTAL)) { return 2; }
+    if (unitType == UnitDB(UNIT_ARCHANGEL)) { return 5; }
+    if (unitType == UnitDB(UNIT_BEHEMOTH)) { return 3; }
+    if (unitType == UnitDB(UNIT_COCKATRICE)) { return 2; }
+    if (unitType == UnitDB(UNIT_DEMON)) { return 3; }
+    if (unitType == UnitDB(UNIT_EFREET)) { return 3; }
+    if (unitType == UnitDB(UNIT_GARGOYLE)) { return 2; }
+    if (unitType == UnitDB(UNIT_GREAT_WYRM)) { return 5; }
+    if (unitType == UnitDB(UNIT_GUARDIAN_SPIRIT)) { return 1; }
+    if (unitType == UnitDB(UNIT_HELL_HOUNDS)) { return 1; }
+    if (unitType == UnitDB(UNIT_HYDRA)) { return 5; }
+    if (unitType == UnitDB(UNIT_PEGASUS)) { return 3; }
+    if (unitType == UnitDB(UNIT_PHANTOM_WARRIORS)) { return 1; }
+    if (unitType == UnitDB(UNIT_STORM_DRAKE)) { return 5; }
+    if (unitType == UnitDB(UNIT_STORM_GIANT)) { return 3; }
+    if (unitType == UnitDB(UNIT_UNDEAD_DRAGON)) { return 5; }
+    if (unitType == UnitDB(UNIT_UNICORN)) { return 2; }
+    if (unitType == UnitDB(UNIT_WARBEARS)) { return 1; }
+    if (unitType == UnitDB(UNIT_WRAITH)) { return 2; }
+    if (unitType == UnitDB(UNIT_ZOMBIES)) { return 1; }
+    return 0;
 }</t>
         </is>
       </c>
@@ -44766,6 +44986,7 @@
 HandleEvent(BeginTurn) 'MomSummonOrderTick' post {
     int_t p;
     int_t summonPick;
+    int_t summonRung;
     city_t tmpCity;
     p = player[0];
     // COST 75 (added 2026-07-26). The order is placed at click time and PAID here,
@@ -44810,7 +45031,19 @@
             // whole reason the roll RETURNS an index instead of spawning: a
             // 2-level user-function chain from a HandleEvent is a 0xC0000005
             // (slic-two-crash-classes). Do NOT fold these into one helper.
-            MomSpawnSphereUnit(p, summonPick);
+            // The third argument is the creature's own rung, which is what it
+            // will be charged in mana upkeep every turn it stays alive
+            // (mom_magic.slc). MomSummonRungOf is GENERATED from the same pools
+            // as the roll.
+            //
+            // RESOLVED INTO A LOCAL FIRST, deliberately. Writing this as
+            // MomSpawnSphereUnit(p, summonPick, MomSummonRungOf(summonPick))
+            // puts a user-function call in an argument position of another user
+            // function call, which is the ambiguous form of the 2-level chain
+            // that is a 0xC0000005. Two sequential statements are unambiguously
+            // two depth-1 calls.
+            summonRung = MomSummonRungOf(summonPick);
+            MomSpawnSphereUnit(p, summonPick, summonRung);
             if (p == 1) {
                 Message(p, 'MomSummonGuard');
             } elseif (p == 2) {
@@ -44869,6 +45102,14 @@
 // segment is reachable from another sphere's branch. Message(p, 'Key') needs
 // 'Key' to be a DEFINED SEGMENT (see the block comment above) -- adding the
 // scen_str.txt keys alone would have displayed nothing.
+// Declared HERE rather than in mom_magic.slc, which is what raises it: segments
+// share ONE flat namespace but still need declaring before use, and mom_msg.slc
+// is #included before mom_magic.slc. Message(p, 'Key') needs 'Key' to be a
+// defined segment -- adding the scen_str.txt key alone displays nothing.
+messagebox 'MomUpkeepDisband' {
+	Show();
+	Text(ID_MOM_MSG_UPKEEP_DISBAND);
+}
 messagebox 'MomSummonGuard' {
 	Show();
 	Text(ID_MOM_MSG_SUMMON_GUARD);
@@ -44978,10 +45219,10 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>14971</v>
+        <v>16151</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
@@ -45058,6 +45299,7 @@
 HandleEvent(BeginTurn) 'MomSummonOrderTick' post {
     int_t p;
     int_t summonPick;
+    int_t summonRung;
     city_t tmpCity;
     p = player[0];
     // COST 75 (added 2026-07-26). The order is placed at click time and PAID here,
@@ -45102,7 +45344,19 @@
             // whole reason the roll RETURNS an index instead of spawning: a
             // 2-level user-function chain from a HandleEvent is a 0xC0000005
             // (slic-two-crash-classes). Do NOT fold these into one helper.
-            MomSpawnSphereUnit(p, summonPick);
+            // The third argument is the creature's own rung, which is what it
+            // will be charged in mana upkeep every turn it stays alive
+            // (mom_magic.slc). MomSummonRungOf is GENERATED from the same pools
+            // as the roll.
+            //
+            // RESOLVED INTO A LOCAL FIRST, deliberately. Writing this as
+            // MomSpawnSphereUnit(p, summonPick, MomSummonRungOf(summonPick))
+            // puts a user-function call in an argument position of another user
+            // function call, which is the ambiguous form of the 2-level chain
+            // that is a 0xC0000005. Two sequential statements are unambiguously
+            // two depth-1 calls.
+            summonRung = MomSummonRungOf(summonPick);
+            MomSpawnSphereUnit(p, summonPick, summonRung);
             if (p == 1) {
                 Message(p, 'MomSummonGuard');
             } elseif (p == 2) {
@@ -45166,6 +45420,14 @@
 // segment is reachable from another sphere's branch. Message(p, 'Key') needs
 // 'Key' to be a DEFINED SEGMENT (see the block comment above) -- adding the
 // scen_str.txt keys alone would have displayed nothing.
+// Declared HERE rather than in mom_magic.slc, which is what raises it: segments
+// share ONE flat namespace but still need declaring before use, and mom_msg.slc
+// is #included before mom_magic.slc. Message(p, 'Key') needs 'Key' to be a
+// defined segment -- adding the scen_str.txt key alone displays nothing.
+messagebox 'MomUpkeepDisband' {
+	Show();
+	Text(ID_MOM_MSG_UPKEEP_DISBAND);
+}
 messagebox 'MomSummonGuard' {
 	Show();
 	Text(ID_MOM_MSG_SUMMON_GUARD);
@@ -45304,17 +45566,44 @@
     int_t gen;
     int_t pct;
     int_t nodes;
+    int_t upkeep;
+    int_t base;
+    int_t idx;
     city_t tmpCity;
     location_t cloc;
     location_t nloc;
     gen = 10;
     nodes = 0;
+    upkeep = 0;
     // NEVER player[mp_1]: player[N] indexes the event ARG array (size 1), so mp_1&gt;=1
     // throws "Array index 1 out of bounds". The turn player is player[0].
     for (i = 0; i &lt; player[0].cities; i = i + 1) {
         GetCityByIndex(player[0], i, tmpCity);
         if (CityIsValid(tmpCity)) {
             gen = gen + tmpCity.population * 2;
+            // BUILDING TALLY (2026-08-01). The sphere's own thematic buildings
+            // generate mana, so a tribe can INVEST in income rather than only
+            // waiting on population. The lists are deliberately the same ones
+            // mom_city_effects.slc already rewards on construction -- one set of
+            // sphere-defining buildings, not a second table to keep in sync.
+            // Builtins only: CityHasBuilding is a builtin (217 uses in corpus),
+            // so this adds no user-function call level.
+            if (mp_1 == 1) {
+                if (CityHasBuilding(tmpCity, "IMPROVE_WIZARDS_FORTRESS")) { gen = gen + 8; }
+                if (CityHasBuilding(tmpCity, "IMPROVE_TEMPLE")) { gen = gen + 3; }
+            } elseif (mp_1 == 2) {
+                if (CityHasBuilding(tmpCity, "IMPROVE_PRIMAL_SOURCE")) { gen = gen + 8; }
+                if (CityHasBuilding(tmpCity, "IMPROVE_FANTASTIC_STABLE")) { gen = gen + 3; }
+            } elseif (mp_1 == 3) {
+                if (CityHasBuilding(tmpCity, "IMPROVE_BEACON_OF_WISDOM")) { gen = gen + 8; }
+                if (CityHasBuilding(tmpCity, "IMPROVE_LIBRARY")) { gen = gen + 3; }
+            } elseif (mp_1 == 4) {
+                if (CityHasBuilding(tmpCity, "IMPROVE_MECHANICIANS_GUILD")) { gen = gen + 8; }
+                if (CityHasBuilding(tmpCity, "IMPROVE_BARRACKS")) { gen = gen + 3; }
+            } elseif (mp_1 == 5) {
+                if (CityHasBuilding(tmpCity, "IMPROVE_MERCHANTS_GUILD")) { gen = gen + 8; }
+                if (CityHasBuilding(tmpCity, "IMPROVE_COLOSSEUM")) { gen = gen + 3; }
+            }
             // M4 mana nodes: good-bearing tiles in the city inner radius (center + 8 neighbors).
             cloc = tmpCity.location;
             if (HasGood(cloc) &gt;= 0) {
@@ -45350,7 +45639,43 @@
         pct = 100;
     }
     gen = gen * pct / 100;
-    return gen;
+    // ---------------------------------------------------------------------
+    // UPKEEP (2026-08-01) -- the deduction half of "tally - upkeep".
+    //
+    // Charged on SUMMONED creatures only, scaled by the rung they came from, so
+    // a rung-5 Great Wyrm is a real commitment and a rung-1 Warbears is cheap.
+    // The scan is a LIVE read of the ledger rather than a running counter,
+    // which makes it self-correcting: a creature lost in combat leaves a handle
+    // that is no longer .valid, and the slot is reclaimed right here. That is
+    // why no KillUnit handler is needed to keep the books straight.
+    //
+    // Inline and builtins-only ON PURPOSE. This function is already called at
+    // depth 1 from the MomMagicPoolTick handler, and a 2-level user-function
+    // chain from a handler body is the documented 0xC0000005.
+    if (mp_1 &gt;= 1 &amp;&amp; mp_1 &lt;= 5) {
+        base = (mp_1 - 1) * 32;
+        for (i = 0; i &lt; 32; i = i + 1) {
+            idx = base + i;
+            if (MomSummonRung[idx] &gt; 0) {
+                if (MomSummonUnit[idx].valid) {
+                    upkeep = upkeep + MomSummonRung[idx] * 2;
+                } else {
+                    MomSummonRung[idx] = 0;   // creature died -- free the slot
+                }
+            }
+        }
+    }
+    // Guarded: this function runs for AI tribes too, and an unguarded write
+    // would leak an AI's books into the human's MAGIC STATUS panel -- the same
+    // reason the other Disp scalars sit behind IsHumanPlayer in the tick below.
+    if (IsHumanPlayer(mp_1)) {
+        MomUpkeepDisp = upkeep;
+        MomNetDisp = gen - upkeep;
+    }
+    // Deliberately allowed to go NEGATIVE. A tribe that over-summons must feel
+    // its pool drain; MomMagicPoolTick is what turns a sustained deficit into a
+    // disband, and it needs to see the real shortfall to do that.
+    return gen - upkeep;
 }</t>
         </is>
       </c>
@@ -45358,6 +45683,10 @@
         <is>
           <t>HandleEvent(BeginTurn) 'MomMagicPoolTick' post {
     int_t p;
+    int_t insBase;
+    int_t insSlot;
+    int_t insIdx;
+    int_t insI;
     p = player[0];
     // CRASH FIX (turn-10): magic is for sphere players 1..5 only. Player 0 (barbarians) and
     // any non-sphere player must skip. SLIC 'post' handlers cannot bare-return, so gate the
@@ -45370,6 +45699,49 @@
         MomMagicCur[p] = MomMagicCur[p] + MomMagicPerTurn[p];
         if (MomMagicCur[p] &gt; MomMagicMax[p]) {
             MomMagicCur[p] = MomMagicMax[p];
+        }
+        // -----------------------------------------------------------------
+        // HARD INSOLVENCY (2026-08-01). Upkeep can push the pool below zero.
+        // When it does, the tribe cannot feed what it has summoned and the
+        // NEWEST creature is released -- last in, first out, so a long-held
+        // high-rung creature is not the first thing lost.
+        //
+        // EXACTLY ONE disband per turn, by construction. The loop only FINDS
+        // the victim; the single KillUnit sits outside it. That bound is
+        // deliberate on two counts: a sustained deficit should bleed off
+        // gradually rather than wipe an army in one tick, and an unbounded
+        // kill loop inside a BeginTurn handler sits right next to the known
+        // AI end-turn stack-overflow class. tools/gate_mana_upkeep.py asserts
+        // KillUnit never moves inside a loop.
+        if (MomMagicCur[p] &lt; 0) {
+            insBase = (p - 1) * 32;
+            insSlot = -1;
+            for (insI = 31; insI &gt;= 0; insI = insI - 1) {
+                if (insSlot &lt; 0) {
+                    if (MomSummonRung[insBase + insI] &gt; 0) {
+                        insSlot = insI;
+                    }
+                }
+            }
+            if (insSlot &gt;= 0) {
+                insIdx = insBase + insSlot;
+                if (MomSummonUnit[insIdx].valid) {
+                    KillUnit(MomSummonUnit[insIdx]);
+                }
+                // Refund this turn's charge for the creature just released, so
+                // the pool reflects the lighter army immediately instead of
+                // disbanding a second one next turn for a debt already paid.
+                MomMagicCur[p] = MomMagicCur[p] + MomSummonRung[insIdx] * 2;
+                MomSummonRung[insIdx] = 0;
+                if (IsHumanPlayer(p)) {
+                    Message(p, 'MomUpkeepDisband');
+                }
+            }
+        }
+        // Floor at zero whether or not a creature was available to release: a
+        // tribe with nothing left to disband simply sits at empty.
+        if (MomMagicCur[p] &lt; 0) {
+            MomMagicCur[p] = 0;
         }
         // M3 pool-overflow auto-summon: REMOVED 2026-07-26. It zeroed the pool the
         // moment it capped, so mana could never sit at the cap and the 50/100-cost
@@ -45461,7 +45833,7 @@
         <v>3</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>8189</v>
+        <v>14243</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
@@ -45479,17 +45851,44 @@
     int_t gen;
     int_t pct;
     int_t nodes;
+    int_t upkeep;
+    int_t base;
+    int_t idx;
     city_t tmpCity;
     location_t cloc;
     location_t nloc;
     gen = 10;
     nodes = 0;
+    upkeep = 0;
     // NEVER player[mp_1]: player[N] indexes the event ARG array (size 1), so mp_1&gt;=1
     // throws "Array index 1 out of bounds". The turn player is player[0].
     for (i = 0; i &lt; player[0].cities; i = i + 1) {
         GetCityByIndex(player[0], i, tmpCity);
         if (CityIsValid(tmpCity)) {
             gen = gen + tmpCity.population * 2;
+            // BUILDING TALLY (2026-08-01). The sphere's own thematic buildings
+            // generate mana, so a tribe can INVEST in income rather than only
+            // waiting on population. The lists are deliberately the same ones
+            // mom_city_effects.slc already rewards on construction -- one set of
+            // sphere-defining buildings, not a second table to keep in sync.
+            // Builtins only: CityHasBuilding is a builtin (217 uses in corpus),
+            // so this adds no user-function call level.
+            if (mp_1 == 1) {
+                if (CityHasBuilding(tmpCity, "IMPROVE_WIZARDS_FORTRESS")) { gen = gen + 8; }
+                if (CityHasBuilding(tmpCity, "IMPROVE_TEMPLE")) { gen = gen + 3; }
+            } elseif (mp_1 == 2) {
+                if (CityHasBuilding(tmpCity, "IMPROVE_PRIMAL_SOURCE")) { gen = gen + 8; }
+                if (CityHasBuilding(tmpCity, "IMPROVE_FANTASTIC_STABLE")) { gen = gen + 3; }
+            } elseif (mp_1 == 3) {
+                if (CityHasBuilding(tmpCity, "IMPROVE_BEACON_OF_WISDOM")) { gen = gen + 8; }
+                if (CityHasBuilding(tmpCity, "IMPROVE_LIBRARY")) { gen = gen + 3; }
+            } elseif (mp_1 == 4) {
+                if (CityHasBuilding(tmpCity, "IMPROVE_MECHANICIANS_GUILD")) { gen = gen + 8; }
+                if (CityHasBuilding(tmpCity, "IMPROVE_BARRACKS")) { gen = gen + 3; }
+            } elseif (mp_1 == 5) {
+                if (CityHasBuilding(tmpCity, "IMPROVE_MERCHANTS_GUILD")) { gen = gen + 8; }
+                if (CityHasBuilding(tmpCity, "IMPROVE_COLOSSEUM")) { gen = gen + 3; }
+            }
             // M4 mana nodes: good-bearing tiles in the city inner radius (center + 8 neighbors).
             cloc = tmpCity.location;
             if (HasGood(cloc) &gt;= 0) {
@@ -45525,7 +45924,43 @@
         pct = 100;
     }
     gen = gen * pct / 100;
-    return gen;
+    // ---------------------------------------------------------------------
+    // UPKEEP (2026-08-01) -- the deduction half of "tally - upkeep".
+    //
+    // Charged on SUMMONED creatures only, scaled by the rung they came from, so
+    // a rung-5 Great Wyrm is a real commitment and a rung-1 Warbears is cheap.
+    // The scan is a LIVE read of the ledger rather than a running counter,
+    // which makes it self-correcting: a creature lost in combat leaves a handle
+    // that is no longer .valid, and the slot is reclaimed right here. That is
+    // why no KillUnit handler is needed to keep the books straight.
+    //
+    // Inline and builtins-only ON PURPOSE. This function is already called at
+    // depth 1 from the MomMagicPoolTick handler, and a 2-level user-function
+    // chain from a handler body is the documented 0xC0000005.
+    if (mp_1 &gt;= 1 &amp;&amp; mp_1 &lt;= 5) {
+        base = (mp_1 - 1) * 32;
+        for (i = 0; i &lt; 32; i = i + 1) {
+            idx = base + i;
+            if (MomSummonRung[idx] &gt; 0) {
+                if (MomSummonUnit[idx].valid) {
+                    upkeep = upkeep + MomSummonRung[idx] * 2;
+                } else {
+                    MomSummonRung[idx] = 0;   // creature died -- free the slot
+                }
+            }
+        }
+    }
+    // Guarded: this function runs for AI tribes too, and an unguarded write
+    // would leak an AI's books into the human's MAGIC STATUS panel -- the same
+    // reason the other Disp scalars sit behind IsHumanPlayer in the tick below.
+    if (IsHumanPlayer(mp_1)) {
+        MomUpkeepDisp = upkeep;
+        MomNetDisp = gen - upkeep;
+    }
+    // Deliberately allowed to go NEGATIVE. A tribe that over-summons must feel
+    // its pool drain; MomMagicPoolTick is what turns a sustained deficit into a
+    // disband, and it needs to see the real shortfall to do that.
+    return gen - upkeep;
 }
 // MomSphereSummonUnit() was REMOVED 2026-07-26 along with its only caller, the
 // pool-overflow auto-summon below. The sphere -&gt; creature mapping now lives
@@ -45534,6 +45969,10 @@
 // it anyway -- so nothing was lost but a level of indirection.
 HandleEvent(BeginTurn) 'MomMagicPoolTick' post {
     int_t p;
+    int_t insBase;
+    int_t insSlot;
+    int_t insIdx;
+    int_t insI;
     p = player[0];
     // CRASH FIX (turn-10): magic is for sphere players 1..5 only. Player 0 (barbarians) and
     // any non-sphere player must skip. SLIC 'post' handlers cannot bare-return, so gate the
@@ -45546,6 +45985,49 @@
         MomMagicCur[p] = MomMagicCur[p] + MomMagicPerTurn[p];
         if (MomMagicCur[p] &gt; MomMagicMax[p]) {
             MomMagicCur[p] = MomMagicMax[p];
+        }
+        // -----------------------------------------------------------------
+        // HARD INSOLVENCY (2026-08-01). Upkeep can push the pool below zero.
+        // When it does, the tribe cannot feed what it has summoned and the
+        // NEWEST creature is released -- last in, first out, so a long-held
+        // high-rung creature is not the first thing lost.
+        //
+        // EXACTLY ONE disband per turn, by construction. The loop only FINDS
+        // the victim; the single KillUnit sits outside it. That bound is
+        // deliberate on two counts: a sustained deficit should bleed off
+        // gradually rather than wipe an army in one tick, and an unbounded
+        // kill loop inside a BeginTurn handler sits right next to the known
+        // AI end-turn stack-overflow class. tools/gate_mana_upkeep.py asserts
+        // KillUnit never moves inside a loop.
+        if (MomMagicCur[p] &lt; 0) {
+            insBase = (p - 1) * 32;
+            insSlot = -1;
+            for (insI = 31; insI &gt;= 0; insI = insI - 1) {
+                if (insSlot &lt; 0) {
+                    if (MomSummonRung[insBase + insI] &gt; 0) {
+                        insSlot = insI;
+                    }
+                }
+            }
+            if (insSlot &gt;= 0) {
+                insIdx = insBase + insSlot;
+                if (MomSummonUnit[insIdx].valid) {
+                    KillUnit(MomSummonUnit[insIdx]);
+                }
+                // Refund this turn's charge for the creature just released, so
+                // the pool reflects the lighter army immediately instead of
+                // disbanding a second one next turn for a debt already paid.
+                MomMagicCur[p] = MomMagicCur[p] + MomSummonRung[insIdx] * 2;
+                MomSummonRung[insIdx] = 0;
+                if (IsHumanPlayer(p)) {
+                    Message(p, 'MomUpkeepDisband');
+                }
+            }
+        }
+        // Floor at zero whether or not a creature was available to release: a
+        // tribe with nothing left to disband simply sits at empty.
+        if (MomMagicCur[p] &lt; 0) {
+            MomMagicCur[p] = 0;
         }
         // M3 pool-overflow auto-summon: REMOVED 2026-07-26. It zeroed the pool the
         // moment it capped, so mana could never sit at the cap and the 50/100-cost
@@ -46347,6 +46829,7 @@
           <t>HandleEvent(BeginTurn) 'MomAiMagicTick' post {
     int_t p;
     int_t pick;
+    int_t pickRung;
     int_t roll;
     int_t atWar;
     int_t i;
@@ -46381,6 +46864,22 @@
             // identically.
             GetCityByIndex(player[0], 0, tmpCity);
             pick = MomSummonRoll(p);
+            // See the note above the spawn: resolved into a local, never nested
+            // into an argument position.
+            pickRung = MomSummonRungOf(pick);
+            // SUSTAINABILITY, not just affordability (2026-08-01). Creatures now
+            // cost mana every turn they live (mom_magic.slc), so "I have 75
+            // banked" is no longer a reason to summon -- an AI that spends on
+            // that test alone marches into insolvency and the pool tick disbands
+            // the creature it just bought, burning 75 mana per turn forever.
+            //
+            // MomMagicPerTurn[p] is last turn's NET (generation minus upkeep),
+            // so requiring it to stay &gt;= 0 after taking on this creature's keep
+            // is the whole check. When it fails the AI simply banks, and its
+            // production goes where it should -- city units, the mainstay.
+            if (MomMagicPerTurn[p] - pickRung * 2 &lt; 0) {
+                pick = 0;
+            }
             if (CityIsValid(tmpCity) &amp;&amp; pick != 0) {
                 MomMagicCur[p] = MomMagicCur[p] - 75;
                 // Reuses the human path's placement so an AI summon gets the
@@ -46388,7 +46887,7 @@
                 // would stack it under the garrison: CTP2 draws exactly one unit
                 // per tile and orders own units by MaxMovePoints, so a fast
                 // creature permanently hides whatever was standing there.
-                MomSpawnSphereUnit(p, pick);
+                MomSpawnSphereUnit(p, pick, pickRung);
             }
         } elseif (MomMagicCur[p] &gt;= 50 &amp;&amp; atWar == 1 &amp;&amp; roll &lt; 40) {
             // A cheap working while it cannot yet afford a creature. Modelled as
@@ -46408,7 +46907,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5561</v>
+        <v>6706</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
@@ -46457,6 +46956,7 @@
 HandleEvent(BeginTurn) 'MomAiMagicTick' post {
     int_t p;
     int_t pick;
+    int_t pickRung;
     int_t roll;
     int_t atWar;
     int_t i;
@@ -46491,6 +46991,22 @@
             // identically.
             GetCityByIndex(player[0], 0, tmpCity);
             pick = MomSummonRoll(p);
+            // See the note above the spawn: resolved into a local, never nested
+            // into an argument position.
+            pickRung = MomSummonRungOf(pick);
+            // SUSTAINABILITY, not just affordability (2026-08-01). Creatures now
+            // cost mana every turn they live (mom_magic.slc), so "I have 75
+            // banked" is no longer a reason to summon -- an AI that spends on
+            // that test alone marches into insolvency and the pool tick disbands
+            // the creature it just bought, burning 75 mana per turn forever.
+            //
+            // MomMagicPerTurn[p] is last turn's NET (generation minus upkeep),
+            // so requiring it to stay &gt;= 0 after taking on this creature's keep
+            // is the whole check. When it fails the AI simply banks, and its
+            // production goes where it should -- city units, the mainstay.
+            if (MomMagicPerTurn[p] - pickRung * 2 &lt; 0) {
+                pick = 0;
+            }
             if (CityIsValid(tmpCity) &amp;&amp; pick != 0) {
                 MomMagicCur[p] = MomMagicCur[p] - 75;
                 // Reuses the human path's placement so an AI summon gets the
@@ -46498,7 +47014,7 @@
                 // would stack it under the garrison: CTP2 draws exactly one unit
                 // per tile and orders own units by MaxMovePoints, so a fast
                 // creature permanently hides whatever was standing there.
-                MomSpawnSphereUnit(p, pick);
+                MomSpawnSphereUnit(p, pick, pickRung);
             }
         } elseif (MomMagicCur[p] &gt;= 50 &amp;&amp; atWar == 1 &amp;&amp; roll &lt; 40) {
             // A cheap working while it cannot yet afford a creature. Modelled as
@@ -46983,7 +47499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -47686,7 +48202,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p_13, int_t unitType)</t>
+          <t>void_f(int_t p_13, int_t unitType, int_t rung)</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -47915,32 +48431,28 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>mom_msg.slc</t>
+          <t>mom_summon.slc</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>MomSphereBlessingMessages</t>
+          <t>MomSummonRungOf</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
-        </is>
-      </c>
+          <t>int_f(int_t unitType)</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>?</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -47950,7 +48462,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -47967,17 +48479,17 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>MomSummonOrderTick</t>
+          <t>MomSphereBlessingMessages</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>spawn the creature ordered last turn, resolved from the CASTER'S OWN sphere; debits 75 mana</t>
+          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -47992,7 +48504,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -48004,22 +48516,22 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>MomMsgSlicAlive</t>
+          <t>MomSummonOrderTick</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>segment: SLIC liveness confirmation text</t>
+          <t>spawn the creature ordered last turn, resolved from the CASTER'S OWN sphere; debits 75 mana</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -48051,7 +48563,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>MomBlessLife</t>
+          <t>MomMsgSlicAlive</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -48061,7 +48573,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>segment: Life sphere blessing popup</t>
+          <t>segment: SLIC liveness confirmation text</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -48076,7 +48588,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -48093,7 +48605,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>MomBlessNature</t>
+          <t>MomBlessLife</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -48103,7 +48615,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>segment: Nature sphere blessing popup</t>
+          <t>segment: Life sphere blessing popup</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -48118,7 +48630,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -48135,7 +48647,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>MomBlessSorcery</t>
+          <t>MomBlessNature</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -48145,7 +48657,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>segment: Sorcery sphere blessing popup</t>
+          <t>segment: Nature sphere blessing popup</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -48160,7 +48672,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>sorcery</t>
+          <t>nature</t>
         </is>
       </c>
     </row>
@@ -48177,7 +48689,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>MomBlessDeath</t>
+          <t>MomBlessSorcery</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -48187,7 +48699,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>segment: Death sphere blessing popup</t>
+          <t>segment: Sorcery sphere blessing popup</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -48202,7 +48714,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>sorcery</t>
         </is>
       </c>
     </row>
@@ -48219,7 +48731,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>MomBlessChaos</t>
+          <t>MomBlessDeath</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -48229,7 +48741,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>segment: Chaos sphere blessing popup</t>
+          <t>segment: Death sphere blessing popup</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -48244,7 +48756,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -48261,7 +48773,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>MomSummonGuard</t>
+          <t>MomBlessChaos</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -48271,7 +48783,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
+          <t>segment: Chaos sphere blessing popup</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -48286,7 +48798,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -48303,7 +48815,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>MomSummonBear</t>
+          <t>MomUpkeepDisband</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -48311,11 +48823,7 @@
           <t>messagebox</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>segment: Nature summon result (War Bear)</t>
-        </is>
-      </c>
+      <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
           <t>C</t>
@@ -48345,7 +48853,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>MomSummonMage</t>
+          <t>MomSummonGuard</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -48355,7 +48863,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>segment: Sorcery summon result (Mage)</t>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -48387,7 +48895,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>MomSummonZombie</t>
+          <t>MomSummonBear</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -48397,7 +48905,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>segment: Death summon result (Zombies)</t>
+          <t>segment: Nature summon result (War Bear)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -48429,7 +48937,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>MomSummonHound</t>
+          <t>MomSummonMage</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -48439,7 +48947,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>segment: Chaos summon result (Hell Hound)</t>
+          <t>segment: Sorcery summon result (Mage)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -48471,7 +48979,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>MomSummonNoMana</t>
+          <t>MomSummonZombie</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -48481,7 +48989,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+          <t>segment: Death summon result (Zombies)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -48513,7 +49021,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>MomMagicPower</t>
+          <t>MomSummonHound</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -48523,7 +49031,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>segment: mana pool / income readout body</t>
+          <t>segment: Chaos summon result (Hell Hound)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -48550,22 +49058,22 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>MagicMenu</t>
+          <t>MomSummonNoMana</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -48587,32 +49095,32 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>MomRecalcMagicPerTurn</t>
+          <t>MomMagicPower</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t mp_1)</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
+          <t>segment: mana pool / income readout body</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -48629,32 +49137,32 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>MomMagicPoolTick</t>
+          <t>MagicMenu</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -48676,22 +49184,22 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>MomMagicSchoolGrant</t>
+          <t>MomRecalcMagicPerTurn</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
+          <t>int_f(int_t mp_1)</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>apply per-school mana multipliers when a magic advance is granted</t>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -48706,34 +49214,34 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>MomCastFlameStrike</t>
+          <t>MomMagicPoolTick</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
+          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -48755,27 +49263,27 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>MomCastDemonStrike</t>
+          <t>MomMagicSchoolGrant</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -48790,7 +49298,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -48807,7 +49315,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>MomSpellShowBook</t>
+          <t>MomCastFlameStrike</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -48817,7 +49325,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -48832,7 +49340,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -48844,22 +49352,22 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>MomSpellMenuTick</t>
+          <t>MomCastDemonStrike</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -48874,7 +49382,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -48886,22 +49394,22 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>MomOpenSpellbook</t>
+          <t>MomSpellShowBook</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>UI trigger bound to the control-panel MagicButton</t>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -48916,7 +49424,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -48933,7 +49441,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>MomSpellAICast</t>
+          <t>MomSpellMenuTick</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -48943,7 +49451,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>let AI players cast their sphere's spell when mana allows</t>
+          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -48970,22 +49478,22 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>MomMsgSpellbook</t>
+          <t>MomOpenSpellbook</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>segment: generic spellbook menu</t>
+          <t>UI trigger bound to the control-panel MagicButton</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -49012,22 +49520,22 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>MomMsgSpellbookChaos</t>
+          <t>MomSpellAICast</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>segment: Chaos-specific spellbook menu</t>
+          <t>let AI players cast their sphere's spell when mana allows</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -49042,7 +49550,7 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -49059,7 +49567,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>MomMsgDemonCast</t>
+          <t>MomMsgSpellbook</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -49069,7 +49577,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>segment: Demon Strike cast confirmation</t>
+          <t>segment: generic spellbook menu</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -49101,7 +49609,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>MomMsgFlameCast</t>
+          <t>MomMsgSpellbookChaos</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -49111,7 +49619,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>segment: Flame Strike cast confirmation</t>
+          <t>segment: Chaos-specific spellbook menu</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -49126,7 +49634,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -49143,7 +49651,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNoTarget</t>
+          <t>MomMsgDemonCast</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -49153,7 +49661,7 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>segment: no enemy unit in range</t>
+          <t>segment: Demon Strike cast confirmation</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -49185,7 +49693,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNoMana</t>
+          <t>MomMsgFlameCast</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -49195,7 +49703,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+          <t>segment: Flame Strike cast confirmation</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -49227,7 +49735,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNotChaos</t>
+          <t>MomMsgNoTarget</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -49237,7 +49745,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>segment: caster's sphere does not grant this spell</t>
+          <t>segment: no enemy unit in range</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -49252,35 +49760,39 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>mom_ai_magic.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>MomAiMagicTick</t>
+          <t>MomMsgNoMana</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr"/>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+        </is>
+      </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -49297,32 +49809,32 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>mod_CanPlayerHaveAdvance</t>
+          <t>MomMsgNotChaos</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
+          <t>segment: caster's sphere does not grant this spell</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -49332,36 +49844,32 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_ai_magic.slc</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildUnit</t>
+          <t>MomAiMagicTick</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theUnit)</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
-        </is>
-      </c>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr"/>
       <c r="F57" s="5" t="inlineStr">
         <is>
           <t>?</t>
@@ -49391,17 +49899,17 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildBuilding</t>
+          <t>mod_CanPlayerHaveAdvance</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theBuilding)</t>
+          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -49416,7 +49924,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -49433,37 +49941,121 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
+          <t>mod_CanCityBuildUnit</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theUnit)</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>mod_CanCityBuildBuilding</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theBuilding)</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
           <t>mod_CanCityBuildWonder</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>int_f(city_t theCity, int_t theWonder)</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>same wall for wonders.</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H59"/>
+  <autoFilter ref="A1:H61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -71,7 +71,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improvements'!$A$1:$H$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'order_mask'!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'players'!$A$1:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'sprite_pick_rules'!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'terrain'!$A$1:$J$27</definedName>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E36" t="n">
         <v>8</v>
@@ -23544,7 +23544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24898,7 +24898,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MomSummonGuard</t>
+          <t>MomSummonBegun</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -24906,11 +24906,7 @@
           <t>messagebox</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>C</t>
@@ -24940,7 +24936,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MomSummonBear</t>
+          <t>MomSummonBusy</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -24948,11 +24944,7 @@
           <t>messagebox</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>segment: Nature summon result (War Bear)</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>C</t>
@@ -24982,7 +24974,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MomSummonMage</t>
+          <t>MomSummonGuard</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -24992,7 +24984,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>segment: Sorcery summon result (Mage)</t>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -25024,7 +25016,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MomSummonZombie</t>
+          <t>MomSummonBear</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -25034,7 +25026,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>segment: Death summon result (Zombies)</t>
+          <t>segment: Nature summon result (War Bear)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -25066,7 +25058,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MomSummonHound</t>
+          <t>MomSummonMage</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -25076,7 +25068,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>segment: Chaos summon result (Hell Hound)</t>
+          <t>segment: Sorcery summon result (Mage)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -25108,7 +25100,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MomSummonNoMana</t>
+          <t>MomSummonZombie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -25118,7 +25110,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+          <t>segment: Death summon result (Zombies)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -25150,7 +25142,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MomMagicPower</t>
+          <t>MomSummonHound</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -25160,7 +25152,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>segment: mana pool / income readout body</t>
+          <t>segment: Chaos summon result (Hell Hound)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -25187,22 +25179,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MagicMenu</t>
+          <t>MomSummonNoMana</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -25224,32 +25216,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MomRecalcMagicPerTurn</t>
+          <t>MomMagicPower</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>int_f(int_t mp_1)</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
+          <t>segment: mana pool / income readout body</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -25266,32 +25258,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MomMagicPoolTick</t>
+          <t>MagicMenu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -25313,22 +25305,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MomMagicSchoolGrant</t>
+          <t>MomRecalcMagicPerTurn</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
+          <t>int_f(int_t mp_1)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>apply per-school mana multipliers when a magic advance is granted</t>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -25343,34 +25335,34 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MomCastFlameStrike</t>
+          <t>MomMagicPoolTick</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
+          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -25392,27 +25384,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MomCastDemonStrike</t>
+          <t>MomMagicSchoolGrant</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -25427,7 +25419,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -25444,7 +25436,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MomSpellShowBook</t>
+          <t>MomCastFlameStrike</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -25454,7 +25446,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -25469,7 +25461,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25481,22 +25473,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MomSpellMenuTick</t>
+          <t>MomCastDemonStrike</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -25511,7 +25503,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -25523,22 +25515,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MomOpenSpellbook</t>
+          <t>MomSpellShowBook</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UI trigger bound to the control-panel MagicButton</t>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -25553,7 +25545,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -25570,7 +25562,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MomSpellAICast</t>
+          <t>MomSpellMenuTick</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -25580,7 +25572,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>let AI players cast their sphere's spell when mana allows</t>
+          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -25607,22 +25599,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MomMsgSpellbook</t>
+          <t>MomOpenSpellbook</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>segment: generic spellbook menu</t>
+          <t>UI trigger bound to the control-panel MagicButton</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -25649,22 +25641,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MomMsgSpellbookChaos</t>
+          <t>MomSpellAICast</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>segment: Chaos-specific spellbook menu</t>
+          <t>let AI players cast their sphere's spell when mana allows</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -25679,7 +25671,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25688,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MomMsgDemonCast</t>
+          <t>MomMsgSpellbook</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -25706,7 +25698,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>segment: Demon Strike cast confirmation</t>
+          <t>segment: generic spellbook menu</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -25738,7 +25730,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MomMsgFlameCast</t>
+          <t>MomMsgSpellbookChaos</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -25748,7 +25740,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>segment: Flame Strike cast confirmation</t>
+          <t>segment: Chaos-specific spellbook menu</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -25763,7 +25755,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -25780,7 +25772,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MomMsgNoTarget</t>
+          <t>MomMsgDemonCast</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -25790,7 +25782,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>segment: no enemy unit in range</t>
+          <t>segment: Demon Strike cast confirmation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -25822,7 +25814,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MomMsgNoMana</t>
+          <t>MomMsgFlameCast</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -25832,7 +25824,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+          <t>segment: Flame Strike cast confirmation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -25864,7 +25856,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MomMsgNotChaos</t>
+          <t>MomMsgNoTarget</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -25874,7 +25866,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>segment: caster's sphere does not grant this spell</t>
+          <t>segment: no enemy unit in range</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -25889,35 +25881,39 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>mom_ai_magic.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MomAiMagicTick</t>
+          <t>MomMsgNoMana</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -25934,32 +25930,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mod_CanPlayerHaveAdvance</t>
+          <t>MomMsgNotChaos</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
+          <t>segment: caster's sphere does not grant this spell</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -25969,36 +25965,32 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_ai_magic.slc</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildUnit</t>
+          <t>MomAiMagicTick</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theUnit)</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
-        </is>
-      </c>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>?</t>
@@ -26028,17 +26020,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildBuilding</t>
+          <t>mod_CanPlayerHaveAdvance</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theBuilding)</t>
+          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -26053,7 +26045,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -26070,37 +26062,121 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>mod_CanCityBuildUnit</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theUnit)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>mod_CanCityBuildBuilding</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theBuilding)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>mod_CanCityBuildWonder</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>int_f(city_t theCity, int_t theWonder)</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>same wall for wonders.</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H61"/>
+  <autoFilter ref="A1:H63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -47305,11 +47305,23 @@
                 MomSummonPending[p] = pick;
                 MomSummonPrep[p] = MomSummonPendRung[p];
             }
-        } elseif (MomMagicCur[p] &gt;= 50 &amp;&amp; atWar == 1 &amp;&amp; roll &lt; 40) {
-            // A cheap working while it cannot yet afford a creature. Modelled as
-            // a war chest rather than a spell effect: the spell bodies in
-            // mom_spells.slc are button-driven and reaching them from here would
-            // be the 2-level chain this file is careful to avoid.
+        } elseif (MomMagicCur[p] &gt;= 50 &amp;&amp; atWar == 1 &amp;&amp; roll &lt; 40
+                  &amp;&amp; MomMagicPerTurn[p] - MomUpkeepRate &lt; 0) {
+            // A cheap working, and ONLY when a creature is out of reach anyway.
+            //
+            // THE STARVATION BUG THIS GUARD CLOSES (measured 2026-08-01). The
+            // working costs 50 and a summon costs 75, so an AI at war drained
+            // its pool at 50 every time it got the chance and COULD NEVER SAVE
+            // TO 75. Magic was structurally unreachable for a warring tribe --
+            // Sorcery was observed at 26 mana on turn 12 with zero creatures and
+            // no preparation pending, having burned everything on gold. The
+            // cheaper option starving the more expensive one is the shape to
+            // watch for whenever two spends share a pool.
+            //
+            // The guard is sustainability, the same test the summon uses: if the
+            // tribe could not feed even a rung-1 creature, magic-as-force is not
+            // available to it and converting power to gold is the right call.
+            // If it COULD feed one, it saves instead.
             MomMagicCur[p] = MomMagicCur[p] - 50;
             AddGold(p, 50 + Random(100));
         }
@@ -47323,7 +47335,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>7731</v>
+        <v>8520</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
@@ -47447,11 +47459,23 @@
                 MomSummonPending[p] = pick;
                 MomSummonPrep[p] = MomSummonPendRung[p];
             }
-        } elseif (MomMagicCur[p] &gt;= 50 &amp;&amp; atWar == 1 &amp;&amp; roll &lt; 40) {
-            // A cheap working while it cannot yet afford a creature. Modelled as
-            // a war chest rather than a spell effect: the spell bodies in
-            // mom_spells.slc are button-driven and reaching them from here would
-            // be the 2-level chain this file is careful to avoid.
+        } elseif (MomMagicCur[p] &gt;= 50 &amp;&amp; atWar == 1 &amp;&amp; roll &lt; 40
+                  &amp;&amp; MomMagicPerTurn[p] - MomUpkeepRate &lt; 0) {
+            // A cheap working, and ONLY when a creature is out of reach anyway.
+            //
+            // THE STARVATION BUG THIS GUARD CLOSES (measured 2026-08-01). The
+            // working costs 50 and a summon costs 75, so an AI at war drained
+            // its pool at 50 every time it got the chance and COULD NEVER SAVE
+            // TO 75. Magic was structurally unreachable for a warring tribe --
+            // Sorcery was observed at 26 mana on turn 12 with zero creatures and
+            // no preparation pending, having burned everything on gold. The
+            // cheaper option starving the more expensive one is the shape to
+            // watch for whenever two spends share a pool.
+            //
+            // The guard is sustainability, the same test the summon uses: if the
+            // tribe could not feed even a rung-1 creature, magic-as-force is not
+            // available to it and converting power to gold is the right call.
+            // If it COULD feed one, it saves instead.
             MomMagicCur[p] = MomMagicCur[p] - 50;
             AddGold(p, 50 + Random(100));
         }

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -73,7 +73,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improvements'!$A$1:$H$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'order_mask'!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'players'!$A$1:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'sprite_pick_rules'!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'terrain'!$A$1:$J$27</definedName>
@@ -86,7 +86,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'slic'!$A$1:$L$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E36" t="n">
         <v>8</v>
@@ -21597,6 +21597,11 @@
           <t>Ariel</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>mom_tribe</t>
@@ -21666,7 +21671,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Freya</t>
+          <t>Raven</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -21736,6 +21741,11 @@
           <t>Jafar</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Zarah</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>mom_tribe</t>
@@ -21803,6 +21813,11 @@
           <t>Rjak</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Kali</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>mom_tribe</t>
@@ -21868,6 +21883,11 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>Tauron</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ignara</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -23039,7 +23059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24463,17 +24483,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MomSummonGuard</t>
+          <t>MomSummonNoMagic</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>messagebox</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -24505,7 +24520,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MomSummonBear</t>
+          <t>MomSummonGuard</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -24515,7 +24530,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>segment: Nature summon result (War Bear)</t>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -24547,7 +24562,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MomSummonMage</t>
+          <t>MomSummonBear</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -24557,7 +24572,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>segment: Sorcery summon result (Mage)</t>
+          <t>segment: Nature summon result (War Bear)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -24589,7 +24604,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MomSummonZombie</t>
+          <t>MomSummonMage</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -24599,7 +24614,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>segment: Death summon result (Zombies)</t>
+          <t>segment: Sorcery summon result (Mage)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -24631,7 +24646,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MomSummonHound</t>
+          <t>MomSummonZombie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -24641,7 +24656,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>segment: Chaos summon result (Hell Hound)</t>
+          <t>segment: Death summon result (Zombies)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -24673,7 +24688,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MomSummonNoMana</t>
+          <t>MomSummonHound</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -24683,7 +24698,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+          <t>segment: Chaos summon result (Hell Hound)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -24715,7 +24730,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MomMagicPower</t>
+          <t>MomSummonNoMana</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -24725,7 +24740,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>segment: mana pool / income readout body</t>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -24752,22 +24767,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MagicMenu</t>
+          <t>MomMagicPower</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+          <t>segment: mana pool / income readout body</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -24789,32 +24804,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MomRecalcMagicPerTurn</t>
+          <t>MagicMenu</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>int_f(int_t mp_1)</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -24836,22 +24851,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MomMagicPoolTick</t>
+          <t>MomRecalcMagicPerTurn</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>int_f(int_t mp_1)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -24883,17 +24898,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MomMagicSchoolGrant</t>
+          <t>MomMagicPoolTick</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>apply per-school mana multipliers when a magic advance is granted</t>
+          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -24908,34 +24923,34 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MomCastFlameStrike</t>
+          <t>MomMagicSchoolGrant</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -24950,7 +24965,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -24967,7 +24982,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MomCastDemonStrike</t>
+          <t>MomCastFlameStrike</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -24977,7 +24992,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
+          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -24992,7 +25007,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25009,7 +25024,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MomSpellShowBook</t>
+          <t>MomCastDemonStrike</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -25019,7 +25034,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -25046,22 +25061,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MomSpellMenuTick</t>
+          <t>MomSpellShowBook</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -25076,7 +25091,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -25088,22 +25103,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MomOpenSpellbook</t>
+          <t>MomSpellMenuTick</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UI trigger bound to the control-panel MagicButton</t>
+          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -25130,22 +25145,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MomSpellAICast</t>
+          <t>MomOpenSpellbook</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>let AI players cast their sphere's spell when mana allows</t>
+          <t>UI trigger bound to the control-panel MagicButton</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -25172,22 +25187,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MomMsgSpellbook</t>
+          <t>MomSpellAICast</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>segment: generic spellbook menu</t>
+          <t>let AI players cast their sphere's spell when mana allows</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -25219,7 +25234,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MomMsgSpellbookChaos</t>
+          <t>MomMsgSpellbook</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -25229,7 +25244,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>segment: Chaos-specific spellbook menu</t>
+          <t>segment: generic spellbook menu</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -25244,7 +25259,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25261,7 +25276,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MomMsgDemonCast</t>
+          <t>MomMsgSpellbookChaos</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -25271,7 +25286,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>segment: Demon Strike cast confirmation</t>
+          <t>segment: Chaos-specific spellbook menu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -25286,7 +25301,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -25303,7 +25318,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MomMsgFlameCast</t>
+          <t>MomMsgDemonCast</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -25313,7 +25328,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>segment: Flame Strike cast confirmation</t>
+          <t>segment: Demon Strike cast confirmation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -25345,7 +25360,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MomMsgNoTarget</t>
+          <t>MomMsgFlameCast</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -25355,7 +25370,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>segment: no enemy unit in range</t>
+          <t>segment: Flame Strike cast confirmation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -25387,7 +25402,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MomMsgNoMana</t>
+          <t>MomMsgNoTarget</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -25397,7 +25412,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+          <t>segment: no enemy unit in range</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -25429,7 +25444,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MomMsgNotChaos</t>
+          <t>MomMsgNoMana</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -25439,7 +25454,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>segment: caster's sphere does not grant this spell</t>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -25454,34 +25469,39 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>mom_ai_magic.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MomAiMagicTick</t>
+          <t>MomMsgNotChaos</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>segment: caster's sphere does not grant this spell</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -25491,34 +25511,29 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_ai_magic.slc</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mod_CanPlayerHaveAdvance</t>
+          <t>MomAiMagicTick</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -25533,7 +25548,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25550,17 +25565,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildUnit</t>
+          <t>mod_CanPlayerHaveAdvance</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theUnit)</t>
+          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -25575,7 +25590,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -25592,17 +25607,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildBuilding</t>
+          <t>mod_CanCityBuildUnit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theBuilding)</t>
+          <t>int_f(city_t theCity, int_t theUnit)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -25634,37 +25649,79 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>mod_CanCityBuildBuilding</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theBuilding)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>mod_CanCityBuildWonder</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>int_f(city_t theCity, int_t theWonder)</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>same wall for wonders.</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H63"/>
+  <autoFilter ref="A1:H64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44571,13 +44628,27 @@
     int_t r;
     int_t roll;
     r = MomSphereRung[p];
-    // FLOOR AT 1. MomSphereRungTick only sees advances GRANTED during play,
-    // so a tribe that starts the scenario already holding its sphere root
-    // never fires it and would sit at 0 forever -- and rung 0 owns no
-    // creature, so its summon would silently do nothing while still looking
-    // affordable. The floor makes the opening pool reachable no matter how
-    // the root was acquired.
-    if (r &lt; 1) { r = 1; }
+    // NO FLOOR. Rung 0 means 'this tribe has learned no magic of its own
+    // sphere', and it must fall through every band below so this function
+    // returns 0 -- which every caller already reads as 'no summon' and
+    // which leaves the pool undebited (mom_msg.slc gates the 75 on
+    // summonPick != 0, mom_ai_magic.slc on pick != 0).
+    //
+    // A `if (r &lt; 1) { r = 1; }` FLOOR LIVED HERE from v3.2.0 until
+    // 2026-08-02 and was the whole reason a tribe's army was creatures it
+    // could never have built. A Warbears costs 1970 science to BUILD
+    // (ADVANCE_NATURE_LORE) and, with the floor, 0 science to SUMMON: every
+    // tribe had rung-1 summoning from turn one and the summon path skipped
+    // the tech tree entirely.
+    //
+    // The floor was justified as 'a tribe that starts holding its sphere
+    // root never fires the GrantAdvance that would raise it off 0'. That
+    // premise is FALSE in this scenario -- nothing anywhere grants a
+    // *_MAGIC or *_LORE advance and there is no starting-advance mechanism,
+    // so no tribe ever starts holding its root. It guarded a case that does
+    // not exist and cost a whole tech gate. Do not restore it; if a
+    // starting-advance mechanism is ever added, seed MomSphereRung[] there
+    // rather than flooring here (gate_mana_upkeep.py assertion 12).
     roll = Random(100);
     // LIFE (player 1)
     if (p == 1) {
@@ -44796,7 +44867,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>12625</v>
+        <v>13535</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
@@ -44874,13 +44945,27 @@
     int_t r;
     int_t roll;
     r = MomSphereRung[p];
-    // FLOOR AT 1. MomSphereRungTick only sees advances GRANTED during play,
-    // so a tribe that starts the scenario already holding its sphere root
-    // never fires it and would sit at 0 forever -- and rung 0 owns no
-    // creature, so its summon would silently do nothing while still looking
-    // affordable. The floor makes the opening pool reachable no matter how
-    // the root was acquired.
-    if (r &lt; 1) { r = 1; }
+    // NO FLOOR. Rung 0 means 'this tribe has learned no magic of its own
+    // sphere', and it must fall through every band below so this function
+    // returns 0 -- which every caller already reads as 'no summon' and
+    // which leaves the pool undebited (mom_msg.slc gates the 75 on
+    // summonPick != 0, mom_ai_magic.slc on pick != 0).
+    //
+    // A `if (r &lt; 1) { r = 1; }` FLOOR LIVED HERE from v3.2.0 until
+    // 2026-08-02 and was the whole reason a tribe's army was creatures it
+    // could never have built. A Warbears costs 1970 science to BUILD
+    // (ADVANCE_NATURE_LORE) and, with the floor, 0 science to SUMMON: every
+    // tribe had rung-1 summoning from turn one and the summon path skipped
+    // the tech tree entirely.
+    //
+    // The floor was justified as 'a tribe that starts holding its sphere
+    // root never fires the GrantAdvance that would raise it off 0'. That
+    // premise is FALSE in this scenario -- nothing anywhere grants a
+    // *_MAGIC or *_LORE advance and there is no starting-advance mechanism,
+    // so no tribe ever starts holding its root. It guarded a case that does
+    // not exist and cost a whole tech gate. Do not restore it; if a
+    // starting-advance mechanism is ever added, seed MomSphereRung[] there
+    // rather than flooring here (gate_mana_upkeep.py assertion 12).
     roll = Random(100);
     // LIFE (player 1)
     if (p == 1) {
@@ -45289,6 +45374,10 @@
 	Show();
 	Text(ID_MOM_MSG_SUMMON_BUSY);
 }
+messagebox 'MomSummonNoMagic' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_NOMAGIC);
+}
 messagebox 'MomSummonGuard' {
 	Show();
 	Text(ID_MOM_MSG_SUMMON_GUARD);
@@ -45385,7 +45474,15 @@
 	// resolve time). Still comparisons and Message(), both builtins, so the body
 	// remains at call depth 0 and the Class 1 budget is untouched.
 	Button(ID_MOM_MSG_BTN_SUMMON) {
-		if (MomSummonPrep[g.player] &gt; 0) {
+		// NO MAGIC LEARNED comes FIRST, ahead of both other refusals. With the
+		// rung floor gone (2026-08-02) a tribe that has not researched its
+		// sphere's MAGIC advance genuinely cannot summon -- MomSummonRoll
+		// returns 0 for rung 0 -- and without this branch the arm would take
+		// the click, place an order, and resolve into nothing. Silence is the
+		// one outcome a button must never produce.
+		if (MomSphereRung[g.player] &lt; 1) {
+			Message(g.player, 'MomSummonNoMagic');
+		} elseif (MomSummonPrep[g.player] &gt; 0) {
 			Message(g.player, 'MomSummonBusy');
 		} elseif (MomMagicCur[g.player] &gt;= 75) {
 			MomSummonChoice[g.player] = 1;
@@ -45407,10 +45504,10 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>21780</v>
+        <v>22360</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
@@ -45690,6 +45787,10 @@
 	Show();
 	Text(ID_MOM_MSG_SUMMON_BUSY);
 }
+messagebox 'MomSummonNoMagic' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_NOMAGIC);
+}
 messagebox 'MomSummonGuard' {
 	Show();
 	Text(ID_MOM_MSG_SUMMON_GUARD);
@@ -45786,7 +45887,15 @@
 	// resolve time). Still comparisons and Message(), both builtins, so the body
 	// remains at call depth 0 and the Class 1 budget is untouched.
 	Button(ID_MOM_MSG_BTN_SUMMON) {
-		if (MomSummonPrep[g.player] &gt; 0) {
+		// NO MAGIC LEARNED comes FIRST, ahead of both other refusals. With the
+		// rung floor gone (2026-08-02) a tribe that has not researched its
+		// sphere's MAGIC advance genuinely cannot summon -- MomSummonRoll
+		// returns 0 for rung 0 -- and without this branch the arm would take
+		// the click, place an order, and resolve into nothing. Silence is the
+		// one outcome a button must never produce.
+		if (MomSphereRung[g.player] &lt; 1) {
+			Message(g.player, 'MomSummonNoMagic');
+		} elseif (MomSummonPrep[g.player] &gt; 0) {
 			Message(g.player, 'MomSummonBusy');
 		} elseif (MomMagicCur[g.player] &gt;= 75) {
 			MomSummonChoice[g.player] = 1;
@@ -46091,13 +46200,14 @@
             // Income/Upkeep/Net lines fail to add up. MomRecalcMagicPerTurn
             // is the sole writer of all three.
             // The rung decides WHICH creatures the 75-mana summon can roll
-            // (mom_summon.slc). Floored at 1 for the same reason MomSummonRoll
-            // floors it: a tribe that starts holding its sphere root never fires
-            // the GrantAdvance that would raise it off 0.
+            // (mom_summon.slc). REPORTED HONESTLY, including 0.
+            //
+            // This used to be floored at 1 to match MomSummonRoll's floor. Both
+            // floors went on 2026-08-02: rung 0 means the tribe has learned no
+            // magic of its own sphere and genuinely cannot summon, so a panel
+            // claiming "rung 1 of 5" while every summon silently fails was
+            // reporting a capability that did not exist.
             MomRungDisp = MomSphereRung[p];
-            if (MomRungDisp &lt; 1) {
-                MomRungDisp = 1;
-            }
         }
         // Periodic popup every 10 rounds: REMOVED 2026-07-25, redundant and harmful.
         //
@@ -46169,7 +46279,7 @@
         <v>3</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>18119</v>
+        <v>18271</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
@@ -46442,13 +46552,14 @@
             // Income/Upkeep/Net lines fail to add up. MomRecalcMagicPerTurn
             // is the sole writer of all three.
             // The rung decides WHICH creatures the 75-mana summon can roll
-            // (mom_summon.slc). Floored at 1 for the same reason MomSummonRoll
-            // floors it: a tribe that starts holding its sphere root never fires
-            // the GrantAdvance that would raise it off 0.
+            // (mom_summon.slc). REPORTED HONESTLY, including 0.
+            //
+            // This used to be floored at 1 to match MomSummonRoll's floor. Both
+            // floors went on 2026-08-02: rung 0 means the tribe has learned no
+            // magic of its own sphere and genuinely cannot summon, so a panel
+            // claiming "rung 1 of 5" while every summon silently fails was
+            // reporting a capability that did not exist.
             MomRungDisp = MomSphereRung[p];
-            if (MomRungDisp &lt; 1) {
-                MomRungDisp = 1;
-            }
         }
         // Periodic popup every 10 rounds: REMOVED 2026-07-25, redundant and harmful.
         //
@@ -47954,7 +48065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -49384,7 +49495,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>MomSummonGuard</t>
+          <t>MomSummonNoMagic</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -49392,11 +49503,7 @@
           <t>messagebox</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
-        </is>
-      </c>
+      <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="5" t="inlineStr">
         <is>
           <t>C</t>
@@ -49426,7 +49533,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>MomSummonBear</t>
+          <t>MomSummonGuard</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -49436,7 +49543,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>segment: Nature summon result (War Bear)</t>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -49468,7 +49575,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>MomSummonMage</t>
+          <t>MomSummonBear</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -49478,7 +49585,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>segment: Sorcery summon result (Mage)</t>
+          <t>segment: Nature summon result (War Bear)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -49510,7 +49617,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>MomSummonZombie</t>
+          <t>MomSummonMage</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -49520,7 +49627,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>segment: Death summon result (Zombies)</t>
+          <t>segment: Sorcery summon result (Mage)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -49552,7 +49659,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>MomSummonHound</t>
+          <t>MomSummonZombie</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -49562,7 +49669,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>segment: Chaos summon result (Hell Hound)</t>
+          <t>segment: Death summon result (Zombies)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -49594,7 +49701,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>MomSummonNoMana</t>
+          <t>MomSummonHound</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -49604,7 +49711,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+          <t>segment: Chaos summon result (Hell Hound)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -49636,7 +49743,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>MomMagicPower</t>
+          <t>MomSummonNoMana</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -49646,7 +49753,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>segment: mana pool / income readout body</t>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -49673,22 +49780,22 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>MagicMenu</t>
+          <t>MomMagicPower</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+          <t>segment: mana pool / income readout body</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -49710,32 +49817,32 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>MomRecalcMagicPerTurn</t>
+          <t>MagicMenu</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t mp_1)</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -49757,22 +49864,22 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>MomMagicPoolTick</t>
+          <t>MomRecalcMagicPerTurn</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>int_f(int_t mp_1)</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -49804,17 +49911,17 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>MomMagicSchoolGrant</t>
+          <t>MomMagicPoolTick</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>apply per-school mana multipliers when a magic advance is granted</t>
+          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -49829,34 +49936,34 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>MomCastFlameStrike</t>
+          <t>MomMagicSchoolGrant</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -49871,7 +49978,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -49888,7 +49995,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>MomCastDemonStrike</t>
+          <t>MomCastFlameStrike</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -49898,7 +50005,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
+          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -49913,7 +50020,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -49930,7 +50037,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>MomSpellShowBook</t>
+          <t>MomCastDemonStrike</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -49940,7 +50047,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -49967,22 +50074,22 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>MomSpellMenuTick</t>
+          <t>MomSpellShowBook</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -49997,7 +50104,7 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -50009,22 +50116,22 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>MomOpenSpellbook</t>
+          <t>MomSpellMenuTick</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>UI trigger bound to the control-panel MagicButton</t>
+          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -50051,22 +50158,22 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>MomSpellAICast</t>
+          <t>MomOpenSpellbook</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>let AI players cast their sphere's spell when mana allows</t>
+          <t>UI trigger bound to the control-panel MagicButton</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -50093,22 +50200,22 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>MomMsgSpellbook</t>
+          <t>MomSpellAICast</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>segment: generic spellbook menu</t>
+          <t>let AI players cast their sphere's spell when mana allows</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -50140,7 +50247,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>MomMsgSpellbookChaos</t>
+          <t>MomMsgSpellbook</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -50150,7 +50257,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>segment: Chaos-specific spellbook menu</t>
+          <t>segment: generic spellbook menu</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -50165,7 +50272,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -50182,7 +50289,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>MomMsgDemonCast</t>
+          <t>MomMsgSpellbookChaos</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -50192,7 +50299,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>segment: Demon Strike cast confirmation</t>
+          <t>segment: Chaos-specific spellbook menu</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -50207,7 +50314,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -50224,7 +50331,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>MomMsgFlameCast</t>
+          <t>MomMsgDemonCast</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -50234,7 +50341,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>segment: Flame Strike cast confirmation</t>
+          <t>segment: Demon Strike cast confirmation</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -50266,7 +50373,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNoTarget</t>
+          <t>MomMsgFlameCast</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -50276,7 +50383,7 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>segment: no enemy unit in range</t>
+          <t>segment: Flame Strike cast confirmation</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -50308,7 +50415,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNoMana</t>
+          <t>MomMsgNoTarget</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -50318,7 +50425,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+          <t>segment: no enemy unit in range</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -50350,7 +50457,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNotChaos</t>
+          <t>MomMsgNoMana</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -50360,7 +50467,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>segment: caster's sphere does not grant this spell</t>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -50375,35 +50482,39 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>mom_ai_magic.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>MomAiMagicTick</t>
+          <t>MomMsgNotChaos</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr"/>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>segment: caster's sphere does not grant this spell</t>
+        </is>
+      </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -50413,36 +50524,32 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_ai_magic.slc</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>mod_CanPlayerHaveAdvance</t>
+          <t>MomAiMagicTick</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
-        </is>
-      </c>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="5" t="inlineStr">
         <is>
           <t>?</t>
@@ -50455,7 +50562,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -50472,17 +50579,17 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildUnit</t>
+          <t>mod_CanPlayerHaveAdvance</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theUnit)</t>
+          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -50497,7 +50604,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -50514,17 +50621,17 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildBuilding</t>
+          <t>mod_CanCityBuildUnit</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theBuilding)</t>
+          <t>int_f(city_t theCity, int_t theUnit)</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -50556,37 +50663,79 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
+          <t>mod_CanCityBuildBuilding</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theBuilding)</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
           <t>mod_CanCityBuildWonder</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>int_f(city_t theCity, int_t theWonder)</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>same wall for wonders.</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H63"/>
+  <autoFilter ref="A1:H64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -43650,6 +43650,7 @@
 int_t MomSummonPending[31];  // the rolled unit type awaiting arrival
 int_t MomSummonPendRung[31]; // its rung, carried so arrival can ledger upkeep
 int_t MomPrepDisp;           // countdown scalar for the 'j' panel
+int_t MomSummonCostDisp;     // price the summon arm quotes: 45 + 30*rung.
 int_t MomMagicShownTurn[31]; // per-round re-entry latch for the popup (flood safety)
 int_t MomMagicSchoolPct[31]; // per-turn multiplier as integer percent (M2); 0 read as 100</t>
         </is>
@@ -43942,7 +43943,7 @@
         <v>16</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>16924</v>
+        <v>17666</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
@@ -44325,6 +44326,10 @@
 int_t MomSummonPending[31];  // the rolled unit type awaiting arrival
 int_t MomSummonPendRung[31]; // its rung, carried so arrival can ledger upkeep
 int_t MomPrepDisp;           // countdown scalar for the 'j' panel
+int_t MomSummonCostDisp;     // price the summon arm quotes: 45 + 30*rung.
+                             // A scalar, not an array -- an undeclared scalar is
+                             // silently auto-created and would read a permanent 0,
+                             // so the arm would advertise 'Summon Creature (0)'.
 int_t MomMagicShownTurn[31]; // per-round re-entry latch for the popup (flood safety)
 int_t MomMagicSchoolPct[31]; // per-turn multiplier as integer percent (M2); 0 read as 100</t>
         </is>
@@ -45225,28 +45230,52 @@
     // this negative. The check is a plain comparison at call depth 0.
     // COMMIT. An order only starts a preparation when nothing is already
     // preparing -- one at a time, so this is a plan and not a queue.
+    // PRICE SCALES WITH RUNG: 45 + 30*rung -&gt; 75 / 105 / 135 / 165 / 195.
+    //
+    // It was a FLAT 75 for everything, which priced a 150-shield Phantom
+    // Warriors and a 4000-shield Storm Drake identically -- a 27x swing in what
+    // the same coin bought. Upkeep already scaled (rung * MomUpkeepRate) since
+    // v3.5.0, so acquisition was the missing half of that system, and the gap
+    // pushed play the wrong way: summoning was poor value at rung 1 and absurd
+    // value at rung 5.
+    //
+    // THE CEILING IS 195 AND IT IS NOT ARBITRARY. MomMagicSchoolGrant caps the
+    // pool per sphere at Life 200 / Nature 220 / Sorcery 260 / Chaos 300. A
+    // curve topping above 200 would make rung 5 literally unaffordable for Life
+    // -- its pool cannot hold the price -- so 195 is the largest step that keeps
+    // every sphere able to reach its own best creature.
+    //
+    // THE GATE USES THE LADDER RUNG, THE DEBIT USES THE ROLLED RUNG. The roll
+    // can return any creature at or below the caster's rung, so requiring
+    // 45+30*MomSphereRung up front means whatever comes back is affordable and
+    // a click can never be consumed by a summon that cannot be paid for. You
+    // then pay for what you actually got, not for what you might have got.
     if (p &gt;= 1 &amp;&amp; p &lt;= 5 &amp;&amp; MomSummonChoice[p] != 0 &amp;&amp; MomSummonPrep[p] == 0
-        &amp;&amp; player[0].cities &gt; 0 &amp;&amp; MomMagicCur[p] &gt;= 75) {
+        &amp;&amp; player[0].cities &gt; 0
+        &amp;&amp; MomMagicCur[p] &gt;= 45 + 30 * MomSphereRung[p]) {
         GetCityByIndex(player[0], 0, tmpCity);
         // Roll BEFORE the debit, and gate the debit on it. MomSummonRoll returns
         // 0 when the caster has not reached rung 1 of its own ladder, and
-        // charging 75 mana for a creature that never appears would be a silent
+        // charging mana for a creature that never appears would be a silent
         // theft that looks exactly like a spawn that failed to render.
         summonPick = MomSummonRoll(p);
         summonRung = MomSummonRungOf(summonPick);
+        // Floor BEFORE the debit so price and countdown read the same rung. A
+        // creature reporting rung 0 is charged and timed as rung 1 rather than
+        // being handed out for 45 mana on a zero-turn wait.
+        if (summonRung &lt; 1) { summonRung = 1; }
         if (CityIsValid(tmpCity) &amp;&amp; summonPick != 0) {
             // Mana is committed the moment preparation STARTS, not on arrival.
             // Paying at arrival would let the pool be spent elsewhere while the
             // creature was notionally on its way, and there is no cancel, so the
             // commitment has to bite immediately or it is not a commitment.
-            MomMagicCur[p] = MomMagicCur[p] - 75;
+            MomMagicCur[p] = MomMagicCur[p] - (45 + 30 * summonRung);
             // The countdown IS the creature's rung: 1 turn for a rung-1 Warbears
             // (unchanged from the old instant-next-turn behaviour) up to 5 for a
-            // rung-5 Great Wyrm. Floored at 1 so a creature that somehow reports
-            // rung 0 still arrives rather than sticking forever at zero without
-            // ever passing through the arrival branch.
+            // rung-5 Great Wyrm. summonRung was floored to &gt;= 1 above, before
+            // the debit, so the price and the wait always describe the same
+            // creature.
             MomSummonPendRung[p] = summonRung;
-            if (summonRung &lt; 1) { MomSummonPendRung[p] = 1; }
             MomSummonPending[p] = summonPick;
             MomSummonPrep[p] = MomSummonPendRung[p];
             if (IsHumanPlayer(p)) {
@@ -45521,7 +45550,12 @@
 			Message(g.player, 'MomSummonNoMagic');
 		} elseif (MomSummonPrep[g.player] &gt; 0) {
 			Message(g.player, 'MomSummonBusy');
-		} elseif (MomMagicCur[g.player] &gt;= 75) {
+		// SAME PRICE EXPRESSION AS THE COMMIT, deliberately. The click must
+		// demand exactly what the commit will demand -- 45 + 30*ladder rung --
+		// or the button accepts an order the commit then refuses, which reads
+		// to the player as the arm doing nothing. That divergence class already
+		// bit this mod once on the upkeep rate and is what gate 27 watches for.
+		} elseif (MomMagicCur[g.player] &gt;= 45 + 30 * MomSphereRung[g.player]) {
 			MomSummonChoice[g.player] = 1;
 		} else {
 			Message(g.player, 'MomSummonNoMana');
@@ -45544,7 +45578,7 @@
         <v>20</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>22360</v>
+        <v>24284</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
@@ -45633,28 +45667,52 @@
     // this negative. The check is a plain comparison at call depth 0.
     // COMMIT. An order only starts a preparation when nothing is already
     // preparing -- one at a time, so this is a plan and not a queue.
+    // PRICE SCALES WITH RUNG: 45 + 30*rung -&gt; 75 / 105 / 135 / 165 / 195.
+    //
+    // It was a FLAT 75 for everything, which priced a 150-shield Phantom
+    // Warriors and a 4000-shield Storm Drake identically -- a 27x swing in what
+    // the same coin bought. Upkeep already scaled (rung * MomUpkeepRate) since
+    // v3.5.0, so acquisition was the missing half of that system, and the gap
+    // pushed play the wrong way: summoning was poor value at rung 1 and absurd
+    // value at rung 5.
+    //
+    // THE CEILING IS 195 AND IT IS NOT ARBITRARY. MomMagicSchoolGrant caps the
+    // pool per sphere at Life 200 / Nature 220 / Sorcery 260 / Chaos 300. A
+    // curve topping above 200 would make rung 5 literally unaffordable for Life
+    // -- its pool cannot hold the price -- so 195 is the largest step that keeps
+    // every sphere able to reach its own best creature.
+    //
+    // THE GATE USES THE LADDER RUNG, THE DEBIT USES THE ROLLED RUNG. The roll
+    // can return any creature at or below the caster's rung, so requiring
+    // 45+30*MomSphereRung up front means whatever comes back is affordable and
+    // a click can never be consumed by a summon that cannot be paid for. You
+    // then pay for what you actually got, not for what you might have got.
     if (p &gt;= 1 &amp;&amp; p &lt;= 5 &amp;&amp; MomSummonChoice[p] != 0 &amp;&amp; MomSummonPrep[p] == 0
-        &amp;&amp; player[0].cities &gt; 0 &amp;&amp; MomMagicCur[p] &gt;= 75) {
+        &amp;&amp; player[0].cities &gt; 0
+        &amp;&amp; MomMagicCur[p] &gt;= 45 + 30 * MomSphereRung[p]) {
         GetCityByIndex(player[0], 0, tmpCity);
         // Roll BEFORE the debit, and gate the debit on it. MomSummonRoll returns
         // 0 when the caster has not reached rung 1 of its own ladder, and
-        // charging 75 mana for a creature that never appears would be a silent
+        // charging mana for a creature that never appears would be a silent
         // theft that looks exactly like a spawn that failed to render.
         summonPick = MomSummonRoll(p);
         summonRung = MomSummonRungOf(summonPick);
+        // Floor BEFORE the debit so price and countdown read the same rung. A
+        // creature reporting rung 0 is charged and timed as rung 1 rather than
+        // being handed out for 45 mana on a zero-turn wait.
+        if (summonRung &lt; 1) { summonRung = 1; }
         if (CityIsValid(tmpCity) &amp;&amp; summonPick != 0) {
             // Mana is committed the moment preparation STARTS, not on arrival.
             // Paying at arrival would let the pool be spent elsewhere while the
             // creature was notionally on its way, and there is no cancel, so the
             // commitment has to bite immediately or it is not a commitment.
-            MomMagicCur[p] = MomMagicCur[p] - 75;
+            MomMagicCur[p] = MomMagicCur[p] - (45 + 30 * summonRung);
             // The countdown IS the creature's rung: 1 turn for a rung-1 Warbears
             // (unchanged from the old instant-next-turn behaviour) up to 5 for a
-            // rung-5 Great Wyrm. Floored at 1 so a creature that somehow reports
-            // rung 0 still arrives rather than sticking forever at zero without
-            // ever passing through the arrival branch.
+            // rung-5 Great Wyrm. summonRung was floored to &gt;= 1 above, before
+            // the debit, so the price and the wait always describe the same
+            // creature.
             MomSummonPendRung[p] = summonRung;
-            if (summonRung &lt; 1) { MomSummonPendRung[p] = 1; }
             MomSummonPending[p] = summonPick;
             MomSummonPrep[p] = MomSummonPendRung[p];
             if (IsHumanPlayer(p)) {
@@ -45934,7 +45992,12 @@
 			Message(g.player, 'MomSummonNoMagic');
 		} elseif (MomSummonPrep[g.player] &gt; 0) {
 			Message(g.player, 'MomSummonBusy');
-		} elseif (MomMagicCur[g.player] &gt;= 75) {
+		// SAME PRICE EXPRESSION AS THE COMMIT, deliberately. The click must
+		// demand exactly what the commit will demand -- 45 + 30*ladder rung --
+		// or the button accepts an order the commit then refuses, which reads
+		// to the player as the arm doing nothing. That divergence class already
+		// bit this mod once on the upkeep rate and is what gate 27 watches for.
+		} elseif (MomMagicCur[g.player] &gt;= 45 + 30 * MomSphereRung[g.player]) {
 			MomSummonChoice[g.player] = 1;
 		} else {
 			Message(g.player, 'MomSummonNoMana');
@@ -46245,6 +46308,12 @@
             // claiming "rung 1 of 5" while every summon silently fails was
             // reporting a capability that did not exist.
             MomRungDisp = MomSphereRung[p];
+            // The summon arm's LABEL reads this. It used to be the literal
+            // string "Summon Creature (75)", which stopped being true the
+            // moment price scaled with rung -- a button that misquotes its own
+            // price is worse than one that quotes none. Same expression as the
+            // click gate and the AI gate: 45 + 30*ladder rung.
+            MomSummonCostDisp = 45 + 30 * MomSphereRung[p];
         }
         // Periodic popup every 10 rounds: REMOVED 2026-07-25, redundant and harmful.
         //
@@ -46373,7 +46442,7 @@
         <v>4</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>21402</v>
+        <v>21843</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
@@ -46654,6 +46723,12 @@
             // claiming "rung 1 of 5" while every summon silently fails was
             // reporting a capability that did not exist.
             MomRungDisp = MomSphereRung[p];
+            // The summon arm's LABEL reads this. It used to be the literal
+            // string "Summon Creature (75)", which stopped being true the
+            // moment price scaled with rung -- a button that misquotes its own
+            // price is worse than one that quotes none. Same expression as the
+            // click gate and the AI gate: 45 + 30*ladder rung.
+            MomSummonCostDisp = 45 + 30 * MomSphereRung[p];
         }
         // Periodic popup every 10 rounds: REMOVED 2026-07-25, redundant and harmful.
         //
@@ -47525,7 +47600,13 @@
         // creature was already on the way, overwriting its own pending creature
         // and paying repeatedly for a single arrival -- a silent mana leak that
         // would look exactly like the AI being poor.
-        if (MomMagicCur[p] &gt;= 75 &amp;&amp; MomSummonPrep[p] == 0
+        // PRICE SCALES WITH RUNG: 45 + 30*rung -&gt; 75/105/135/165/195, the SAME
+        // expression the human pays in mom_msg.slc (gate on the ladder rung,
+        // debit the rolled rung). The AI must not play a cheaper economy than
+        // the player; when these two drifted on the UPKEEP rate it produced an
+        // AI that could afford what a human could not, which is the defect gate
+        // 27 assertion 10 exists to catch.
+        if (MomMagicCur[p] &gt;= 45 + 30 * MomSphereRung[p] &amp;&amp; MomSummonPrep[p] == 0
             &amp;&amp; (atWar == 1 || roll &lt; 70)) {
             // The default sink, and the aggressive choice. At war it always
             // prefers a creature; at peace it summons most of the time and
@@ -47550,7 +47631,11 @@
                 pick = 0;
             }
             if (CityIsValid(tmpCity) &amp;&amp; pick != 0) {
-                MomMagicCur[p] = MomMagicCur[p] - 75;
+                // pickRung is floored to &gt;= 1 below before it is stored, so
+                // floor it HERE too -- the debit must not read a rung of 0 and
+                // hand a creature over for 45 mana.
+                if (pickRung &lt; 1) { pickRung = 1; }
+                MomMagicCur[p] = MomMagicCur[p] - (45 + 30 * pickRung);
                 // PREPARATION (2026-08-01): the AI no longer spawns here. It
                 // commits the mana and starts the same countdown the human uses,
                 // and MomSummonOrderTick's arrival branch (mom_msg.slc) does the
@@ -47562,8 +47647,9 @@
                 // free-land-neighbour search still applies: spawning on the city
                 // tile would stack the creature under the garrison, because CTP2
                 // draws one unit per tile ordered by MaxMovePoints.
+                // pickRung was floored to &gt;= 1 at the debit above, so price,
+                // countdown and ledger all describe one rung.
                 MomSummonPendRung[p] = pickRung;
-                if (pickRung &lt; 1) { MomSummonPendRung[p] = 1; }
                 MomSummonPending[p] = pick;
                 MomSummonPrep[p] = MomSummonPendRung[p];
             }
@@ -47597,7 +47683,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>8373</v>
+        <v>9196</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
@@ -47679,7 +47765,13 @@
         // creature was already on the way, overwriting its own pending creature
         // and paying repeatedly for a single arrival -- a silent mana leak that
         // would look exactly like the AI being poor.
-        if (MomMagicCur[p] &gt;= 75 &amp;&amp; MomSummonPrep[p] == 0
+        // PRICE SCALES WITH RUNG: 45 + 30*rung -&gt; 75/105/135/165/195, the SAME
+        // expression the human pays in mom_msg.slc (gate on the ladder rung,
+        // debit the rolled rung). The AI must not play a cheaper economy than
+        // the player; when these two drifted on the UPKEEP rate it produced an
+        // AI that could afford what a human could not, which is the defect gate
+        // 27 assertion 10 exists to catch.
+        if (MomMagicCur[p] &gt;= 45 + 30 * MomSphereRung[p] &amp;&amp; MomSummonPrep[p] == 0
             &amp;&amp; (atWar == 1 || roll &lt; 70)) {
             // The default sink, and the aggressive choice. At war it always
             // prefers a creature; at peace it summons most of the time and
@@ -47704,7 +47796,11 @@
                 pick = 0;
             }
             if (CityIsValid(tmpCity) &amp;&amp; pick != 0) {
-                MomMagicCur[p] = MomMagicCur[p] - 75;
+                // pickRung is floored to &gt;= 1 below before it is stored, so
+                // floor it HERE too -- the debit must not read a rung of 0 and
+                // hand a creature over for 45 mana.
+                if (pickRung &lt; 1) { pickRung = 1; }
+                MomMagicCur[p] = MomMagicCur[p] - (45 + 30 * pickRung);
                 // PREPARATION (2026-08-01): the AI no longer spawns here. It
                 // commits the mana and starts the same countdown the human uses,
                 // and MomSummonOrderTick's arrival branch (mom_msg.slc) does the
@@ -47716,8 +47812,9 @@
                 // free-land-neighbour search still applies: spawning on the city
                 // tile would stack the creature under the garrison, because CTP2
                 // draws one unit per tile ordered by MaxMovePoints.
+                // pickRung was floored to &gt;= 1 at the debit above, so price,
+                // countdown and ledger all describe one rung.
                 MomSummonPendRung[p] = pickRung;
-                if (pickRung &lt; 1) { MomSummonPendRung[p] = 1; }
                 MomSummonPending[p] = pick;
                 MomSummonPrep[p] = MomSummonPendRung[p];
             }

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -43650,6 +43650,7 @@
 int_t MomSummonPending[31];  // the rolled unit type awaiting arrival
 int_t MomSummonPendRung[31]; // its rung, carried so arrival can ledger upkeep
 int_t MomPrepDisp;           // countdown scalar for the 'j' panel
+int_t MomSummonCivPct[31];   // per-civ summon price, as a PERCENT of the rung curve.
 int_t MomSummonCostDisp;     // price the summon arm quotes: 45 + 30*rung.
 int_t MomMagicShownTurn[31]; // per-round re-entry latch for the popup (flood safety)
 int_t MomMagicSchoolPct[31]; // per-turn multiplier as integer percent (M2); 0 read as 100</t>
@@ -43943,7 +43944,7 @@
         <v>16</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>17666</v>
+        <v>18256</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
@@ -44326,6 +44327,13 @@
 int_t MomSummonPending[31];  // the rolled unit type awaiting arrival
 int_t MomSummonPendRung[31]; // its rung, carried so arrival can ledger upkeep
 int_t MomPrepDisp;           // countdown scalar for the 'j' panel
+int_t MomSummonCivPct[31];   // per-civ summon price, as a PERCENT of the rung curve.
+                             // Life 64 / Nature 68 / Sorcery 54 / Death 54 / Chaos 92,
+                             // derived from each sphere's own roster cost at equal rung
+                             // and scaled so the dearest civ's rung-5 creature lands at
+                             // 90% of the fixed 200 pool. 0 is read as 100 by every
+                             // caller, so an unseeded player pays the base curve rather
+                             // than summoning for free.
 int_t MomSummonCostDisp;     // price the summon arm quotes: 45 + 30*rung.
                              // A scalar, not an array -- an undeclared scalar is
                              // silently auto-created and would read a permanent 0,
@@ -45221,7 +45229,7 @@
     int_t summonRung;
     city_t tmpCity;
     p = player[0];
-    // COST 75 (added 2026-07-26). The order is placed at click time and PAID here,
+    // The order is placed at click time and PAID here,
     // at spawn time, so the pool is only debited when a creature actually appears.
     // Re-checking the balance is not redundant with the button-body check: the
     // only thing that can move the pool between the two is MomMagicPoolTick's
@@ -45239,11 +45247,25 @@
     // pushed play the wrong way: summoning was poor value at rung 1 and absurd
     // value at rung 5.
     //
-    // THE CEILING IS 195 AND IT IS NOT ARBITRARY. MomMagicSchoolGrant caps the
-    // pool per sphere at Life 200 / Nature 220 / Sorcery 260 / Chaos 300. A
-    // curve topping above 200 would make rung 5 literally unaffordable for Life
-    // -- its pool cannot hold the price -- so 195 is the largest step that keeps
-    // every sphere able to reach its own best creature.
+    // THEN SCALED PER CIV: * MomSummonCivPct / 100, Life 64 / Nature 68 /
+    // Sorcery 54 / Death 54 / Chaos 92. Two dials, deliberately separable --
+    // RUNG is what the player can know before clicking (it is their own ladder
+    // position), and CIV is a fixed property of the tribe. Which creature the
+    // roll returns stays unknown; that is the spin, and it is not the price.
+    //
+    // THE POOL IS A FIXED 200 FOR EVERY CIV and that is the anchor the whole
+    // economy is measured against. It used to vary (Life 200 / Nature 220 /
+    // Sorcery 260 / Death 240 / Chaos 300) AND correlate with the generation
+    // multiplier, so Chaos got 140% income and a 50% bigger bank -- two
+    // advantages stacking multiplicatively. Worse, the SMALLEST cap silently
+    // dictated the price ceiling for everyone. Fixing the pool decouples the
+    // dials and gives a constant to express every other number against.
+    //
+    // The percentages are DERIVED, not chosen: each sphere's own roster cost at
+    // equal rung (Chaos creatures are 1.39x the all-sphere mean, Death 0.81x),
+    // rescaled so the dearest civ's rung-5 creature costs 179 -- 90% of the
+    // fixed pool. Cheapest summon in the game is 40, dearest 179, and every civ
+    // can afford its own best creature.
     //
     // THE GATE USES THE LADDER RUNG, THE DEBIT USES THE ROLLED RUNG. The roll
     // can return any creature at or below the caster's rung, so requiring
@@ -45252,7 +45274,7 @@
     // then pay for what you actually got, not for what you might have got.
     if (p &gt;= 1 &amp;&amp; p &lt;= 5 &amp;&amp; MomSummonChoice[p] != 0 &amp;&amp; MomSummonPrep[p] == 0
         &amp;&amp; player[0].cities &gt; 0
-        &amp;&amp; MomMagicCur[p] &gt;= 45 + 30 * MomSphereRung[p]) {
+        &amp;&amp; MomMagicCur[p] &gt;= ((45 + 30 * MomSphereRung[p]) * MomSummonCivPct[p]) / 100) {
         GetCityByIndex(player[0], 0, tmpCity);
         // Roll BEFORE the debit, and gate the debit on it. MomSummonRoll returns
         // 0 when the caster has not reached rung 1 of its own ladder, and
@@ -45262,14 +45284,14 @@
         summonRung = MomSummonRungOf(summonPick);
         // Floor BEFORE the debit so price and countdown read the same rung. A
         // creature reporting rung 0 is charged and timed as rung 1 rather than
-        // being handed out for 45 mana on a zero-turn wait.
+        // being handed over at the curve's intercept on a zero-turn wait.
         if (summonRung &lt; 1) { summonRung = 1; }
         if (CityIsValid(tmpCity) &amp;&amp; summonPick != 0) {
             // Mana is committed the moment preparation STARTS, not on arrival.
             // Paying at arrival would let the pool be spent elsewhere while the
             // creature was notionally on its way, and there is no cancel, so the
             // commitment has to bite immediately or it is not a commitment.
-            MomMagicCur[p] = MomMagicCur[p] - (45 + 30 * summonRung);
+            MomMagicCur[p] = MomMagicCur[p] - (((45 + 30 * summonRung) * MomSummonCivPct[p]) / 100);
             // The countdown IS the creature's rung: 1 turn for a rung-1 Warbears
             // (unchanged from the old instant-next-turn behaviour) up to 5 for a
             // rung-5 Great Wyrm. summonRung was floored to &gt;= 1 above, before
@@ -45555,7 +45577,7 @@
 		// or the button accepts an order the commit then refuses, which reads
 		// to the player as the arm doing nothing. That divergence class already
 		// bit this mod once on the upkeep rate and is what gate 27 watches for.
-		} elseif (MomMagicCur[g.player] &gt;= 45 + 30 * MomSphereRung[g.player]) {
+		} elseif (MomMagicCur[g.player] &gt;= ((45 + 30 * MomSphereRung[g.player]) * MomSummonCivPct[g.player]) / 100) {
 			MomSummonChoice[g.player] = 1;
 		} else {
 			Message(g.player, 'MomSummonNoMana');
@@ -45578,7 +45600,7 @@
         <v>20</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>24284</v>
+        <v>25306</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
@@ -45658,7 +45680,7 @@
     int_t summonRung;
     city_t tmpCity;
     p = player[0];
-    // COST 75 (added 2026-07-26). The order is placed at click time and PAID here,
+    // The order is placed at click time and PAID here,
     // at spawn time, so the pool is only debited when a creature actually appears.
     // Re-checking the balance is not redundant with the button-body check: the
     // only thing that can move the pool between the two is MomMagicPoolTick's
@@ -45676,11 +45698,25 @@
     // pushed play the wrong way: summoning was poor value at rung 1 and absurd
     // value at rung 5.
     //
-    // THE CEILING IS 195 AND IT IS NOT ARBITRARY. MomMagicSchoolGrant caps the
-    // pool per sphere at Life 200 / Nature 220 / Sorcery 260 / Chaos 300. A
-    // curve topping above 200 would make rung 5 literally unaffordable for Life
-    // -- its pool cannot hold the price -- so 195 is the largest step that keeps
-    // every sphere able to reach its own best creature.
+    // THEN SCALED PER CIV: * MomSummonCivPct / 100, Life 64 / Nature 68 /
+    // Sorcery 54 / Death 54 / Chaos 92. Two dials, deliberately separable --
+    // RUNG is what the player can know before clicking (it is their own ladder
+    // position), and CIV is a fixed property of the tribe. Which creature the
+    // roll returns stays unknown; that is the spin, and it is not the price.
+    //
+    // THE POOL IS A FIXED 200 FOR EVERY CIV and that is the anchor the whole
+    // economy is measured against. It used to vary (Life 200 / Nature 220 /
+    // Sorcery 260 / Death 240 / Chaos 300) AND correlate with the generation
+    // multiplier, so Chaos got 140% income and a 50% bigger bank -- two
+    // advantages stacking multiplicatively. Worse, the SMALLEST cap silently
+    // dictated the price ceiling for everyone. Fixing the pool decouples the
+    // dials and gives a constant to express every other number against.
+    //
+    // The percentages are DERIVED, not chosen: each sphere's own roster cost at
+    // equal rung (Chaos creatures are 1.39x the all-sphere mean, Death 0.81x),
+    // rescaled so the dearest civ's rung-5 creature costs 179 -- 90% of the
+    // fixed pool. Cheapest summon in the game is 40, dearest 179, and every civ
+    // can afford its own best creature.
     //
     // THE GATE USES THE LADDER RUNG, THE DEBIT USES THE ROLLED RUNG. The roll
     // can return any creature at or below the caster's rung, so requiring
@@ -45689,7 +45725,7 @@
     // then pay for what you actually got, not for what you might have got.
     if (p &gt;= 1 &amp;&amp; p &lt;= 5 &amp;&amp; MomSummonChoice[p] != 0 &amp;&amp; MomSummonPrep[p] == 0
         &amp;&amp; player[0].cities &gt; 0
-        &amp;&amp; MomMagicCur[p] &gt;= 45 + 30 * MomSphereRung[p]) {
+        &amp;&amp; MomMagicCur[p] &gt;= ((45 + 30 * MomSphereRung[p]) * MomSummonCivPct[p]) / 100) {
         GetCityByIndex(player[0], 0, tmpCity);
         // Roll BEFORE the debit, and gate the debit on it. MomSummonRoll returns
         // 0 when the caster has not reached rung 1 of its own ladder, and
@@ -45699,14 +45735,14 @@
         summonRung = MomSummonRungOf(summonPick);
         // Floor BEFORE the debit so price and countdown read the same rung. A
         // creature reporting rung 0 is charged and timed as rung 1 rather than
-        // being handed out for 45 mana on a zero-turn wait.
+        // being handed over at the curve's intercept on a zero-turn wait.
         if (summonRung &lt; 1) { summonRung = 1; }
         if (CityIsValid(tmpCity) &amp;&amp; summonPick != 0) {
             // Mana is committed the moment preparation STARTS, not on arrival.
             // Paying at arrival would let the pool be spent elsewhere while the
             // creature was notionally on its way, and there is no cancel, so the
             // commitment has to bite immediately or it is not a commitment.
-            MomMagicCur[p] = MomMagicCur[p] - (45 + 30 * summonRung);
+            MomMagicCur[p] = MomMagicCur[p] - (((45 + 30 * summonRung) * MomSummonCivPct[p]) / 100);
             // The countdown IS the creature's rung: 1 turn for a rung-1 Warbears
             // (unchanged from the old instant-next-turn behaviour) up to 5 for a
             // rung-5 Great Wyrm. summonRung was floored to &gt;= 1 above, before
@@ -45997,7 +46033,7 @@
 		// or the button accepts an order the commit then refuses, which reads
 		// to the player as the arm doing nothing. That divergence class already
 		// bit this mod once on the upkeep rate and is what gate 27 watches for.
-		} elseif (MomMagicCur[g.player] &gt;= 45 + 30 * MomSphereRung[g.player]) {
+		} elseif (MomMagicCur[g.player] &gt;= ((45 + 30 * MomSphereRung[g.player]) * MomSummonCivPct[g.player]) / 100) {
 			MomSummonChoice[g.player] = 1;
 		} else {
 			Message(g.player, 'MomSummonNoMana');
@@ -46141,6 +46177,13 @@
         MomUpkeepRate = 2;
     }
     if (mp_1 &gt;= 1 &amp;&amp; mp_1 &lt;= 5) {
+        // Same lazy-seed idiom as MomUpkeepRate above, and for the same
+        // reason: SLIC globals start at 0, and a 0 percent would make every
+        // summon FREE. 100 means 'pay the base rung curve', so an unseeded
+        // player is merely un-discounted rather than exploitable.
+        if (MomSummonCivPct[mp_1] == 0) {
+            MomSummonCivPct[mp_1] = 100;
+        }
         base = (mp_1 - 1) * 32;
         for (i = 0; i &lt; 32; i = i + 1) {
             idx = base + i;
@@ -46313,7 +46356,7 @@
             // moment price scaled with rung -- a button that misquotes its own
             // price is worse than one that quotes none. Same expression as the
             // click gate and the AI gate: 45 + 30*ladder rung.
-            MomSummonCostDisp = 45 + 30 * MomSphereRung[p];
+            MomSummonCostDisp = ((45 + 30 * MomSphereRung[p]) * MomSummonCivPct[p]) / 100;
         }
         // Periodic popup every 10 rounds: REMOVED 2026-07-25, redundant and harmful.
         //
@@ -46346,22 +46389,27 @@
     if (MomPlayerIsLife(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC)) {
         MomMagicSchoolPct[p] = 100;
         MomMagicMax[p] = 200;
+        MomSummonCivPct[p] = 64;
         granted = 1;
     } elseif (MomPlayerIsNature(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC)) {
         MomMagicSchoolPct[p] = 110;
-        MomMagicMax[p] = 220;
+        MomMagicMax[p] = 200;
+        MomSummonCivPct[p] = 68;
         granted = 1;
     } elseif (MomPlayerIsSorcery(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY)) {
         MomMagicSchoolPct[p] = 125;
-        MomMagicMax[p] = 260;
+        MomMagicMax[p] = 200;
+        MomSummonCivPct[p] = 54;
         granted = 1;
     } elseif (MomPlayerIsDeath(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC)) {
         MomMagicSchoolPct[p] = 115;
-        MomMagicMax[p] = 240;
+        MomMagicMax[p] = 200;
+        MomSummonCivPct[p] = 54;
         granted = 1;
     } elseif (MomPlayerIsChaos(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC)) {
         MomMagicSchoolPct[p] = 140;
-        MomMagicMax[p] = 300;
+        MomMagicMax[p] = 200;
+        MomSummonCivPct[p] = 92;
         granted = 1;
     }
     if (granted &amp;&amp; IsHumanPlayer(p)) {
@@ -46442,7 +46490,7 @@
         <v>4</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>21843</v>
+        <v>22437</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
@@ -46555,6 +46603,13 @@
         MomUpkeepRate = 2;
     }
     if (mp_1 &gt;= 1 &amp;&amp; mp_1 &lt;= 5) {
+        // Same lazy-seed idiom as MomUpkeepRate above, and for the same
+        // reason: SLIC globals start at 0, and a 0 percent would make every
+        // summon FREE. 100 means 'pay the base rung curve', so an unseeded
+        // player is merely un-discounted rather than exploitable.
+        if (MomSummonCivPct[mp_1] == 0) {
+            MomSummonCivPct[mp_1] = 100;
+        }
         base = (mp_1 - 1) * 32;
         for (i = 0; i &lt; 32; i = i + 1) {
             idx = base + i;
@@ -46728,7 +46783,7 @@
             // moment price scaled with rung -- a button that misquotes its own
             // price is worse than one that quotes none. Same expression as the
             // click gate and the AI gate: 45 + 30*ladder rung.
-            MomSummonCostDisp = 45 + 30 * MomSphereRung[p];
+            MomSummonCostDisp = ((45 + 30 * MomSphereRung[p]) * MomSummonCivPct[p]) / 100;
         }
         // Periodic popup every 10 rounds: REMOVED 2026-07-25, redundant and harmful.
         //
@@ -46761,22 +46816,27 @@
     if (MomPlayerIsLife(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC)) {
         MomMagicSchoolPct[p] = 100;
         MomMagicMax[p] = 200;
+        MomSummonCivPct[p] = 64;
         granted = 1;
     } elseif (MomPlayerIsNature(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC)) {
         MomMagicSchoolPct[p] = 110;
-        MomMagicMax[p] = 220;
+        MomMagicMax[p] = 200;
+        MomSummonCivPct[p] = 68;
         granted = 1;
     } elseif (MomPlayerIsSorcery(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY)) {
         MomMagicSchoolPct[p] = 125;
-        MomMagicMax[p] = 260;
+        MomMagicMax[p] = 200;
+        MomSummonCivPct[p] = 54;
         granted = 1;
     } elseif (MomPlayerIsDeath(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC)) {
         MomMagicSchoolPct[p] = 115;
-        MomMagicMax[p] = 240;
+        MomMagicMax[p] = 200;
+        MomSummonCivPct[p] = 54;
         granted = 1;
     } elseif (MomPlayerIsChaos(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC)) {
         MomMagicSchoolPct[p] = 140;
-        MomMagicMax[p] = 300;
+        MomMagicMax[p] = 200;
+        MomSummonCivPct[p] = 92;
         granted = 1;
     }
     if (granted &amp;&amp; IsHumanPlayer(p)) {
@@ -47592,8 +47652,9 @@
         }
         roll = Random(100);
         // The ladder, cheapest test first. Thresholds are the SAME prices the
-        // human pays -- 75 to summon, 50 for a working -- so the AI is playing
-        // the same economy rather than a discounted one. Below 50 it banks,
+        // human pays -- the shared rung x civ expression to summon, 50 for a
+        // working -- so the AI plays the same economy rather than a discounted
+        // one. Below the summon price it banks,
         // which is what makes a later summon possible at all.
         // MomSummonPrep == 0 is the same one-at-a-time rule the human's button
         // enforces. Without it the AI would re-commit 75 mana every turn while a
@@ -47606,7 +47667,7 @@
         // the player; when these two drifted on the UPKEEP rate it produced an
         // AI that could afford what a human could not, which is the defect gate
         // 27 assertion 10 exists to catch.
-        if (MomMagicCur[p] &gt;= 45 + 30 * MomSphereRung[p] &amp;&amp; MomSummonPrep[p] == 0
+        if (MomMagicCur[p] &gt;= ((45 + 30 * MomSphereRung[p]) * MomSummonCivPct[p]) / 100 &amp;&amp; MomSummonPrep[p] == 0
             &amp;&amp; (atWar == 1 || roll &lt; 70)) {
             // The default sink, and the aggressive choice. At war it always
             // prefers a creature; at peace it summons most of the time and
@@ -47633,9 +47694,9 @@
             if (CityIsValid(tmpCity) &amp;&amp; pick != 0) {
                 // pickRung is floored to &gt;= 1 below before it is stored, so
                 // floor it HERE too -- the debit must not read a rung of 0 and
-                // hand a creature over for 45 mana.
+                // hand a creature over at the curve's intercept.
                 if (pickRung &lt; 1) { pickRung = 1; }
-                MomMagicCur[p] = MomMagicCur[p] - (45 + 30 * pickRung);
+                MomMagicCur[p] = MomMagicCur[p] - (((45 + 30 * pickRung) * MomSummonCivPct[p]) / 100);
                 // PREPARATION (2026-08-01): the AI no longer spawns here. It
                 // commits the mana and starts the same countdown the human uses,
                 // and MomSummonOrderTick's arrival branch (mom_msg.slc) does the
@@ -47683,7 +47744,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>9196</v>
+        <v>9480</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
@@ -47757,8 +47818,9 @@
         }
         roll = Random(100);
         // The ladder, cheapest test first. Thresholds are the SAME prices the
-        // human pays -- 75 to summon, 50 for a working -- so the AI is playing
-        // the same economy rather than a discounted one. Below 50 it banks,
+        // human pays -- the shared rung x civ expression to summon, 50 for a
+        // working -- so the AI plays the same economy rather than a discounted
+        // one. Below the summon price it banks,
         // which is what makes a later summon possible at all.
         // MomSummonPrep == 0 is the same one-at-a-time rule the human's button
         // enforces. Without it the AI would re-commit 75 mana every turn while a
@@ -47771,7 +47833,7 @@
         // the player; when these two drifted on the UPKEEP rate it produced an
         // AI that could afford what a human could not, which is the defect gate
         // 27 assertion 10 exists to catch.
-        if (MomMagicCur[p] &gt;= 45 + 30 * MomSphereRung[p] &amp;&amp; MomSummonPrep[p] == 0
+        if (MomMagicCur[p] &gt;= ((45 + 30 * MomSphereRung[p]) * MomSummonCivPct[p]) / 100 &amp;&amp; MomSummonPrep[p] == 0
             &amp;&amp; (atWar == 1 || roll &lt; 70)) {
             // The default sink, and the aggressive choice. At war it always
             // prefers a creature; at peace it summons most of the time and
@@ -47798,9 +47860,9 @@
             if (CityIsValid(tmpCity) &amp;&amp; pick != 0) {
                 // pickRung is floored to &gt;= 1 below before it is stored, so
                 // floor it HERE too -- the debit must not read a rung of 0 and
-                // hand a creature over for 45 mana.
+                // hand a creature over at the curve's intercept.
                 if (pickRung &lt; 1) { pickRung = 1; }
-                MomMagicCur[p] = MomMagicCur[p] - (45 + 30 * pickRung);
+                MomMagicCur[p] = MomMagicCur[p] - (((45 + 30 * pickRung) * MomSummonCivPct[p]) / 100);
                 // PREPARATION (2026-08-01): the AI no longer spawns here. It
                 // commits the mana and starts the same countdown the human uses,
                 // and MomSummonOrderTick's arrival branch (mom_msg.slc) does the

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -47203,10 +47203,17 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>alertbox 'MomMsgSpellbook' {
+          <t>// THE ARMS WERE LABELLED WITH STOCK CTP2 STRINGS UNTIL 2026-08-03, and that is
+// the whole reason this layer read as unfinished. ID_BUTTON_RESEARCH cast Flame
+// Strike and ID_BUTTON_GOAL cast Demon Strike, so a fully working spellbook
+// rendered its arms as "Research" and "Goal" -- no player could know either was
+// a spell. MOM_MSG_BTN_FLAME and MOM_MSG_BTN_DEMON were already authored in
+// scen_str.txt and simply never bound. The code was done; the wiring to the
+// words was the only thing missing.
+alertbox 'MomMsgSpellbook' {
     Show();
     Text(ID_MOM_MSG_SPELLBOOK);
-    Button(ID_BUTTON_RESEARCH) {
+    Button(ID_MOM_MSG_BTN_FLAME) {
         MomCastFlameStrike(g.player);
         Kill();
     }
@@ -47217,11 +47224,11 @@
 alertbox 'MomMsgSpellbookChaos' {
     Show();
     Text(ID_MOM_MSG_SPELLBOOK);
-    Button(ID_BUTTON_GOAL) {
+    Button(ID_MOM_MSG_BTN_DEMON) {
         MomCastDemonStrike(g.player);
         Kill();
     }
-    Button(ID_BUTTON_RESEARCH) {
+    Button(ID_MOM_MSG_BTN_FLAME) {
         MomCastFlameStrike(g.player);
         Kill();
     }
@@ -47255,7 +47262,7 @@
         <v>13</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>15933</v>
+        <v>16822</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
@@ -47553,10 +47560,17 @@
 // Messagebox segments (see lessons_learned 2026-07-17: Message() requires a
 // DEFINED segment; names must not collide with handlers or string keys).
 // ---------------------------------------------------------------------------
+// THE ARMS WERE LABELLED WITH STOCK CTP2 STRINGS UNTIL 2026-08-03, and that is
+// the whole reason this layer read as unfinished. ID_BUTTON_RESEARCH cast Flame
+// Strike and ID_BUTTON_GOAL cast Demon Strike, so a fully working spellbook
+// rendered its arms as "Research" and "Goal" -- no player could know either was
+// a spell. MOM_MSG_BTN_FLAME and MOM_MSG_BTN_DEMON were already authored in
+// scen_str.txt and simply never bound. The code was done; the wiring to the
+// words was the only thing missing.
 alertbox 'MomMsgSpellbook' {
     Show();
     Text(ID_MOM_MSG_SPELLBOOK);
-    Button(ID_BUTTON_RESEARCH) {
+    Button(ID_MOM_MSG_BTN_FLAME) {
         MomCastFlameStrike(g.player);
         Kill();
     }
@@ -47567,11 +47581,11 @@
 alertbox 'MomMsgSpellbookChaos' {
     Show();
     Text(ID_MOM_MSG_SPELLBOOK);
-    Button(ID_BUTTON_GOAL) {
+    Button(ID_MOM_MSG_BTN_DEMON) {
         MomCastDemonStrike(g.player);
         Kill();
     }
-    Button(ID_BUTTON_RESEARCH) {
+    Button(ID_MOM_MSG_BTN_FLAME) {
         MomCastFlameStrike(g.player);
         Kill();
     }

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -86,7 +86,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'slic'!$A$1:$L$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45412,11 +45412,7 @@
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>messagebox 'MomMsgSlicAlive' {
-	Show();
-	Text(ID_MOM_MSG_SLIC_ALIVE);
-}
-messagebox 'MomBlessLife' {
+          <t>messagebox 'MomBlessLife' {
 	Show();
 	Text(ID_MOM_MSG_BLESS_LIFE);
 }
@@ -45534,6 +45530,14 @@
 alertbox 'MagicMenu' {
 	Show();
 	Text(ID_MOM_MSG_MAGIC_MENU);
+	// CLOSE IS DECLARED FIRST, and that ordering is load-bearing. MEASURED
+	// 2026-08-03: an alertbox renders at most FIVE arms, drops the overflow
+	// from the TAIL of the declaration list in silence, and paints what
+	// survives in REVERSE order. Declaring Close last is how a sixth arm
+	// silently deletes the player's only way out.
+	Button(ID_BUTTON_CLOSE) {
+		Kill();
+	}
 	// SUMMON: place a summon ORDER. The body only writes a global; the spawn
 	// happens next BeginTurn in MomSummonOrderTick, which resolves the creature
 	// from the caster's own sphere. The body stays assignment-only -- a button
@@ -45590,17 +45594,36 @@
 	// closed, and what remained was a free-money button sitting in the player's
 	// magic menu. The boundary is still exercised in play by the summon path's
 	// CreateUnit, so nothing is lost as evidence.
-	Button(ID_BUTTON_CLOSE) {
+	// WORKINGS -- the NavArm into the spellbook spoke.
+	//
+	// Kill() FIRST, then Message(). Boxes STACK rather than replace, and a
+	// stacked pair freezes the turn loop; the base-verified navigation pattern
+	// is tut2_msg.slc's TMTurn0B, which does exactly this and whose statements
+	// after Kill() demonstrably still run.
+	//
+	// The Chaos branch is inline rather than delegated to MomSpellShowBook,
+	// which lives in mom_spells.slc (include 65) -- FIVE INCLUDES AFTER this
+	// file. Calling it from here would reference a symbol whose declaring file
+	// has not loaded, the same hard error that bit MomSphereRung. Segment names
+	// are resolved by the engine when Message() runs, not at include time, so
+	// naming a later-defined segment is safe where calling a later-defined
+	// FUNCTION is not.
+	Button(ID_MOM_MSG_BTN_WORKINGS) {
 		Kill();
+		if (MomPlayerIsChaos(g.player)) {
+			Message(g.player, 'MomMsgSpellbookChaos');
+		} else {
+			Message(g.player, 'MomMsgSpellbook');
+		}
 	}
 }</t>
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>25306</v>
+        <v>26586</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
@@ -45868,10 +45891,6 @@
 // Text(ID_T_TURN_0) &lt;-&gt; tut2_str.txt key T_TURN_0). MessageType is optional
 // (24 base messageboxes omit it) and is deliberately omitted here.
 // ---------------------------------------------------------------------------
-messagebox 'MomMsgSlicAlive' {
-	Show();
-	Text(ID_MOM_MSG_SLIC_ALIVE);
-}
 messagebox 'MomBlessLife' {
 	Show();
 	Text(ID_MOM_MSG_BLESS_LIFE);
@@ -45990,6 +46009,14 @@
 alertbox 'MagicMenu' {
 	Show();
 	Text(ID_MOM_MSG_MAGIC_MENU);
+	// CLOSE IS DECLARED FIRST, and that ordering is load-bearing. MEASURED
+	// 2026-08-03: an alertbox renders at most FIVE arms, drops the overflow
+	// from the TAIL of the declaration list in silence, and paints what
+	// survives in REVERSE order. Declaring Close last is how a sixth arm
+	// silently deletes the player's only way out.
+	Button(ID_BUTTON_CLOSE) {
+		Kill();
+	}
 	// SUMMON: place a summon ORDER. The body only writes a global; the spawn
 	// happens next BeginTurn in MomSummonOrderTick, which resolves the creature
 	// from the caster's own sphere. The body stays assignment-only -- a button
@@ -46046,8 +46073,27 @@
 	// closed, and what remained was a free-money button sitting in the player's
 	// magic menu. The boundary is still exercised in play by the summon path's
 	// CreateUnit, so nothing is lost as evidence.
-	Button(ID_BUTTON_CLOSE) {
+	// WORKINGS -- the NavArm into the spellbook spoke.
+	//
+	// Kill() FIRST, then Message(). Boxes STACK rather than replace, and a
+	// stacked pair freezes the turn loop; the base-verified navigation pattern
+	// is tut2_msg.slc's TMTurn0B, which does exactly this and whose statements
+	// after Kill() demonstrably still run.
+	//
+	// The Chaos branch is inline rather than delegated to MomSpellShowBook,
+	// which lives in mom_spells.slc (include 65) -- FIVE INCLUDES AFTER this
+	// file. Calling it from here would reference a symbol whose declaring file
+	// has not loaded, the same hard error that bit MomSphereRung. Segment names
+	// are resolved by the engine when Message() runs, not at include time, so
+	// naming a later-defined segment is safe where calling a later-defined
+	// FUNCTION is not.
+	Button(ID_MOM_MSG_BTN_WORKINGS) {
 		Kill();
+		if (MomPlayerIsChaos(g.player)) {
+			Message(g.player, 'MomMsgSpellbookChaos');
+		} else {
+			Message(g.player, 'MomMsgSpellbook');
+		}
 	}
 }</t>
         </is>
@@ -47213,17 +47259,42 @@
 alertbox 'MomMsgSpellbook' {
     Show();
     Text(ID_MOM_MSG_SPELLBOOK);
+    // CLOSE FIRST -- overflow is dropped from the TAIL of the declaration list,
+    // silently, so the first-declared arm is the one guaranteed to survive.
+    Button(ID_BUTTON_CLOSE) {
+        Kill();
+    }
+    // BACK to the hub. MagicMenu is declared in mom_msg.slc (include 55), which
+    // loads BEFORE this file (65), so naming it here is safe in both directions.
+    Button(ID_BUTTON_BACK) {
+        Kill();
+        Message(g.player, 'MagicMenu');
+    }
     Button(ID_MOM_MSG_BTN_FLAME) {
         MomCastFlameStrike(g.player);
         Kill();
     }
-    Button(ID_BUTTON_CLOSE) {
+    // STORE POWER -- the honest third option beside spend-50 and spend-100, and
+    // what makes the body's own promise ("or store your power for later") true.
+    // Banking is simply declining to cast, so the body is a bare Kill(); the
+    // arm exists to SAY so rather than leaving Close to mean two different
+    // things. MOM_MSG_BTN_STORE was authored long ago and never bound.
+    Button(ID_MOM_MSG_BTN_STORE) {
         Kill();
     }
 }
 alertbox 'MomMsgSpellbookChaos' {
     Show();
     Text(ID_MOM_MSG_SPELLBOOK);
+    // FIVE ARMS EXACTLY -- the measured ceiling. Do not add a sixth: it would
+    // not error, it would silently delete whichever arm is declared last.
+    Button(ID_BUTTON_CLOSE) {
+        Kill();
+    }
+    Button(ID_BUTTON_BACK) {
+        Kill();
+        Message(g.player, 'MagicMenu');
+    }
     Button(ID_MOM_MSG_BTN_DEMON) {
         MomCastDemonStrike(g.player);
         Kill();
@@ -47232,7 +47303,7 @@
         MomCastFlameStrike(g.player);
         Kill();
     }
-    Button(ID_BUTTON_CLOSE) {
+    Button(ID_MOM_MSG_BTN_STORE) {
         Kill();
     }
 }
@@ -47262,7 +47333,7 @@
         <v>13</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>16822</v>
+        <v>18006</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
@@ -47570,17 +47641,42 @@
 alertbox 'MomMsgSpellbook' {
     Show();
     Text(ID_MOM_MSG_SPELLBOOK);
+    // CLOSE FIRST -- overflow is dropped from the TAIL of the declaration list,
+    // silently, so the first-declared arm is the one guaranteed to survive.
+    Button(ID_BUTTON_CLOSE) {
+        Kill();
+    }
+    // BACK to the hub. MagicMenu is declared in mom_msg.slc (include 55), which
+    // loads BEFORE this file (65), so naming it here is safe in both directions.
+    Button(ID_BUTTON_BACK) {
+        Kill();
+        Message(g.player, 'MagicMenu');
+    }
     Button(ID_MOM_MSG_BTN_FLAME) {
         MomCastFlameStrike(g.player);
         Kill();
     }
-    Button(ID_BUTTON_CLOSE) {
+    // STORE POWER -- the honest third option beside spend-50 and spend-100, and
+    // what makes the body's own promise ("or store your power for later") true.
+    // Banking is simply declining to cast, so the body is a bare Kill(); the
+    // arm exists to SAY so rather than leaving Close to mean two different
+    // things. MOM_MSG_BTN_STORE was authored long ago and never bound.
+    Button(ID_MOM_MSG_BTN_STORE) {
         Kill();
     }
 }
 alertbox 'MomMsgSpellbookChaos' {
     Show();
     Text(ID_MOM_MSG_SPELLBOOK);
+    // FIVE ARMS EXACTLY -- the measured ceiling. Do not add a sixth: it would
+    // not error, it would silently delete whichever arm is declared last.
+    Button(ID_BUTTON_CLOSE) {
+        Kill();
+    }
+    Button(ID_BUTTON_BACK) {
+        Kill();
+        Message(g.player, 'MagicMenu');
+    }
     Button(ID_MOM_MSG_BTN_DEMON) {
         MomCastDemonStrike(g.player);
         Kill();
@@ -47589,7 +47685,7 @@
         MomCastFlameStrike(g.player);
         Kill();
     }
-    Button(ID_BUTTON_CLOSE) {
+    Button(ID_MOM_MSG_BTN_STORE) {
         Kill();
     }
 }
@@ -48389,7 +48485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -49453,7 +49549,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>MomMsgSlicAlive</t>
+          <t>MomBlessLife</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -49463,7 +49559,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>segment: SLIC liveness confirmation text</t>
+          <t>segment: Life sphere blessing popup</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -49478,7 +49574,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -49495,7 +49591,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>MomBlessLife</t>
+          <t>MomBlessNature</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -49505,7 +49601,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>segment: Life sphere blessing popup</t>
+          <t>segment: Nature sphere blessing popup</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -49520,7 +49616,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>nature</t>
         </is>
       </c>
     </row>
@@ -49537,7 +49633,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>MomBlessNature</t>
+          <t>MomBlessSorcery</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -49547,7 +49643,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>segment: Nature sphere blessing popup</t>
+          <t>segment: Sorcery sphere blessing popup</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -49562,7 +49658,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>sorcery</t>
         </is>
       </c>
     </row>
@@ -49579,7 +49675,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>MomBlessSorcery</t>
+          <t>MomBlessDeath</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -49589,7 +49685,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>segment: Sorcery sphere blessing popup</t>
+          <t>segment: Death sphere blessing popup</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -49604,7 +49700,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>sorcery</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -49621,7 +49717,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>MomBlessDeath</t>
+          <t>MomBlessChaos</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -49631,7 +49727,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>segment: Death sphere blessing popup</t>
+          <t>segment: Chaos sphere blessing popup</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -49646,7 +49742,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -49663,7 +49759,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>MomBlessChaos</t>
+          <t>MomUpkeepDisband</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -49671,11 +49767,7 @@
           <t>messagebox</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>segment: Chaos sphere blessing popup</t>
-        </is>
-      </c>
+      <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr">
         <is>
           <t>C</t>
@@ -49688,7 +49780,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -49705,7 +49797,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>MomUpkeepDisband</t>
+          <t>MomSummonBegun</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -49743,7 +49835,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>MomSummonBegun</t>
+          <t>MomSummonBusy</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -49781,7 +49873,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>MomSummonBusy</t>
+          <t>MomSummonNoMagic</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -49819,7 +49911,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>MomSummonNoMagic</t>
+          <t>MomSummonGuard</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -49827,7 +49919,11 @@
           <t>messagebox</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
+        </is>
+      </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
           <t>C</t>
@@ -49857,7 +49953,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>MomSummonGuard</t>
+          <t>MomSummonBear</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -49867,7 +49963,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
+          <t>segment: Nature summon result (War Bear)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -49899,7 +49995,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>MomSummonBear</t>
+          <t>MomSummonMage</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -49909,7 +50005,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>segment: Nature summon result (War Bear)</t>
+          <t>segment: Sorcery summon result (Mage)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -49941,7 +50037,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>MomSummonMage</t>
+          <t>MomSummonZombie</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -49951,7 +50047,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>segment: Sorcery summon result (Mage)</t>
+          <t>segment: Death summon result (Zombies)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -49983,7 +50079,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>MomSummonZombie</t>
+          <t>MomSummonHound</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -49993,7 +50089,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>segment: Death summon result (Zombies)</t>
+          <t>segment: Chaos summon result (Hell Hound)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -50025,7 +50121,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>MomSummonHound</t>
+          <t>MomSummonNoMana</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -50035,7 +50131,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>segment: Chaos summon result (Hell Hound)</t>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -50067,7 +50163,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>MomSummonNoMana</t>
+          <t>MomMagicPower</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -50077,7 +50173,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+          <t>segment: mana pool / income readout body</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -50104,22 +50200,22 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>MomMagicPower</t>
+          <t>MagicMenu</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>segment: mana pool / income readout body</t>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -50134,39 +50230,39 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>mom_msg.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>MagicMenu</t>
+          <t>MomRecalcMagicPerTurn</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>int_f(int_t mp_1)</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -50188,22 +50284,22 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>MomRecalcMagicPerTurn</t>
+          <t>MomMagicPoolTick</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t mp_1)</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
+          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -50235,17 +50331,17 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>MomMagicPoolTick</t>
+          <t>MomMagicSchoolGrant</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -50260,7 +50356,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -50277,19 +50373,15 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>MomMagicSchoolGrant</t>
+          <t>MomSphereRootGrant</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>apply per-school mana multipliers when a magic advance is granted</t>
-        </is>
-      </c>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="5" t="inlineStr">
         <is>
           <t>M</t>
@@ -50309,25 +50401,29 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>MomSphereRootGrant</t>
+          <t>MomCastFlameStrike</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr"/>
+          <t>void_f(int_t p)</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
+        </is>
+      </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
           <t>M</t>
@@ -50340,7 +50436,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -50357,7 +50453,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>MomCastFlameStrike</t>
+          <t>MomCastDemonStrike</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -50367,7 +50463,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -50382,7 +50478,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -50399,7 +50495,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>MomCastDemonStrike</t>
+          <t>MomSpellShowBook</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -50409,7 +50505,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -50436,22 +50532,22 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>MomSpellShowBook</t>
+          <t>MomSpellMenuTick</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -50466,7 +50562,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -50478,22 +50574,22 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>MomSpellMenuTick</t>
+          <t>MomOpenSpellbook</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
+          <t>UI trigger bound to the control-panel MagicButton</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -50520,22 +50616,22 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>MomOpenSpellbook</t>
+          <t>MomSpellAICast</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>UI trigger bound to the control-panel MagicButton</t>
+          <t>let AI players cast their sphere's spell when mana allows</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -50562,22 +50658,22 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>MomSpellAICast</t>
+          <t>MomMsgSpellbook</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>let AI players cast their sphere's spell when mana allows</t>
+          <t>segment: generic spellbook menu</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -50609,7 +50705,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>MomMsgSpellbook</t>
+          <t>MomMsgSpellbookChaos</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -50619,7 +50715,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>segment: generic spellbook menu</t>
+          <t>segment: Chaos-specific spellbook menu</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -50634,7 +50730,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -50651,7 +50747,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>MomMsgSpellbookChaos</t>
+          <t>MomMsgDemonCast</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -50661,7 +50757,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>segment: Chaos-specific spellbook menu</t>
+          <t>segment: Demon Strike cast confirmation</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -50676,7 +50772,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -50693,7 +50789,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>MomMsgDemonCast</t>
+          <t>MomMsgFlameCast</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -50703,7 +50799,7 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>segment: Demon Strike cast confirmation</t>
+          <t>segment: Flame Strike cast confirmation</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -50735,7 +50831,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>MomMsgFlameCast</t>
+          <t>MomMsgNoTarget</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -50745,7 +50841,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>segment: Flame Strike cast confirmation</t>
+          <t>segment: no enemy unit in range</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -50777,7 +50873,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNoTarget</t>
+          <t>MomMsgNoMana</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -50787,7 +50883,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>segment: no enemy unit in range</t>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -50819,7 +50915,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNoMana</t>
+          <t>MomMsgNotChaos</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -50829,7 +50925,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+          <t>segment: caster's sphere does not grant this spell</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -50844,39 +50940,35 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_ai_magic.slc</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNotChaos</t>
+          <t>MomAiMagicTick</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>segment: caster's sphere does not grant this spell</t>
-        </is>
-      </c>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>?</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -50886,32 +50978,36 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>mom_ai_magic.slc</t>
+          <t>mom_gating.slc</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>MomAiMagicTick</t>
+          <t>mod_CanPlayerHaveAdvance</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr"/>
+          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
+        </is>
+      </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
           <t>?</t>
@@ -50924,7 +51020,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -50941,17 +51037,17 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>mod_CanPlayerHaveAdvance</t>
+          <t>mod_CanCityBuildUnit</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
+          <t>int_f(city_t theCity, int_t theUnit)</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
+          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -50966,7 +51062,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -50983,17 +51079,17 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildUnit</t>
+          <t>mod_CanCityBuildBuilding</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theUnit)</t>
+          <t>int_f(city_t theCity, int_t theBuilding)</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -51025,17 +51121,17 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildBuilding</t>
+          <t>mod_CanCityBuildWonder</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theBuilding)</t>
+          <t>int_f(city_t theCity, int_t theWonder)</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+          <t>same wall for wonders.</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -51050,54 +51146,12 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>mom_gating.slc</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>mod_CanCityBuildWonder</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>int_f(city_t theCity, int_t theWonder)</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>same wall for wonders.</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
           <t>chaos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H65"/>
+  <autoFilter ref="A1:H64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -73,7 +73,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improvements'!$A$1:$H$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'order_mask'!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'players'!$A$1:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'sprite_pick_rules'!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'terrain'!$A$1:$J$27</definedName>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E36" t="n">
         <v>8</v>
@@ -23059,7 +23059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24120,7 +24120,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MomMsgSlicAlive</t>
+          <t>MomBlessLife</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -24130,7 +24130,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>segment: SLIC liveness confirmation text</t>
+          <t>segment: Life sphere blessing popup</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -24145,7 +24145,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -24162,7 +24162,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MomBlessLife</t>
+          <t>MomBlessNature</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>segment: Life sphere blessing popup</t>
+          <t>segment: Nature sphere blessing popup</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -24187,7 +24187,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>nature</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24204,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MomBlessNature</t>
+          <t>MomBlessSorcery</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>segment: Nature sphere blessing popup</t>
+          <t>segment: Sorcery sphere blessing popup</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -24229,7 +24229,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>sorcery</t>
         </is>
       </c>
     </row>
@@ -24246,7 +24246,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MomBlessSorcery</t>
+          <t>MomBlessDeath</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -24256,7 +24256,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>segment: Sorcery sphere blessing popup</t>
+          <t>segment: Death sphere blessing popup</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -24271,7 +24271,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>sorcery</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -24288,7 +24288,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MomBlessDeath</t>
+          <t>MomBlessChaos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -24298,7 +24298,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>segment: Death sphere blessing popup</t>
+          <t>segment: Chaos sphere blessing popup</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -24313,7 +24313,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -24330,7 +24330,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MomBlessChaos</t>
+          <t>MomUpkeepDisband</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -24338,11 +24338,6 @@
           <t>messagebox</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>segment: Chaos sphere blessing popup</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>C</t>
@@ -24355,7 +24350,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24372,7 +24367,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MomUpkeepDisband</t>
+          <t>MomSummonBegun</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -24409,7 +24404,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MomSummonBegun</t>
+          <t>MomSummonBusy</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -24446,7 +24441,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MomSummonBusy</t>
+          <t>MomSummonNoMagic</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -24483,12 +24478,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MomSummonNoMagic</t>
+          <t>MomSummonGuard</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -24520,7 +24520,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MomSummonGuard</t>
+          <t>MomSummonBear</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
+          <t>segment: Nature summon result (War Bear)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MomSummonBear</t>
+          <t>MomSummonMage</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -24572,7 +24572,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>segment: Nature summon result (War Bear)</t>
+          <t>segment: Sorcery summon result (Mage)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MomSummonMage</t>
+          <t>MomSummonZombie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -24614,7 +24614,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>segment: Sorcery summon result (Mage)</t>
+          <t>segment: Death summon result (Zombies)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -24646,7 +24646,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MomSummonZombie</t>
+          <t>MomSummonHound</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -24656,7 +24656,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>segment: Death summon result (Zombies)</t>
+          <t>segment: Chaos summon result (Hell Hound)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -24688,7 +24688,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MomSummonHound</t>
+          <t>MomSummonNoMana</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -24698,7 +24698,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>segment: Chaos summon result (Hell Hound)</t>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MomSummonNoMana</t>
+          <t>MomMagicPower</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -24740,7 +24740,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+          <t>segment: mana pool / income readout body</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -24767,22 +24767,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MomMagicPower</t>
+          <t>MagicMenu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>segment: mana pool / income readout body</t>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -24797,39 +24797,39 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>mom_msg.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MagicMenu</t>
+          <t>MomRecalcMagicPerTurn</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>int_f(int_t mp_1)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -24851,22 +24851,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MomRecalcMagicPerTurn</t>
+          <t>MomMagicPoolTick</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>int_f(int_t mp_1)</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
+          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -24898,17 +24898,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MomMagicPoolTick</t>
+          <t>MomMagicSchoolGrant</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -24923,7 +24923,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -24940,17 +24940,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MomMagicSchoolGrant</t>
+          <t>MomSphereRootGrant</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>apply per-school mana multipliers when a magic advance is granted</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -24972,22 +24967,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MomSphereRootGrant</t>
+          <t>MomCastFlameStrike</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>void_f(int_t p)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -25002,7 +25002,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25019,7 +25019,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MomCastFlameStrike</t>
+          <t>MomCastDemonStrike</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -25029,7 +25029,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -25044,7 +25044,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -25061,7 +25061,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MomCastDemonStrike</t>
+          <t>MomSpellShowBook</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -25098,22 +25098,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MomSpellShowBook</t>
+          <t>MomSpellMenuTick</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -25128,7 +25128,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25140,22 +25140,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MomSpellMenuTick</t>
+          <t>MomOpenSpellbook</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
+          <t>UI trigger bound to the control-panel MagicButton</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -25182,22 +25182,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MomOpenSpellbook</t>
+          <t>MomSpellAICast</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UI trigger bound to the control-panel MagicButton</t>
+          <t>let AI players cast their sphere's spell when mana allows</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -25224,22 +25224,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MomSpellAICast</t>
+          <t>MomMsgSpellbook</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>let AI players cast their sphere's spell when mana allows</t>
+          <t>segment: generic spellbook menu</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -25271,7 +25271,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MomMsgSpellbook</t>
+          <t>MomMsgSpellbookChaos</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>segment: generic spellbook menu</t>
+          <t>segment: Chaos-specific spellbook menu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -25313,7 +25313,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MomMsgSpellbookChaos</t>
+          <t>MomMsgDemonCast</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -25323,7 +25323,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>segment: Chaos-specific spellbook menu</t>
+          <t>segment: Demon Strike cast confirmation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -25338,7 +25338,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25355,7 +25355,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MomMsgDemonCast</t>
+          <t>MomMsgFlameCast</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -25365,7 +25365,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>segment: Demon Strike cast confirmation</t>
+          <t>segment: Flame Strike cast confirmation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -25397,7 +25397,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MomMsgFlameCast</t>
+          <t>MomMsgNoTarget</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -25407,7 +25407,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>segment: Flame Strike cast confirmation</t>
+          <t>segment: no enemy unit in range</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -25439,7 +25439,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MomMsgNoTarget</t>
+          <t>MomMsgNoMana</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>segment: no enemy unit in range</t>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -25481,7 +25481,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MomMsgNoMana</t>
+          <t>MomMsgNotChaos</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -25491,7 +25491,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+          <t>segment: caster's sphere does not grant this spell</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -25506,39 +25506,34 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_ai_magic.slc</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MomMsgNotChaos</t>
+          <t>MomAiMagicTick</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>alertbox</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>segment: caster's sphere does not grant this spell</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>?</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -25548,29 +25543,34 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>mom_ai_magic.slc</t>
+          <t>mom_gating.slc</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MomAiMagicTick</t>
+          <t>mod_CanPlayerHaveAdvance</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -25602,17 +25602,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mod_CanPlayerHaveAdvance</t>
+          <t>mod_CanCityBuildUnit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
+          <t>int_f(city_t theCity, int_t theUnit)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
+          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -25627,7 +25627,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25644,17 +25644,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildUnit</t>
+          <t>mod_CanCityBuildBuilding</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theUnit)</t>
+          <t>int_f(city_t theCity, int_t theBuilding)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -25686,17 +25686,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildBuilding</t>
+          <t>mod_CanCityBuildWonder</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theBuilding)</t>
+          <t>int_f(city_t theCity, int_t theWonder)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+          <t>same wall for wonders.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -25711,54 +25711,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>mom_gating.slc</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>mod_CanCityBuildWonder</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>int_f(city_t theCity, int_t theWonder)</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>same wall for wonders.</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
           <t>chaos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H65"/>
+  <autoFilter ref="A1:H64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44677,6 +44635,7 @@
 {
     int_t r;
     int_t roll;
+    int_t wild;
     r = MomSphereRung[p];
     // NO FLOOR. Rung 0 means 'this tribe has learned no magic of its own
     // sphere', and it must fall through every band below so this function
@@ -44806,6 +44765,76 @@
     }
     // CHAOS (player 5)
     if (p == 5) {
+        wild = Random(100);
+        if (wild &lt; 15) {
+            if (r == 5) {
+                wild = Random(16);
+                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
+                if (wild &lt; 2) { return UnitDB(UNIT_ARCHANGEL); }
+                if (wild &lt; 3) { return UnitDB(UNIT_BEHEMOTH); }
+                if (wild &lt; 4) { return UnitDB(UNIT_COCKATRICE); }
+                if (wild &lt; 5) { return UnitDB(UNIT_DEMON); }
+                if (wild &lt; 6) { return UnitDB(UNIT_GREAT_WYRM); }
+                if (wild &lt; 7) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 8) { return UnitDB(UNIT_PEGASUS); }
+                if (wild &lt; 9) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 10) { return UnitDB(UNIT_STORM_DRAKE); }
+                if (wild &lt; 11) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 12) { return UnitDB(UNIT_UNDEAD_DRAGON); }
+                if (wild &lt; 13) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 14) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 15) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 16) { return UnitDB(UNIT_ZOMBIES); }
+            }
+            if (r == 4) {
+                wild = Random(12);
+                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
+                if (wild &lt; 2) { return UnitDB(UNIT_BEHEMOTH); }
+                if (wild &lt; 3) { return UnitDB(UNIT_COCKATRICE); }
+                if (wild &lt; 4) { return UnitDB(UNIT_DEMON); }
+                if (wild &lt; 5) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 6) { return UnitDB(UNIT_PEGASUS); }
+                if (wild &lt; 7) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 8) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 9) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 10) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 11) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
+            }
+            if (r == 3) {
+                wild = Random(12);
+                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
+                if (wild &lt; 2) { return UnitDB(UNIT_BEHEMOTH); }
+                if (wild &lt; 3) { return UnitDB(UNIT_COCKATRICE); }
+                if (wild &lt; 4) { return UnitDB(UNIT_DEMON); }
+                if (wild &lt; 5) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 6) { return UnitDB(UNIT_PEGASUS); }
+                if (wild &lt; 7) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 8) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 9) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 10) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 11) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
+            }
+            if (r == 2) {
+                wild = Random(8);
+                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
+                if (wild &lt; 2) { return UnitDB(UNIT_COCKATRICE); }
+                if (wild &lt; 3) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 4) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 5) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 6) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 7) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 8) { return UnitDB(UNIT_ZOMBIES); }
+            }
+            if (r == 1) {
+                wild = Random(4);
+                if (wild &lt; 1) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 2) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 3) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 4) { return UnitDB(UNIT_ZOMBIES); }
+            }
+        }
         if (r == 5) {
             if (roll &lt; 16) { return UnitDB(UNIT_HELL_HOUNDS); }
             if (roll &lt; 32) { return UnitDB(UNIT_GARGOYLE); }
@@ -44917,7 +44946,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>13535</v>
+        <v>17422</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
@@ -44994,6 +45023,7 @@
 {
     int_t r;
     int_t roll;
+    int_t wild;
     r = MomSphereRung[p];
     // NO FLOOR. Rung 0 means 'this tribe has learned no magic of its own
     // sphere', and it must fall through every band below so this function
@@ -45123,6 +45153,76 @@
     }
     // CHAOS (player 5)
     if (p == 5) {
+        wild = Random(100);
+        if (wild &lt; 15) {
+            if (r == 5) {
+                wild = Random(16);
+                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
+                if (wild &lt; 2) { return UnitDB(UNIT_ARCHANGEL); }
+                if (wild &lt; 3) { return UnitDB(UNIT_BEHEMOTH); }
+                if (wild &lt; 4) { return UnitDB(UNIT_COCKATRICE); }
+                if (wild &lt; 5) { return UnitDB(UNIT_DEMON); }
+                if (wild &lt; 6) { return UnitDB(UNIT_GREAT_WYRM); }
+                if (wild &lt; 7) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 8) { return UnitDB(UNIT_PEGASUS); }
+                if (wild &lt; 9) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 10) { return UnitDB(UNIT_STORM_DRAKE); }
+                if (wild &lt; 11) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 12) { return UnitDB(UNIT_UNDEAD_DRAGON); }
+                if (wild &lt; 13) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 14) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 15) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 16) { return UnitDB(UNIT_ZOMBIES); }
+            }
+            if (r == 4) {
+                wild = Random(12);
+                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
+                if (wild &lt; 2) { return UnitDB(UNIT_BEHEMOTH); }
+                if (wild &lt; 3) { return UnitDB(UNIT_COCKATRICE); }
+                if (wild &lt; 4) { return UnitDB(UNIT_DEMON); }
+                if (wild &lt; 5) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 6) { return UnitDB(UNIT_PEGASUS); }
+                if (wild &lt; 7) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 8) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 9) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 10) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 11) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
+            }
+            if (r == 3) {
+                wild = Random(12);
+                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
+                if (wild &lt; 2) { return UnitDB(UNIT_BEHEMOTH); }
+                if (wild &lt; 3) { return UnitDB(UNIT_COCKATRICE); }
+                if (wild &lt; 4) { return UnitDB(UNIT_DEMON); }
+                if (wild &lt; 5) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 6) { return UnitDB(UNIT_PEGASUS); }
+                if (wild &lt; 7) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 8) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 9) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 10) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 11) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
+            }
+            if (r == 2) {
+                wild = Random(8);
+                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
+                if (wild &lt; 2) { return UnitDB(UNIT_COCKATRICE); }
+                if (wild &lt; 3) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 4) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 5) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 6) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 7) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 8) { return UnitDB(UNIT_ZOMBIES); }
+            }
+            if (r == 1) {
+                wild = Random(4);
+                if (wild &lt; 1) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 2) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 3) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 4) { return UnitDB(UNIT_ZOMBIES); }
+            }
+        }
         if (r == 5) {
             if (roll &lt; 16) { return UnitDB(UNIT_HELL_HOUNDS); }
             if (roll &lt; 32) { return UnitDB(UNIT_GARGOYLE); }

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -83,7 +83,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'unit_block_overrides'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'unit_factions'!$A$1:$I$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'slic'!$A$1:$L$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$64</definedName>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E46" t="n">
         <v>17</v>
@@ -36995,7 +36995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42585,8 +42585,356 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Skeletons</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2d</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1f</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Rfg</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>ICON_UNIT_SKELETONS</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>SPRITE_SKELETONS</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>SOUND_SELECT1_SKELETONS</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>SOUND_MOVE_SKELETONS</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SOUND_ATTACK_SKELETONS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>death</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Dracolich</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>14a</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2f</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Sth</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>ICON_UNIT_DRACOLICH</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>SPRITE_DRACOLICH</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>SOUND_SELECT1_DRACOLICH</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>SOUND_MOVE_DRACOLICH</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SOUND_ATTACK_DRACOLICH</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>death</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Death Knight</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>8a</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1f</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Mys</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>ICON_UNIT_DEATH_KNIGHT</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>SPRITE_DEATH_KNIGHT</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>SOUND_SELECT1_DEATH_KNIGHT</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>SOUND_MOVE_DEATH_KNIGHT</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SOUND_ATTACK_DEATH_KNIGHT</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>death</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Lich</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>6a</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>8d</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2f</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>ICON_UNIT_LICH</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>SPRITE_LICH</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>SOUND_SELECT1_LICH</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>SOUND_MOVE_LICH</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SOUND_ATTACK_LICH</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>death</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q64"/>
+  <autoFilter ref="A1:Q68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44740,26 +45088,33 @@
     // DEATH (player 4)
     if (p == 4) {
         if (r == 5) {
+            if (roll &lt; 6) { return UnitDB(UNIT_SKELETONS); }
+            if (roll &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
+            if (roll &lt; 24) { return UnitDB(UNIT_WRAITH); }
+            if (roll &lt; 36) { return UnitDB(UNIT_DEMON); }
+            if (roll &lt; 48) { return UnitDB(UNIT_DRACOLICH); }
+            if (roll &lt; 100) { return UnitDB(UNIT_UNDEAD_DRAGON); }
+        }
+        if (r == 4) {
+            if (roll &lt; 8) { return UnitDB(UNIT_SKELETONS); }
             if (roll &lt; 16) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 32) { return UnitDB(UNIT_WRAITH); }
             if (roll &lt; 48) { return UnitDB(UNIT_DEMON); }
-            if (roll &lt; 100) { return UnitDB(UNIT_UNDEAD_DRAGON); }
-        }
-        if (r == 4) {
-            if (roll &lt; 25) { return UnitDB(UNIT_ZOMBIES); }
-            if (roll &lt; 50) { return UnitDB(UNIT_WRAITH); }
-            if (roll &lt; 100) { return UnitDB(UNIT_DEMON); }
+            if (roll &lt; 100) { return UnitDB(UNIT_DRACOLICH); }
         }
         if (r == 3) {
+            if (roll &lt; 12) { return UnitDB(UNIT_SKELETONS); }
             if (roll &lt; 25) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 50) { return UnitDB(UNIT_WRAITH); }
             if (roll &lt; 100) { return UnitDB(UNIT_DEMON); }
         }
         if (r == 2) {
+            if (roll &lt; 25) { return UnitDB(UNIT_SKELETONS); }
             if (roll &lt; 50) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 100) { return UnitDB(UNIT_WRAITH); }
         }
         if (r == 1) {
+            if (roll &lt; 50) { return UnitDB(UNIT_SKELETONS); }
             if (roll &lt; 100) { return UnitDB(UNIT_ZOMBIES); }
         }
     }
@@ -44768,26 +45123,45 @@
         wild = Random(100);
         if (wild &lt; 15) {
             if (r == 5) {
-                wild = Random(16);
+                wild = Random(18);
                 if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
                 if (wild &lt; 2) { return UnitDB(UNIT_ARCHANGEL); }
                 if (wild &lt; 3) { return UnitDB(UNIT_BEHEMOTH); }
                 if (wild &lt; 4) { return UnitDB(UNIT_COCKATRICE); }
                 if (wild &lt; 5) { return UnitDB(UNIT_DEMON); }
-                if (wild &lt; 6) { return UnitDB(UNIT_GREAT_WYRM); }
-                if (wild &lt; 7) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-                if (wild &lt; 8) { return UnitDB(UNIT_PEGASUS); }
-                if (wild &lt; 9) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
-                if (wild &lt; 10) { return UnitDB(UNIT_STORM_DRAKE); }
-                if (wild &lt; 11) { return UnitDB(UNIT_STORM_GIANT); }
-                if (wild &lt; 12) { return UnitDB(UNIT_UNDEAD_DRAGON); }
-                if (wild &lt; 13) { return UnitDB(UNIT_UNICORN); }
-                if (wild &lt; 14) { return UnitDB(UNIT_WARBEARS); }
-                if (wild &lt; 15) { return UnitDB(UNIT_WRAITH); }
-                if (wild &lt; 16) { return UnitDB(UNIT_ZOMBIES); }
+                if (wild &lt; 6) { return UnitDB(UNIT_DRACOLICH); }
+                if (wild &lt; 7) { return UnitDB(UNIT_GREAT_WYRM); }
+                if (wild &lt; 8) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 9) { return UnitDB(UNIT_PEGASUS); }
+                if (wild &lt; 10) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 11) { return UnitDB(UNIT_SKELETONS); }
+                if (wild &lt; 12) { return UnitDB(UNIT_STORM_DRAKE); }
+                if (wild &lt; 13) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 14) { return UnitDB(UNIT_UNDEAD_DRAGON); }
+                if (wild &lt; 15) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 16) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 17) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 18) { return UnitDB(UNIT_ZOMBIES); }
             }
             if (r == 4) {
-                wild = Random(12);
+                wild = Random(14);
+                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
+                if (wild &lt; 2) { return UnitDB(UNIT_BEHEMOTH); }
+                if (wild &lt; 3) { return UnitDB(UNIT_COCKATRICE); }
+                if (wild &lt; 4) { return UnitDB(UNIT_DEMON); }
+                if (wild &lt; 5) { return UnitDB(UNIT_DRACOLICH); }
+                if (wild &lt; 6) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 7) { return UnitDB(UNIT_PEGASUS); }
+                if (wild &lt; 8) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 9) { return UnitDB(UNIT_SKELETONS); }
+                if (wild &lt; 10) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 11) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 12) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 13) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 14) { return UnitDB(UNIT_ZOMBIES); }
+            }
+            if (r == 3) {
+                wild = Random(13);
                 if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
                 if (wild &lt; 2) { return UnitDB(UNIT_BEHEMOTH); }
                 if (wild &lt; 3) { return UnitDB(UNIT_COCKATRICE); }
@@ -44795,44 +45169,32 @@
                 if (wild &lt; 5) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
                 if (wild &lt; 6) { return UnitDB(UNIT_PEGASUS); }
                 if (wild &lt; 7) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
-                if (wild &lt; 8) { return UnitDB(UNIT_STORM_GIANT); }
-                if (wild &lt; 9) { return UnitDB(UNIT_UNICORN); }
-                if (wild &lt; 10) { return UnitDB(UNIT_WARBEARS); }
-                if (wild &lt; 11) { return UnitDB(UNIT_WRAITH); }
-                if (wild &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
-            }
-            if (r == 3) {
-                wild = Random(12);
-                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
-                if (wild &lt; 2) { return UnitDB(UNIT_BEHEMOTH); }
-                if (wild &lt; 3) { return UnitDB(UNIT_COCKATRICE); }
-                if (wild &lt; 4) { return UnitDB(UNIT_DEMON); }
-                if (wild &lt; 5) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-                if (wild &lt; 6) { return UnitDB(UNIT_PEGASUS); }
-                if (wild &lt; 7) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
-                if (wild &lt; 8) { return UnitDB(UNIT_STORM_GIANT); }
-                if (wild &lt; 9) { return UnitDB(UNIT_UNICORN); }
-                if (wild &lt; 10) { return UnitDB(UNIT_WARBEARS); }
-                if (wild &lt; 11) { return UnitDB(UNIT_WRAITH); }
-                if (wild &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
+                if (wild &lt; 8) { return UnitDB(UNIT_SKELETONS); }
+                if (wild &lt; 9) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 10) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 11) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 12) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 13) { return UnitDB(UNIT_ZOMBIES); }
             }
             if (r == 2) {
-                wild = Random(8);
+                wild = Random(9);
                 if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
                 if (wild &lt; 2) { return UnitDB(UNIT_COCKATRICE); }
                 if (wild &lt; 3) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
                 if (wild &lt; 4) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
-                if (wild &lt; 5) { return UnitDB(UNIT_UNICORN); }
-                if (wild &lt; 6) { return UnitDB(UNIT_WARBEARS); }
-                if (wild &lt; 7) { return UnitDB(UNIT_WRAITH); }
-                if (wild &lt; 8) { return UnitDB(UNIT_ZOMBIES); }
+                if (wild &lt; 5) { return UnitDB(UNIT_SKELETONS); }
+                if (wild &lt; 6) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 7) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 8) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 9) { return UnitDB(UNIT_ZOMBIES); }
             }
             if (r == 1) {
-                wild = Random(4);
+                wild = Random(5);
                 if (wild &lt; 1) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
                 if (wild &lt; 2) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
-                if (wild &lt; 3) { return UnitDB(UNIT_WARBEARS); }
-                if (wild &lt; 4) { return UnitDB(UNIT_ZOMBIES); }
+                if (wild &lt; 3) { return UnitDB(UNIT_SKELETONS); }
+                if (wild &lt; 4) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 5) { return UnitDB(UNIT_ZOMBIES); }
             }
         }
         if (r == 5) {
@@ -44871,6 +45233,7 @@
     if (unitType == UnitDB(UNIT_BEHEMOTH)) { return 3; }
     if (unitType == UnitDB(UNIT_COCKATRICE)) { return 2; }
     if (unitType == UnitDB(UNIT_DEMON)) { return 3; }
+    if (unitType == UnitDB(UNIT_DRACOLICH)) { return 4; }
     if (unitType == UnitDB(UNIT_EFREET)) { return 3; }
     if (unitType == UnitDB(UNIT_GARGOYLE)) { return 2; }
     if (unitType == UnitDB(UNIT_GREAT_WYRM)) { return 5; }
@@ -44879,6 +45242,7 @@
     if (unitType == UnitDB(UNIT_HYDRA)) { return 5; }
     if (unitType == UnitDB(UNIT_PEGASUS)) { return 3; }
     if (unitType == UnitDB(UNIT_PHANTOM_WARRIORS)) { return 1; }
+    if (unitType == UnitDB(UNIT_SKELETONS)) { return 1; }
     if (unitType == UnitDB(UNIT_STORM_DRAKE)) { return 5; }
     if (unitType == UnitDB(UNIT_STORM_GIANT)) { return 3; }
     if (unitType == UnitDB(UNIT_UNDEAD_DRAGON)) { return 5; }
@@ -44946,7 +45310,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>17422</v>
+        <v>18430</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
@@ -45128,26 +45492,33 @@
     // DEATH (player 4)
     if (p == 4) {
         if (r == 5) {
+            if (roll &lt; 6) { return UnitDB(UNIT_SKELETONS); }
+            if (roll &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
+            if (roll &lt; 24) { return UnitDB(UNIT_WRAITH); }
+            if (roll &lt; 36) { return UnitDB(UNIT_DEMON); }
+            if (roll &lt; 48) { return UnitDB(UNIT_DRACOLICH); }
+            if (roll &lt; 100) { return UnitDB(UNIT_UNDEAD_DRAGON); }
+        }
+        if (r == 4) {
+            if (roll &lt; 8) { return UnitDB(UNIT_SKELETONS); }
             if (roll &lt; 16) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 32) { return UnitDB(UNIT_WRAITH); }
             if (roll &lt; 48) { return UnitDB(UNIT_DEMON); }
-            if (roll &lt; 100) { return UnitDB(UNIT_UNDEAD_DRAGON); }
-        }
-        if (r == 4) {
-            if (roll &lt; 25) { return UnitDB(UNIT_ZOMBIES); }
-            if (roll &lt; 50) { return UnitDB(UNIT_WRAITH); }
-            if (roll &lt; 100) { return UnitDB(UNIT_DEMON); }
+            if (roll &lt; 100) { return UnitDB(UNIT_DRACOLICH); }
         }
         if (r == 3) {
+            if (roll &lt; 12) { return UnitDB(UNIT_SKELETONS); }
             if (roll &lt; 25) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 50) { return UnitDB(UNIT_WRAITH); }
             if (roll &lt; 100) { return UnitDB(UNIT_DEMON); }
         }
         if (r == 2) {
+            if (roll &lt; 25) { return UnitDB(UNIT_SKELETONS); }
             if (roll &lt; 50) { return UnitDB(UNIT_ZOMBIES); }
             if (roll &lt; 100) { return UnitDB(UNIT_WRAITH); }
         }
         if (r == 1) {
+            if (roll &lt; 50) { return UnitDB(UNIT_SKELETONS); }
             if (roll &lt; 100) { return UnitDB(UNIT_ZOMBIES); }
         }
     }
@@ -45156,26 +45527,45 @@
         wild = Random(100);
         if (wild &lt; 15) {
             if (r == 5) {
-                wild = Random(16);
+                wild = Random(18);
                 if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
                 if (wild &lt; 2) { return UnitDB(UNIT_ARCHANGEL); }
                 if (wild &lt; 3) { return UnitDB(UNIT_BEHEMOTH); }
                 if (wild &lt; 4) { return UnitDB(UNIT_COCKATRICE); }
                 if (wild &lt; 5) { return UnitDB(UNIT_DEMON); }
-                if (wild &lt; 6) { return UnitDB(UNIT_GREAT_WYRM); }
-                if (wild &lt; 7) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-                if (wild &lt; 8) { return UnitDB(UNIT_PEGASUS); }
-                if (wild &lt; 9) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
-                if (wild &lt; 10) { return UnitDB(UNIT_STORM_DRAKE); }
-                if (wild &lt; 11) { return UnitDB(UNIT_STORM_GIANT); }
-                if (wild &lt; 12) { return UnitDB(UNIT_UNDEAD_DRAGON); }
-                if (wild &lt; 13) { return UnitDB(UNIT_UNICORN); }
-                if (wild &lt; 14) { return UnitDB(UNIT_WARBEARS); }
-                if (wild &lt; 15) { return UnitDB(UNIT_WRAITH); }
-                if (wild &lt; 16) { return UnitDB(UNIT_ZOMBIES); }
+                if (wild &lt; 6) { return UnitDB(UNIT_DRACOLICH); }
+                if (wild &lt; 7) { return UnitDB(UNIT_GREAT_WYRM); }
+                if (wild &lt; 8) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 9) { return UnitDB(UNIT_PEGASUS); }
+                if (wild &lt; 10) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 11) { return UnitDB(UNIT_SKELETONS); }
+                if (wild &lt; 12) { return UnitDB(UNIT_STORM_DRAKE); }
+                if (wild &lt; 13) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 14) { return UnitDB(UNIT_UNDEAD_DRAGON); }
+                if (wild &lt; 15) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 16) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 17) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 18) { return UnitDB(UNIT_ZOMBIES); }
             }
             if (r == 4) {
-                wild = Random(12);
+                wild = Random(14);
+                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
+                if (wild &lt; 2) { return UnitDB(UNIT_BEHEMOTH); }
+                if (wild &lt; 3) { return UnitDB(UNIT_COCKATRICE); }
+                if (wild &lt; 4) { return UnitDB(UNIT_DEMON); }
+                if (wild &lt; 5) { return UnitDB(UNIT_DRACOLICH); }
+                if (wild &lt; 6) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
+                if (wild &lt; 7) { return UnitDB(UNIT_PEGASUS); }
+                if (wild &lt; 8) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
+                if (wild &lt; 9) { return UnitDB(UNIT_SKELETONS); }
+                if (wild &lt; 10) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 11) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 12) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 13) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 14) { return UnitDB(UNIT_ZOMBIES); }
+            }
+            if (r == 3) {
+                wild = Random(13);
                 if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
                 if (wild &lt; 2) { return UnitDB(UNIT_BEHEMOTH); }
                 if (wild &lt; 3) { return UnitDB(UNIT_COCKATRICE); }
@@ -45183,44 +45573,32 @@
                 if (wild &lt; 5) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
                 if (wild &lt; 6) { return UnitDB(UNIT_PEGASUS); }
                 if (wild &lt; 7) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
-                if (wild &lt; 8) { return UnitDB(UNIT_STORM_GIANT); }
-                if (wild &lt; 9) { return UnitDB(UNIT_UNICORN); }
-                if (wild &lt; 10) { return UnitDB(UNIT_WARBEARS); }
-                if (wild &lt; 11) { return UnitDB(UNIT_WRAITH); }
-                if (wild &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
-            }
-            if (r == 3) {
-                wild = Random(12);
-                if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
-                if (wild &lt; 2) { return UnitDB(UNIT_BEHEMOTH); }
-                if (wild &lt; 3) { return UnitDB(UNIT_COCKATRICE); }
-                if (wild &lt; 4) { return UnitDB(UNIT_DEMON); }
-                if (wild &lt; 5) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
-                if (wild &lt; 6) { return UnitDB(UNIT_PEGASUS); }
-                if (wild &lt; 7) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
-                if (wild &lt; 8) { return UnitDB(UNIT_STORM_GIANT); }
-                if (wild &lt; 9) { return UnitDB(UNIT_UNICORN); }
-                if (wild &lt; 10) { return UnitDB(UNIT_WARBEARS); }
-                if (wild &lt; 11) { return UnitDB(UNIT_WRAITH); }
-                if (wild &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
+                if (wild &lt; 8) { return UnitDB(UNIT_SKELETONS); }
+                if (wild &lt; 9) { return UnitDB(UNIT_STORM_GIANT); }
+                if (wild &lt; 10) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 11) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 12) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 13) { return UnitDB(UNIT_ZOMBIES); }
             }
             if (r == 2) {
-                wild = Random(8);
+                wild = Random(9);
                 if (wild &lt; 1) { return UnitDB(UNIT_AIR_ELEMENTAL); }
                 if (wild &lt; 2) { return UnitDB(UNIT_COCKATRICE); }
                 if (wild &lt; 3) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
                 if (wild &lt; 4) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
-                if (wild &lt; 5) { return UnitDB(UNIT_UNICORN); }
-                if (wild &lt; 6) { return UnitDB(UNIT_WARBEARS); }
-                if (wild &lt; 7) { return UnitDB(UNIT_WRAITH); }
-                if (wild &lt; 8) { return UnitDB(UNIT_ZOMBIES); }
+                if (wild &lt; 5) { return UnitDB(UNIT_SKELETONS); }
+                if (wild &lt; 6) { return UnitDB(UNIT_UNICORN); }
+                if (wild &lt; 7) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 8) { return UnitDB(UNIT_WRAITH); }
+                if (wild &lt; 9) { return UnitDB(UNIT_ZOMBIES); }
             }
             if (r == 1) {
-                wild = Random(4);
+                wild = Random(5);
                 if (wild &lt; 1) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
                 if (wild &lt; 2) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
-                if (wild &lt; 3) { return UnitDB(UNIT_WARBEARS); }
-                if (wild &lt; 4) { return UnitDB(UNIT_ZOMBIES); }
+                if (wild &lt; 3) { return UnitDB(UNIT_SKELETONS); }
+                if (wild &lt; 4) { return UnitDB(UNIT_WARBEARS); }
+                if (wild &lt; 5) { return UnitDB(UNIT_ZOMBIES); }
             }
         }
         if (r == 5) {
@@ -45259,6 +45637,7 @@
     if (unitType == UnitDB(UNIT_BEHEMOTH)) { return 3; }
     if (unitType == UnitDB(UNIT_COCKATRICE)) { return 2; }
     if (unitType == UnitDB(UNIT_DEMON)) { return 3; }
+    if (unitType == UnitDB(UNIT_DRACOLICH)) { return 4; }
     if (unitType == UnitDB(UNIT_EFREET)) { return 3; }
     if (unitType == UnitDB(UNIT_GARGOYLE)) { return 2; }
     if (unitType == UnitDB(UNIT_GREAT_WYRM)) { return 5; }
@@ -45267,6 +45646,7 @@
     if (unitType == UnitDB(UNIT_HYDRA)) { return 5; }
     if (unitType == UnitDB(UNIT_PEGASUS)) { return 3; }
     if (unitType == UnitDB(UNIT_PHANTOM_WARRIORS)) { return 1; }
+    if (unitType == UnitDB(UNIT_SKELETONS)) { return 1; }
     if (unitType == UnitDB(UNIT_STORM_DRAKE)) { return 5; }
     if (unitType == UnitDB(UNIT_STORM_GIANT)) { return 3; }
     if (unitType == UnitDB(UNIT_UNDEAD_DRAGON)) { return 5; }
@@ -48235,12 +48615,16 @@
         || theUnit == UnitDB(UNIT_WARLOCK)
         ) { return 0; }
     }
-    // DEATH -- 7 block(s)
+    // DEATH -- 11 block(s)
     if (theCity.owner != 4) {
-        if (theUnit == UnitDB(UNIT_DEMON)
+        if (theUnit == UnitDB(UNIT_DEATH_KNIGHT)
+        || theUnit == UnitDB(UNIT_DEMON)
+        || theUnit == UnitDB(UNIT_DRACOLICH)
+        || theUnit == UnitDB(UNIT_LICH)
         || theUnit == UnitDB(UNIT_MALLEUS)
         || theUnit == UnitDB(UNIT_MINION)
         || theUnit == UnitDB(UNIT_RJAK)
+        || theUnit == UnitDB(UNIT_SKELETONS)
         || theUnit == UnitDB(UNIT_UNDEAD_DRAGON)
         || theUnit == UnitDB(UNIT_WRAITH)
         || theUnit == UnitDB(UNIT_ZOMBIES)
@@ -48322,7 +48706,7 @@
         <v>4</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>7699</v>
+        <v>7878</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
@@ -48445,12 +48829,16 @@
         || theUnit == UnitDB(UNIT_WARLOCK)
         ) { return 0; }
     }
-    // DEATH -- 7 block(s)
+    // DEATH -- 11 block(s)
     if (theCity.owner != 4) {
-        if (theUnit == UnitDB(UNIT_DEMON)
+        if (theUnit == UnitDB(UNIT_DEATH_KNIGHT)
+        || theUnit == UnitDB(UNIT_DEMON)
+        || theUnit == UnitDB(UNIT_DRACOLICH)
+        || theUnit == UnitDB(UNIT_LICH)
         || theUnit == UnitDB(UNIT_MALLEUS)
         || theUnit == UnitDB(UNIT_MINION)
         || theUnit == UnitDB(UNIT_RJAK)
+        || theUnit == UnitDB(UNIT_SKELETONS)
         || theUnit == UnitDB(UNIT_UNDEAD_DRAGON)
         || theUnit == UnitDB(UNIT_WRAITH)
         || theUnit == UnitDB(UNIT_ZOMBIES)
@@ -51162,7 +51550,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>death</t>
         </is>
       </c>
     </row>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -85,8 +85,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'slic'!$A$1:$L$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'slic'!$A$1:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25627,7 +25627,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -43730,7 +43730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -43836,7 +43836,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4449</v>
+        <v>4549</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
@@ -43911,7 +43911,8 @@
 // Per-tribe gating via the engine's four mod functions. Last: it defines only
 // int_f mod_* segments, calls into nothing, and must be able to name every
 // UNIT_/IMPROVE_/ADVANCE_ symbol the other modules assume exists.
-#include "mom_gating.slc"</t>
+#include "mom_gating.slc"
+#include "mom_probe.slc"</t>
         </is>
       </c>
     </row>
@@ -43936,7 +43937,8 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>unit_t MomSummonUnit[160];   // 5 players x 32 slots -- the creature handle
+          <t>int_t MomSphere[31];
+unit_t MomSummonUnit[160];   // 5 players x 32 slots -- the creature handle
 int_t  MomSummonRung[160];   // its rung 1..5; 0 == FREE SLOT
 int_t  MomUpkeepDisp;        // display scalars for the 'j' MAGIC STATUS panel
 int_t  MomNetDisp;           // net = generation - upkeep, may be negative
@@ -43966,36 +43968,35 @@
         <is>
           <t>int_f MomPlayerIsLife(int_t p_1)
 {
-    // Player 1 == Tribes of Life (civ #1). Numeric index, not TRIBES_LIFE (undefined in SLIC).
-    if (p_1 == 1) {
+    if (MomSphere[p_1] == 1) {
         return 1;
     }
     return 0;
 }
 int_f MomPlayerIsNature(int_t p_2)
 {
-    if (p_2 == 2) {
+    if (MomSphere[p_2] == 2) {
         return 1;
     }
     return 0;
 }
 int_f MomPlayerIsSorcery(int_t p_3)
 {
-    if (p_3 == 3) {
+    if (MomSphere[p_3] == 3) {
         return 1;
     }
     return 0;
 }
 int_f MomPlayerIsDeath(int_t p_4)
 {
-    if (p_4 == 4) {
+    if (MomSphere[p_4] == 4) {
         return 1;
     }
     return 0;
 }
 int_f MomPlayerIsChaos(int_t p_5)
 {
-    if (p_5 == 5) {
+    if (MomSphere[p_5] == 5) {
         return 1;
     }
     return 0;
@@ -44243,14 +44244,38 @@
 }</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) 'MomSphereIdentify' post {
+    int_t sp;
+    sp = player[0];
+    // Guard the index before touching the array, as everywhere else in this mod:
+    // player 0 is the barbarian and indexing the sphere arrays for it was the
+    // original turn-10 crash.
+    if (sp &gt;= 0 &amp;&amp; sp &lt;= 30) {
+        MomSphere[sp] = 0;
+        if (PlayerCivilization(sp) == CivilizationIndex("TRIBES_LIFE")) {
+            MomSphere[sp] = 1;
+        } elseif (PlayerCivilization(sp) == CivilizationIndex("TRIBES_NATURE")) {
+            MomSphere[sp] = 2;
+        } elseif (PlayerCivilization(sp) == CivilizationIndex("TRIBES_SORCERY")) {
+            MomSphere[sp] = 3;
+        } elseif (PlayerCivilization(sp) == CivilizationIndex("TRIBES_DEATH")) {
+            MomSphere[sp] = 4;
+        } elseif (PlayerCivilization(sp) == CivilizationIndex("TRIBES_CHAOS")) {
+            MomSphere[sp] = 5;
+        }
+    }
+}</t>
+        </is>
+      </c>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>18256</v>
+        <v>21179</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
@@ -44268,38 +44293,90 @@
 //     quoted string literal (slicfunc.cpp: SA_TYPE_HARD_STRING, looked up via StringDB).
 //     BuildingDB() refs or variables raise "Wrong type of argument".
 //   Helpers take int_t p (a player index); callers pass the event-local player[0].
+// Seat -&gt; sphere, 1..5, 0 == not a MoM tribe. Written only by MomSphereIdentify.
+int_t MomSphere[31];
+// ---------------------------------------------------------------------------
+// SPHERE IDENTITY COMES FROM THE CIVILISATION, NOT THE SEAT (2026-08-04).
+//
+// These predicates used to be `p == 1`, `p == 2` ... with a comment asserting
+// "Player 1 == Tribes of Life (civ #1)". That premise is FALSE and the comment
+// was the only thing defending it. The New Game screen has an EMPIRE selector:
+// it defaults to Tribes of Nature while the human sits at SEAT 1, so the human
+// was Nature and received LIFE's magic. Visible in a build list -- playing
+// Tribes of Nature, the Build Manager offered Guardian Spirit, Life's rung-1
+// creature, because mod_CanCityBuildUnit walled by seat.
+//
+// The seat is now resolved to a sphere ONCE PER TURN, in MomSphereIdentify
+// below, and every predicate reads that array. Three reasons it is an array and
+// not a function call:
+//
+//   * CALL DEPTH. These predicates are already called FROM handlers, and
+//     several are called from inside other user functions. Adding a
+//     PlayerCivilization() lookup inside them is free (it is a builtin), but
+//     making them call another USER function would build a 2-level chain, which
+//     is the documented 0xC0000005.
+//   * COST. PlayerCivilization/CivilizationIndex per predicate per call would
+//     run dozens of times a turn for an answer that cannot change mid-game.
+//   * ONE WRITER. The mapping is established in exactly one place, so a seat
+//     that is not a tribe reads 0 everywhere rather than accidentally matching.
+//
+// CivilizationIndex takes a QUOTED civ record name ("TRIBES_LIFE" from
+// civilisation.txt), unlike UnitDB()/AdvanceDB() which take bare idents -- the
+// same split documented in slic-builtin-ident-quoting-splits. Verified against
+// 484 call sites of this idiom in Ages of Man.
+// ---------------------------------------------------------------------------
+HandleEvent(BeginTurn) 'MomSphereIdentify' post {
+    int_t sp;
+    sp = player[0];
+    // Guard the index before touching the array, as everywhere else in this mod:
+    // player 0 is the barbarian and indexing the sphere arrays for it was the
+    // original turn-10 crash.
+    if (sp &gt;= 0 &amp;&amp; sp &lt;= 30) {
+        MomSphere[sp] = 0;
+        if (PlayerCivilization(sp) == CivilizationIndex("TRIBES_LIFE")) {
+            MomSphere[sp] = 1;
+        } elseif (PlayerCivilization(sp) == CivilizationIndex("TRIBES_NATURE")) {
+            MomSphere[sp] = 2;
+        } elseif (PlayerCivilization(sp) == CivilizationIndex("TRIBES_SORCERY")) {
+            MomSphere[sp] = 3;
+        } elseif (PlayerCivilization(sp) == CivilizationIndex("TRIBES_DEATH")) {
+            MomSphere[sp] = 4;
+        } elseif (PlayerCivilization(sp) == CivilizationIndex("TRIBES_CHAOS")) {
+            MomSphere[sp] = 5;
+        }
+    }
+}
 int_f MomPlayerIsLife(int_t p_1)
 {
-    // Player 1 == Tribes of Life (civ #1). Numeric index, not TRIBES_LIFE (undefined in SLIC).
-    if (p_1 == 1) {
+    if (MomSphere[p_1] == 1) {
         return 1;
     }
     return 0;
 }
 int_f MomPlayerIsNature(int_t p_2)
 {
-    if (p_2 == 2) {
+    if (MomSphere[p_2] == 2) {
         return 1;
     }
     return 0;
 }
 int_f MomPlayerIsSorcery(int_t p_3)
 {
-    if (p_3 == 3) {
+    if (MomSphere[p_3] == 3) {
         return 1;
     }
     return 0;
 }
 int_f MomPlayerIsDeath(int_t p_4)
 {
-    if (p_4 == 4) {
+    if (MomSphere[p_4] == 4) {
         return 1;
     }
     return 0;
 }
 int_f MomPlayerIsChaos(int_t p_5)
 {
-    if (p_5 == 5) {
+    if (MomSphere[p_5] == 5) {
         return 1;
     }
     return 0;
@@ -45008,7 +45085,7 @@
     // rather than flooring here (gate_mana_upkeep.py assertion 12).
     roll = Random(100);
     // LIFE (player 1)
-    if (p == 1) {
+    if (MomSphere[p] == 1) {
         if (r == 5) {
             if (roll &lt; 16) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
             if (roll &lt; 32) { return UnitDB(UNIT_UNICORN); }
@@ -45034,7 +45111,7 @@
         }
     }
     // NATURE (player 2)
-    if (p == 2) {
+    if (MomSphere[p] == 2) {
         if (r == 5) {
             if (roll &lt; 16) { return UnitDB(UNIT_WARBEARS); }
             if (roll &lt; 32) { return UnitDB(UNIT_COCKATRICE); }
@@ -45060,7 +45137,7 @@
         }
     }
     // SORCERY (player 3)
-    if (p == 3) {
+    if (MomSphere[p] == 3) {
         if (r == 5) {
             if (roll &lt; 16) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
             if (roll &lt; 32) { return UnitDB(UNIT_AIR_ELEMENTAL); }
@@ -45086,7 +45163,7 @@
         }
     }
     // DEATH (player 4)
-    if (p == 4) {
+    if (MomSphere[p] == 4) {
         if (r == 5) {
             if (roll &lt; 6) { return UnitDB(UNIT_SKELETONS); }
             if (roll &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
@@ -45119,7 +45196,7 @@
         }
     }
     // CHAOS (player 5)
-    if (p == 5) {
+    if (MomSphere[p] == 5) {
         wild = Random(100);
         if (wild &lt; 15) {
             if (r == 5) {
@@ -45266,40 +45343,40 @@
     p = player[0];
     if (p &gt;= 1 &amp;&amp; p &lt;= 5 &amp;&amp; value[0] != 0) {
         // LIFE (player 1)
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
         // NATURE (player 2)
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
         // SORCERY (player 3)
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCEROUS_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCEROUS_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
         // DEATH (player 4)
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
         // CHAOS (player 5)
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
     }
 }</t>
         </is>
@@ -45310,7 +45387,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>18430</v>
+        <v>18815</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
@@ -45342,40 +45419,40 @@
     p = player[0];
     if (p &gt;= 1 &amp;&amp; p &lt;= 5 &amp;&amp; value[0] != 0) {
         // LIFE (player 1)
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
-        if (p == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
+        if (MomSphere[p] == 1 &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
         // NATURE (player 2)
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
-        if (p == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
+        if (MomSphere[p] == 2 &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
         // SORCERY (player 3)
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCEROUS_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
-        if (p == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCEROUS_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
+        if (MomSphere[p] == 3 &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
         // DEATH (player 4)
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
-        if (p == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
+        if (MomSphere[p] == 4 &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
         // CHAOS (player 5)
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
-        if (p == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_LORE) &amp;&amp; MomSphereRung[p] &lt; 1) { MomSphereRung[p] = 1; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_ADEPT) &amp;&amp; MomSphereRung[p] &lt; 2) { MomSphereRung[p] = 2; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGE) &amp;&amp; MomSphereRung[p] &lt; 3) { MomSphereRung[p] = 3; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_WIZARD) &amp;&amp; MomSphereRung[p] &lt; 4) { MomSphereRung[p] = 4; }
+        if (MomSphere[p] == 5 &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MASTER) &amp;&amp; MomSphereRung[p] &lt; 5) { MomSphereRung[p] = 5; }
     }
 }
 // The weighted roll. Bands are cut from the COUNT of unlocked rungs, not from
@@ -45412,7 +45489,7 @@
     // rather than flooring here (gate_mana_upkeep.py assertion 12).
     roll = Random(100);
     // LIFE (player 1)
-    if (p == 1) {
+    if (MomSphere[p] == 1) {
         if (r == 5) {
             if (roll &lt; 16) { return UnitDB(UNIT_GUARDIAN_SPIRIT); }
             if (roll &lt; 32) { return UnitDB(UNIT_UNICORN); }
@@ -45438,7 +45515,7 @@
         }
     }
     // NATURE (player 2)
-    if (p == 2) {
+    if (MomSphere[p] == 2) {
         if (r == 5) {
             if (roll &lt; 16) { return UnitDB(UNIT_WARBEARS); }
             if (roll &lt; 32) { return UnitDB(UNIT_COCKATRICE); }
@@ -45464,7 +45541,7 @@
         }
     }
     // SORCERY (player 3)
-    if (p == 3) {
+    if (MomSphere[p] == 3) {
         if (r == 5) {
             if (roll &lt; 16) { return UnitDB(UNIT_PHANTOM_WARRIORS); }
             if (roll &lt; 32) { return UnitDB(UNIT_AIR_ELEMENTAL); }
@@ -45490,7 +45567,7 @@
         }
     }
     // DEATH (player 4)
-    if (p == 4) {
+    if (MomSphere[p] == 4) {
         if (r == 5) {
             if (roll &lt; 6) { return UnitDB(UNIT_SKELETONS); }
             if (roll &lt; 12) { return UnitDB(UNIT_ZOMBIES); }
@@ -45523,7 +45600,7 @@
         }
     }
     // CHAOS (player 5)
-    if (p == 5) {
+    if (MomSphere[p] == 5) {
         wild = Random(100);
         if (wild &lt; 15) {
             if (r == 5) {
@@ -46630,19 +46707,19 @@
             // sphere-defining buildings, not a second table to keep in sync.
             // Builtins only: CityHasBuilding is a builtin (217 uses in corpus),
             // so this adds no user-function call level.
-            if (mp_1 == 1) {
+            if (MomSphere[mp_1] == 1) {
                 if (CityHasBuilding(tmpCity, "IMPROVE_WIZARDS_FORTRESS")) { gen = gen + 8; }
                 if (CityHasBuilding(tmpCity, "IMPROVE_TEMPLE")) { gen = gen + 3; }
-            } elseif (mp_1 == 2) {
+            } elseif (MomSphere[mp_1] == 2) {
                 if (CityHasBuilding(tmpCity, "IMPROVE_PRIMAL_SOURCE")) { gen = gen + 8; }
                 if (CityHasBuilding(tmpCity, "IMPROVE_FANTASTIC_STABLE")) { gen = gen + 3; }
-            } elseif (mp_1 == 3) {
+            } elseif (MomSphere[mp_1] == 3) {
                 if (CityHasBuilding(tmpCity, "IMPROVE_BEACON_OF_WISDOM")) { gen = gen + 8; }
                 if (CityHasBuilding(tmpCity, "IMPROVE_LIBRARY")) { gen = gen + 3; }
-            } elseif (mp_1 == 4) {
+            } elseif (MomSphere[mp_1] == 4) {
                 if (CityHasBuilding(tmpCity, "IMPROVE_MECHANICIANS_GUILD")) { gen = gen + 8; }
                 if (CityHasBuilding(tmpCity, "IMPROVE_BARRACKS")) { gen = gen + 3; }
-            } elseif (mp_1 == 5) {
+            } elseif (MomSphere[mp_1] == 5) {
                 if (CityHasBuilding(tmpCity, "IMPROVE_MERCHANTS_GUILD")) { gen = gen + 8; }
                 if (CityHasBuilding(tmpCity, "IMPROVE_COLOSSEUM")) { gen = gen + 3; }
             }
@@ -46994,16 +47071,16 @@
 HandleEvent(BeginTurn) 'MomSphereRootGrant' post {
     int_t rp;
     rp = player[0];
-    if (rp &gt;= 1 &amp;&amp; rp &lt;= 5 &amp;&amp; MomSphereRung[rp] &lt; 1) {
-        if (rp == 1) {
+    if (rp &gt;= 1 &amp;&amp; rp &lt;= 30 &amp;&amp; MomSphere[rp] &gt;= 1 &amp;&amp; MomSphereRung[rp] &lt; 1) {
+        if (MomSphere[rp] == 1) {
             GrantAdvance(rp, AdvanceDB(ADVANCE_LIFE_MAGIC));
-        } elseif (rp == 2) {
+        } elseif (MomSphere[rp] == 2) {
             GrantAdvance(rp, AdvanceDB(ADVANCE_NATURE_MAGIC));
-        } elseif (rp == 3) {
+        } elseif (MomSphere[rp] == 3) {
             GrantAdvance(rp, AdvanceDB(ADVANCE_SORCERY));
-        } elseif (rp == 4) {
+        } elseif (MomSphere[rp] == 4) {
             GrantAdvance(rp, AdvanceDB(ADVANCE_DEATH_MAGIC));
-        } elseif (rp == 5) {
+        } elseif (MomSphere[rp] == 5) {
             GrantAdvance(rp, AdvanceDB(ADVANCE_CHAOS_MAGIC));
         }
     }
@@ -47016,7 +47093,7 @@
         <v>4</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>22437</v>
+        <v>22570</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
@@ -47056,19 +47133,19 @@
             // sphere-defining buildings, not a second table to keep in sync.
             // Builtins only: CityHasBuilding is a builtin (217 uses in corpus),
             // so this adds no user-function call level.
-            if (mp_1 == 1) {
+            if (MomSphere[mp_1] == 1) {
                 if (CityHasBuilding(tmpCity, "IMPROVE_WIZARDS_FORTRESS")) { gen = gen + 8; }
                 if (CityHasBuilding(tmpCity, "IMPROVE_TEMPLE")) { gen = gen + 3; }
-            } elseif (mp_1 == 2) {
+            } elseif (MomSphere[mp_1] == 2) {
                 if (CityHasBuilding(tmpCity, "IMPROVE_PRIMAL_SOURCE")) { gen = gen + 8; }
                 if (CityHasBuilding(tmpCity, "IMPROVE_FANTASTIC_STABLE")) { gen = gen + 3; }
-            } elseif (mp_1 == 3) {
+            } elseif (MomSphere[mp_1] == 3) {
                 if (CityHasBuilding(tmpCity, "IMPROVE_BEACON_OF_WISDOM")) { gen = gen + 8; }
                 if (CityHasBuilding(tmpCity, "IMPROVE_LIBRARY")) { gen = gen + 3; }
-            } elseif (mp_1 == 4) {
+            } elseif (MomSphere[mp_1] == 4) {
                 if (CityHasBuilding(tmpCity, "IMPROVE_MECHANICIANS_GUILD")) { gen = gen + 8; }
                 if (CityHasBuilding(tmpCity, "IMPROVE_BARRACKS")) { gen = gen + 3; }
-            } elseif (mp_1 == 5) {
+            } elseif (MomSphere[mp_1] == 5) {
                 if (CityHasBuilding(tmpCity, "IMPROVE_MERCHANTS_GUILD")) { gen = gen + 8; }
                 if (CityHasBuilding(tmpCity, "IMPROVE_COLOSSEUM")) { gen = gen + 3; }
             }
@@ -47421,16 +47498,16 @@
 HandleEvent(BeginTurn) 'MomSphereRootGrant' post {
     int_t rp;
     rp = player[0];
-    if (rp &gt;= 1 &amp;&amp; rp &lt;= 5 &amp;&amp; MomSphereRung[rp] &lt; 1) {
-        if (rp == 1) {
+    if (rp &gt;= 1 &amp;&amp; rp &lt;= 30 &amp;&amp; MomSphere[rp] &gt;= 1 &amp;&amp; MomSphereRung[rp] &lt; 1) {
+        if (MomSphere[rp] == 1) {
             GrantAdvance(rp, AdvanceDB(ADVANCE_LIFE_MAGIC));
-        } elseif (rp == 2) {
+        } elseif (MomSphere[rp] == 2) {
             GrantAdvance(rp, AdvanceDB(ADVANCE_NATURE_MAGIC));
-        } elseif (rp == 3) {
+        } elseif (MomSphere[rp] == 3) {
             GrantAdvance(rp, AdvanceDB(ADVANCE_SORCERY));
-        } elseif (rp == 4) {
+        } elseif (MomSphere[rp] == 4) {
             GrantAdvance(rp, AdvanceDB(ADVANCE_DEATH_MAGIC));
-        } elseif (rp == 5) {
+        } elseif (MomSphere[rp] == 5) {
             GrantAdvance(rp, AdvanceDB(ADVANCE_CHAOS_MAGIC));
         }
     }
@@ -47746,7 +47823,7 @@
     }
     // BACK to the hub. MagicMenu is declared in mom_msg.slc (include 55), which
     // loads BEFORE this file (65), so naming it here is safe in both directions.
-    Button(ID_BUTTON_BACK) {
+    Button(ID_MOM_MSG_BTN_BACK) {
         Kill();
         Message(g.player, 'MagicMenu');
     }
@@ -47771,7 +47848,7 @@
     Button(ID_BUTTON_CLOSE) {
         Kill();
     }
-    Button(ID_BUTTON_BACK) {
+    Button(ID_MOM_MSG_BTN_BACK) {
         Kill();
         Message(g.player, 'MagicMenu');
     }
@@ -47813,7 +47890,7 @@
         <v>13</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>18006</v>
+        <v>18016</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
@@ -48128,7 +48205,7 @@
     }
     // BACK to the hub. MagicMenu is declared in mom_msg.slc (include 55), which
     // loads BEFORE this file (65), so naming it here is safe in both directions.
-    Button(ID_BUTTON_BACK) {
+    Button(ID_MOM_MSG_BTN_BACK) {
         Kill();
         Message(g.player, 'MagicMenu');
     }
@@ -48153,7 +48230,7 @@
     Button(ID_BUTTON_CLOSE) {
         Kill();
     }
-    Button(ID_BUTTON_BACK) {
+    Button(ID_MOM_MSG_BTN_BACK) {
         Kill();
         Message(g.player, 'MagicMenu');
     }
@@ -48520,9 +48597,9 @@
           <t>int_f mod_CanPlayerHaveAdvance(int_t thePlayer, int_t theAdvance)
 {
     // Barbarians and any out-of-range player are unrestricted.
-    if (g.player &lt; 1 || g.player &gt; 5) { return 1; }
+    if (MomSphere[g.player] &lt; 1) { return 1; }
     // LIFE -- 6 block(s)
-    if (g.player != 1) {
+    if (MomSphere[g.player] != 1) {
         if (theAdvance == AdvanceDB(ADVANCE_LIFE_MAGIC)
         || theAdvance == AdvanceDB(ADVANCE_LIFE_LORE)
         || theAdvance == AdvanceDB(ADVANCE_LIFE_ADEPT)
@@ -48532,7 +48609,7 @@
         ) { return 0; }
     }
     // NATURE -- 6 block(s)
-    if (g.player != 2) {
+    if (MomSphere[g.player] != 2) {
         if (theAdvance == AdvanceDB(ADVANCE_NATURE_MAGIC)
         || theAdvance == AdvanceDB(ADVANCE_NATURE_LORE)
         || theAdvance == AdvanceDB(ADVANCE_NATURE_ADEPT)
@@ -48542,7 +48619,7 @@
         ) { return 0; }
     }
     // SORCERY -- 6 block(s)
-    if (g.player != 3) {
+    if (MomSphere[g.player] != 3) {
         if (theAdvance == AdvanceDB(ADVANCE_SORCERY)
         || theAdvance == AdvanceDB(ADVANCE_SORCEROUS_LORE)
         || theAdvance == AdvanceDB(ADVANCE_SORCERY_ADEPT)
@@ -48552,7 +48629,7 @@
         ) { return 0; }
     }
     // DEATH -- 6 block(s)
-    if (g.player != 4) {
+    if (MomSphere[g.player] != 4) {
         if (theAdvance == AdvanceDB(ADVANCE_DEATH_MAGIC)
         || theAdvance == AdvanceDB(ADVANCE_DEATH_LORE)
         || theAdvance == AdvanceDB(ADVANCE_DEATH_ADEPT)
@@ -48562,7 +48639,7 @@
         ) { return 0; }
     }
     // CHAOS -- 6 block(s)
-    if (g.player != 5) {
+    if (MomSphere[g.player] != 5) {
         if (theAdvance == AdvanceDB(ADVANCE_CHAOS_MAGIC)
         || theAdvance == AdvanceDB(ADVANCE_CHAOS_LORE)
         || theAdvance == AdvanceDB(ADVANCE_CHAOS_ADEPT)
@@ -48577,7 +48654,7 @@
 {
     if (theCity.owner &lt; 1 || theCity.owner &gt; 5) { return 1; }
     // LIFE -- 7 block(s)
-    if (theCity.owner != 1) {
+    if (MomSphere[theCity.owner] != 1) {
         if (theUnit == UnitDB(UNIT_ARCHANGEL)
         || theUnit == UnitDB(UNIT_ARIEL)
         || theUnit == UnitDB(UNIT_GUARDIAN_SPIRIT)
@@ -48588,7 +48665,7 @@
         ) { return 0; }
     }
     // NATURE -- 13 block(s)
-    if (theCity.owner != 2) {
+    if (MomSphere[theCity.owner] != 2) {
         if (theUnit == UnitDB(UNIT_ALORRA)
         || theUnit == UnitDB(UNIT_BEHEMOTH)
         || theUnit == UnitDB(UNIT_CENTAURS)
@@ -48605,7 +48682,7 @@
         ) { return 0; }
     }
     // SORCERY -- 7 block(s)
-    if (theCity.owner != 3) {
+    if (MomSphere[theCity.owner] != 3) {
         if (theUnit == UnitDB(UNIT_AIR_ELEMENTAL)
         || theUnit == UnitDB(UNIT_JAFAR)
         || theUnit == UnitDB(UNIT_MAGE)
@@ -48616,7 +48693,7 @@
         ) { return 0; }
     }
     // DEATH -- 11 block(s)
-    if (theCity.owner != 4) {
+    if (MomSphere[theCity.owner] != 4) {
         if (theUnit == UnitDB(UNIT_DEATH_KNIGHT)
         || theUnit == UnitDB(UNIT_DEMON)
         || theUnit == UnitDB(UNIT_DRACOLICH)
@@ -48631,7 +48708,7 @@
         ) { return 0; }
     }
     // CHAOS -- 9 block(s)
-    if (theCity.owner != 5) {
+    if (MomSphere[theCity.owner] != 5) {
         if (theUnit == UnitDB(UNIT_EFREET)
         || theUnit == UnitDB(UNIT_GARGOYLE)
         || theUnit == UnitDB(UNIT_HELL_HOUNDS)
@@ -48649,13 +48726,13 @@
 {
     if (theCity.owner &lt; 1 || theCity.owner &gt; 5) { return 1; }
     // NATURE -- 2 block(s)
-    if (theCity.owner != 2) {
+    if (MomSphere[theCity.owner] != 2) {
         if (theBuilding == BuildingDB(IMPROVE_FANTASTIC_STABLE)
         || theBuilding == BuildingDB(IMPROVE_PRIMAL_SOURCE)
         ) { return 0; }
     }
     // SORCERY -- 1 block(s)
-    if (theCity.owner != 3) {
+    if (MomSphere[theCity.owner] != 3) {
         if (theBuilding == BuildingDB(IMPROVE_BEACON_OF_WISDOM)
         ) { return 0; }
     }
@@ -48665,32 +48742,32 @@
 {
     if (theCity.owner &lt; 1 || theCity.owner &gt; 5) { return 1; }
     // LIFE -- 2 block(s)
-    if (theCity.owner != 1) {
+    if (MomSphere[theCity.owner] != 1) {
         if (theWonder == WonderDB(WONDER_CELESTIAL_BEACON)
         || theWonder == WonderDB(WONDER_ENCHANTED_GROTTO)
         ) { return 0; }
     }
     // NATURE -- 2 block(s)
-    if (theCity.owner != 2) {
+    if (MomSphere[theCity.owner] != 2) {
         if (theWonder == WonderDB(WONDER_FONT_OF_BOUNTY)
         || theWonder == WonderDB(WONDER_GAIAS_SHRINE)
         ) { return 0; }
     }
     // SORCERY -- 3 block(s)
-    if (theCity.owner != 3) {
+    if (MomSphere[theCity.owner] != 3) {
         if (theWonder == WonderDB(WONDER_ELDRITCH_COLLEGE)
         || theWonder == WonderDB(WONDER_LEAGUE_OF_WIZARDS)
         || theWonder == WonderDB(WONDER_PLEASURE_DOME)
         ) { return 0; }
     }
     // DEATH -- 2 block(s)
-    if (theCity.owner != 4) {
+    if (MomSphere[theCity.owner] != 4) {
         if (theWonder == WonderDB(WONDER_ENTROPY_ENGINE)
         || theWonder == WonderDB(WONDER_WALL_OF_BONE)
         ) { return 0; }
     }
     // CHAOS -- 2 block(s)
-    if (theCity.owner != 5) {
+    if (MomSphere[theCity.owner] != 5) {
         if (theWonder == WonderDB(WONDER_ELIXIR_OF_METAMORPHOSIS)
         || theWonder == WonderDB(WONDER_FORGE_OF_CHAOS)
         ) { return 0; }
@@ -48706,7 +48783,7 @@
         <v>4</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>7878</v>
+        <v>8060</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
@@ -48734,9 +48811,9 @@
 int_f mod_CanPlayerHaveAdvance(int_t thePlayer, int_t theAdvance)
 {
     // Barbarians and any out-of-range player are unrestricted.
-    if (g.player &lt; 1 || g.player &gt; 5) { return 1; }
+    if (MomSphere[g.player] &lt; 1) { return 1; }
     // LIFE -- 6 block(s)
-    if (g.player != 1) {
+    if (MomSphere[g.player] != 1) {
         if (theAdvance == AdvanceDB(ADVANCE_LIFE_MAGIC)
         || theAdvance == AdvanceDB(ADVANCE_LIFE_LORE)
         || theAdvance == AdvanceDB(ADVANCE_LIFE_ADEPT)
@@ -48746,7 +48823,7 @@
         ) { return 0; }
     }
     // NATURE -- 6 block(s)
-    if (g.player != 2) {
+    if (MomSphere[g.player] != 2) {
         if (theAdvance == AdvanceDB(ADVANCE_NATURE_MAGIC)
         || theAdvance == AdvanceDB(ADVANCE_NATURE_LORE)
         || theAdvance == AdvanceDB(ADVANCE_NATURE_ADEPT)
@@ -48756,7 +48833,7 @@
         ) { return 0; }
     }
     // SORCERY -- 6 block(s)
-    if (g.player != 3) {
+    if (MomSphere[g.player] != 3) {
         if (theAdvance == AdvanceDB(ADVANCE_SORCERY)
         || theAdvance == AdvanceDB(ADVANCE_SORCEROUS_LORE)
         || theAdvance == AdvanceDB(ADVANCE_SORCERY_ADEPT)
@@ -48766,7 +48843,7 @@
         ) { return 0; }
     }
     // DEATH -- 6 block(s)
-    if (g.player != 4) {
+    if (MomSphere[g.player] != 4) {
         if (theAdvance == AdvanceDB(ADVANCE_DEATH_MAGIC)
         || theAdvance == AdvanceDB(ADVANCE_DEATH_LORE)
         || theAdvance == AdvanceDB(ADVANCE_DEATH_ADEPT)
@@ -48776,7 +48853,7 @@
         ) { return 0; }
     }
     // CHAOS -- 6 block(s)
-    if (g.player != 5) {
+    if (MomSphere[g.player] != 5) {
         if (theAdvance == AdvanceDB(ADVANCE_CHAOS_MAGIC)
         || theAdvance == AdvanceDB(ADVANCE_CHAOS_LORE)
         || theAdvance == AdvanceDB(ADVANCE_CHAOS_ADEPT)
@@ -48791,7 +48868,7 @@
 {
     if (theCity.owner &lt; 1 || theCity.owner &gt; 5) { return 1; }
     // LIFE -- 7 block(s)
-    if (theCity.owner != 1) {
+    if (MomSphere[theCity.owner] != 1) {
         if (theUnit == UnitDB(UNIT_ARCHANGEL)
         || theUnit == UnitDB(UNIT_ARIEL)
         || theUnit == UnitDB(UNIT_GUARDIAN_SPIRIT)
@@ -48802,7 +48879,7 @@
         ) { return 0; }
     }
     // NATURE -- 13 block(s)
-    if (theCity.owner != 2) {
+    if (MomSphere[theCity.owner] != 2) {
         if (theUnit == UnitDB(UNIT_ALORRA)
         || theUnit == UnitDB(UNIT_BEHEMOTH)
         || theUnit == UnitDB(UNIT_CENTAURS)
@@ -48819,7 +48896,7 @@
         ) { return 0; }
     }
     // SORCERY -- 7 block(s)
-    if (theCity.owner != 3) {
+    if (MomSphere[theCity.owner] != 3) {
         if (theUnit == UnitDB(UNIT_AIR_ELEMENTAL)
         || theUnit == UnitDB(UNIT_JAFAR)
         || theUnit == UnitDB(UNIT_MAGE)
@@ -48830,7 +48907,7 @@
         ) { return 0; }
     }
     // DEATH -- 11 block(s)
-    if (theCity.owner != 4) {
+    if (MomSphere[theCity.owner] != 4) {
         if (theUnit == UnitDB(UNIT_DEATH_KNIGHT)
         || theUnit == UnitDB(UNIT_DEMON)
         || theUnit == UnitDB(UNIT_DRACOLICH)
@@ -48845,7 +48922,7 @@
         ) { return 0; }
     }
     // CHAOS -- 9 block(s)
-    if (theCity.owner != 5) {
+    if (MomSphere[theCity.owner] != 5) {
         if (theUnit == UnitDB(UNIT_EFREET)
         || theUnit == UnitDB(UNIT_GARGOYLE)
         || theUnit == UnitDB(UNIT_HELL_HOUNDS)
@@ -48863,13 +48940,13 @@
 {
     if (theCity.owner &lt; 1 || theCity.owner &gt; 5) { return 1; }
     // NATURE -- 2 block(s)
-    if (theCity.owner != 2) {
+    if (MomSphere[theCity.owner] != 2) {
         if (theBuilding == BuildingDB(IMPROVE_FANTASTIC_STABLE)
         || theBuilding == BuildingDB(IMPROVE_PRIMAL_SOURCE)
         ) { return 0; }
     }
     // SORCERY -- 1 block(s)
-    if (theCity.owner != 3) {
+    if (MomSphere[theCity.owner] != 3) {
         if (theBuilding == BuildingDB(IMPROVE_BEACON_OF_WISDOM)
         ) { return 0; }
     }
@@ -48879,32 +48956,32 @@
 {
     if (theCity.owner &lt; 1 || theCity.owner &gt; 5) { return 1; }
     // LIFE -- 2 block(s)
-    if (theCity.owner != 1) {
+    if (MomSphere[theCity.owner] != 1) {
         if (theWonder == WonderDB(WONDER_CELESTIAL_BEACON)
         || theWonder == WonderDB(WONDER_ENCHANTED_GROTTO)
         ) { return 0; }
     }
     // NATURE -- 2 block(s)
-    if (theCity.owner != 2) {
+    if (MomSphere[theCity.owner] != 2) {
         if (theWonder == WonderDB(WONDER_FONT_OF_BOUNTY)
         || theWonder == WonderDB(WONDER_GAIAS_SHRINE)
         ) { return 0; }
     }
     // SORCERY -- 3 block(s)
-    if (theCity.owner != 3) {
+    if (MomSphere[theCity.owner] != 3) {
         if (theWonder == WonderDB(WONDER_ELDRITCH_COLLEGE)
         || theWonder == WonderDB(WONDER_LEAGUE_OF_WIZARDS)
         || theWonder == WonderDB(WONDER_PLEASURE_DOME)
         ) { return 0; }
     }
     // DEATH -- 2 block(s)
-    if (theCity.owner != 4) {
+    if (MomSphere[theCity.owner] != 4) {
         if (theWonder == WonderDB(WONDER_ENTROPY_ENGINE)
         || theWonder == WonderDB(WONDER_WALL_OF_BONE)
         ) { return 0; }
     }
     // CHAOS -- 2 block(s)
-    if (theCity.owner != 5) {
+    if (MomSphere[theCity.owner] != 5) {
         if (theWonder == WonderDB(WONDER_ELIXIR_OF_METAMORPHOSIS)
         || theWonder == WonderDB(WONDER_FORGE_OF_CHAOS)
         ) { return 0; }
@@ -48917,34 +48994,324 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>tutorial.slc</t>
+          <t>mom_probe.slc</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>?</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>retires stock tut2_main.slc tutorial triggers</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
+          <t>mom_probe.slc -- HARNESS INSTRUMENT, NOT PART OF THE MOD.</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>int_t MomDbgUnits[31];    // total units owned, sampled on that player's turn
+int_t MomDbgCre[31];      // summoned creatures still alive (ledger occupancy)
+int_t MomDbgMana[31];     // current pool
+int_t MomDbgPrep[31];     // preparation countdown, sampled on that player's OWN turn
+int_t MomDbgPend[31];     // pending creature type, 0 == nothing queued
+int_t MomDbgSph[31];      // sphere resolved from the CIV, 0 == not a tribe
+int_t MomDbgTick[31];     // turns taken by EACH seat, spheres or not
+int_t MomDbgHum[31];      // 1 == this seat is the human
+int_t MomDbgCity[31];     // cities owned -- the AI summon gate's first clause
+int_t MomDbgRung[31];     // sphere-ladder rung 0..5 -- the surviving hypothesis
+int_t MomDbgU1; int_t MomDbgU2; int_t MomDbgU3; int_t MomDbgU4; int_t MomDbgU5;
+int_t MomDbgC1; int_t MomDbgC2; int_t MomDbgC3; int_t MomDbgC4; int_t MomDbgC5;
+int_t MomDbgM1; int_t MomDbgM2; int_t MomDbgM3; int_t MomDbgM4; int_t MomDbgM5;
+int_t MomDbgP1; int_t MomDbgP2; int_t MomDbgP3; int_t MomDbgP4; int_t MomDbgP5;
+int_t MomDbgS1; int_t MomDbgS2; int_t MomDbgS3; int_t MomDbgS4; int_t MomDbgS5;
+int_t MomDbgR1; int_t MomDbgR2; int_t MomDbgR3; int_t MomDbgR4; int_t MomDbgR5;
+int_t MomDbgY1; int_t MomDbgY2; int_t MomDbgY3; int_t MomDbgY4; int_t MomDbgY5;</t>
+        </is>
+      </c>
       <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) 'MomProbeSample' post {
+    int_t p;
+    int_t i;
+    int_t base;
+    int_t cre;
+    p = player[0];
+    if (p &gt;= 0 &amp;&amp; p &lt;= 15) {
+        MomDbgTick[p] = MomDbgTick[p] + 1;
+    }
+    if (p &gt;= 1 &amp;&amp; p &lt;= 5) {
+        // Own-turn sampling: player[0] IS p here, so .units is p's unit count.
+        MomDbgUnits[p] = player[0].units;
+        MomDbgMana[p] = MomMagicCur[p];
+        // Ledger occupancy = creatures this player summoned that are still
+        // alive. Counts slots, not upkeep, so "how many creatures" is separated
+        // from "what they cost" -- the mix question needs the count.
+        base = (p - 1) * 32;
+        cre = 0;
+        for (i = 0; i &lt; 32; i = i + 1) {
+            if (MomSummonRung[base + i] &gt; 0) {
+                if (MomSummonUnit[base + i].valid) {
+                    cre = cre + 1;
+                }
+            }
+        }
+        MomDbgCre[p] = cre;
+        // SAMPLED ON p's OWN TURN. The earlier version read MomSummonPrep in
+        // the human's flatten pass, by which point every AI countdown had
+        // already ticked down and resolved -- so it always read 0 and could not
+        // distinguish "never committed" from "committed and resolved".
+        MomDbgPrep[p] = MomSummonPrep[p];
+        MomDbgPend[p] = MomSummonPending[p];
+        MomDbgRung[p] = MomSphereRung[p];
+        // THE SPHERE THE MOD RESOLVED for this seat. Before 2026-08-04 sphere
+        // WAS the seat, so this row would have been the identity function and
+        // told us nothing; now it reads MomSphere[], set from
+        // PlayerCivilization, and a mismatch between the tribe chosen at setup
+        // and the sphere granted is visible directly.
+        MomDbgSph[p] = MomSphere[p];
+        // WHICH SEAT IS THE HUMAN. mom_ai_magic skips !IsHumanPlayer(p), and an
+        // observe-only run never clicks the summon arm -- so the human's column
+        // MUST read zero summons with a monotonically climbing pool. That is
+        // Death's exact signature, and it would make the whole investigation an
+        // observer effect rather than a defect.
+        if (IsHumanPlayer(p)) {
+            MomDbgHum[p] = 1;
+        } else {
+            MomDbgHum[p] = 0;
+        }
+        // CITIES. The AI magic tick is gated on `player[0].cities &gt; 0` before
+        // anything else, so a tribe with no city can hold a full pool at rung 1
+        // and never summon -- which is exactly Death's signature. Sampled on
+        // p's own turn, where player[0] IS p.
+        MomDbgCity[p] = player[0].cities;
+        // Flatten for display on the human's turn only. Every tribe's latest
+        // sample is already in the arrays by now, whatever the seating order.
+        if (IsHumanPlayer(p)) {
+            MomDbgU1 = MomDbgUnits[1]; MomDbgU2 = MomDbgUnits[2];
+            MomDbgU3 = MomDbgUnits[3]; MomDbgU4 = MomDbgUnits[4];
+            MomDbgU5 = MomDbgUnits[5];
+            MomDbgC1 = MomDbgCre[1]; MomDbgC2 = MomDbgCre[2];
+            MomDbgC3 = MomDbgCre[3]; MomDbgC4 = MomDbgCre[4];
+            MomDbgC5 = MomDbgCre[5];
+            MomDbgM1 = MomDbgMana[1]; MomDbgM2 = MomDbgMana[2];
+            MomDbgM3 = MomDbgMana[3]; MomDbgM4 = MomDbgMana[4];
+            MomDbgM5 = MomDbgMana[5];
+            MomDbgP1 = MomDbgPend[1]; MomDbgP2 = MomDbgPend[2];
+            MomDbgP3 = MomDbgPend[3]; MomDbgP4 = MomDbgPend[4];
+            MomDbgP5 = MomDbgPend[5];
+            MomDbgR1 = MomDbgRung[1]; MomDbgR2 = MomDbgRung[2];
+            MomDbgR3 = MomDbgRung[3]; MomDbgR4 = MomDbgRung[4];
+            MomDbgR5 = MomDbgRung[5];
+            // NET INCOME -- the last unmeasured input to the AI summon gate.
+            // mom_ai_magic rejects a pick when
+            //     MomMagicPerTurn[p] - pickRung * MomUpkeepRate &lt; 0
+            // so a tribe whose net is 0 or 1 can never afford even a rung-1
+            // creature's keep of 2, no matter how full its bank is. Death sits
+            // pinned at its cap, which is exactly what a tribe that cannot
+            // spend looks like.
+            // Seats 4..8. If a sphere is seated above 5 it gets no magic at
+            // all -- every magic handler is guarded p &gt;= 1 &amp;&amp; p &lt;= 5 -- which
+            // would be a hard defect rather than a balance problem.
+            MomDbgS1 = MomDbgSph[1]; MomDbgS2 = MomDbgSph[2];
+            MomDbgS3 = MomDbgSph[3]; MomDbgS4 = MomDbgSph[4];
+            MomDbgS5 = MomDbgSph[5];
+        }
+    }
+}</t>
+        </is>
+      </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>8460</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>// mom_probe.slc -- HARNESS INSTRUMENT, NOT PART OF THE MOD.
+//
+// Injected into scen0000 by tools/uiwalk/probe_long_game.py for the duration of
+// one headless run and REMOVED afterwards. It must never be committed into the
+// scenario; the probe restores scenario.slc and scen_str.txt in a finally block.
+//
+// WHY IT EXISTS. The harness reads PIXELS. An AI player's mana, its unit count
+// and its summoned-creature count are never rendered for anybody, so three
+// claims about v3.5.0 were unfalsifiable from the outside:
+//
+//   1. the AI's summon respects sustainability rather than bare affordability;
+//   2. insolvency actually releases a creature (rung 1 cannot reach it);
+//   3. an AI army is now mostly BUILT units with summons as a minority --
+//      the original "only ever one unit type" report.
+//
+// WHY IT IS SAFE TO TEST WITH THIS PRESENT. It is strictly READ-ONLY with
+// respect to the logic under test: it reads MomMagicCur[], MomSummonRung[] and
+// player[0].units, and writes ONLY display scalars that nothing else reads. It
+// adds no spend, no spawn, no kill, and takes no branch that game logic sees. So
+// the economy it measures is the shipped economy, not an instrumented variant.
+//
+// THE player[0] RULE STILL APPLIES. player[N] indexes the event ARG array, so a
+// player's own data can only be read during that player's own BeginTurn -- which
+// is exactly what this does, accumulating into per-player arrays that the human's
+// own tick then flattens into interpolatable scalars. Array-indexed {Arr[Idx]}
+// interpolation silently drops the whole message, so the flat copies are
+// mandatory, not stylistic.
+int_t MomDbgUnits[31];    // total units owned, sampled on that player's turn
+int_t MomDbgCre[31];      // summoned creatures still alive (ledger occupancy)
+int_t MomDbgMana[31];     // current pool
+int_t MomDbgPrep[31];     // preparation countdown, sampled on that player's OWN turn
+int_t MomDbgPend[31];     // pending creature type, 0 == nothing queued
+int_t MomDbgSph[31];      // sphere resolved from the CIV, 0 == not a tribe
+int_t MomDbgTick[31];     // turns taken by EACH seat, spheres or not
+int_t MomDbgHum[31];      // 1 == this seat is the human
+int_t MomDbgCity[31];     // cities owned -- the AI summon gate's first clause
+int_t MomDbgRung[31];     // sphere-ladder rung 0..5 -- the surviving hypothesis
+                          // for Death's zero summons. MomSummonRoll returns 0
+                          // for rung 0, so a tribe stuck there can never summon
+                          // no matter how much mana it holds. Two other
+                          // hypotheses (bank, price) are already falsified; this
+                          // reads the variable instead of inferring it again.
+int_t MomDbgU1; int_t MomDbgU2; int_t MomDbgU3; int_t MomDbgU4; int_t MomDbgU5;
+int_t MomDbgC1; int_t MomDbgC2; int_t MomDbgC3; int_t MomDbgC4; int_t MomDbgC5;
+int_t MomDbgM1; int_t MomDbgM2; int_t MomDbgM3; int_t MomDbgM4; int_t MomDbgM5;
+// Preparation state, added to discriminate a STUCK COUNTDOWN from a SILENT
+// SPAWN FAILURE. Measured 2026-08-01: AI tribes are spending ~75 mana (Nature
+// went 50 -&gt; 66 over ten turns while base income alone is +10/turn, so it burned
+// roughly a summon's worth) and their ledgered creature count stays at ZERO.
+// Those two hypotheses look identical from the outside and need different fixes:
+//   prep stuck &gt; 0  -&gt; the arrival branch never runs for AI players
+//   prep 0, cre 0   -&gt; arrival ran and the spawn produced nothing to ledger
+int_t MomDbgP1; int_t MomDbgP2; int_t MomDbgP3; int_t MomDbgP4; int_t MomDbgP5;
+int_t MomDbgS1; int_t MomDbgS2; int_t MomDbgS3; int_t MomDbgS4; int_t MomDbgS5;
+int_t MomDbgR1; int_t MomDbgR2; int_t MomDbgR3; int_t MomDbgR4; int_t MomDbgR5;
+int_t MomDbgY1; int_t MomDbgY2; int_t MomDbgY3; int_t MomDbgY4; int_t MomDbgY5;
+HandleEvent(BeginTurn) 'MomProbeSample' post {
+    int_t p;
+    int_t i;
+    int_t base;
+    int_t cre;
+    p = player[0];
+    if (p &gt;= 0 &amp;&amp; p &lt;= 15) {
+        MomDbgTick[p] = MomDbgTick[p] + 1;
+    }
+    if (p &gt;= 1 &amp;&amp; p &lt;= 5) {
+        // Own-turn sampling: player[0] IS p here, so .units is p's unit count.
+        MomDbgUnits[p] = player[0].units;
+        MomDbgMana[p] = MomMagicCur[p];
+        // Ledger occupancy = creatures this player summoned that are still
+        // alive. Counts slots, not upkeep, so "how many creatures" is separated
+        // from "what they cost" -- the mix question needs the count.
+        base = (p - 1) * 32;
+        cre = 0;
+        for (i = 0; i &lt; 32; i = i + 1) {
+            if (MomSummonRung[base + i] &gt; 0) {
+                if (MomSummonUnit[base + i].valid) {
+                    cre = cre + 1;
+                }
+            }
+        }
+        MomDbgCre[p] = cre;
+        // SAMPLED ON p's OWN TURN. The earlier version read MomSummonPrep in
+        // the human's flatten pass, by which point every AI countdown had
+        // already ticked down and resolved -- so it always read 0 and could not
+        // distinguish "never committed" from "committed and resolved".
+        MomDbgPrep[p] = MomSummonPrep[p];
+        MomDbgPend[p] = MomSummonPending[p];
+        MomDbgRung[p] = MomSphereRung[p];
+        // THE SPHERE THE MOD RESOLVED for this seat. Before 2026-08-04 sphere
+        // WAS the seat, so this row would have been the identity function and
+        // told us nothing; now it reads MomSphere[], set from
+        // PlayerCivilization, and a mismatch between the tribe chosen at setup
+        // and the sphere granted is visible directly.
+        MomDbgSph[p] = MomSphere[p];
+        // WHICH SEAT IS THE HUMAN. mom_ai_magic skips !IsHumanPlayer(p), and an
+        // observe-only run never clicks the summon arm -- so the human's column
+        // MUST read zero summons with a monotonically climbing pool. That is
+        // Death's exact signature, and it would make the whole investigation an
+        // observer effect rather than a defect.
+        if (IsHumanPlayer(p)) {
+            MomDbgHum[p] = 1;
+        } else {
+            MomDbgHum[p] = 0;
+        }
+        // CITIES. The AI magic tick is gated on `player[0].cities &gt; 0` before
+        // anything else, so a tribe with no city can hold a full pool at rung 1
+        // and never summon -- which is exactly Death's signature. Sampled on
+        // p's own turn, where player[0] IS p.
+        MomDbgCity[p] = player[0].cities;
+        // Flatten for display on the human's turn only. Every tribe's latest
+        // sample is already in the arrays by now, whatever the seating order.
+        if (IsHumanPlayer(p)) {
+            MomDbgU1 = MomDbgUnits[1]; MomDbgU2 = MomDbgUnits[2];
+            MomDbgU3 = MomDbgUnits[3]; MomDbgU4 = MomDbgUnits[4];
+            MomDbgU5 = MomDbgUnits[5];
+            MomDbgC1 = MomDbgCre[1]; MomDbgC2 = MomDbgCre[2];
+            MomDbgC3 = MomDbgCre[3]; MomDbgC4 = MomDbgCre[4];
+            MomDbgC5 = MomDbgCre[5];
+            MomDbgM1 = MomDbgMana[1]; MomDbgM2 = MomDbgMana[2];
+            MomDbgM3 = MomDbgMana[3]; MomDbgM4 = MomDbgMana[4];
+            MomDbgM5 = MomDbgMana[5];
+            MomDbgP1 = MomDbgPend[1]; MomDbgP2 = MomDbgPend[2];
+            MomDbgP3 = MomDbgPend[3]; MomDbgP4 = MomDbgPend[4];
+            MomDbgP5 = MomDbgPend[5];
+            MomDbgR1 = MomDbgRung[1]; MomDbgR2 = MomDbgRung[2];
+            MomDbgR3 = MomDbgRung[3]; MomDbgR4 = MomDbgRung[4];
+            MomDbgR5 = MomDbgRung[5];
+            // NET INCOME -- the last unmeasured input to the AI summon gate.
+            // mom_ai_magic rejects a pick when
+            //     MomMagicPerTurn[p] - pickRung * MomUpkeepRate &lt; 0
+            // so a tribe whose net is 0 or 1 can never afford even a rung-1
+            // creature's keep of 2, no matter how full its bank is. Death sits
+            // pinned at its cap, which is exactly what a tribe that cannot
+            // spend looks like.
+            // Seats 4..8. If a sphere is seated above 5 it gets no magic at
+            // all -- every magic handler is guarded p &gt;= 1 &amp;&amp; p &lt;= 5 -- which
+            // would be a hard defect rather than a balance problem.
+            MomDbgS1 = MomDbgSph[1]; MomDbgS2 = MomDbgSph[2];
+            MomDbgS3 = MomDbgSph[3]; MomDbgS4 = MomDbgSph[4];
+            MomDbgS5 = MomDbgSph[5];
+        }
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>tutorial.slc</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>retires stock tut2_main.slc tutorial triggers</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="K13" s="5" t="n">
         <v>758</v>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>//=============================================================================
 // tutorial.slc -- Master of Magic override: stock tutorial SLIC RETIRED
@@ -48962,7 +49329,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L12"/>
+  <autoFilter ref="A1:L13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48973,7 +49340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -49036,24 +49403,20 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>MomPlayerIsLife</t>
+          <t>MomSphereIdentify</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p_1)</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>faction predicate p==1 (Life)</t>
-        </is>
-      </c>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr">
         <is>
           <t>B</t>
@@ -49066,7 +49429,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -49083,17 +49446,17 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>MomPlayerIsNature</t>
+          <t>MomPlayerIsLife</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p_2)</t>
+          <t>int_f(int_t p_1)</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>faction predicate p==2 (Nature)</t>
+          <t>faction predicate p==1 (Life)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -49108,7 +49471,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -49125,17 +49488,17 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>MomPlayerIsSorcery</t>
+          <t>MomPlayerIsNature</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p_3)</t>
+          <t>int_f(int_t p_2)</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>faction predicate p==3 (Sorcery)</t>
+          <t>faction predicate p==2 (Nature)</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -49150,7 +49513,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>sorcery</t>
+          <t>nature</t>
         </is>
       </c>
     </row>
@@ -49167,17 +49530,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>MomPlayerIsDeath</t>
+          <t>MomPlayerIsSorcery</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p_4)</t>
+          <t>int_f(int_t p_3)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>faction predicate p==4 (Death)</t>
+          <t>faction predicate p==3 (Sorcery)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -49192,7 +49555,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>sorcery</t>
         </is>
       </c>
     </row>
@@ -49209,17 +49572,17 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>MomPlayerIsChaos</t>
+          <t>MomPlayerIsDeath</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p_5)</t>
+          <t>int_f(int_t p_4)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>faction predicate p==5 (Chaos)</t>
+          <t>faction predicate p==4 (Death)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -49234,7 +49597,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -49251,17 +49614,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>MomCountLifeBlessings</t>
+          <t>MomPlayerIsChaos</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p_6)</t>
+          <t>int_f(int_t p_5)</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>weighted count of Life buildings (TEMPLE/CITY_WALLS/WIZARDS_FORTRESS)</t>
+          <t>faction predicate p==5 (Chaos)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -49276,7 +49639,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -49293,17 +49656,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>MomCountNatureFoci</t>
+          <t>MomCountLifeBlessings</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p_7)</t>
+          <t>int_f(int_t p_6)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>weighted count of Nature buildings (GRANARY/PRIMAL_SOURCE/FANTASTIC_STABLE)</t>
+          <t>weighted count of Life buildings (TEMPLE/CITY_WALLS/WIZARDS_FORTRESS)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -49318,7 +49681,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -49335,17 +49698,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>MomCountSorceryFoci</t>
+          <t>MomCountNatureFoci</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p_8)</t>
+          <t>int_f(int_t p_7)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>weighted count of Sorcery buildings (LIBRARY/BEACON_OF_WISDOM)</t>
+          <t>weighted count of Nature buildings (GRANARY/PRIMAL_SOURCE/FANTASTIC_STABLE)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -49360,7 +49723,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>sorcery</t>
+          <t>nature</t>
         </is>
       </c>
     </row>
@@ -49377,17 +49740,17 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>MomGrantLifeBuilding</t>
+          <t>MomCountSorceryFoci</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p_9)</t>
+          <t>int_f(int_t p_8)</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>grant the Life-sphere themed building in the player's first city</t>
+          <t>weighted count of Sorcery buildings (LIBRARY/BEACON_OF_WISDOM)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -49402,7 +49765,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>sorcery</t>
         </is>
       </c>
     </row>
@@ -49419,17 +49782,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>MomGrantNatureBuilding</t>
+          <t>MomGrantLifeBuilding</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p_10)</t>
+          <t>void_f(int_t p_9)</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>grant the Nature-sphere themed building in the player's first city</t>
+          <t>grant the Life-sphere themed building in the player's first city</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -49444,7 +49807,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -49461,17 +49824,17 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>MomGrantSorceryBuilding</t>
+          <t>MomGrantNatureBuilding</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p_11)</t>
+          <t>void_f(int_t p_10)</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>grant the Sorcery-sphere themed building in the player's first city</t>
+          <t>grant the Nature-sphere themed building in the player's first city</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -49486,7 +49849,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>sorcery</t>
+          <t>nature</t>
         </is>
       </c>
     </row>
@@ -49503,17 +49866,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>MomGrantDeathBuilding</t>
+          <t>MomGrantSorceryBuilding</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p_12)</t>
+          <t>void_f(int_t p_11)</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>grant the Death-sphere themed building in the player's first city</t>
+          <t>grant the Sorcery-sphere themed building in the player's first city</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -49528,7 +49891,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>sorcery</t>
         </is>
       </c>
     </row>
@@ -49545,17 +49908,17 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>MomGrantChaosBuilding</t>
+          <t>MomGrantDeathBuilding</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p_14)</t>
+          <t>void_f(int_t p_12)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>grant the Chaos-sphere milestone building (COLOSSEUM) in the player's first city -- the only unclaimed chaos-reading improvement, every other sphere's milestone being spoken for</t>
+          <t>grant the Death-sphere themed building in the player's first city</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -49570,7 +49933,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -49587,17 +49950,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>MomCountDeathFoci</t>
+          <t>MomGrantChaosBuilding</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p_15)</t>
+          <t>void_f(int_t p_14)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>weighted count of Death buildings (BARRACKS 1 / MECHANICIANS_GUILD 2) -- the additive city-focus term that squares the 5-column income matrix; Death keeps its army-fed units/3 identity term alongside it</t>
+          <t>grant the Chaos-sphere milestone building (COLOSSEUM) in the player's first city -- the only unclaimed chaos-reading improvement, every other sphere's milestone being spoken for</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -49612,7 +49975,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -49629,17 +49992,17 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>MomCountChaosFoci</t>
+          <t>MomCountDeathFoci</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p_16)</t>
+          <t>int_f(int_t p_15)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>weighted count of Chaos buildings (COLOSSEUM 2 / MERCHANTS_GUILD 1) -- the deterministic floor under the random-windfall identity term</t>
+          <t>weighted count of Death buildings (BARRACKS 1 / MECHANICIANS_GUILD 2) -- the additive city-focus term that squares the 5-column income matrix; Death keeps its army-fed units/3 identity term alongside it</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -49654,7 +50017,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -49671,17 +50034,17 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>MomSpawnSphereUnit</t>
+          <t>MomCountChaosFoci</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p_13, int_t unitType, int_t rung)</t>
+          <t>int_f(int_t p_16)</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>spawn a sphere unit on a free non-water NEIGHBOUR of the first city, never the city tile: CTP2 draws exactly ONE unit per tile and orders own units by MaxMovePoints, so a fast summon on the capital permanently hides the garrison. GetNeighbor returns 0 at the map edge and does not write its out-arg, so the return value gates the read.</t>
+          <t>weighted count of Chaos buildings (COLOSSEUM 2 / MERCHANTS_GUILD 1) -- the deterministic floor under the random-windfall identity term</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -49696,34 +50059,34 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>mom_turns.slc</t>
+          <t>mom_func.slc</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>MomSphereTurnBlessings</t>
+          <t>MomSpawnSphereUnit</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>void_f(int_t p_13, int_t unitType, int_t rung)</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>per-turn sphere gold income by faction</t>
+          <t>spawn a sphere unit on a free non-water NEIGHBOUR of the first city, never the city tile: CTP2 draws exactly ONE unit per tile and orders own units by MaxMovePoints, so a fast summon on the capital permanently hides the garrison. GetNeighbor returns 0 at the map edge and does not write its out-arg, so the return value gates the read.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -49738,14 +50101,14 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>mom_city_effects.slc</t>
+          <t>mom_turns.slc</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -49755,17 +50118,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>MomSphereAdvanceBlessings</t>
+          <t>MomSphereTurnBlessings</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>sphere magic-advance milestone: grant blessing building + spawn sphere unit (Chaos = random gold)</t>
+          <t>per-turn sphere gold income by faction</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -49797,17 +50160,17 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>MomSphereCityEffects</t>
+          <t>MomSphereAdvanceBlessings</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(CreateBuilding) post</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>+30 burst gold on themed building completion</t>
+          <t>sphere magic-advance milestone: grant blessing building + spawn sphere unit (Chaos = random gold)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -49829,7 +50192,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>mom_summon.slc</t>
+          <t>mom_city_effects.slc</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -49839,18 +50202,22 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>MomSphereRungTick</t>
+          <t>MomSphereCityEffects</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr"/>
+          <t>HandleEvent(CreateBuilding) post</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>+30 burst gold on themed building completion</t>
+        </is>
+      </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -49872,17 +50239,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>MomSummonRoll</t>
+          <t>MomSphereRungTick</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t p)</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
@@ -49898,7 +50265,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -49915,12 +50282,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>MomSummonRungOf</t>
+          <t>MomSummonRoll</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t unitType)</t>
+          <t>int_f(int_t p)</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr"/>
@@ -49943,32 +50310,28 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>mom_msg.slc</t>
+          <t>mom_summon.slc</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>MomSphereBlessingMessages</t>
+          <t>MomSummonRungOf</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
-        </is>
-      </c>
+          <t>int_f(int_t unitType)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>?</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -49978,7 +50341,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -49995,17 +50358,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>MomSummonOrderTick</t>
+          <t>MomSphereBlessingMessages</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>spawn the creature ordered last turn, resolved from the CASTER'S OWN sphere; debits 75 mana</t>
+          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -50020,7 +50383,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -50032,22 +50395,22 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>MomBlessLife</t>
+          <t>MomSummonOrderTick</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>messagebox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>segment: Life sphere blessing popup</t>
+          <t>spawn the creature ordered last turn, resolved from the CASTER'S OWN sphere; debits 75 mana</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -50062,7 +50425,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -50079,7 +50442,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>MomBlessNature</t>
+          <t>MomBlessLife</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -50089,7 +50452,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>segment: Nature sphere blessing popup</t>
+          <t>segment: Life sphere blessing popup</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -50104,7 +50467,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>life</t>
         </is>
       </c>
     </row>
@@ -50121,7 +50484,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>MomBlessSorcery</t>
+          <t>MomBlessNature</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -50131,7 +50494,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>segment: Sorcery sphere blessing popup</t>
+          <t>segment: Nature sphere blessing popup</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -50146,7 +50509,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>sorcery</t>
+          <t>nature</t>
         </is>
       </c>
     </row>
@@ -50163,7 +50526,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>MomBlessDeath</t>
+          <t>MomBlessSorcery</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -50173,7 +50536,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>segment: Death sphere blessing popup</t>
+          <t>segment: Sorcery sphere blessing popup</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -50188,7 +50551,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>sorcery</t>
         </is>
       </c>
     </row>
@@ -50205,7 +50568,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>MomBlessChaos</t>
+          <t>MomBlessDeath</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -50215,7 +50578,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>segment: Chaos sphere blessing popup</t>
+          <t>segment: Death sphere blessing popup</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -50230,7 +50593,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -50247,7 +50610,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>MomUpkeepDisband</t>
+          <t>MomBlessChaos</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -50255,7 +50618,11 @@
           <t>messagebox</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>segment: Chaos sphere blessing popup</t>
+        </is>
+      </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
           <t>C</t>
@@ -50268,7 +50635,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -50285,7 +50652,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>MomSummonBegun</t>
+          <t>MomUpkeepDisband</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -50323,7 +50690,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>MomSummonBusy</t>
+          <t>MomSummonBegun</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -50361,7 +50728,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>MomSummonNoMagic</t>
+          <t>MomSummonBusy</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -50399,7 +50766,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>MomSummonGuard</t>
+          <t>MomSummonNoMagic</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -50407,11 +50774,7 @@
           <t>messagebox</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
-        </is>
-      </c>
+      <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="5" t="inlineStr">
         <is>
           <t>C</t>
@@ -50441,7 +50804,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>MomSummonBear</t>
+          <t>MomSummonGuard</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -50451,7 +50814,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>segment: Nature summon result (War Bear)</t>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -50483,7 +50846,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>MomSummonMage</t>
+          <t>MomSummonBear</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -50493,7 +50856,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>segment: Sorcery summon result (Mage)</t>
+          <t>segment: Nature summon result (War Bear)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -50525,7 +50888,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>MomSummonZombie</t>
+          <t>MomSummonMage</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -50535,7 +50898,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>segment: Death summon result (Zombies)</t>
+          <t>segment: Sorcery summon result (Mage)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -50567,7 +50930,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>MomSummonHound</t>
+          <t>MomSummonZombie</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -50577,7 +50940,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>segment: Chaos summon result (Hell Hound)</t>
+          <t>segment: Death summon result (Zombies)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -50609,7 +50972,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>MomSummonNoMana</t>
+          <t>MomSummonHound</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -50619,7 +50982,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+          <t>segment: Chaos summon result (Hell Hound)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -50651,7 +51014,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>MomMagicPower</t>
+          <t>MomSummonNoMana</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -50661,7 +51024,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>segment: mana pool / income readout body</t>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -50688,22 +51051,22 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>MagicMenu</t>
+          <t>MomMagicPower</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>messagebox</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+          <t>segment: mana pool / income readout body</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -50718,39 +51081,39 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>mom_magic.slc</t>
+          <t>mom_msg.slc</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>MomRecalcMagicPerTurn</t>
+          <t>MagicMenu</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t mp_1)</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -50760,7 +51123,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -50772,22 +51135,22 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>MomMagicPoolTick</t>
+          <t>MomRecalcMagicPerTurn</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>int_f(int_t mp_1)</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -50819,17 +51182,17 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>MomMagicSchoolGrant</t>
+          <t>MomMagicPoolTick</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>apply per-school mana multipliers when a magic advance is granted</t>
+          <t>per-turn mana accrual into MomMagicCur, clamped at the per-sphere MomMagicMax ceiling (200-300, set by MomMagicSchoolGrant; 100 only as the pre-grant default). Gated to players 1..5 -- running for player 0 was the turn-10 crash. The old pool-overflow auto-summon is REMOVED: it zeroed the pool on cap, so the 50/100-cost workings were unreachable by construction.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -50844,7 +51207,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -50861,15 +51224,19 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>MomSphereRootGrant</t>
+          <t>MomMagicSchoolGrant</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr"/>
+          <t>HandleEvent(GrantAdvance) post</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
+        </is>
+      </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
           <t>M</t>
@@ -50889,29 +51256,25 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>mom_spells.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>MomCastFlameStrike</t>
+          <t>MomSphereRootGrant</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>void_f(int_t p)</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
-        </is>
-      </c>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="5" t="inlineStr">
         <is>
           <t>M</t>
@@ -50924,7 +51287,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -50941,7 +51304,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>MomCastDemonStrike</t>
+          <t>MomCastFlameStrike</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -50951,7 +51314,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
+          <t>Chaos spell: damage the nearest enemy unit. The targeting scan is INLINED because a 2-level user-function chain from an engine callback is an access violation (slic-two-crash-classes), not because of any call-count budget.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -50966,7 +51329,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -50983,7 +51346,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>MomSpellShowBook</t>
+          <t>MomCastDemonStrike</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -50993,7 +51356,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same 2-level-chain reason as MomCastFlameStrike.</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -51020,22 +51383,22 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>MomSpellMenuTick</t>
+          <t>MomSpellShowBook</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>void_f(int_t p)</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -51050,7 +51413,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -51062,22 +51425,22 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>trigger</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>MomOpenSpellbook</t>
+          <t>MomSpellMenuTick</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>UI trigger bound to the control-panel MagicButton</t>
+          <t>per-turn latched spellbook prompt for HUMAN sphere players: re-arms MomSpellPromptArmed only after the pool drops back under 60% of max. Unlatched Message here floods the BeginTurn queue -&gt; 0xC0000005 (measured 2/2).</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -51104,22 +51467,22 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>trigger</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>MomSpellAICast</t>
+          <t>MomOpenSpellbook</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>let AI players cast their sphere's spell when mana allows</t>
+          <t>UI trigger bound to the control-panel MagicButton</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -51146,22 +51509,22 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>MomMsgSpellbook</t>
+          <t>MomSpellAICast</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>alertbox</t>
+          <t>HandleEvent(BeginTurn) post</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>segment: generic spellbook menu</t>
+          <t>let AI players cast their sphere's spell when mana allows</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -51193,7 +51556,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>MomMsgSpellbookChaos</t>
+          <t>MomMsgSpellbook</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -51203,7 +51566,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>segment: Chaos-specific spellbook menu</t>
+          <t>segment: generic spellbook menu</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -51218,7 +51581,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -51235,7 +51598,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>MomMsgDemonCast</t>
+          <t>MomMsgSpellbookChaos</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -51245,7 +51608,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>segment: Demon Strike cast confirmation</t>
+          <t>segment: Chaos-specific spellbook menu</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -51260,7 +51623,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -51277,7 +51640,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>MomMsgFlameCast</t>
+          <t>MomMsgDemonCast</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -51287,7 +51650,7 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>segment: Flame Strike cast confirmation</t>
+          <t>segment: Demon Strike cast confirmation</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -51319,7 +51682,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNoTarget</t>
+          <t>MomMsgFlameCast</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -51329,7 +51692,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>segment: no enemy unit in range</t>
+          <t>segment: Flame Strike cast confirmation</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -51361,7 +51724,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNoMana</t>
+          <t>MomMsgNoTarget</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -51371,7 +51734,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+          <t>segment: no enemy unit in range</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -51403,7 +51766,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>MomMsgNotChaos</t>
+          <t>MomMsgNoMana</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -51413,7 +51776,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>segment: caster's sphere does not grant this spell</t>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -51428,35 +51791,39 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>mom_ai_magic.slc</t>
+          <t>mom_spells.slc</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>alertbox</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>MomAiMagicTick</t>
+          <t>MomMsgNotChaos</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr"/>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>segment: caster's sphere does not grant this spell</t>
+        </is>
+      </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -51466,36 +51833,32 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>mom_gating.slc</t>
+          <t>mom_ai_magic.slc</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>function</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>mod_CanPlayerHaveAdvance</t>
+          <t>MomAiMagicTick</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
-        </is>
-      </c>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr"/>
       <c r="F61" s="5" t="inlineStr">
         <is>
           <t>?</t>
@@ -51508,7 +51871,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -51525,17 +51888,17 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildUnit</t>
+          <t>mod_CanPlayerHaveAdvance</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theUnit)</t>
+          <t>int_f(int_t thePlayer, int_t theAdvance)</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
+          <t>deny a tribe every ladder advance outside its own sphere. Guards on g.player FIRST (ResetCanResearch calls this once per advance per player) and intercepts every acquisition path including scenario-start seeding, so seed advances are unnecessary.</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -51550,7 +51913,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -51567,17 +51930,17 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>mod_CanCityBuildBuilding</t>
+          <t>mod_CanCityBuildUnit</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>int_f(city_t theCity, int_t theBuilding)</t>
+          <t>int_f(city_t theCity, int_t theUnit)</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+          <t>deny a city any unit whose sphere is not its owner tribe; neutral units always permitted. Identity via theCity.owner (proven to resolve, probe B2).</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -51592,7 +51955,7 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>death</t>
         </is>
       </c>
     </row>
@@ -51609,37 +51972,117 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
+          <t>mod_CanCityBuildBuilding</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>int_f(city_t theCity, int_t theBuilding)</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>same wall for improvements: deny off-sphere buildings, permit neutral ones.</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>mom_gating.slc</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
           <t>mod_CanCityBuildWonder</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>int_f(city_t theCity, int_t theWonder)</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>same wall for wonders.</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>chaos</t>
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>mom_probe.slc</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>MomProbeSample</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H64"/>
+  <autoFilter ref="A1:H66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -85,8 +85,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'slic'!$A$1:$L$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'slic'!$A$1:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'slic_index'!$A$1:$H$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43730,7 +43730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -43836,7 +43836,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4549</v>
+        <v>4449</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
@@ -43911,8 +43911,7 @@
 // Per-tribe gating via the engine's four mod functions. Last: it defines only
 // int_f mod_* segments, calls into nothing, and must be able to name every
 // UNIT_/IMPROVE_/ADVANCE_ symbol the other modules assume exists.
-#include "mom_gating.slc"
-#include "mom_probe.slc"</t>
+#include "mom_gating.slc"</t>
         </is>
       </c>
     </row>
@@ -48994,324 +48993,34 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>mom_probe.slc</t>
+          <t>tutorial.slc</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>mom_probe.slc -- HARNESS INSTRUMENT, NOT PART OF THE MOD.</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>int_t MomDbgUnits[31];    // total units owned, sampled on that player's turn
-int_t MomDbgCre[31];      // summoned creatures still alive (ledger occupancy)
-int_t MomDbgMana[31];     // current pool
-int_t MomDbgPrep[31];     // preparation countdown, sampled on that player's OWN turn
-int_t MomDbgPend[31];     // pending creature type, 0 == nothing queued
-int_t MomDbgSph[31];      // sphere resolved from the CIV, 0 == not a tribe
-int_t MomDbgTick[31];     // turns taken by EACH seat, spheres or not
-int_t MomDbgHum[31];      // 1 == this seat is the human
-int_t MomDbgCity[31];     // cities owned -- the AI summon gate's first clause
-int_t MomDbgRung[31];     // sphere-ladder rung 0..5 -- the surviving hypothesis
-int_t MomDbgU1; int_t MomDbgU2; int_t MomDbgU3; int_t MomDbgU4; int_t MomDbgU5;
-int_t MomDbgC1; int_t MomDbgC2; int_t MomDbgC3; int_t MomDbgC4; int_t MomDbgC5;
-int_t MomDbgM1; int_t MomDbgM2; int_t MomDbgM3; int_t MomDbgM4; int_t MomDbgM5;
-int_t MomDbgP1; int_t MomDbgP2; int_t MomDbgP3; int_t MomDbgP4; int_t MomDbgP5;
-int_t MomDbgS1; int_t MomDbgS2; int_t MomDbgS3; int_t MomDbgS4; int_t MomDbgS5;
-int_t MomDbgR1; int_t MomDbgR2; int_t MomDbgR3; int_t MomDbgR4; int_t MomDbgR5;
-int_t MomDbgY1; int_t MomDbgY2; int_t MomDbgY3; int_t MomDbgY4; int_t MomDbgY5;</t>
-        </is>
-      </c>
+          <t>retires stock tut2_main.slc tutorial triggers</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>HandleEvent(BeginTurn) 'MomProbeSample' post {
-    int_t p;
-    int_t i;
-    int_t base;
-    int_t cre;
-    p = player[0];
-    if (p &gt;= 0 &amp;&amp; p &lt;= 15) {
-        MomDbgTick[p] = MomDbgTick[p] + 1;
-    }
-    if (p &gt;= 1 &amp;&amp; p &lt;= 5) {
-        // Own-turn sampling: player[0] IS p here, so .units is p's unit count.
-        MomDbgUnits[p] = player[0].units;
-        MomDbgMana[p] = MomMagicCur[p];
-        // Ledger occupancy = creatures this player summoned that are still
-        // alive. Counts slots, not upkeep, so "how many creatures" is separated
-        // from "what they cost" -- the mix question needs the count.
-        base = (p - 1) * 32;
-        cre = 0;
-        for (i = 0; i &lt; 32; i = i + 1) {
-            if (MomSummonRung[base + i] &gt; 0) {
-                if (MomSummonUnit[base + i].valid) {
-                    cre = cre + 1;
-                }
-            }
-        }
-        MomDbgCre[p] = cre;
-        // SAMPLED ON p's OWN TURN. The earlier version read MomSummonPrep in
-        // the human's flatten pass, by which point every AI countdown had
-        // already ticked down and resolved -- so it always read 0 and could not
-        // distinguish "never committed" from "committed and resolved".
-        MomDbgPrep[p] = MomSummonPrep[p];
-        MomDbgPend[p] = MomSummonPending[p];
-        MomDbgRung[p] = MomSphereRung[p];
-        // THE SPHERE THE MOD RESOLVED for this seat. Before 2026-08-04 sphere
-        // WAS the seat, so this row would have been the identity function and
-        // told us nothing; now it reads MomSphere[], set from
-        // PlayerCivilization, and a mismatch between the tribe chosen at setup
-        // and the sphere granted is visible directly.
-        MomDbgSph[p] = MomSphere[p];
-        // WHICH SEAT IS THE HUMAN. mom_ai_magic skips !IsHumanPlayer(p), and an
-        // observe-only run never clicks the summon arm -- so the human's column
-        // MUST read zero summons with a monotonically climbing pool. That is
-        // Death's exact signature, and it would make the whole investigation an
-        // observer effect rather than a defect.
-        if (IsHumanPlayer(p)) {
-            MomDbgHum[p] = 1;
-        } else {
-            MomDbgHum[p] = 0;
-        }
-        // CITIES. The AI magic tick is gated on `player[0].cities &gt; 0` before
-        // anything else, so a tribe with no city can hold a full pool at rung 1
-        // and never summon -- which is exactly Death's signature. Sampled on
-        // p's own turn, where player[0] IS p.
-        MomDbgCity[p] = player[0].cities;
-        // Flatten for display on the human's turn only. Every tribe's latest
-        // sample is already in the arrays by now, whatever the seating order.
-        if (IsHumanPlayer(p)) {
-            MomDbgU1 = MomDbgUnits[1]; MomDbgU2 = MomDbgUnits[2];
-            MomDbgU3 = MomDbgUnits[3]; MomDbgU4 = MomDbgUnits[4];
-            MomDbgU5 = MomDbgUnits[5];
-            MomDbgC1 = MomDbgCre[1]; MomDbgC2 = MomDbgCre[2];
-            MomDbgC3 = MomDbgCre[3]; MomDbgC4 = MomDbgCre[4];
-            MomDbgC5 = MomDbgCre[5];
-            MomDbgM1 = MomDbgMana[1]; MomDbgM2 = MomDbgMana[2];
-            MomDbgM3 = MomDbgMana[3]; MomDbgM4 = MomDbgMana[4];
-            MomDbgM5 = MomDbgMana[5];
-            MomDbgP1 = MomDbgPend[1]; MomDbgP2 = MomDbgPend[2];
-            MomDbgP3 = MomDbgPend[3]; MomDbgP4 = MomDbgPend[4];
-            MomDbgP5 = MomDbgPend[5];
-            MomDbgR1 = MomDbgRung[1]; MomDbgR2 = MomDbgRung[2];
-            MomDbgR3 = MomDbgRung[3]; MomDbgR4 = MomDbgRung[4];
-            MomDbgR5 = MomDbgRung[5];
-            // NET INCOME -- the last unmeasured input to the AI summon gate.
-            // mom_ai_magic rejects a pick when
-            //     MomMagicPerTurn[p] - pickRung * MomUpkeepRate &lt; 0
-            // so a tribe whose net is 0 or 1 can never afford even a rung-1
-            // creature's keep of 2, no matter how full its bank is. Death sits
-            // pinned at its cap, which is exactly what a tribe that cannot
-            // spend looks like.
-            // Seats 4..8. If a sphere is seated above 5 it gets no magic at
-            // all -- every magic handler is guarded p &gt;= 1 &amp;&amp; p &lt;= 5 -- which
-            // would be a hard defect rather than a balance problem.
-            MomDbgS1 = MomDbgSph[1]; MomDbgS2 = MomDbgSph[2];
-            MomDbgS3 = MomDbgSph[3]; MomDbgS4 = MomDbgSph[4];
-            MomDbgS5 = MomDbgSph[5];
-        }
-    }
-}</t>
-        </is>
-      </c>
+      <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>8460</v>
+        <v>758</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>// mom_probe.slc -- HARNESS INSTRUMENT, NOT PART OF THE MOD.
-//
-// Injected into scen0000 by tools/uiwalk/probe_long_game.py for the duration of
-// one headless run and REMOVED afterwards. It must never be committed into the
-// scenario; the probe restores scenario.slc and scen_str.txt in a finally block.
-//
-// WHY IT EXISTS. The harness reads PIXELS. An AI player's mana, its unit count
-// and its summoned-creature count are never rendered for anybody, so three
-// claims about v3.5.0 were unfalsifiable from the outside:
-//
-//   1. the AI's summon respects sustainability rather than bare affordability;
-//   2. insolvency actually releases a creature (rung 1 cannot reach it);
-//   3. an AI army is now mostly BUILT units with summons as a minority --
-//      the original "only ever one unit type" report.
-//
-// WHY IT IS SAFE TO TEST WITH THIS PRESENT. It is strictly READ-ONLY with
-// respect to the logic under test: it reads MomMagicCur[], MomSummonRung[] and
-// player[0].units, and writes ONLY display scalars that nothing else reads. It
-// adds no spend, no spawn, no kill, and takes no branch that game logic sees. So
-// the economy it measures is the shipped economy, not an instrumented variant.
-//
-// THE player[0] RULE STILL APPLIES. player[N] indexes the event ARG array, so a
-// player's own data can only be read during that player's own BeginTurn -- which
-// is exactly what this does, accumulating into per-player arrays that the human's
-// own tick then flattens into interpolatable scalars. Array-indexed {Arr[Idx]}
-// interpolation silently drops the whole message, so the flat copies are
-// mandatory, not stylistic.
-int_t MomDbgUnits[31];    // total units owned, sampled on that player's turn
-int_t MomDbgCre[31];      // summoned creatures still alive (ledger occupancy)
-int_t MomDbgMana[31];     // current pool
-int_t MomDbgPrep[31];     // preparation countdown, sampled on that player's OWN turn
-int_t MomDbgPend[31];     // pending creature type, 0 == nothing queued
-int_t MomDbgSph[31];      // sphere resolved from the CIV, 0 == not a tribe
-int_t MomDbgTick[31];     // turns taken by EACH seat, spheres or not
-int_t MomDbgHum[31];      // 1 == this seat is the human
-int_t MomDbgCity[31];     // cities owned -- the AI summon gate's first clause
-int_t MomDbgRung[31];     // sphere-ladder rung 0..5 -- the surviving hypothesis
-                          // for Death's zero summons. MomSummonRoll returns 0
-                          // for rung 0, so a tribe stuck there can never summon
-                          // no matter how much mana it holds. Two other
-                          // hypotheses (bank, price) are already falsified; this
-                          // reads the variable instead of inferring it again.
-int_t MomDbgU1; int_t MomDbgU2; int_t MomDbgU3; int_t MomDbgU4; int_t MomDbgU5;
-int_t MomDbgC1; int_t MomDbgC2; int_t MomDbgC3; int_t MomDbgC4; int_t MomDbgC5;
-int_t MomDbgM1; int_t MomDbgM2; int_t MomDbgM3; int_t MomDbgM4; int_t MomDbgM5;
-// Preparation state, added to discriminate a STUCK COUNTDOWN from a SILENT
-// SPAWN FAILURE. Measured 2026-08-01: AI tribes are spending ~75 mana (Nature
-// went 50 -&gt; 66 over ten turns while base income alone is +10/turn, so it burned
-// roughly a summon's worth) and their ledgered creature count stays at ZERO.
-// Those two hypotheses look identical from the outside and need different fixes:
-//   prep stuck &gt; 0  -&gt; the arrival branch never runs for AI players
-//   prep 0, cre 0   -&gt; arrival ran and the spawn produced nothing to ledger
-int_t MomDbgP1; int_t MomDbgP2; int_t MomDbgP3; int_t MomDbgP4; int_t MomDbgP5;
-int_t MomDbgS1; int_t MomDbgS2; int_t MomDbgS3; int_t MomDbgS4; int_t MomDbgS5;
-int_t MomDbgR1; int_t MomDbgR2; int_t MomDbgR3; int_t MomDbgR4; int_t MomDbgR5;
-int_t MomDbgY1; int_t MomDbgY2; int_t MomDbgY3; int_t MomDbgY4; int_t MomDbgY5;
-HandleEvent(BeginTurn) 'MomProbeSample' post {
-    int_t p;
-    int_t i;
-    int_t base;
-    int_t cre;
-    p = player[0];
-    if (p &gt;= 0 &amp;&amp; p &lt;= 15) {
-        MomDbgTick[p] = MomDbgTick[p] + 1;
-    }
-    if (p &gt;= 1 &amp;&amp; p &lt;= 5) {
-        // Own-turn sampling: player[0] IS p here, so .units is p's unit count.
-        MomDbgUnits[p] = player[0].units;
-        MomDbgMana[p] = MomMagicCur[p];
-        // Ledger occupancy = creatures this player summoned that are still
-        // alive. Counts slots, not upkeep, so "how many creatures" is separated
-        // from "what they cost" -- the mix question needs the count.
-        base = (p - 1) * 32;
-        cre = 0;
-        for (i = 0; i &lt; 32; i = i + 1) {
-            if (MomSummonRung[base + i] &gt; 0) {
-                if (MomSummonUnit[base + i].valid) {
-                    cre = cre + 1;
-                }
-            }
-        }
-        MomDbgCre[p] = cre;
-        // SAMPLED ON p's OWN TURN. The earlier version read MomSummonPrep in
-        // the human's flatten pass, by which point every AI countdown had
-        // already ticked down and resolved -- so it always read 0 and could not
-        // distinguish "never committed" from "committed and resolved".
-        MomDbgPrep[p] = MomSummonPrep[p];
-        MomDbgPend[p] = MomSummonPending[p];
-        MomDbgRung[p] = MomSphereRung[p];
-        // THE SPHERE THE MOD RESOLVED for this seat. Before 2026-08-04 sphere
-        // WAS the seat, so this row would have been the identity function and
-        // told us nothing; now it reads MomSphere[], set from
-        // PlayerCivilization, and a mismatch between the tribe chosen at setup
-        // and the sphere granted is visible directly.
-        MomDbgSph[p] = MomSphere[p];
-        // WHICH SEAT IS THE HUMAN. mom_ai_magic skips !IsHumanPlayer(p), and an
-        // observe-only run never clicks the summon arm -- so the human's column
-        // MUST read zero summons with a monotonically climbing pool. That is
-        // Death's exact signature, and it would make the whole investigation an
-        // observer effect rather than a defect.
-        if (IsHumanPlayer(p)) {
-            MomDbgHum[p] = 1;
-        } else {
-            MomDbgHum[p] = 0;
-        }
-        // CITIES. The AI magic tick is gated on `player[0].cities &gt; 0` before
-        // anything else, so a tribe with no city can hold a full pool at rung 1
-        // and never summon -- which is exactly Death's signature. Sampled on
-        // p's own turn, where player[0] IS p.
-        MomDbgCity[p] = player[0].cities;
-        // Flatten for display on the human's turn only. Every tribe's latest
-        // sample is already in the arrays by now, whatever the seating order.
-        if (IsHumanPlayer(p)) {
-            MomDbgU1 = MomDbgUnits[1]; MomDbgU2 = MomDbgUnits[2];
-            MomDbgU3 = MomDbgUnits[3]; MomDbgU4 = MomDbgUnits[4];
-            MomDbgU5 = MomDbgUnits[5];
-            MomDbgC1 = MomDbgCre[1]; MomDbgC2 = MomDbgCre[2];
-            MomDbgC3 = MomDbgCre[3]; MomDbgC4 = MomDbgCre[4];
-            MomDbgC5 = MomDbgCre[5];
-            MomDbgM1 = MomDbgMana[1]; MomDbgM2 = MomDbgMana[2];
-            MomDbgM3 = MomDbgMana[3]; MomDbgM4 = MomDbgMana[4];
-            MomDbgM5 = MomDbgMana[5];
-            MomDbgP1 = MomDbgPend[1]; MomDbgP2 = MomDbgPend[2];
-            MomDbgP3 = MomDbgPend[3]; MomDbgP4 = MomDbgPend[4];
-            MomDbgP5 = MomDbgPend[5];
-            MomDbgR1 = MomDbgRung[1]; MomDbgR2 = MomDbgRung[2];
-            MomDbgR3 = MomDbgRung[3]; MomDbgR4 = MomDbgRung[4];
-            MomDbgR5 = MomDbgRung[5];
-            // NET INCOME -- the last unmeasured input to the AI summon gate.
-            // mom_ai_magic rejects a pick when
-            //     MomMagicPerTurn[p] - pickRung * MomUpkeepRate &lt; 0
-            // so a tribe whose net is 0 or 1 can never afford even a rung-1
-            // creature's keep of 2, no matter how full its bank is. Death sits
-            // pinned at its cap, which is exactly what a tribe that cannot
-            // spend looks like.
-            // Seats 4..8. If a sphere is seated above 5 it gets no magic at
-            // all -- every magic handler is guarded p &gt;= 1 &amp;&amp; p &lt;= 5 -- which
-            // would be a hard defect rather than a balance problem.
-            MomDbgS1 = MomDbgSph[1]; MomDbgS2 = MomDbgSph[2];
-            MomDbgS3 = MomDbgSph[3]; MomDbgS4 = MomDbgSph[4];
-            MomDbgS5 = MomDbgSph[5];
-        }
-    }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>tutorial.slc</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>retires stock tut2_main.slc tutorial triggers</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>758</v>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>//=============================================================================
 // tutorial.slc -- Master of Magic override: stock tutorial SLIC RETIRED
@@ -49329,7 +49038,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L13"/>
+  <autoFilter ref="A1:L12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49340,7 +49049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -52043,46 +51752,8 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>mom_probe.slc</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>handler</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>MomProbeSample</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>HandleEvent(BeginTurn) post</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H66"/>
+  <autoFilter ref="A1:H65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -45939,15 +45939,16 @@
             // on the AI path for the first time, and a messagebox aimed at an AI
             // player is how the message-queue overflow AV was hit.
             if (IsHumanPlayer(p)) {
-                if (p == 1) {
+                // Sphere, NOT seat -- an array read, so no call depth added.
+                if (MomSphere[p] == 1) {
                     Message(p, 'MomSummonGuard');
-                } elseif (p == 2) {
+                } elseif (MomSphere[p] == 2) {
                     Message(p, 'MomSummonBear');
-                } elseif (p == 3) {
+                } elseif (MomSphere[p] == 3) {
                     Message(p, 'MomSummonMage');
-                } elseif (p == 4) {
+                } elseif (MomSphere[p] == 4) {
                     Message(p, 'MomSummonZombie');
-                } elseif (p == 5) {
+                } elseif (MomSphere[p] == 5) {
                     Message(p, 'MomSummonHound');
                 }
             }
@@ -46179,7 +46180,7 @@
         <v>19</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>26586</v>
+        <v>26720</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
@@ -46413,15 +46414,16 @@
             // on the AI path for the first time, and a messagebox aimed at an AI
             // player is how the message-queue overflow AV was hit.
             if (IsHumanPlayer(p)) {
-                if (p == 1) {
+                // Sphere, NOT seat -- an array read, so no call depth added.
+                if (MomSphere[p] == 1) {
                     Message(p, 'MomSummonGuard');
-                } elseif (p == 2) {
+                } elseif (MomSphere[p] == 2) {
                     Message(p, 'MomSummonBear');
-                } elseif (p == 3) {
+                } elseif (MomSphere[p] == 3) {
                     Message(p, 'MomSummonMage');
-                } elseif (p == 4) {
+                } elseif (MomSphere[p] == 4) {
                     Message(p, 'MomSummonZombie');
-                } elseif (p == 5) {
+                } elseif (MomSphere[p] == 5) {
                     Message(p, 'MomSummonHound');
                 }
             }
@@ -47566,13 +47568,21 @@
                 Message(g.player, 'MomMsgNoMana');
             }
         } else {
-            // inlined MomSphereSummonUnit: seating is player N == civ N
+            // Sphere, NOT seat. This block used to read `p == 1` with a comment
+            // asserting "seating is player N == civ N" -- false, because the New
+            // Game EMPIRE selector decides the civ. A Chaos player at seat 1 was
+            // handed Life's Guardian Spirit here.
+            //
+            // MomSphere[] is an ARRAY, so this is a bare read and adds no call
+            // depth -- which is why the predicates resolve into an array rather
+            // than staying as functions. Calling MomPlayerIsChaos(p) from this
+            // body would rebuild the 2-level chain that kills the process.
             summon = 0;
-            if (p == 1) { summon = UnitDB(UNIT_GUARDIAN_SPIRIT); }
-            if (p == 2) { summon = UnitDB(UNIT_WARBEARS); }
-            if (p == 3) { summon = UnitDB(UNIT_MAGE); }
-            if (p == 4) { summon = UnitDB(UNIT_ZOMBIES); }
-            if (p == 5) { summon = UnitDB(UNIT_HELL_HOUNDS); }
+            if (MomSphere[p] == 1) { summon = UnitDB(UNIT_GUARDIAN_SPIRIT); }
+            if (MomSphere[p] == 2) { summon = UnitDB(UNIT_WARBEARS); }
+            if (MomSphere[p] == 3) { summon = UnitDB(UNIT_MAGE); }
+            if (MomSphere[p] == 4) { summon = UnitDB(UNIT_ZOMBIES); }
+            if (MomSphere[p] == 5) { summon = UnitDB(UNIT_HELL_HOUNDS); }
             // inlined MomCastAtNearestEnemy(p, summon, 50, 0)
             found = 0;
             best = 999999;
@@ -47637,10 +47647,11 @@
     location_t homeLoc;
     location_t bestLoc;
     if (p &gt;= 1 &amp;&amp; p &lt;= 5) {
-        // Inlined (p == 5) rather than MomPlayerIsChaos(p): this runs from a
-        // Button body, and a nested user call on that path is the measured
-        // 0xC0000005 documented in MomSpellShowBook below.
-        if (p != 5) {
+        // Inlined MomSphere[p] read rather than a MomPlayerIsChaos(p) call:
+        // this runs from a Button body, and a nested user call on that path is
+        // the measured 0xC0000005 documented in MomSpellShowBook below. An
+        // array subscript is not a call, so it is safe here.
+        if (MomSphere[p] != 5) {
             if (IsHumanPlayer(p)) {
                 Message(g.player, 'MomMsgNotChaos');
             }
@@ -47710,10 +47721,11 @@
         // One level of user call from a trigger body is fine; a SECOND level is
         // not. No SLIC error dialog -- the process dies. An explicit `== 1`
         // comparison does NOT help; the crash is the nested call itself, not the
-        // truthiness form. MomPlayerIsChaos is just `p == 5` (mom_func.slc:49),
-        // so inline the comparison here rather than call it. Any other helper
-        // reached from a trigger or Button body needs the same treatment.
-        if (p == 5) {
+        // truthiness form. MomPlayerIsChaos is now just a read of MomSphere[p]
+        // (mom_func.slc), so inline that read here rather than call it -- an
+        // array subscript costs no call depth. Any other helper reached from a
+        // trigger or Button body needs the same treatment.
+        if (MomSphere[p] == 5) {
             Message(g.player, 'MomMsgSpellbookChaos');
         } else {
             Message(g.player, 'MomMsgSpellbook');
@@ -47772,7 +47784,7 @@
     if (p &gt;= 1 &amp;&amp; p &lt;= 5 &amp;&amp; IsHumanPlayer(p) == 0 &amp;&amp; MomMagicMax[p] &gt; 0) {
         if (MomMagicCur[p] * 4 &gt;= MomMagicMax[p] * 3) {
             // Inlined chaos test -- see MomSpellShowBook for the nested-call crash.
-            if (p == 5 &amp;&amp; MomMagicCur[p] &gt;= 100) {
+            if (MomSphere[p] == 5 &amp;&amp; MomMagicCur[p] &gt;= 100) {
                 MomCastDemonStrike(p);
             } else {
                 MomCastFlameStrike(p);
@@ -47889,7 +47901,7 @@
         <v>13</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>18016</v>
+        <v>18813</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
@@ -47956,13 +47968,21 @@
                 Message(g.player, 'MomMsgNoMana');
             }
         } else {
-            // inlined MomSphereSummonUnit: seating is player N == civ N
+            // Sphere, NOT seat. This block used to read `p == 1` with a comment
+            // asserting "seating is player N == civ N" -- false, because the New
+            // Game EMPIRE selector decides the civ. A Chaos player at seat 1 was
+            // handed Life's Guardian Spirit here.
+            //
+            // MomSphere[] is an ARRAY, so this is a bare read and adds no call
+            // depth -- which is why the predicates resolve into an array rather
+            // than staying as functions. Calling MomPlayerIsChaos(p) from this
+            // body would rebuild the 2-level chain that kills the process.
             summon = 0;
-            if (p == 1) { summon = UnitDB(UNIT_GUARDIAN_SPIRIT); }
-            if (p == 2) { summon = UnitDB(UNIT_WARBEARS); }
-            if (p == 3) { summon = UnitDB(UNIT_MAGE); }
-            if (p == 4) { summon = UnitDB(UNIT_ZOMBIES); }
-            if (p == 5) { summon = UnitDB(UNIT_HELL_HOUNDS); }
+            if (MomSphere[p] == 1) { summon = UnitDB(UNIT_GUARDIAN_SPIRIT); }
+            if (MomSphere[p] == 2) { summon = UnitDB(UNIT_WARBEARS); }
+            if (MomSphere[p] == 3) { summon = UnitDB(UNIT_MAGE); }
+            if (MomSphere[p] == 4) { summon = UnitDB(UNIT_ZOMBIES); }
+            if (MomSphere[p] == 5) { summon = UnitDB(UNIT_HELL_HOUNDS); }
             // inlined MomCastAtNearestEnemy(p, summon, 50, 0)
             found = 0;
             best = 999999;
@@ -48027,10 +48047,11 @@
     location_t homeLoc;
     location_t bestLoc;
     if (p &gt;= 1 &amp;&amp; p &lt;= 5) {
-        // Inlined (p == 5) rather than MomPlayerIsChaos(p): this runs from a
-        // Button body, and a nested user call on that path is the measured
-        // 0xC0000005 documented in MomSpellShowBook below.
-        if (p != 5) {
+        // Inlined MomSphere[p] read rather than a MomPlayerIsChaos(p) call:
+        // this runs from a Button body, and a nested user call on that path is
+        // the measured 0xC0000005 documented in MomSpellShowBook below. An
+        // array subscript is not a call, so it is safe here.
+        if (MomSphere[p] != 5) {
             if (IsHumanPlayer(p)) {
                 Message(g.player, 'MomMsgNotChaos');
             }
@@ -48100,10 +48121,11 @@
         // One level of user call from a trigger body is fine; a SECOND level is
         // not. No SLIC error dialog -- the process dies. An explicit `== 1`
         // comparison does NOT help; the crash is the nested call itself, not the
-        // truthiness form. MomPlayerIsChaos is just `p == 5` (mom_func.slc:49),
-        // so inline the comparison here rather than call it. Any other helper
-        // reached from a trigger or Button body needs the same treatment.
-        if (p == 5) {
+        // truthiness form. MomPlayerIsChaos is now just a read of MomSphere[p]
+        // (mom_func.slc), so inline that read here rather than call it -- an
+        // array subscript costs no call depth. Any other helper reached from a
+        // trigger or Button body needs the same treatment.
+        if (MomSphere[p] == 5) {
             Message(g.player, 'MomMsgSpellbookChaos');
         } else {
             Message(g.player, 'MomMsgSpellbook');
@@ -48175,7 +48197,7 @@
     if (p &gt;= 1 &amp;&amp; p &lt;= 5 &amp;&amp; IsHumanPlayer(p) == 0 &amp;&amp; MomMagicMax[p] &gt; 0) {
         if (MomMagicCur[p] * 4 &gt;= MomMagicMax[p] * 3) {
             // Inlined chaos test -- see MomSpellShowBook for the nested-call crash.
-            if (p == 5 &amp;&amp; MomMagicCur[p] &gt;= 100) {
+            if (MomSphere[p] == 5 &amp;&amp; MomMagicCur[p] &gt;= 100) {
                 MomCastDemonStrike(p);
             } else {
                 MomCastFlameStrike(p);

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -21,32 +21,33 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="advances" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="advances_cell_remap" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="building_uniticon" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="civ2_converted_graphics" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="concept_mask" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="feats" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_descriptions" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_section_overrides" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_text_rewrites" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="governicon_fallback" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="improveicon" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="improvements" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="order_mask" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="players" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="slic_inventory" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sprite_pick_rules" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_advances" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="terrain" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tileimp" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tileimp_mask" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tribe_cities" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_block_overrides" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_mask" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="units" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wonders" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="calendar_periods" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="civ2_converted_graphics" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="concept_mask" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="feats" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_descriptions" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_section_overrides" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_text_rewrites" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="governicon_fallback" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="improveicon" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="improvements" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="order_mask" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="players" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="slic_inventory" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sprite_pick_rules" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_advances" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="terrain" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tileimp" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tileimp_mask" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tribe_cities" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_block_overrides" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_mask" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="units" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wonders" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'index'!$A$10:$E$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'index'!$A$10:$E$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'table_Dimension_Mapping__Civ2_M'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'table_Civ2_Count_Matrix'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'table_CTP2_Current_Full_Kit_Cou'!$A$1:$R$2</definedName>
@@ -60,29 +61,30 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'advances'!$A$1:$M$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'advances_cell_remap'!$A$1:$F$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'building_uniticon'!$A$1:$B$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'civ2_converted_graphics'!$A$1:$G$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'concept_mask'!$A$1:$A$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'feats'!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'gl_descriptions'!$A$1:$C$282</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'gl_section_overrides'!$A$1:$E$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'gl_text_rewrites'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'governicon_fallback'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'improveicon'!$A$1:$A$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improvements'!$A$1:$H$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'order_mask'!$A$1:$A$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'players'!$A$1:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'sprite_pick_rules'!$A$1:$F$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'terrain'!$A$1:$J$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'tileimp'!$A$1:$T$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'tileimp_mask'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'tribe_cities'!$A$1:$P$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'unit_block_overrides'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'unit_factions'!$A$1:$I$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'calendar_periods'!$A$1:$C$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'civ2_converted_graphics'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'concept_mask'!$A$1:$A$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'feats'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'gl_descriptions'!$A$1:$C$282</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'gl_section_overrides'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'gl_text_rewrites'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'governicon_fallback'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improveicon'!$A$1:$A$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'improvements'!$A$1:$H$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'order_mask'!$A$1:$A$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'players'!$A$1:$N$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'slic_inventory'!$A$1:$H$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'sprite_pick_rules'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'terrain'!$A$1:$J$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'tileimp'!$A$1:$T$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'tileimp_mask'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'tribe_cities'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'unit_block_overrides'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'unit_factions'!$A$1:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'units'!$A$1:$Q$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'wonders'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -580,7 +582,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -929,7 +931,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>civ2_converted_graphics</t>
+          <t>calendar_periods</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -939,20 +941,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>civ2_converted_graphics.csv</t>
+          <t>calendar_periods.csv</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>concept_mask</t>
+          <t>civ2_converted_graphics</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -962,20 +964,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>concept_mask.csv</t>
+          <t>civ2_converted_graphics.csv</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>feats</t>
+          <t>concept_mask</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -985,20 +987,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feats.csv</t>
+          <t>concept_mask.csv</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gl_descriptions</t>
+          <t>feats</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1008,20 +1010,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>gl_descriptions.csv</t>
+          <t>feats.csv</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gl_section_overrides</t>
+          <t>gl_descriptions</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1031,20 +1033,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gl_section_overrides.csv</t>
+          <t>gl_descriptions.csv</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>281</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gl_text_rewrites</t>
+          <t>gl_section_overrides</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1054,20 +1056,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>gl_text_rewrites.csv</t>
+          <t>gl_section_overrides.csv</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>governicon_fallback</t>
+          <t>gl_text_rewrites</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1077,11 +1079,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>governicon_fallback.csv</t>
+          <t>gl_text_rewrites.csv</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -1090,7 +1092,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>improveicon</t>
+          <t>governicon_fallback</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1100,20 +1102,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>improveicon.csv</t>
+          <t>governicon_fallback.csv</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>improvements</t>
+          <t>improveicon</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1123,20 +1125,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>improvements.csv</t>
+          <t>improveicon.csv</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>order_mask</t>
+          <t>improvements</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1146,20 +1148,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>order_mask.csv</t>
+          <t>improvements.csv</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>players</t>
+          <t>order_mask</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1169,20 +1171,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>players.csv</t>
+          <t>order_mask.csv</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E35" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>slic_inventory</t>
+          <t>players</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1192,20 +1194,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>slic_inventory.csv</t>
+          <t>players.csv</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="E36" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sprite_pick_rules</t>
+          <t>slic_inventory</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1215,20 +1217,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sprite_pick_rules.csv</t>
+          <t>slic_inventory.csv</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>stub_advances</t>
+          <t>sprite_pick_rules</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1238,20 +1240,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>stub_advances.csv</t>
+          <t>sprite_pick_rules.csv</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>stub_advances</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1261,20 +1263,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>terrain.csv</t>
+          <t>stub_advances.csv</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tileimp</t>
+          <t>terrain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1284,20 +1286,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tileimp.csv</t>
+          <t>terrain.csv</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="E40" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tileimp_mask</t>
+          <t>tileimp</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1307,20 +1309,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>tileimp_mask.csv</t>
+          <t>tileimp.csv</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tribe_cities</t>
+          <t>tileimp_mask</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1330,20 +1332,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tribe_cities.csv</t>
+          <t>tileimp_mask.csv</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E42" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>unit_block_overrides</t>
+          <t>tribe_cities</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,20 +1355,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>unit_block_overrides.csv</t>
+          <t>tribe_cities.csv</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>unit_factions</t>
+          <t>unit_block_overrides</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1376,20 +1378,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>unit_factions.csv</t>
+          <t>unit_block_overrides.csv</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>unit_mask</t>
+          <t>unit_factions</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1399,20 +1401,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>unit_mask.csv</t>
+          <t>unit_factions.csv</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>units</t>
+          <t>unit_mask</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1422,41 +1424,64 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>units.csv</t>
+          <t>unit_mask.csv</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>units.csv</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>68</v>
+      </c>
+      <c r="E47" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>wonders</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>csv</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>wonders.csv</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D48" t="n">
         <v>23</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E48" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A10:E47"/>
+  <autoFilter ref="A10:E48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14076,6 +14101,786 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t># SHAPE of the game calendar</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> per difficulty tier. One row per TIME_SCALE</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t># PERIOD. Read by ctp2_generator._write_calendar()</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> which rewrites the six</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t># TIME_SCALE blocks in default/gamedata/DiffDB.txt and derives</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t># END_OF_GAME_YEAR in default/gamedata/Const.txt from it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t># tier             difficulty block index 0-5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> in DiffDB file order</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#                  (0 Beginner .. 5 Impossible). Every tier needs &gt;=1 row and</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>#                  a row with start_turn 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t># start_turn       first turn this period governs. Must ascend within a tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t># years_per_turn   calendar years each turn advances during this period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t># The engine ends the game at Const END_OF_GAME_YEAR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> so a tier that burns</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t># through the calendar faster gets a SHORTER game in turns. That coupling is</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t># real and intended (harder = tighter)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> but it is easy to change by accident:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t># after editing</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> the generator prints the resulting end turn for every tier so</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t># the drift is visible instead of silent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t># Overall PACE is not here -- it is mod_policy.json calendar.turns_target</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t># which sets how long the reference tier's game runs and back-solves the year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>start_turn</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>years_per_turn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C54"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14877,7 +15682,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14923,7 +15728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14954,7 +15759,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18640,428 +19445,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C282"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>library</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>section</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>find</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TILEIMP_RAILROAD_PREREQ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Requires:
-&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TILEIMP_RAILROAD_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Enchanted Roads reduce the movement cost for units.  They are an improvement on &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, and allow units to travel greater distances in a single turn.  Build them on any land tile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ADVANCE_OIL_REFINING_PREREQ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Requires:
-&lt;L:DATABASE_ADVANCES,ADVANCE_INDUSTRIAL_REVOLUTION&gt;Industrial Revolution&lt;e&gt;
-&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TERRAIN_SWAMP_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>replace</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Railroads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Enchanted Roads&lt;e&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_PREREQ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_STATISTICS</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_HISTORICAL</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ADVANCE_HT_SUPERCONDUCTOR_STATISTICS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>replace</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ADVANCE_HT_SUPERCONDUCTOR_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>replace</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Magnetic Levitation Trains, or &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;, are transit systems that whiz along the surface of the earth at speeds well in excess of any other form of land transportation.  As a &lt;L:DATABASE_CONCEPTS,CONCEPT_TILE_IMPROVEMENTS&gt;Tile Improvement&lt;e&gt;, they are the fastest way to get around, dramatically reducing the movement costs associated with any terrain they are built on.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TILEIMP_RAILROAD_PREREQ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Requires:
-&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TILEIMP_RAILROAD_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Enchanted Roads reduce the movement cost for units.  They are an improvement on &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, and allow units to travel greater distances in a single turn.  Build them on any land tile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TERRAIN_SWAMP_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>replace</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Railroads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Enchanted Roads&lt;e&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_PREREQ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_STATISTICS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_HISTORICAL</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19423,6 +19806,428 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>find</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TILEIMP_RAILROAD_PREREQ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Requires:
+&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TILEIMP_RAILROAD_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Enchanted Roads reduce the movement cost for units.  They are an improvement on &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, and allow units to travel greater distances in a single turn.  Build them on any land tile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADVANCE_OIL_REFINING_PREREQ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Requires:
+&lt;L:DATABASE_ADVANCES,ADVANCE_INDUSTRIAL_REVOLUTION&gt;Industrial Revolution&lt;e&gt;
+&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TERRAIN_SWAMP_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Railroads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Enchanted Roads&lt;e&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_PREREQ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_STATISTICS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_HISTORICAL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ADVANCE_HT_SUPERCONDUCTOR_STATISTICS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ADVANCE_HT_SUPERCONDUCTOR_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Magnetic Levitation Trains, or &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;, are transit systems that whiz along the surface of the earth at speeds well in excess of any other form of land transportation.  As a &lt;L:DATABASE_CONCEPTS,CONCEPT_TILE_IMPROVEMENTS&gt;Tile Improvement&lt;e&gt;, they are the fastest way to get around, dramatically reducing the movement costs associated with any terrain they are built on.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TILEIMP_RAILROAD_PREREQ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Requires:
+&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TILEIMP_RAILROAD_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Enchanted Roads reduce the movement cost for units.  They are an improvement on &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, and allow units to travel greater distances in a single turn.  Build them on any land tile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TERRAIN_SWAMP_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Railroads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Enchanted Roads&lt;e&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_PREREQ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_STATISTICS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_HISTORICAL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -19580,7 +20385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19635,7 +20440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19940,7 +20745,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21831,7 +22636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21947,7 +22752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23554,7 +24359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26269,7 +27074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26688,7 +27493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27651,1329 +28456,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D43"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>terrain_id</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>tileset_index</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>hut_tileset_index_a</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>hut_tileset_index_b</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>internal_type</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>movement_type</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>add_advance</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>remove_advance</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>resources</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TERRAIN_FOREST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_FORESTS</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Forest</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ADVANCE_CONSERVATION</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ADVANCE_TOOLMAKING</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TERRAIN_FOREST_GOOD_ONE; TERRAIN_FOREST_GOOD_TWO; TERRAIN_FOREST_GOOD_THREE; TERRAIN_FOREST_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TERRAIN_PLAINS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_PLAINS</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Plains</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ADVANCE_TOOLMAKING</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TERRAIN_PLAINS_GOOD_ONE; TERRAIN_PLAINS_GOOD_TWO; TERRAIN_PLAINS_GOOD_THREE; TERRAIN_PLAINS_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TERRAIN_TUNDRA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_TUNDRA</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tundra</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ADVANCE_ADVANCED_COMPOSITES</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>TERRAIN_TUNDRA_GOOD_ONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TERRAIN_GLACIER</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_GLACIERS</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Glacier</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ADVANCE_ADVANCED_COMPOSITES</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TERRAIN_GRASSLAND</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_GRASSLANDS</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Grassland</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>TERRAIN_GRASSLAND_GOOD_TWO; TERRAIN_GRASSLAND_GOOD_ONE; TERRAIN_GRASSLAND_GOOD_THREE; TERRAIN_GRASSLAND_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TERRAIN_DESERT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_DESERTS</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Desert</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>TERRAIN_DESERT_GOOD_ONE; TERRAIN_DESERT_GOOD_TWO; TERRAIN_DESERT_GOOD_THREE; TERRAIN_DESERT_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TERRAIN_SWAMP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_SWAMPS</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Swamp</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>TERRAIN_SWAMP_GOOD_ONE; TERRAIN_SWAMP_GOOD_TWO; TERRAIN_SWAMP_GOOD_THREE; TERRAIN_SWAMP_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TERRAIN_JUNGLE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_JUNGLES</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Jungle</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ADVANCE_CONSERVATION</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ADVANCE_TOOLMAKING</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>TERRAIN_JUNGLE_GOOD_TWO; TERRAIN_JUNGLE_GOOD_ONE; TERRAIN_JUNGLE_GOOD_FOUR; TERRAIN_JUNGLE_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TERRAIN_MOUNTAIN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_MOUNTAIN</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mountain</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Air; Mountain</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ADVANCE_FUSION</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>TERRAIN_MOUNTAIN_GOOD_ONE; TERRAIN_MOUNTAIN_GOOD_TWO; TERRAIN_MOUNTAIN_GOOD_THREE; TERRAIN_MOUNTAIN_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TERRAIN_HILL</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_HILLS</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hill</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ADVANCE_EXPLOSIVES</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>TERRAIN_HILL_GOOD_TWO; TERRAIN_HILL_GOOD_ONE; TERRAIN_HILL_GOOD_FOUR; TERRAIN_HILL_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHALLOW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_SHALLOW_WATER</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>WaterShallow</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Air; Sea; ShallowWater</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_FOUR; TERRAIN_WATER_SHALLOW_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_DEEP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_DEEP_WATER</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>WaterDeep</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Air; Sea</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_VOLCANO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_VOLCANO</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>WaterVolcano</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Air; Sea</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>TERRAIN_ARCTIC_MOUNTAIN_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_TWO; TERRAIN_WHITE_HILL_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_BEACH</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_BEACH</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>WaterBeach</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Air; Sea; ShallowWater</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_BEACH_GOOD_ONE; TERRAIN_WATER_BEACH_GOOD_TWO; TERRAIN_WATER_BEACH_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHELF</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_CONTINENTAL_SHELF</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>WaterShelf</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Air; Sea</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_TRENCH</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_TRENCH</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>WaterTrench</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Air; Sea</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_RIFT</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_RIFT</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>WaterRift</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Air; Sea</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TERRAIN_DEAD</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_DEAD</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Dead</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>ADVANCE_CONSERVATION</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TERRAIN_BROWN_HILL</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_BHILLS</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>BrownHill</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>ADVANCE_EXPLOSIVES</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>TERRAIN_BROWN_HILL_GOOD_ONE; TERRAIN_BROWN_HILL_GOOD_TWO; TERRAIN_DESERT_GOOD_ONE; TERRAIN_DESERT_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TERRAIN_BROWN_MOUNTAIN</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_BMOUNTAIN</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>BrownMountain</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Air; Mountain</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>ADVANCE_FUSION</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>TERRAIN_BROWN_MOUNTAIN_GOOD_ONE; TERRAIN_BROWN_MOUNTAIN_GOOD_TWO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TERRAIN_WHITE_HILL</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_WHILLS</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>WhiteHill</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>ADVANCE_EXPLOSIVES</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>TERRAIN_WHITE_HILL_GOOD_ONE; TERRAIN_WHITE_HILL_GOOD_TWO</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TERRAIN_WHITE_MOUNTAIN</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_WMOUNTAIN</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>WhiteMountain</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Air; Mountain</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>ADVANCE_FUSION</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>TERRAIN_ARCTIC_MOUNTAIN_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_TWO; TERRAIN_ARCTIC_MOUNTAIN_GOOD_THREE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_KELP</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_KELP_BED</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>WaterKelp</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Air; Sea; ShallowWater</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_REEF</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_CORAL_REEF</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>WaterReef</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Air; Sea; ShallowWater</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TERRAIN_SPECIAL1</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_GRASSLANDS</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TERRAIN_SPECIAL2</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_DESERTS</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29193,6 +28675,1329 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>terrain_id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>tileset_index</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>hut_tileset_index_a</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>hut_tileset_index_b</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>internal_type</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>movement_type</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>add_advance</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>remove_advance</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TERRAIN_FOREST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_FORESTS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ADVANCE_CONSERVATION</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ADVANCE_TOOLMAKING</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TERRAIN_FOREST_GOOD_ONE; TERRAIN_FOREST_GOOD_TWO; TERRAIN_FOREST_GOOD_THREE; TERRAIN_FOREST_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TERRAIN_PLAINS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_PLAINS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Plains</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ADVANCE_TOOLMAKING</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TERRAIN_PLAINS_GOOD_ONE; TERRAIN_PLAINS_GOOD_TWO; TERRAIN_PLAINS_GOOD_THREE; TERRAIN_PLAINS_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TERRAIN_TUNDRA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_TUNDRA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tundra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ADVANCE_ADVANCED_COMPOSITES</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TERRAIN_TUNDRA_GOOD_ONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TERRAIN_GLACIER</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_GLACIERS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Glacier</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ADVANCE_ADVANCED_COMPOSITES</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TERRAIN_GRASSLAND</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_GRASSLANDS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grassland</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TERRAIN_GRASSLAND_GOOD_TWO; TERRAIN_GRASSLAND_GOOD_ONE; TERRAIN_GRASSLAND_GOOD_THREE; TERRAIN_GRASSLAND_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TERRAIN_DESERT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_DESERTS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Desert</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TERRAIN_DESERT_GOOD_ONE; TERRAIN_DESERT_GOOD_TWO; TERRAIN_DESERT_GOOD_THREE; TERRAIN_DESERT_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TERRAIN_SWAMP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_SWAMPS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Swamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TERRAIN_SWAMP_GOOD_ONE; TERRAIN_SWAMP_GOOD_TWO; TERRAIN_SWAMP_GOOD_THREE; TERRAIN_SWAMP_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TERRAIN_JUNGLE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_JUNGLES</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungle</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ADVANCE_CONSERVATION</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ADVANCE_TOOLMAKING</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TERRAIN_JUNGLE_GOOD_TWO; TERRAIN_JUNGLE_GOOD_ONE; TERRAIN_JUNGLE_GOOD_FOUR; TERRAIN_JUNGLE_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TERRAIN_MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Air; Mountain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUSION</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TERRAIN_MOUNTAIN_GOOD_ONE; TERRAIN_MOUNTAIN_GOOD_TWO; TERRAIN_MOUNTAIN_GOOD_THREE; TERRAIN_MOUNTAIN_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TERRAIN_HILL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_HILLS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ADVANCE_EXPLOSIVES</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TERRAIN_HILL_GOOD_TWO; TERRAIN_HILL_GOOD_ONE; TERRAIN_HILL_GOOD_FOUR; TERRAIN_HILL_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHALLOW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_SHALLOW_WATER</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>WaterShallow</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Air; Sea; ShallowWater</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_FOUR; TERRAIN_WATER_SHALLOW_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_DEEP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_DEEP_WATER</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>WaterDeep</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Air; Sea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_VOLCANO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_VOLCANO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>WaterVolcano</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Air; Sea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TERRAIN_ARCTIC_MOUNTAIN_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_TWO; TERRAIN_WHITE_HILL_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_BEACH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_BEACH</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>WaterBeach</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Air; Sea; ShallowWater</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_BEACH_GOOD_ONE; TERRAIN_WATER_BEACH_GOOD_TWO; TERRAIN_WATER_BEACH_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHELF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_CONTINENTAL_SHELF</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>WaterShelf</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Air; Sea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_TRENCH</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_TRENCH</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>WaterTrench</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Air; Sea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_RIFT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_RIFT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>WaterRift</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Air; Sea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TERRAIN_DEAD</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_DEAD</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dead</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ADVANCE_CONSERVATION</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TERRAIN_BROWN_HILL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_BHILLS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BrownHill</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ADVANCE_EXPLOSIVES</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TERRAIN_BROWN_HILL_GOOD_ONE; TERRAIN_BROWN_HILL_GOOD_TWO; TERRAIN_DESERT_GOOD_ONE; TERRAIN_DESERT_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TERRAIN_BROWN_MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_BMOUNTAIN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BrownMountain</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Air; Mountain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUSION</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TERRAIN_BROWN_MOUNTAIN_GOOD_ONE; TERRAIN_BROWN_MOUNTAIN_GOOD_TWO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TERRAIN_WHITE_HILL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_WHILLS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>WhiteHill</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ADVANCE_EXPLOSIVES</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TERRAIN_WHITE_HILL_GOOD_ONE; TERRAIN_WHITE_HILL_GOOD_TWO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TERRAIN_WHITE_MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_WMOUNTAIN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>WhiteMountain</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Air; Mountain</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUSION</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>TERRAIN_ARCTIC_MOUNTAIN_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_TWO; TERRAIN_ARCTIC_MOUNTAIN_GOOD_THREE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_KELP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_KELP_BED</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>WaterKelp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Air; Sea; ShallowWater</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_REEF</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_CORAL_REEF</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>WaterReef</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Air; Sea; ShallowWater</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TERRAIN_SPECIAL1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_GRASSLANDS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TERRAIN_SPECIAL2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_DESERTS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J27"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34391,7 +35196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34701,7 +35506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35226,7 +36031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35392,7 +36197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37838,7 +38643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37881,7 +38686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43918,7 +44723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -21,33 +21,32 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="advances" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="advances_cell_remap" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="building_uniticon" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="calendar_periods" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="civ2_converted_graphics" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="concept_mask" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="feats" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_descriptions" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_section_overrides" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_text_rewrites" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="governicon_fallback" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="improveicon" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="improvements" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="order_mask" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="players" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="slic_inventory" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sprite_pick_rules" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_advances" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="terrain" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tileimp" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tileimp_mask" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tribe_cities" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_block_overrides" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_mask" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="units" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wonders" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="civ2_converted_graphics" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="concept_mask" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="feats" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_descriptions" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_section_overrides" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gl_text_rewrites" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="governicon_fallback" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="improveicon" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="improvements" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="order_mask" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="players" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="slic_inventory" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sprite_pick_rules" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stub_advances" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="terrain" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tileimp" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tileimp_mask" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tribe_cities" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_block_overrides" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_factions" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_mask" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="units" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wonders" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'index'!$A$10:$E$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'index'!$A$10:$E$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'table_Dimension_Mapping__Civ2_M'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'table_Civ2_Count_Matrix'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'table_CTP2_Current_Full_Kit_Cou'!$A$1:$R$2</definedName>
@@ -61,30 +60,29 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'advances'!$A$1:$M$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'advances_cell_remap'!$A$1:$F$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'building_uniticon'!$A$1:$B$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'calendar_periods'!$A$1:$C$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'civ2_converted_graphics'!$A$1:$G$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'concept_mask'!$A$1:$A$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'feats'!$A$1:$B$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'gl_descriptions'!$A$1:$C$282</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'gl_section_overrides'!$A$1:$E$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'gl_text_rewrites'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'governicon_fallback'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improveicon'!$A$1:$A$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'improvements'!$A$1:$H$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'order_mask'!$A$1:$A$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'players'!$A$1:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'slic_inventory'!$A$1:$H$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'sprite_pick_rules'!$A$1:$F$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'terrain'!$A$1:$J$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'tileimp'!$A$1:$T$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'tileimp_mask'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'tribe_cities'!$A$1:$P$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'unit_block_overrides'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'unit_factions'!$A$1:$I$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'units'!$A$1:$Q$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'wonders'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'civ2_converted_graphics'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'concept_mask'!$A$1:$A$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'feats'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'gl_descriptions'!$A$1:$C$282</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'gl_section_overrides'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'gl_text_rewrites'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'governicon_fallback'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'improveicon'!$A$1:$A$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'improvements'!$A$1:$H$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'order_mask'!$A$1:$A$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'players'!$A$1:$N$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'slic_inventory'!$A$1:$H$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'sprite_pick_rules'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'terrain'!$A$1:$J$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'tileimp'!$A$1:$T$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'tileimp_mask'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'tribe_cities'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'unit_block_overrides'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'unit_factions'!$A$1:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'units'!$A$1:$Q$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'wonders'!$A$1:$E$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -510,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -582,7 +580,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -931,7 +929,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>calendar_periods</t>
+          <t>civ2_converted_graphics</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -941,20 +939,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>calendar_periods.csv</t>
+          <t>civ2_converted_graphics.csv</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>civ2_converted_graphics</t>
+          <t>concept_mask</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -964,20 +962,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>civ2_converted_graphics.csv</t>
+          <t>concept_mask.csv</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>concept_mask</t>
+          <t>feats</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -987,20 +985,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>concept_mask.csv</t>
+          <t>feats.csv</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>feats</t>
+          <t>gl_descriptions</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1010,20 +1008,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feats.csv</t>
+          <t>gl_descriptions.csv</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gl_descriptions</t>
+          <t>gl_section_overrides</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1033,20 +1031,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gl_descriptions.csv</t>
+          <t>gl_section_overrides.csv</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gl_section_overrides</t>
+          <t>gl_text_rewrites</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1056,20 +1054,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>gl_section_overrides.csv</t>
+          <t>gl_text_rewrites.csv</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gl_text_rewrites</t>
+          <t>governicon_fallback</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1079,11 +1077,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>gl_text_rewrites.csv</t>
+          <t>governicon_fallback.csv</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -1092,7 +1090,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>governicon_fallback</t>
+          <t>improveicon</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1102,20 +1100,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>governicon_fallback.csv</t>
+          <t>improveicon.csv</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>improveicon</t>
+          <t>improvements</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1125,20 +1123,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>improveicon.csv</t>
+          <t>improvements.csv</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>improvements</t>
+          <t>order_mask</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1148,20 +1146,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>improvements.csv</t>
+          <t>order_mask.csv</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>order_mask</t>
+          <t>players</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1171,20 +1169,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>order_mask.csv</t>
+          <t>players.csv</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>players</t>
+          <t>slic_inventory</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1194,20 +1192,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>players.csv</t>
+          <t>slic_inventory.csv</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>slic_inventory</t>
+          <t>sprite_pick_rules</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1217,20 +1215,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>slic_inventory.csv</t>
+          <t>sprite_pick_rules.csv</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sprite_pick_rules</t>
+          <t>stub_advances</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1240,20 +1238,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sprite_pick_rules.csv</t>
+          <t>stub_advances.csv</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>stub_advances</t>
+          <t>terrain</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1263,20 +1261,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>stub_advances.csv</t>
+          <t>terrain.csv</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>tileimp</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1286,20 +1284,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>terrain.csv</t>
+          <t>tileimp.csv</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tileimp</t>
+          <t>tileimp_mask</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,20 +1307,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>tileimp.csv</t>
+          <t>tileimp_mask.csv</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="E41" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tileimp_mask</t>
+          <t>tribe_cities</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1332,20 +1330,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tileimp_mask.csv</t>
+          <t>tribe_cities.csv</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tribe_cities</t>
+          <t>unit_block_overrides</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1355,20 +1353,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>tribe_cities.csv</t>
+          <t>unit_block_overrides.csv</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>unit_block_overrides</t>
+          <t>unit_factions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1378,20 +1376,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>unit_block_overrides.csv</t>
+          <t>unit_factions.csv</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>unit_factions</t>
+          <t>unit_mask</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1401,20 +1399,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>unit_factions.csv</t>
+          <t>unit_mask.csv</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>unit_mask</t>
+          <t>units</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1424,20 +1422,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>unit_mask.csv</t>
+          <t>units.csv</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>units</t>
+          <t>wonders</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1447,41 +1445,18 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>units.csv</t>
+          <t>wonders.csv</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="E47" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>wonders</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>csv</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>wonders.csv</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>23</v>
-      </c>
-      <c r="E48" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A10:E48"/>
+  <autoFilter ref="A10:E47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14101,786 +14076,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t># SHAPE of the game calendar</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> per difficulty tier. One row per TIME_SCALE</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t># PERIOD. Read by ctp2_generator._write_calendar()</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> which rewrites the six</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t># TIME_SCALE blocks in default/gamedata/DiffDB.txt and derives</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t># END_OF_GAME_YEAR in default/gamedata/Const.txt from it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t># tier             difficulty block index 0-5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> in DiffDB file order</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>#                  (0 Beginner .. 5 Impossible). Every tier needs &gt;=1 row and</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>#                  a row with start_turn 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t># start_turn       first turn this period governs. Must ascend within a tier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t># years_per_turn   calendar years each turn advances during this period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t># The engine ends the game at Const END_OF_GAME_YEAR</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> so a tier that burns</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t># through the calendar faster gets a SHORTER game in turns. That coupling is</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t># real and intended (harder = tighter)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> but it is easy to change by accident:</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t># after editing</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> the generator prints the resulting end turn for every tier so</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t># the drift is visible instead of silent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t># Overall PACE is not here -- it is mod_policy.json calendar.turns_target</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t># which sets how long the reference tier's game runs and back-solves the year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>tier</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>start_turn</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>years_per_turn</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C54"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15682,7 +14877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15728,7 +14923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15759,7 +14954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19445,6 +18640,428 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C282"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>find</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TILEIMP_RAILROAD_PREREQ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Requires:
+&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TILEIMP_RAILROAD_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Enchanted Roads reduce the movement cost for units.  They are an improvement on &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, and allow units to travel greater distances in a single turn.  Build them on any land tile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADVANCE_OIL_REFINING_PREREQ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Requires:
+&lt;L:DATABASE_ADVANCES,ADVANCE_INDUSTRIAL_REVOLUTION&gt;Industrial Revolution&lt;e&gt;
+&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TERRAIN_SWAMP_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Railroads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Enchanted Roads&lt;e&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_PREREQ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_STATISTICS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_HISTORICAL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ADVANCE_HT_SUPERCONDUCTOR_STATISTICS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gl</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ADVANCE_HT_SUPERCONDUCTOR_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Magnetic Levitation Trains, or &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;, are transit systems that whiz along the surface of the earth at speeds well in excess of any other form of land transportation.  As a &lt;L:DATABASE_CONCEPTS,CONCEPT_TILE_IMPROVEMENTS&gt;Tile Improvement&lt;e&gt;, they are the fastest way to get around, dramatically reducing the movement costs associated with any terrain they are built on.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TILEIMP_RAILROAD_PREREQ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Requires:
+&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TILEIMP_RAILROAD_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Enchanted Roads reduce the movement cost for units.  They are an improvement on &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, and allow units to travel greater distances in a single turn.  Build them on any land tile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TERRAIN_SWAMP_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>replace</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Railroads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Enchanted Roads&lt;e&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_PREREQ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_STATISTICS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_GAMEPLAY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>waw</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TILEIMP_MAGLEV_HISTORICAL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19806,428 +19423,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>library</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>section</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>find</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TILEIMP_RAILROAD_PREREQ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Requires:
-&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TILEIMP_RAILROAD_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Enchanted Roads reduce the movement cost for units.  They are an improvement on &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, and allow units to travel greater distances in a single turn.  Build them on any land tile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ADVANCE_OIL_REFINING_PREREQ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Requires:
-&lt;L:DATABASE_ADVANCES,ADVANCE_INDUSTRIAL_REVOLUTION&gt;Industrial Revolution&lt;e&gt;
-&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TERRAIN_SWAMP_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>replace</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Railroads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Enchanted Roads&lt;e&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_PREREQ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_STATISTICS</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_HISTORICAL</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ADVANCE_HT_SUPERCONDUCTOR_STATISTICS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>replace</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>gl</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ADVANCE_HT_SUPERCONDUCTOR_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>replace</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Magnetic Levitation Trains, or &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;, are transit systems that whiz along the surface of the earth at speeds well in excess of any other form of land transportation.  As a &lt;L:DATABASE_CONCEPTS,CONCEPT_TILE_IMPROVEMENTS&gt;Tile Improvement&lt;e&gt;, they are the fastest way to get around, dramatically reducing the movement costs associated with any terrain they are built on.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TILEIMP_RAILROAD_PREREQ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Requires:
-&lt;L:DATABASE_ADVANCES,ADVANCE_GREATER_ENCHANTMENTS&gt;Greater Enchantments&lt;e&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TILEIMP_RAILROAD_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Enchanted Roads reduce the movement cost for units.  They are an improvement on &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, and allow units to travel greater distances in a single turn.  Build them on any land tile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TERRAIN_SWAMP_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>replace</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Railroads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>&lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt; and &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_RAILROAD&gt;Enchanted Roads&lt;e&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_PREREQ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_STATISTICS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_GAMEPLAY</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>waw</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TILEIMP_MAGLEV_HISTORICAL</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>pop</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E18"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20385,7 +19580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20440,7 +19635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20745,7 +19940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22636,7 +21831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22752,7 +21947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24359,7 +23554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27074,7 +26269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27493,7 +26688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28456,6 +27651,1329 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D43"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>terrain_id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>tileset_index</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>hut_tileset_index_a</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>hut_tileset_index_b</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>internal_type</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>movement_type</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>add_advance</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>remove_advance</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TERRAIN_FOREST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_FORESTS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ADVANCE_CONSERVATION</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ADVANCE_TOOLMAKING</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TERRAIN_FOREST_GOOD_ONE; TERRAIN_FOREST_GOOD_TWO; TERRAIN_FOREST_GOOD_THREE; TERRAIN_FOREST_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TERRAIN_PLAINS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_PLAINS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Plains</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ADVANCE_TOOLMAKING</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TERRAIN_PLAINS_GOOD_ONE; TERRAIN_PLAINS_GOOD_TWO; TERRAIN_PLAINS_GOOD_THREE; TERRAIN_PLAINS_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TERRAIN_TUNDRA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_TUNDRA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tundra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ADVANCE_ADVANCED_COMPOSITES</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TERRAIN_TUNDRA_GOOD_ONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TERRAIN_GLACIER</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_GLACIERS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Glacier</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ADVANCE_ADVANCED_COMPOSITES</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TERRAIN_GRASSLAND</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_GRASSLANDS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grassland</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TERRAIN_GRASSLAND_GOOD_TWO; TERRAIN_GRASSLAND_GOOD_ONE; TERRAIN_GRASSLAND_GOOD_THREE; TERRAIN_GRASSLAND_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TERRAIN_DESERT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_DESERTS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Desert</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TERRAIN_DESERT_GOOD_ONE; TERRAIN_DESERT_GOOD_TWO; TERRAIN_DESERT_GOOD_THREE; TERRAIN_DESERT_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TERRAIN_SWAMP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_SWAMPS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Swamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TERRAIN_SWAMP_GOOD_ONE; TERRAIN_SWAMP_GOOD_TWO; TERRAIN_SWAMP_GOOD_THREE; TERRAIN_SWAMP_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TERRAIN_JUNGLE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_JUNGLES</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungle</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ADVANCE_CONSERVATION</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ADVANCE_TOOLMAKING</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TERRAIN_JUNGLE_GOOD_TWO; TERRAIN_JUNGLE_GOOD_ONE; TERRAIN_JUNGLE_GOOD_FOUR; TERRAIN_JUNGLE_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TERRAIN_MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Air; Mountain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUSION</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TERRAIN_MOUNTAIN_GOOD_ONE; TERRAIN_MOUNTAIN_GOOD_TWO; TERRAIN_MOUNTAIN_GOOD_THREE; TERRAIN_MOUNTAIN_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TERRAIN_HILL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_HILLS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ADVANCE_EXPLOSIVES</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TERRAIN_HILL_GOOD_TWO; TERRAIN_HILL_GOOD_ONE; TERRAIN_HILL_GOOD_FOUR; TERRAIN_HILL_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHALLOW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_SHALLOW_WATER</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>WaterShallow</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Air; Sea; ShallowWater</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_FOUR; TERRAIN_WATER_SHALLOW_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_DEEP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_DEEP_WATER</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>WaterDeep</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Air; Sea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_VOLCANO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_VOLCANO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>WaterVolcano</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Air; Sea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TERRAIN_ARCTIC_MOUNTAIN_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_TWO; TERRAIN_WHITE_HILL_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_BEACH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_BEACH</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>WaterBeach</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Air; Sea; ShallowWater</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_BEACH_GOOD_ONE; TERRAIN_WATER_BEACH_GOOD_TWO; TERRAIN_WATER_BEACH_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHELF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_CONTINENTAL_SHELF</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>WaterShelf</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Air; Sea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_TRENCH</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_TRENCH</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>WaterTrench</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Air; Sea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_RIFT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_RIFT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>WaterRift</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Air; Sea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TERRAIN_DEAD</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_DEAD</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dead</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ADVANCE_CONSERVATION</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TERRAIN_BROWN_HILL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_BHILLS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BrownHill</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ADVANCE_EXPLOSIVES</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TERRAIN_BROWN_HILL_GOOD_ONE; TERRAIN_BROWN_HILL_GOOD_TWO; TERRAIN_DESERT_GOOD_ONE; TERRAIN_DESERT_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TERRAIN_BROWN_MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_BMOUNTAIN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BrownMountain</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Air; Mountain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUSION</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TERRAIN_BROWN_MOUNTAIN_GOOD_ONE; TERRAIN_BROWN_MOUNTAIN_GOOD_TWO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TERRAIN_WHITE_HILL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_WHILLS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>WhiteHill</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ADVANCE_EXPLOSIVES</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TERRAIN_WHITE_HILL_GOOD_ONE; TERRAIN_WHITE_HILL_GOOD_TWO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TERRAIN_WHITE_MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_WMOUNTAIN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>WhiteMountain</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Air; Mountain</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ADVANCE_SUBNEURAL_ADS</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ADVANCE_FUSION</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>TERRAIN_ARCTIC_MOUNTAIN_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_TWO; TERRAIN_ARCTIC_MOUNTAIN_GOOD_THREE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_KELP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_KELP_BED</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>WaterKelp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Air; Sea; ShallowWater</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_REEF</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_CORAL_REEF</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>WaterReef</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Air; Sea; ShallowWater</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TERRAIN_SPECIAL1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_GRASSLANDS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TERRAIN_SPECIAL2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ICON_TERRAIN_DESERTS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Air; Land</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28675,1329 +29193,6 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>terrain_id</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>tileset_index</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>hut_tileset_index_a</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>hut_tileset_index_b</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>internal_type</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>movement_type</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>add_advance</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>remove_advance</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>resources</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TERRAIN_FOREST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_FORESTS</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Forest</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ADVANCE_CONSERVATION</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ADVANCE_TOOLMAKING</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TERRAIN_FOREST_GOOD_ONE; TERRAIN_FOREST_GOOD_TWO; TERRAIN_FOREST_GOOD_THREE; TERRAIN_FOREST_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TERRAIN_PLAINS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_PLAINS</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Plains</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ADVANCE_TOOLMAKING</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TERRAIN_PLAINS_GOOD_ONE; TERRAIN_PLAINS_GOOD_TWO; TERRAIN_PLAINS_GOOD_THREE; TERRAIN_PLAINS_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TERRAIN_TUNDRA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_TUNDRA</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tundra</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ADVANCE_ADVANCED_COMPOSITES</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>TERRAIN_TUNDRA_GOOD_ONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TERRAIN_GLACIER</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_GLACIERS</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Glacier</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ADVANCE_ADVANCED_COMPOSITES</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TERRAIN_GRASSLAND</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_GRASSLANDS</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Grassland</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>TERRAIN_GRASSLAND_GOOD_TWO; TERRAIN_GRASSLAND_GOOD_ONE; TERRAIN_GRASSLAND_GOOD_THREE; TERRAIN_GRASSLAND_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TERRAIN_DESERT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_DESERTS</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Desert</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>TERRAIN_DESERT_GOOD_ONE; TERRAIN_DESERT_GOOD_TWO; TERRAIN_DESERT_GOOD_THREE; TERRAIN_DESERT_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TERRAIN_SWAMP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_SWAMPS</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Swamp</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ADVANCE_AGRICULTURAL_REVOLUTION</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>TERRAIN_SWAMP_GOOD_ONE; TERRAIN_SWAMP_GOOD_TWO; TERRAIN_SWAMP_GOOD_THREE; TERRAIN_SWAMP_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TERRAIN_JUNGLE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_JUNGLES</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Jungle</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ADVANCE_CONSERVATION</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ADVANCE_TOOLMAKING</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>TERRAIN_JUNGLE_GOOD_TWO; TERRAIN_JUNGLE_GOOD_ONE; TERRAIN_JUNGLE_GOOD_FOUR; TERRAIN_JUNGLE_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TERRAIN_MOUNTAIN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_MOUNTAIN</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mountain</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Air; Mountain</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ADVANCE_FUSION</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>TERRAIN_MOUNTAIN_GOOD_ONE; TERRAIN_MOUNTAIN_GOOD_TWO; TERRAIN_MOUNTAIN_GOOD_THREE; TERRAIN_MOUNTAIN_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TERRAIN_HILL</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_HILLS</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hill</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ADVANCE_EXPLOSIVES</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>TERRAIN_HILL_GOOD_TWO; TERRAIN_HILL_GOOD_ONE; TERRAIN_HILL_GOOD_FOUR; TERRAIN_HILL_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHALLOW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_SHALLOW_WATER</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>WaterShallow</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Air; Sea; ShallowWater</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_FOUR; TERRAIN_WATER_SHALLOW_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_DEEP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_DEEP_WATER</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>WaterDeep</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Air; Sea</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_VOLCANO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_VOLCANO</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>WaterVolcano</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Air; Sea</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>TERRAIN_ARCTIC_MOUNTAIN_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_TWO; TERRAIN_WHITE_HILL_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_BEACH</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_BEACH</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>WaterBeach</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Air; Sea; ShallowWater</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_BEACH_GOOD_ONE; TERRAIN_WATER_BEACH_GOOD_TWO; TERRAIN_WATER_BEACH_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHELF</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_CONTINENTAL_SHELF</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>WaterShelf</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Air; Sea</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_TRENCH</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_TRENCH</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>WaterTrench</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Air; Sea</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_RIFT</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_RIFT</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>WaterRift</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Air; Sea</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TERRAIN_DEAD</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_DEAD</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Dead</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>ADVANCE_CONSERVATION</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TERRAIN_BROWN_HILL</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_BHILLS</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>BrownHill</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>ADVANCE_EXPLOSIVES</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>TERRAIN_BROWN_HILL_GOOD_ONE; TERRAIN_BROWN_HILL_GOOD_TWO; TERRAIN_DESERT_GOOD_ONE; TERRAIN_DESERT_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TERRAIN_BROWN_MOUNTAIN</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_BMOUNTAIN</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>BrownMountain</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Air; Mountain</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>ADVANCE_FUSION</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>TERRAIN_BROWN_MOUNTAIN_GOOD_ONE; TERRAIN_BROWN_MOUNTAIN_GOOD_TWO</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TERRAIN_WHITE_HILL</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_WHILLS</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>WhiteHill</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>ADVANCE_EXPLOSIVES</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>TERRAIN_WHITE_HILL_GOOD_ONE; TERRAIN_WHITE_HILL_GOOD_TWO</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TERRAIN_WHITE_MOUNTAIN</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_WMOUNTAIN</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>WhiteMountain</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Air; Mountain</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ADVANCE_SUBNEURAL_ADS</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>ADVANCE_FUSION</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>TERRAIN_ARCTIC_MOUNTAIN_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_TWO; TERRAIN_ARCTIC_MOUNTAIN_GOOD_THREE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_KELP</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_KELP_BED</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>WaterKelp</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Air; Sea; ShallowWater</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_REEF</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_CORAL_REEF</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>WaterReef</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Air; Sea; ShallowWater</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TERRAIN_SPECIAL1</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_GRASSLANDS</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TERRAIN_SPECIAL2</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ICON_TERRAIN_DESERTS</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Air; Land</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J27"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35196,7 +34391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35506,7 +34701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36031,7 +35226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36197,7 +35392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38643,7 +37838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38686,7 +37881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44723,7 +43918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/mom_dimension_inventory.xlsx
+++ b/mom_dimension_inventory.xlsx
@@ -72276,7 +72276,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>SPRITE_MAGE</t>
+          <t>SPRITE_WAR_MAGE</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -72363,7 +72363,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>SPRITE_WARLOCK</t>
+          <t>SPRITE_ARCH_MAGE</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -72450,7 +72450,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>SPRITE_IRON_GOLEM</t>
+          <t>SPRITE_DWARF_WARRIOR</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -72537,7 +72537,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>SPRITE_CATAPULT</t>
+          <t>SPRITE_DWARF_CROSSBOW</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -72624,7 +72624,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>SPRITE_IRON_GOLEM</t>
+          <t>SPRITE_DWARF_RUNESMITH</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -72711,7 +72711,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>SPRITE_GUARDIAN_SPIRIT</t>
+          <t>SPRITE_PRIEST</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -72798,7 +72798,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>SPRITE_KNIGHTS</t>
+          <t>SPRITE_CRUSADER</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -72885,7 +72885,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>SPRITE_PALADINS</t>
+          <t>SPRITE_TEMPLAR</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -72972,7 +72972,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>SPRITE_WAR_MAMMOTH</t>
+          <t>SPRITE_TREANT</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -73059,7 +73059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>SPRITE_MAGE</t>
+          <t>SPRITE_DRUID</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -73146,7 +73146,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>SPRITE_PHANTOM_WARRIORS</t>
+          <t>SPRITE_APPRENTICE</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -73233,7 +73233,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>SPRITE_IRON_GOLEM</t>
+          <t>SPRITE_CRYSTAL_GOLEM</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -73320,7 +73320,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>SPRITE_AIR_ELEMENTAL</t>
+          <t>SPRITE_DJINN</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -73407,7 +73407,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>SPRITE_WRAITH</t>
+          <t>SPRITE_VAMPIRE</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -73494,7 +73494,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>SPRITE_IRON_GOLEM</t>
+          <t>SPRITE_BONE_GOLEM</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -73581,7 +73581,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>SPRITE_MINION</t>
+          <t>SPRITE_GOBLIN</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -73668,7 +73668,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>SPRITE_MINOTAUR</t>
+          <t>SPRITE_ORC</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -73755,7 +73755,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>SPRITE_WAR_TROLL</t>
+          <t>SPRITE_OGRE</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -73842,7 +73842,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>SPRITE_WAR_TROLL</t>
+          <t>SPRITE_TROLL</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -73929,7 +73929,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>SPRITE_DEMON</t>
+          <t>SPRITE_DROW</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
